--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -1589,13 +1589,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46156.46528078704</v>
+        <v>46156.6319474537</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70686295139</v>
+        <v>46175.87352961805</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.706874456024</v>
+        <v>46175.87354112268</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1642,13 +1642,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46156.465400671295</v>
+        <v>46156.63206733797</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.70683420139</v>
+        <v>46175.87350086805</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.70686409722</v>
+        <v>46175.873530763885</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1705,13 +1705,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46156.46540380787</v>
+        <v>46156.63207047454</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.706834930555</v>
+        <v>46175.87350159722</v>
       </c>
       <c r="D6" s="5">
-        <v>46184.413204930555</v>
+        <v>46184.57987159722</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1768,13 +1768,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46156.465406550924</v>
+        <v>46156.632073217595</v>
       </c>
       <c r="C7" s="9">
-        <v>46184.41449466435</v>
+        <v>46184.58116133102</v>
       </c>
       <c r="D7" s="9">
-        <v>46184.41449592593</v>
+        <v>46184.58116259259</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -1831,13 +1831,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46156.46540930556</v>
+        <v>46156.63207597222</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.70683589121</v>
+        <v>46175.87350255787</v>
       </c>
       <c r="D8" s="5">
-        <v>46184.412972962964</v>
+        <v>46184.57963962963</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1894,13 +1894,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46156.46541258102</v>
+        <v>46156.63207924768</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.70683657407</v>
+        <v>46175.87350324074</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.70686366898</v>
+        <v>46175.87353033565</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -1957,11 +1957,11 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46156.465284826394</v>
+        <v>46156.63195149305</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46184.413799918984</v>
+        <v>46184.58046658565</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2004,13 +2004,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46156.46541579861</v>
+        <v>46156.63208246528</v>
       </c>
       <c r="C11" s="9">
-        <v>46184.41364805556</v>
+        <v>46184.58031472222</v>
       </c>
       <c r="D11" s="9">
-        <v>46184.413664085645</v>
+        <v>46184.58033075232</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2069,13 +2069,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46156.465420925924</v>
+        <v>46156.63208759259</v>
       </c>
       <c r="C12" s="5">
-        <v>46184.41365743056</v>
+        <v>46184.580324097224</v>
       </c>
       <c r="D12" s="5">
-        <v>46184.41367418981</v>
+        <v>46184.58034085648</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2134,13 +2134,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46156.46542587963</v>
+        <v>46156.63209254629</v>
       </c>
       <c r="C13" s="9">
-        <v>46184.41378944444</v>
+        <v>46184.580456111114</v>
       </c>
       <c r="D13" s="9">
-        <v>46184.41380574074</v>
+        <v>46184.58047240741</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2199,11 +2199,11 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46156.46543094907</v>
+        <v>46156.632097615744</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46184.41380574074</v>
+        <v>46184.58047240741</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2262,11 +2262,11 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46156.465289699074</v>
+        <v>46156.631956365745</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46184.413865925926</v>
+        <v>46184.58053259259</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2309,13 +2309,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46156.465438495376</v>
+        <v>46156.63210516203</v>
       </c>
       <c r="C16" s="5">
-        <v>46184.41381557871</v>
+        <v>46184.58048224537</v>
       </c>
       <c r="D16" s="5">
-        <v>46184.41383159722</v>
+        <v>46184.58049826389</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2374,13 +2374,13 @@
         <v>73</v>
       </c>
       <c r="B17" s="9">
-        <v>46156.4654437037</v>
+        <v>46156.63211037037</v>
       </c>
       <c r="C17" s="9">
-        <v>46184.4138299537</v>
+        <v>46184.58049662037</v>
       </c>
       <c r="D17" s="9">
-        <v>46184.41384527778</v>
+        <v>46184.58051194444</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>74</v>
@@ -2439,11 +2439,11 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46156.465448981486</v>
+        <v>46156.63211564815</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46184.41386193287</v>
+        <v>46184.58052859954</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2502,11 +2502,11 @@
         <v>80</v>
       </c>
       <c r="B19" s="9">
-        <v>46156.46545483796</v>
+        <v>46156.632121504634</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46184.41418550926</v>
+        <v>46184.580852175925</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>81</v>
@@ -2565,11 +2565,11 @@
         <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46156.465459652776</v>
+        <v>46156.63212631944</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46184.414184733796</v>
+        <v>46184.58085140046</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2628,11 +2628,11 @@
         <v>89</v>
       </c>
       <c r="B21" s="9">
-        <v>46156.4654633912</v>
+        <v>46156.63213005787</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46184.414185497684</v>
+        <v>46184.58085216435</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2691,11 +2691,11 @@
         <v>92</v>
       </c>
       <c r="B22" s="5">
-        <v>46156.46546702547</v>
+        <v>46156.632133692125</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46184.41418537037</v>
+        <v>46184.580852037034</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2754,11 +2754,11 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46156.46529391204</v>
+        <v>46156.6319605787</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46156.531661388886</v>
+        <v>46156.69832805556</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2801,11 +2801,11 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46156.46547148148</v>
+        <v>46156.63213814815</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.694632326384</v>
+        <v>46169.861298993055</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2864,11 +2864,11 @@
         <v>104</v>
       </c>
       <c r="B25" s="9">
-        <v>46156.46547592593</v>
+        <v>46156.63214259259</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46184.41383695602</v>
+        <v>46184.58050362268</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>105</v>
@@ -2923,11 +2923,11 @@
         <v>107</v>
       </c>
       <c r="B26" s="5">
-        <v>46156.46548050926</v>
+        <v>46156.63214717593</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46169.69512607639</v>
+        <v>46169.86179274306</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>108</v>
@@ -2982,11 +2982,11 @@
         <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46156.46548547454</v>
+        <v>46156.6321521412</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46169.69465590278</v>
+        <v>46169.86132256944</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3045,11 +3045,11 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46156.46548990741</v>
+        <v>46156.63215657407</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46184.41386644676</v>
+        <v>46184.580533113425</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3104,11 +3104,11 @@
         <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46156.46549501157</v>
+        <v>46156.63216167824</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46169.6950587037</v>
+        <v>46169.86172537037</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3163,11 +3163,11 @@
         <v>119</v>
       </c>
       <c r="B30" s="5">
-        <v>46156.46550090278</v>
+        <v>46156.63216756945</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46169.694669131946</v>
+        <v>46169.86133579861</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3226,11 +3226,11 @@
         <v>122</v>
       </c>
       <c r="B31" s="9">
-        <v>46156.46550612268</v>
+        <v>46156.63217278935</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46184.41382377315</v>
+        <v>46184.58049043981</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>123</v>
@@ -3285,11 +3285,11 @@
         <v>125</v>
       </c>
       <c r="B32" s="5">
-        <v>46156.46551171296</v>
+        <v>46156.63217837963</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46169.694993564815</v>
+        <v>46169.86166023149</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -3344,11 +3344,11 @@
         <v>128</v>
       </c>
       <c r="B33" s="9">
-        <v>46156.46551701389</v>
+        <v>46156.63218368056</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46169.695012638884</v>
+        <v>46169.861679305555</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>129</v>
@@ -3403,11 +3403,11 @@
         <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46156.46552157408</v>
+        <v>46156.632188240736</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.69467996528</v>
+        <v>46169.861346631944</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3466,11 +3466,11 @@
         <v>136</v>
       </c>
       <c r="B35" s="9">
-        <v>46156.465526932865</v>
+        <v>46156.63219359954</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.69492995371</v>
+        <v>46169.861596620365</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3525,11 +3525,11 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46156.46553178241</v>
+        <v>46156.63219844908</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.694951516205</v>
+        <v>46169.86161818287</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3584,11 +3584,11 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46156.46558777778</v>
+        <v>46156.63225444444</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.69469118056</v>
+        <v>46169.86135784722</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3647,11 +3647,11 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46156.46559153935</v>
+        <v>46156.632258206024</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.69487798611</v>
+        <v>46169.86154465278</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>88</v>
@@ -3700,11 +3700,11 @@
         <v>147</v>
       </c>
       <c r="B39" s="9">
-        <v>46156.465595752314</v>
+        <v>46156.63226241898</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.69489491898</v>
+        <v>46169.86156158565</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>148</v>
@@ -3753,11 +3753,11 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46156.46559978009</v>
+        <v>46156.63226644676</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.694705347225</v>
+        <v>46169.86137201389</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3816,11 +3816,11 @@
         <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46156.46560277778</v>
+        <v>46156.632269444446</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.69481809028</v>
+        <v>46169.86148475694</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>94</v>
@@ -3869,11 +3869,11 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46156.465606909725</v>
+        <v>46156.63227357639</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.69483054398</v>
+        <v>46169.861497210644</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -3922,11 +3922,11 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46156.4656109375</v>
+        <v>46156.63227760416</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.694850370375</v>
+        <v>46169.86151703703</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -3975,11 +3975,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46156.46561355324</v>
+        <v>46156.63228021991</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.69471401621</v>
+        <v>46169.861380682865</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4038,11 +4038,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46156.46561649306</v>
+        <v>46156.63228315972</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.69478453704</v>
+        <v>46169.8614512037</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>91</v>
@@ -4091,11 +4091,11 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46156.46562048611</v>
+        <v>46156.63228715278</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.694761597224</v>
+        <v>46169.86142826389</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4144,11 +4144,11 @@
         <v>172</v>
       </c>
       <c r="B47" s="9">
-        <v>46156.46529826389</v>
+        <v>46156.63196493055</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46184.41412429398</v>
+        <v>46184.58079096065</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>173</v>
@@ -4193,13 +4193,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46156.46562497685</v>
+        <v>46156.63229164352</v>
       </c>
       <c r="C48" s="5">
-        <v>46184.41403015047</v>
+        <v>46184.58069681713</v>
       </c>
       <c r="D48" s="5">
-        <v>46184.41404668981</v>
+        <v>46184.58071335648</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4258,13 +4258,13 @@
         <v>181</v>
       </c>
       <c r="B49" s="9">
-        <v>46156.46562959491</v>
+        <v>46156.632296261574</v>
       </c>
       <c r="C49" s="9">
-        <v>46184.414106516204</v>
+        <v>46184.58077318287</v>
       </c>
       <c r="D49" s="9">
-        <v>46184.414121747686</v>
+        <v>46184.58078841435</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>182</v>
@@ -4323,13 +4323,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46156.4656355787</v>
+        <v>46156.63230224537</v>
       </c>
       <c r="C50" s="5">
-        <v>46184.4141585301</v>
+        <v>46184.58082519676</v>
       </c>
       <c r="D50" s="5">
-        <v>46184.414174375</v>
+        <v>46184.580841041665</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>84</v>
@@ -4386,11 +4386,11 @@
         <v>187</v>
       </c>
       <c r="B51" s="9">
-        <v>46156.46564869213</v>
+        <v>46156.632315358795</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46156.55922473379</v>
+        <v>46156.72589140046</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>188</v>
@@ -4449,11 +4449,11 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46156.46565230324</v>
+        <v>46156.6323189699</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46156.55929621527</v>
+        <v>46156.725962881945</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4502,11 +4502,11 @@
         <v>195</v>
       </c>
       <c r="B53" s="9">
-        <v>46156.46566474537</v>
+        <v>46156.63233141204</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46156.537190312505</v>
+        <v>46156.70385697916</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>196</v>
@@ -4549,11 +4549,11 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46156.46566793982</v>
+        <v>46156.63233460648</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46156.55939259259</v>
+        <v>46156.72605925926</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
@@ -4612,11 +4612,11 @@
         <v>203</v>
       </c>
       <c r="B55" s="9">
-        <v>46156.465673032406</v>
+        <v>46156.63233969908</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46156.55945885417</v>
+        <v>46156.72612552083</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>204</v>
@@ -4675,11 +4675,11 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46156.46568400463</v>
+        <v>46156.632350671294</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46156.55939001158</v>
+        <v>46156.72605667824</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>208</v>
@@ -4738,11 +4738,11 @@
         <v>210</v>
       </c>
       <c r="B57" s="9">
-        <v>46156.46568866898</v>
+        <v>46156.63235533565</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46156.55945584491</v>
+        <v>46156.72612251157</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>211</v>
@@ -4801,11 +4801,11 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46156.46569278935</v>
+        <v>46156.63235945602</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46156.559385914356</v>
+        <v>46156.72605258102</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4864,11 +4864,11 @@
         <v>215</v>
       </c>
       <c r="B59" s="9">
-        <v>46156.4656965625</v>
+        <v>46156.63236322917</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46156.55945299768</v>
+        <v>46156.72611966435</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>214</v>
@@ -4927,11 +4927,11 @@
         <v>216</v>
       </c>
       <c r="B60" s="5">
-        <v>46156.46570077546</v>
+        <v>46156.63236744213</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46156.5435802662</v>
+        <v>46156.71024693287</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -4974,11 +4974,11 @@
         <v>219</v>
       </c>
       <c r="B61" s="9">
-        <v>46156.46570341435</v>
+        <v>46156.63237008102</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46161.410576319446</v>
+        <v>46161.57724298611</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>220</v>
@@ -5037,11 +5037,11 @@
         <v>224</v>
       </c>
       <c r="B62" s="5">
-        <v>46156.46570917824</v>
+        <v>46156.63237584491</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46156.559578506945</v>
+        <v>46156.72624517361</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>193</v>
@@ -5090,11 +5090,11 @@
         <v>227</v>
       </c>
       <c r="B63" s="9">
-        <v>46156.46572930556</v>
+        <v>46156.63239597222</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46156.559530266204</v>
+        <v>46156.72619693287</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>228</v>
@@ -5153,11 +5153,11 @@
         <v>229</v>
       </c>
       <c r="B64" s="5">
-        <v>46156.46573340277</v>
+        <v>46156.632400069444</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46184.41417564815</v>
+        <v>46184.58084231481</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>193</v>
@@ -5206,11 +5206,11 @@
         <v>232</v>
       </c>
       <c r="B65" s="9">
-        <v>46156.46580068287</v>
+        <v>46156.63246734954</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46156.55952659722</v>
+        <v>46156.726193263894</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>233</v>
@@ -5269,11 +5269,11 @@
         <v>234</v>
       </c>
       <c r="B66" s="5">
-        <v>46156.465805960645</v>
+        <v>46156.632472627316</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46184.41417393518</v>
+        <v>46184.58084060185</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>193</v>
@@ -5322,11 +5322,11 @@
         <v>236</v>
       </c>
       <c r="B67" s="9">
-        <v>46156.46582619213</v>
+        <v>46156.6324928588</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46156.545767337964</v>
+        <v>46156.71243400463</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>196</v>
@@ -5369,11 +5369,11 @@
         <v>238</v>
       </c>
       <c r="B68" s="5">
-        <v>46156.4658296875</v>
+        <v>46156.63249635417</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46156.55978782407</v>
+        <v>46156.72645449074</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>239</v>
@@ -5432,11 +5432,11 @@
         <v>240</v>
       </c>
       <c r="B69" s="9">
-        <v>46156.465835625</v>
+        <v>46156.63250229167</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46156.55978502315</v>
+        <v>46156.726451689814</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>241</v>
@@ -5495,11 +5495,11 @@
         <v>242</v>
       </c>
       <c r="B70" s="5">
-        <v>46156.46584185185</v>
+        <v>46156.63250851852</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46156.55978221065</v>
+        <v>46156.726448877314</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>243</v>
@@ -5558,11 +5558,11 @@
         <v>244</v>
       </c>
       <c r="B71" s="9">
-        <v>46156.46584798611</v>
+        <v>46156.63251465278</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46156.55977885416</v>
+        <v>46156.726445520835</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>245</v>
@@ -5621,11 +5621,11 @@
         <v>247</v>
       </c>
       <c r="B72" s="5">
-        <v>46156.46585247685</v>
+        <v>46156.63251914352</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46156.54914844908</v>
+        <v>46156.71581511574</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>248</v>
@@ -5668,11 +5668,11 @@
         <v>250</v>
       </c>
       <c r="B73" s="9">
-        <v>46156.465855532406</v>
+        <v>46156.63252219907</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46156.55988152778</v>
+        <v>46156.72654819445</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>251</v>
@@ -5731,11 +5731,11 @@
         <v>253</v>
       </c>
       <c r="B74" s="5">
-        <v>46156.46586267361</v>
+        <v>46156.63252934028</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46156.55990940973</v>
+        <v>46156.726576076384</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>193</v>
@@ -5784,11 +5784,11 @@
         <v>254</v>
       </c>
       <c r="B75" s="9">
-        <v>46156.465879201394</v>
+        <v>46156.63254586805</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46156.559878541666</v>
+        <v>46156.72654520834</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>255</v>
@@ -5847,11 +5847,11 @@
         <v>256</v>
       </c>
       <c r="B76" s="5">
-        <v>46156.465883807876</v>
+        <v>46156.63255047453</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46184.414174606485</v>
+        <v>46184.58084127315</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>193</v>
@@ -5900,11 +5900,11 @@
         <v>259</v>
       </c>
       <c r="B77" s="9">
-        <v>46156.465912071755</v>
+        <v>46156.63257873843</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46156.55987570602</v>
+        <v>46156.726542372686</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>260</v>
@@ -5963,11 +5963,11 @@
         <v>261</v>
       </c>
       <c r="B78" s="5">
-        <v>46156.465916319445</v>
+        <v>46156.632582986116</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46184.41417528935</v>
+        <v>46184.58084195602</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>193</v>
@@ -6016,11 +6016,11 @@
         <v>263</v>
       </c>
       <c r="B79" s="9">
-        <v>46156.46598900463</v>
+        <v>46156.632655671296</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46156.55987254629</v>
+        <v>46156.72653921296</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>264</v>
@@ -6079,11 +6079,11 @@
         <v>265</v>
       </c>
       <c r="B80" s="5">
-        <v>46156.46599484954</v>
+        <v>46156.6326615162</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46184.41417643518</v>
+        <v>46184.58084310185</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>193</v>
@@ -6132,11 +6132,11 @@
         <v>268</v>
       </c>
       <c r="B81" s="9">
-        <v>46156.46601900463</v>
+        <v>46156.6326856713</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46156.559869062505</v>
+        <v>46156.72653572916</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>269</v>
@@ -6195,11 +6195,11 @@
         <v>270</v>
       </c>
       <c r="B82" s="5">
-        <v>46156.46602746528</v>
+        <v>46156.63269413194</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46156.560094942135</v>
+        <v>46156.72676160879</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>193</v>
@@ -6248,11 +6248,11 @@
         <v>272</v>
       </c>
       <c r="B83" s="9">
-        <v>46156.46604914352</v>
+        <v>46156.632715810185</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46156.55986508101</v>
+        <v>46156.726531747685</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>273</v>
@@ -6311,11 +6311,11 @@
         <v>275</v>
       </c>
       <c r="B84" s="5">
-        <v>46156.46605503472</v>
+        <v>46156.63272170139</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46156.56013622685</v>
+        <v>46156.72680289352</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>193</v>
@@ -6364,11 +6364,11 @@
         <v>277</v>
       </c>
       <c r="B85" s="9">
-        <v>46156.46607326389</v>
+        <v>46156.63273993056</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46156.550152615746</v>
+        <v>46156.7168192824</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>278</v>
@@ -6411,11 +6411,11 @@
         <v>280</v>
       </c>
       <c r="B86" s="5">
-        <v>46156.46607689815</v>
+        <v>46156.63274356481</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46156.56020984954</v>
+        <v>46156.7268765162</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>281</v>
@@ -6474,11 +6474,11 @@
         <v>284</v>
       </c>
       <c r="B87" s="9">
-        <v>46156.46608248843</v>
+        <v>46156.63274915509</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46156.56025369213</v>
+        <v>46156.72692035879</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>193</v>
@@ -6527,11 +6527,11 @@
         <v>286</v>
       </c>
       <c r="B88" s="5">
-        <v>46156.46609966435</v>
+        <v>46156.63276633102</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46156.56033458334</v>
+        <v>46156.72700125</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>287</v>
@@ -6588,11 +6588,11 @@
         <v>288</v>
       </c>
       <c r="B89" s="9">
-        <v>46156.46610417824</v>
+        <v>46156.63277084491</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46156.56030546296</v>
+        <v>46156.72697212963</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>193</v>
@@ -6641,11 +6641,11 @@
         <v>290</v>
       </c>
       <c r="B90" s="5">
-        <v>46156.466167314815</v>
+        <v>46156.63283398148</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46156.56042763889</v>
+        <v>46156.727094305556</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>291</v>
@@ -6704,11 +6704,11 @@
         <v>292</v>
       </c>
       <c r="B91" s="9">
-        <v>46156.46617347222</v>
+        <v>46156.63284013889</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46156.56038800926</v>
+        <v>46156.727054675925</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>193</v>
@@ -6757,11 +6757,11 @@
         <v>294</v>
       </c>
       <c r="B92" s="5">
-        <v>46156.466201979165</v>
+        <v>46156.63286864583</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46156.56055357639</v>
+        <v>46156.727220243054</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>295</v>
@@ -6820,11 +6820,11 @@
         <v>297</v>
       </c>
       <c r="B93" s="9">
-        <v>46156.46620930555</v>
+        <v>46156.632875972224</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46156.56051700232</v>
+        <v>46156.727183668976</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>193</v>
@@ -6871,11 +6871,11 @@
         <v>298</v>
       </c>
       <c r="B94" s="5">
-        <v>46156.466237534725</v>
+        <v>46156.63290420139</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46156.5506479051</v>
+        <v>46156.71731457176</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>299</v>
@@ -6918,11 +6918,11 @@
         <v>301</v>
       </c>
       <c r="B95" s="9">
-        <v>46156.46624121528</v>
+        <v>46156.63290788194</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46156.560622523146</v>
+        <v>46156.72728918982</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>302</v>
@@ -6981,11 +6981,11 @@
         <v>305</v>
       </c>
       <c r="B96" s="5">
-        <v>46156.466247476856</v>
+        <v>46156.63291414352</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46156.56067673611</v>
+        <v>46156.727343402774</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>306</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -2805,7 +2805,7 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46169.861298993055</v>
+        <v>46195.929228946756</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2866,9 +2866,11 @@
       <c r="B25" s="9">
         <v>46156.63214259259</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="9">
+        <v>46195.92922075231</v>
+      </c>
       <c r="D25" s="9">
-        <v>46184.58050362268</v>
+        <v>46195.92922337963</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>105</v>
@@ -2927,7 +2929,7 @@
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46169.86179274306</v>
+        <v>46195.92922835649</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>108</v>
@@ -3167,7 +3169,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46169.86133579861</v>
+        <v>46195.92957673611</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3228,9 +3230,11 @@
       <c r="B31" s="9">
         <v>46156.63217278935</v>
       </c>
-      <c r="C31" s="10"/>
+      <c r="C31" s="9">
+        <v>46195.929570740744</v>
+      </c>
       <c r="D31" s="9">
-        <v>46184.58049043981</v>
+        <v>46195.92957241899</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>123</v>
@@ -3289,7 +3293,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46169.86166023149</v>
+        <v>46195.92957792824</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -3348,7 +3352,7 @@
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46169.861679305555</v>
+        <v>46195.929578923606</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>129</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -2266,7 +2266,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46184.58053259259</v>
+        <v>46196.65626502315</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2504,9 +2504,11 @@
       <c r="B19" s="9">
         <v>46156.632121504634</v>
       </c>
-      <c r="C19" s="10"/>
+      <c r="C19" s="9">
+        <v>46196.656259456024</v>
+      </c>
       <c r="D19" s="9">
-        <v>46184.580852175925</v>
+        <v>46196.65627553241</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>81</v>
@@ -2554,10 +2556,10 @@
         <v>33</v>
       </c>
       <c r="T19" s="10">
-        <v>0</v>
-      </c>
-      <c r="U19" s="11" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U19" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -2567,9 +2569,11 @@
       <c r="B20" s="5">
         <v>46156.63212631944</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C20" s="5">
+        <v>46196.65655393519</v>
+      </c>
       <c r="D20" s="5">
-        <v>46184.58085140046</v>
+        <v>46196.656567858794</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2617,10 +2621,10 @@
         <v>33</v>
       </c>
       <c r="T20" s="6">
-        <v>0</v>
-      </c>
-      <c r="U20" s="11" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U20" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -2630,9 +2634,11 @@
       <c r="B21" s="9">
         <v>46156.63213005787</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="9">
+        <v>46196.65716653936</v>
+      </c>
       <c r="D21" s="9">
-        <v>46184.58085216435</v>
+        <v>46196.65718306713</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2680,10 +2686,10 @@
         <v>33</v>
       </c>
       <c r="T21" s="10">
-        <v>0</v>
-      </c>
-      <c r="U21" s="11" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U21" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -2693,9 +2699,11 @@
       <c r="B22" s="5">
         <v>46156.632133692125</v>
       </c>
-      <c r="C22" s="6"/>
+      <c r="C22" s="5">
+        <v>46196.65766008102</v>
+      </c>
       <c r="D22" s="5">
-        <v>46184.580852037034</v>
+        <v>46196.657674409726</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2743,10 +2751,10 @@
         <v>33</v>
       </c>
       <c r="T22" s="6">
-        <v>0</v>
-      </c>
-      <c r="U22" s="11" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U22" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -3474,7 +3482,7 @@
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46169.861596620365</v>
+        <v>46196.656266342594</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3655,7 +3663,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46169.86154465278</v>
+        <v>46196.65655980324</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>88</v>
@@ -3824,7 +3832,7 @@
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46169.86148475694</v>
+        <v>46196.657666886575</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>94</v>
@@ -4046,7 +4054,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46169.8614512037</v>
+        <v>46196.657172465275</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>91</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -3769,7 +3769,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46169.86137201389</v>
+        <v>46196.70204975695</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3830,9 +3830,11 @@
       <c r="B41" s="9">
         <v>46156.632269444446</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="9">
+        <v>46196.699784247685</v>
+      </c>
       <c r="D41" s="9">
-        <v>46196.657666886575</v>
+        <v>46196.69978633102</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>94</v>
@@ -3885,7 +3887,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.861497210644</v>
+        <v>46196.699790694445</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -710,7 +710,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 ,OT2 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>1214809612627656</t>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="308">
   <si>
     <t>50001547 - XEMORTIZ (AMERICAS GOLD)</t>
   </si>
@@ -2264,9 +2264,11 @@
       <c r="B15" s="9">
         <v>46156.631956365745</v>
       </c>
-      <c r="C15" s="10"/>
+      <c r="C15" s="9">
+        <v>46197.50205516204</v>
+      </c>
       <c r="D15" s="9">
-        <v>46196.65626502315</v>
+        <v>46197.50206623843</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2301,8 +2303,12 @@
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
       <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
+      <c r="T15" s="10">
+        <v>1</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -2441,9 +2447,11 @@
       <c r="B18" s="5">
         <v>46156.63211564815</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5">
+        <v>46197.50203898148</v>
+      </c>
       <c r="D18" s="5">
-        <v>46184.58052859954</v>
+        <v>46197.5020416551</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -3059,7 +3067,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46184.580533113425</v>
+        <v>46197.502050625</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -1589,13 +1589,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46156.6319474537</v>
+        <v>46156.46528078704</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.87352961805</v>
+        <v>46175.70686295139</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.87354112268</v>
+        <v>46175.706874456024</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1642,13 +1642,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46156.63206733797</v>
+        <v>46156.465400671295</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.87350086805</v>
+        <v>46175.70683420139</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.873530763885</v>
+        <v>46175.70686409722</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1705,13 +1705,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46156.63207047454</v>
+        <v>46156.46540380787</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.87350159722</v>
+        <v>46175.706834930555</v>
       </c>
       <c r="D6" s="5">
-        <v>46184.57987159722</v>
+        <v>46184.413204930555</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1768,13 +1768,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46156.632073217595</v>
+        <v>46156.465406550924</v>
       </c>
       <c r="C7" s="9">
-        <v>46184.58116133102</v>
+        <v>46184.41449466435</v>
       </c>
       <c r="D7" s="9">
-        <v>46184.58116259259</v>
+        <v>46184.41449592593</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -1831,13 +1831,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46156.63207597222</v>
+        <v>46156.46540930556</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.87350255787</v>
+        <v>46175.70683589121</v>
       </c>
       <c r="D8" s="5">
-        <v>46184.57963962963</v>
+        <v>46184.412972962964</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1894,13 +1894,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46156.63207924768</v>
+        <v>46156.46541258102</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.87350324074</v>
+        <v>46175.70683657407</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.87353033565</v>
+        <v>46175.70686366898</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -1957,11 +1957,11 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46156.63195149305</v>
+        <v>46156.465284826394</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46184.58046658565</v>
+        <v>46184.413799918984</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2004,13 +2004,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46156.63208246528</v>
+        <v>46156.46541579861</v>
       </c>
       <c r="C11" s="9">
-        <v>46184.58031472222</v>
+        <v>46184.41364805556</v>
       </c>
       <c r="D11" s="9">
-        <v>46184.58033075232</v>
+        <v>46184.413664085645</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2069,13 +2069,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46156.63208759259</v>
+        <v>46156.465420925924</v>
       </c>
       <c r="C12" s="5">
-        <v>46184.580324097224</v>
+        <v>46184.41365743056</v>
       </c>
       <c r="D12" s="5">
-        <v>46184.58034085648</v>
+        <v>46184.41367418981</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2134,13 +2134,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46156.63209254629</v>
+        <v>46156.46542587963</v>
       </c>
       <c r="C13" s="9">
-        <v>46184.580456111114</v>
+        <v>46184.41378944444</v>
       </c>
       <c r="D13" s="9">
-        <v>46184.58047240741</v>
+        <v>46184.41380574074</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2199,11 +2199,11 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46156.632097615744</v>
+        <v>46156.46543094907</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46184.58047240741</v>
+        <v>46184.41380574074</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2262,13 +2262,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46156.631956365745</v>
+        <v>46156.465289699074</v>
       </c>
       <c r="C15" s="9">
-        <v>46197.50205516204</v>
+        <v>46197.33538849537</v>
       </c>
       <c r="D15" s="9">
-        <v>46197.50206623843</v>
+        <v>46197.33539957176</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2315,13 +2315,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46156.63210516203</v>
+        <v>46156.465438495376</v>
       </c>
       <c r="C16" s="5">
-        <v>46184.58048224537</v>
+        <v>46184.41381557871</v>
       </c>
       <c r="D16" s="5">
-        <v>46184.58049826389</v>
+        <v>46184.41383159722</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2380,13 +2380,13 @@
         <v>73</v>
       </c>
       <c r="B17" s="9">
-        <v>46156.63211037037</v>
+        <v>46156.4654437037</v>
       </c>
       <c r="C17" s="9">
-        <v>46184.58049662037</v>
+        <v>46184.4138299537</v>
       </c>
       <c r="D17" s="9">
-        <v>46184.58051194444</v>
+        <v>46184.41384527778</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>74</v>
@@ -2445,13 +2445,13 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46156.63211564815</v>
+        <v>46156.465448981486</v>
       </c>
       <c r="C18" s="5">
-        <v>46197.50203898148</v>
+        <v>46197.33537231482</v>
       </c>
       <c r="D18" s="5">
-        <v>46197.5020416551</v>
+        <v>46197.335374988426</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2510,13 +2510,13 @@
         <v>80</v>
       </c>
       <c r="B19" s="9">
-        <v>46156.632121504634</v>
+        <v>46156.46545483796</v>
       </c>
       <c r="C19" s="9">
-        <v>46196.656259456024</v>
+        <v>46196.48959278935</v>
       </c>
       <c r="D19" s="9">
-        <v>46196.65627553241</v>
+        <v>46196.48960886574</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>81</v>
@@ -2575,13 +2575,13 @@
         <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46156.63212631944</v>
+        <v>46156.465459652776</v>
       </c>
       <c r="C20" s="5">
-        <v>46196.65655393519</v>
+        <v>46196.489887268515</v>
       </c>
       <c r="D20" s="5">
-        <v>46196.656567858794</v>
+        <v>46196.48990119213</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2640,13 +2640,13 @@
         <v>89</v>
       </c>
       <c r="B21" s="9">
-        <v>46156.63213005787</v>
+        <v>46156.4654633912</v>
       </c>
       <c r="C21" s="9">
-        <v>46196.65716653936</v>
+        <v>46196.490499872685</v>
       </c>
       <c r="D21" s="9">
-        <v>46196.65718306713</v>
+        <v>46196.49051640046</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2705,13 +2705,13 @@
         <v>92</v>
       </c>
       <c r="B22" s="5">
-        <v>46156.632133692125</v>
+        <v>46156.46546702547</v>
       </c>
       <c r="C22" s="5">
-        <v>46196.65766008102</v>
+        <v>46196.49099341435</v>
       </c>
       <c r="D22" s="5">
-        <v>46196.657674409726</v>
+        <v>46196.491007743054</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2770,11 +2770,11 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46156.6319605787</v>
+        <v>46156.46529391204</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46156.69832805556</v>
+        <v>46156.531661388886</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2817,11 +2817,11 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46156.63213814815</v>
+        <v>46156.46547148148</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46195.929228946756</v>
+        <v>46195.76256228009</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2880,13 +2880,13 @@
         <v>104</v>
       </c>
       <c r="B25" s="9">
-        <v>46156.63214259259</v>
+        <v>46156.46547592593</v>
       </c>
       <c r="C25" s="9">
-        <v>46195.92922075231</v>
+        <v>46195.76255408565</v>
       </c>
       <c r="D25" s="9">
-        <v>46195.92922337963</v>
+        <v>46195.76255671296</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>105</v>
@@ -2941,11 +2941,11 @@
         <v>107</v>
       </c>
       <c r="B26" s="5">
-        <v>46156.63214717593</v>
+        <v>46156.46548050926</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46195.92922835649</v>
+        <v>46195.762561689815</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>108</v>
@@ -3000,11 +3000,11 @@
         <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46156.6321521412</v>
+        <v>46156.46548547454</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46169.86132256944</v>
+        <v>46169.69465590278</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3063,11 +3063,11 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46156.63215657407</v>
+        <v>46156.46548990741</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46197.502050625</v>
+        <v>46197.33538395833</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3122,11 +3122,11 @@
         <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46156.63216167824</v>
+        <v>46156.46549501157</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46169.86172537037</v>
+        <v>46169.6950587037</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3181,11 +3181,11 @@
         <v>119</v>
       </c>
       <c r="B30" s="5">
-        <v>46156.63216756945</v>
+        <v>46156.46550090278</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46195.92957673611</v>
+        <v>46195.76291006945</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3244,13 +3244,13 @@
         <v>122</v>
       </c>
       <c r="B31" s="9">
-        <v>46156.63217278935</v>
+        <v>46156.46550612268</v>
       </c>
       <c r="C31" s="9">
-        <v>46195.929570740744</v>
+        <v>46195.76290407407</v>
       </c>
       <c r="D31" s="9">
-        <v>46195.92957241899</v>
+        <v>46195.762905752315</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>123</v>
@@ -3305,11 +3305,11 @@
         <v>125</v>
       </c>
       <c r="B32" s="5">
-        <v>46156.63217837963</v>
+        <v>46156.46551171296</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46195.92957792824</v>
+        <v>46195.76291126157</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -3364,11 +3364,11 @@
         <v>128</v>
       </c>
       <c r="B33" s="9">
-        <v>46156.63218368056</v>
+        <v>46156.46551701389</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46195.929578923606</v>
+        <v>46195.76291225695</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>129</v>
@@ -3423,11 +3423,11 @@
         <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46156.632188240736</v>
+        <v>46156.46552157408</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.861346631944</v>
+        <v>46169.69467996528</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3486,11 +3486,11 @@
         <v>136</v>
       </c>
       <c r="B35" s="9">
-        <v>46156.63219359954</v>
+        <v>46156.465526932865</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46196.656266342594</v>
+        <v>46196.48959967593</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3545,11 +3545,11 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46156.63219844908</v>
+        <v>46156.46553178241</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.86161818287</v>
+        <v>46169.694951516205</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3604,11 +3604,11 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46156.63225444444</v>
+        <v>46156.46558777778</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.86135784722</v>
+        <v>46169.69469118056</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3667,11 +3667,11 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46156.632258206024</v>
+        <v>46156.46559153935</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46196.65655980324</v>
+        <v>46196.489893136575</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>88</v>
@@ -3720,11 +3720,11 @@
         <v>147</v>
       </c>
       <c r="B39" s="9">
-        <v>46156.63226241898</v>
+        <v>46156.465595752314</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.86156158565</v>
+        <v>46169.69489491898</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>148</v>
@@ -3773,11 +3773,11 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46156.63226644676</v>
+        <v>46156.46559978009</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46196.70204975695</v>
+        <v>46196.535383090275</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3836,13 +3836,13 @@
         <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46156.632269444446</v>
+        <v>46156.46560277778</v>
       </c>
       <c r="C41" s="9">
-        <v>46196.699784247685</v>
+        <v>46196.53311758101</v>
       </c>
       <c r="D41" s="9">
-        <v>46196.69978633102</v>
+        <v>46196.53311966435</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>94</v>
@@ -3891,11 +3891,11 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46156.63227357639</v>
+        <v>46156.465606909725</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46196.699790694445</v>
+        <v>46196.533124027774</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -3944,11 +3944,11 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46156.63227760416</v>
+        <v>46156.4656109375</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.86151703703</v>
+        <v>46169.694850370375</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -3997,11 +3997,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46156.63228021991</v>
+        <v>46156.46561355324</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.861380682865</v>
+        <v>46169.69471401621</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4060,11 +4060,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46156.63228315972</v>
+        <v>46156.46561649306</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46196.657172465275</v>
+        <v>46196.49050579861</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>91</v>
@@ -4113,11 +4113,11 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46156.63228715278</v>
+        <v>46156.46562048611</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.86142826389</v>
+        <v>46169.694761597224</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4166,11 +4166,11 @@
         <v>172</v>
       </c>
       <c r="B47" s="9">
-        <v>46156.63196493055</v>
+        <v>46156.46529826389</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46184.58079096065</v>
+        <v>46184.41412429398</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>173</v>
@@ -4215,13 +4215,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46156.63229164352</v>
+        <v>46156.46562497685</v>
       </c>
       <c r="C48" s="5">
-        <v>46184.58069681713</v>
+        <v>46184.41403015047</v>
       </c>
       <c r="D48" s="5">
-        <v>46184.58071335648</v>
+        <v>46184.41404668981</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4280,13 +4280,13 @@
         <v>181</v>
       </c>
       <c r="B49" s="9">
-        <v>46156.632296261574</v>
+        <v>46156.46562959491</v>
       </c>
       <c r="C49" s="9">
-        <v>46184.58077318287</v>
+        <v>46184.414106516204</v>
       </c>
       <c r="D49" s="9">
-        <v>46184.58078841435</v>
+        <v>46184.414121747686</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>182</v>
@@ -4345,13 +4345,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46156.63230224537</v>
+        <v>46156.4656355787</v>
       </c>
       <c r="C50" s="5">
-        <v>46184.58082519676</v>
+        <v>46184.4141585301</v>
       </c>
       <c r="D50" s="5">
-        <v>46184.580841041665</v>
+        <v>46184.414174375</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>84</v>
@@ -4408,11 +4408,11 @@
         <v>187</v>
       </c>
       <c r="B51" s="9">
-        <v>46156.632315358795</v>
+        <v>46156.46564869213</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46156.72589140046</v>
+        <v>46156.55922473379</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>188</v>
@@ -4471,11 +4471,11 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46156.6323189699</v>
+        <v>46156.46565230324</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46156.725962881945</v>
+        <v>46156.55929621527</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4524,11 +4524,11 @@
         <v>195</v>
       </c>
       <c r="B53" s="9">
-        <v>46156.63233141204</v>
+        <v>46156.46566474537</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46156.70385697916</v>
+        <v>46156.537190312505</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>196</v>
@@ -4571,11 +4571,11 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46156.63233460648</v>
+        <v>46156.46566793982</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46156.72605925926</v>
+        <v>46156.55939259259</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
@@ -4634,11 +4634,11 @@
         <v>203</v>
       </c>
       <c r="B55" s="9">
-        <v>46156.63233969908</v>
+        <v>46156.465673032406</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46156.72612552083</v>
+        <v>46156.55945885417</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>204</v>
@@ -4697,11 +4697,11 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46156.632350671294</v>
+        <v>46156.46568400463</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46156.72605667824</v>
+        <v>46156.55939001158</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>208</v>
@@ -4760,11 +4760,11 @@
         <v>210</v>
       </c>
       <c r="B57" s="9">
-        <v>46156.63235533565</v>
+        <v>46156.46568866898</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46156.72612251157</v>
+        <v>46156.55945584491</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>211</v>
@@ -4823,11 +4823,11 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46156.63235945602</v>
+        <v>46156.46569278935</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46156.72605258102</v>
+        <v>46156.559385914356</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4886,11 +4886,11 @@
         <v>215</v>
       </c>
       <c r="B59" s="9">
-        <v>46156.63236322917</v>
+        <v>46156.4656965625</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46156.72611966435</v>
+        <v>46156.55945299768</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>214</v>
@@ -4949,11 +4949,11 @@
         <v>216</v>
       </c>
       <c r="B60" s="5">
-        <v>46156.63236744213</v>
+        <v>46156.46570077546</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46156.71024693287</v>
+        <v>46156.5435802662</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -4996,11 +4996,11 @@
         <v>219</v>
       </c>
       <c r="B61" s="9">
-        <v>46156.63237008102</v>
+        <v>46156.46570341435</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46161.57724298611</v>
+        <v>46161.410576319446</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>220</v>
@@ -5059,11 +5059,11 @@
         <v>224</v>
       </c>
       <c r="B62" s="5">
-        <v>46156.63237584491</v>
+        <v>46156.46570917824</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46156.72624517361</v>
+        <v>46156.559578506945</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>193</v>
@@ -5112,11 +5112,11 @@
         <v>227</v>
       </c>
       <c r="B63" s="9">
-        <v>46156.63239597222</v>
+        <v>46156.46572930556</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46156.72619693287</v>
+        <v>46156.559530266204</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>228</v>
@@ -5175,11 +5175,11 @@
         <v>229</v>
       </c>
       <c r="B64" s="5">
-        <v>46156.632400069444</v>
+        <v>46156.46573340277</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46184.58084231481</v>
+        <v>46184.41417564815</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>193</v>
@@ -5228,11 +5228,11 @@
         <v>232</v>
       </c>
       <c r="B65" s="9">
-        <v>46156.63246734954</v>
+        <v>46156.46580068287</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46156.726193263894</v>
+        <v>46156.55952659722</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>233</v>
@@ -5291,11 +5291,11 @@
         <v>234</v>
       </c>
       <c r="B66" s="5">
-        <v>46156.632472627316</v>
+        <v>46156.465805960645</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46184.58084060185</v>
+        <v>46184.41417393518</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>193</v>
@@ -5344,11 +5344,11 @@
         <v>236</v>
       </c>
       <c r="B67" s="9">
-        <v>46156.6324928588</v>
+        <v>46156.46582619213</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46156.71243400463</v>
+        <v>46156.545767337964</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>196</v>
@@ -5391,11 +5391,11 @@
         <v>238</v>
       </c>
       <c r="B68" s="5">
-        <v>46156.63249635417</v>
+        <v>46156.4658296875</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46156.72645449074</v>
+        <v>46156.55978782407</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>239</v>
@@ -5454,11 +5454,11 @@
         <v>240</v>
       </c>
       <c r="B69" s="9">
-        <v>46156.63250229167</v>
+        <v>46156.465835625</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46156.726451689814</v>
+        <v>46156.55978502315</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>241</v>
@@ -5517,11 +5517,11 @@
         <v>242</v>
       </c>
       <c r="B70" s="5">
-        <v>46156.63250851852</v>
+        <v>46156.46584185185</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46156.726448877314</v>
+        <v>46156.55978221065</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>243</v>
@@ -5580,11 +5580,11 @@
         <v>244</v>
       </c>
       <c r="B71" s="9">
-        <v>46156.63251465278</v>
+        <v>46156.46584798611</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46156.726445520835</v>
+        <v>46156.55977885416</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>245</v>
@@ -5643,11 +5643,11 @@
         <v>247</v>
       </c>
       <c r="B72" s="5">
-        <v>46156.63251914352</v>
+        <v>46156.46585247685</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46156.71581511574</v>
+        <v>46156.54914844908</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>248</v>
@@ -5690,11 +5690,11 @@
         <v>250</v>
       </c>
       <c r="B73" s="9">
-        <v>46156.63252219907</v>
+        <v>46156.465855532406</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46156.72654819445</v>
+        <v>46156.55988152778</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>251</v>
@@ -5753,11 +5753,11 @@
         <v>253</v>
       </c>
       <c r="B74" s="5">
-        <v>46156.63252934028</v>
+        <v>46156.46586267361</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46156.726576076384</v>
+        <v>46156.55990940973</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>193</v>
@@ -5806,11 +5806,11 @@
         <v>254</v>
       </c>
       <c r="B75" s="9">
-        <v>46156.63254586805</v>
+        <v>46156.465879201394</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46156.72654520834</v>
+        <v>46156.559878541666</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>255</v>
@@ -5869,11 +5869,11 @@
         <v>256</v>
       </c>
       <c r="B76" s="5">
-        <v>46156.63255047453</v>
+        <v>46156.465883807876</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46184.58084127315</v>
+        <v>46184.414174606485</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>193</v>
@@ -5922,11 +5922,11 @@
         <v>259</v>
       </c>
       <c r="B77" s="9">
-        <v>46156.63257873843</v>
+        <v>46156.465912071755</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46156.726542372686</v>
+        <v>46156.55987570602</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>260</v>
@@ -5985,11 +5985,11 @@
         <v>261</v>
       </c>
       <c r="B78" s="5">
-        <v>46156.632582986116</v>
+        <v>46156.465916319445</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46184.58084195602</v>
+        <v>46184.41417528935</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>193</v>
@@ -6038,11 +6038,11 @@
         <v>263</v>
       </c>
       <c r="B79" s="9">
-        <v>46156.632655671296</v>
+        <v>46156.46598900463</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46156.72653921296</v>
+        <v>46156.55987254629</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>264</v>
@@ -6101,11 +6101,11 @@
         <v>265</v>
       </c>
       <c r="B80" s="5">
-        <v>46156.6326615162</v>
+        <v>46156.46599484954</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46184.58084310185</v>
+        <v>46184.41417643518</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>193</v>
@@ -6154,11 +6154,11 @@
         <v>268</v>
       </c>
       <c r="B81" s="9">
-        <v>46156.6326856713</v>
+        <v>46156.46601900463</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46156.72653572916</v>
+        <v>46156.559869062505</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>269</v>
@@ -6217,11 +6217,11 @@
         <v>270</v>
       </c>
       <c r="B82" s="5">
-        <v>46156.63269413194</v>
+        <v>46156.46602746528</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46156.72676160879</v>
+        <v>46156.560094942135</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>193</v>
@@ -6270,11 +6270,11 @@
         <v>272</v>
       </c>
       <c r="B83" s="9">
-        <v>46156.632715810185</v>
+        <v>46156.46604914352</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46156.726531747685</v>
+        <v>46156.55986508101</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>273</v>
@@ -6333,11 +6333,11 @@
         <v>275</v>
       </c>
       <c r="B84" s="5">
-        <v>46156.63272170139</v>
+        <v>46156.46605503472</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46156.72680289352</v>
+        <v>46156.56013622685</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>193</v>
@@ -6386,11 +6386,11 @@
         <v>277</v>
       </c>
       <c r="B85" s="9">
-        <v>46156.63273993056</v>
+        <v>46156.46607326389</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46156.7168192824</v>
+        <v>46156.550152615746</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>278</v>
@@ -6433,11 +6433,11 @@
         <v>280</v>
       </c>
       <c r="B86" s="5">
-        <v>46156.63274356481</v>
+        <v>46156.46607689815</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46156.7268765162</v>
+        <v>46156.56020984954</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>281</v>
@@ -6496,11 +6496,11 @@
         <v>284</v>
       </c>
       <c r="B87" s="9">
-        <v>46156.63274915509</v>
+        <v>46156.46608248843</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46156.72692035879</v>
+        <v>46156.56025369213</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>193</v>
@@ -6549,11 +6549,11 @@
         <v>286</v>
       </c>
       <c r="B88" s="5">
-        <v>46156.63276633102</v>
+        <v>46156.46609966435</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46156.72700125</v>
+        <v>46156.56033458334</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>287</v>
@@ -6610,11 +6610,11 @@
         <v>288</v>
       </c>
       <c r="B89" s="9">
-        <v>46156.63277084491</v>
+        <v>46156.46610417824</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46156.72697212963</v>
+        <v>46156.56030546296</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>193</v>
@@ -6663,11 +6663,11 @@
         <v>290</v>
       </c>
       <c r="B90" s="5">
-        <v>46156.63283398148</v>
+        <v>46156.466167314815</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46156.727094305556</v>
+        <v>46156.56042763889</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>291</v>
@@ -6726,11 +6726,11 @@
         <v>292</v>
       </c>
       <c r="B91" s="9">
-        <v>46156.63284013889</v>
+        <v>46156.46617347222</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46156.727054675925</v>
+        <v>46156.56038800926</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>193</v>
@@ -6779,11 +6779,11 @@
         <v>294</v>
       </c>
       <c r="B92" s="5">
-        <v>46156.63286864583</v>
+        <v>46156.466201979165</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46156.727220243054</v>
+        <v>46156.56055357639</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>295</v>
@@ -6842,11 +6842,11 @@
         <v>297</v>
       </c>
       <c r="B93" s="9">
-        <v>46156.632875972224</v>
+        <v>46156.46620930555</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46156.727183668976</v>
+        <v>46156.56051700232</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>193</v>
@@ -6893,11 +6893,11 @@
         <v>298</v>
       </c>
       <c r="B94" s="5">
-        <v>46156.63290420139</v>
+        <v>46156.466237534725</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46156.71731457176</v>
+        <v>46156.5506479051</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>299</v>
@@ -6940,11 +6940,11 @@
         <v>301</v>
       </c>
       <c r="B95" s="9">
-        <v>46156.63290788194</v>
+        <v>46156.46624121528</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46156.72728918982</v>
+        <v>46156.560622523146</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>302</v>
@@ -7003,11 +7003,11 @@
         <v>305</v>
       </c>
       <c r="B96" s="5">
-        <v>46156.63291414352</v>
+        <v>46156.466247476856</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46156.727343402774</v>
+        <v>46156.56067673611</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>306</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="310">
   <si>
     <t>50001547 - XEMORTIZ (AMERICAS GOLD)</t>
   </si>
@@ -572,31 +572,37 @@
     <t>Planos preliminar</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>1214809534019523</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor OT 4317,Planos preliminar</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214809528759377</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>1214809534019523</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT 4317,Planos preliminar</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214809528759377</t>
   </si>
   <si>
     <t xml:space="preserve">Propuesta Fabricación externa  OT 4317,propuesta Corte Laser OT 4317,Propuesta Corte plasma  OT 4317,Propuesta Mecanizado OT 4317,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 </t>
@@ -1589,13 +1595,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46156.46528078704</v>
+        <v>46156.6319474537</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70686295139</v>
+        <v>46175.87352961805</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.706874456024</v>
+        <v>46175.87354112268</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1642,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46156.465400671295</v>
+        <v>46156.63206733797</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.70683420139</v>
+        <v>46175.87350086805</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.70686409722</v>
+        <v>46175.873530763885</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1705,13 +1711,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46156.46540380787</v>
+        <v>46156.63207047454</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.706834930555</v>
+        <v>46175.87350159722</v>
       </c>
       <c r="D6" s="5">
-        <v>46184.413204930555</v>
+        <v>46184.57987159722</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1768,13 +1774,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46156.465406550924</v>
+        <v>46156.632073217595</v>
       </c>
       <c r="C7" s="9">
-        <v>46184.41449466435</v>
+        <v>46184.58116133102</v>
       </c>
       <c r="D7" s="9">
-        <v>46184.41449592593</v>
+        <v>46184.58116259259</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -1831,13 +1837,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46156.46540930556</v>
+        <v>46156.63207597222</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.70683589121</v>
+        <v>46175.87350255787</v>
       </c>
       <c r="D8" s="5">
-        <v>46184.412972962964</v>
+        <v>46184.57963962963</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1894,13 +1900,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46156.46541258102</v>
+        <v>46156.63207924768</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.70683657407</v>
+        <v>46175.87350324074</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.70686366898</v>
+        <v>46175.87353033565</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -1957,11 +1963,11 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46156.465284826394</v>
+        <v>46156.63195149305</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46184.413799918984</v>
+        <v>46184.58046658565</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2004,13 +2010,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46156.46541579861</v>
+        <v>46156.63208246528</v>
       </c>
       <c r="C11" s="9">
-        <v>46184.41364805556</v>
+        <v>46184.58031472222</v>
       </c>
       <c r="D11" s="9">
-        <v>46184.413664085645</v>
+        <v>46184.58033075232</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2069,13 +2075,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46156.465420925924</v>
+        <v>46156.63208759259</v>
       </c>
       <c r="C12" s="5">
-        <v>46184.41365743056</v>
+        <v>46184.580324097224</v>
       </c>
       <c r="D12" s="5">
-        <v>46184.41367418981</v>
+        <v>46184.58034085648</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2134,13 +2140,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46156.46542587963</v>
+        <v>46156.63209254629</v>
       </c>
       <c r="C13" s="9">
-        <v>46184.41378944444</v>
+        <v>46184.580456111114</v>
       </c>
       <c r="D13" s="9">
-        <v>46184.41380574074</v>
+        <v>46184.58047240741</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2199,11 +2205,11 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46156.46543094907</v>
+        <v>46156.632097615744</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46184.41380574074</v>
+        <v>46184.58047240741</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2262,13 +2268,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46156.465289699074</v>
+        <v>46156.631956365745</v>
       </c>
       <c r="C15" s="9">
-        <v>46197.33538849537</v>
+        <v>46197.50205516204</v>
       </c>
       <c r="D15" s="9">
-        <v>46197.33539957176</v>
+        <v>46197.50206623843</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2315,13 +2321,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46156.465438495376</v>
+        <v>46156.63210516203</v>
       </c>
       <c r="C16" s="5">
-        <v>46184.41381557871</v>
+        <v>46184.58048224537</v>
       </c>
       <c r="D16" s="5">
-        <v>46184.41383159722</v>
+        <v>46184.58049826389</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2380,13 +2386,13 @@
         <v>73</v>
       </c>
       <c r="B17" s="9">
-        <v>46156.4654437037</v>
+        <v>46156.63211037037</v>
       </c>
       <c r="C17" s="9">
-        <v>46184.4138299537</v>
+        <v>46184.58049662037</v>
       </c>
       <c r="D17" s="9">
-        <v>46184.41384527778</v>
+        <v>46184.58051194444</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>74</v>
@@ -2445,13 +2451,13 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46156.465448981486</v>
+        <v>46156.63211564815</v>
       </c>
       <c r="C18" s="5">
-        <v>46197.33537231482</v>
+        <v>46197.50203898148</v>
       </c>
       <c r="D18" s="5">
-        <v>46197.335374988426</v>
+        <v>46197.5020416551</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2510,13 +2516,13 @@
         <v>80</v>
       </c>
       <c r="B19" s="9">
-        <v>46156.46545483796</v>
+        <v>46156.632121504634</v>
       </c>
       <c r="C19" s="9">
-        <v>46196.48959278935</v>
+        <v>46196.656259456024</v>
       </c>
       <c r="D19" s="9">
-        <v>46196.48960886574</v>
+        <v>46196.65627553241</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>81</v>
@@ -2575,13 +2581,13 @@
         <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46156.465459652776</v>
+        <v>46156.63212631944</v>
       </c>
       <c r="C20" s="5">
-        <v>46196.489887268515</v>
+        <v>46196.65655393519</v>
       </c>
       <c r="D20" s="5">
-        <v>46196.48990119213</v>
+        <v>46196.656567858794</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2640,13 +2646,13 @@
         <v>89</v>
       </c>
       <c r="B21" s="9">
-        <v>46156.4654633912</v>
+        <v>46156.63213005787</v>
       </c>
       <c r="C21" s="9">
-        <v>46196.490499872685</v>
+        <v>46196.65716653936</v>
       </c>
       <c r="D21" s="9">
-        <v>46196.49051640046</v>
+        <v>46196.65718306713</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2705,13 +2711,13 @@
         <v>92</v>
       </c>
       <c r="B22" s="5">
-        <v>46156.46546702547</v>
+        <v>46156.632133692125</v>
       </c>
       <c r="C22" s="5">
-        <v>46196.49099341435</v>
+        <v>46196.65766008102</v>
       </c>
       <c r="D22" s="5">
-        <v>46196.491007743054</v>
+        <v>46196.657674409726</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2770,11 +2776,11 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46156.46529391204</v>
+        <v>46156.6319605787</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46156.531661388886</v>
+        <v>46156.69832805556</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2817,11 +2823,11 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46156.46547148148</v>
+        <v>46156.63213814815</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46195.76256228009</v>
+        <v>46195.929228946756</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2880,13 +2886,13 @@
         <v>104</v>
       </c>
       <c r="B25" s="9">
-        <v>46156.46547592593</v>
+        <v>46156.63214259259</v>
       </c>
       <c r="C25" s="9">
-        <v>46195.76255408565</v>
+        <v>46195.92922075231</v>
       </c>
       <c r="D25" s="9">
-        <v>46195.76255671296</v>
+        <v>46195.92922337963</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>105</v>
@@ -2941,11 +2947,11 @@
         <v>107</v>
       </c>
       <c r="B26" s="5">
-        <v>46156.46548050926</v>
+        <v>46156.63214717593</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46195.762561689815</v>
+        <v>46195.92922835649</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>108</v>
@@ -3000,11 +3006,11 @@
         <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46156.46548547454</v>
+        <v>46156.6321521412</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46169.69465590278</v>
+        <v>46169.86132256944</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3063,11 +3069,11 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46156.46548990741</v>
+        <v>46156.63215657407</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46197.33538395833</v>
+        <v>46197.502050625</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3122,11 +3128,11 @@
         <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46156.46549501157</v>
+        <v>46156.63216167824</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46169.6950587037</v>
+        <v>46169.86172537037</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3181,11 +3187,11 @@
         <v>119</v>
       </c>
       <c r="B30" s="5">
-        <v>46156.46550090278</v>
+        <v>46156.63216756945</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46195.76291006945</v>
+        <v>46195.92957673611</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3244,13 +3250,13 @@
         <v>122</v>
       </c>
       <c r="B31" s="9">
-        <v>46156.46550612268</v>
+        <v>46156.63217278935</v>
       </c>
       <c r="C31" s="9">
-        <v>46195.76290407407</v>
+        <v>46195.929570740744</v>
       </c>
       <c r="D31" s="9">
-        <v>46195.762905752315</v>
+        <v>46195.92957241899</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>123</v>
@@ -3305,11 +3311,11 @@
         <v>125</v>
       </c>
       <c r="B32" s="5">
-        <v>46156.46551171296</v>
+        <v>46156.63217837963</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46195.76291126157</v>
+        <v>46195.92957792824</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -3364,11 +3370,11 @@
         <v>128</v>
       </c>
       <c r="B33" s="9">
-        <v>46156.46551701389</v>
+        <v>46156.63218368056</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46195.76291225695</v>
+        <v>46195.929578923606</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>129</v>
@@ -3423,11 +3429,11 @@
         <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46156.46552157408</v>
+        <v>46156.632188240736</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.69467996528</v>
+        <v>46169.861346631944</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3486,11 +3492,11 @@
         <v>136</v>
       </c>
       <c r="B35" s="9">
-        <v>46156.465526932865</v>
+        <v>46156.63219359954</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46196.48959967593</v>
+        <v>46196.656266342594</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3545,11 +3551,11 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46156.46553178241</v>
+        <v>46156.63219844908</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.694951516205</v>
+        <v>46169.86161818287</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3604,11 +3610,11 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46156.46558777778</v>
+        <v>46156.63225444444</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.69469118056</v>
+        <v>46169.86135784722</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3667,11 +3673,11 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46156.46559153935</v>
+        <v>46156.632258206024</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46196.489893136575</v>
+        <v>46196.65655980324</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>88</v>
@@ -3720,11 +3726,11 @@
         <v>147</v>
       </c>
       <c r="B39" s="9">
-        <v>46156.465595752314</v>
+        <v>46156.63226241898</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.69489491898</v>
+        <v>46169.86156158565</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>148</v>
@@ -3773,11 +3779,11 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46156.46559978009</v>
+        <v>46156.63226644676</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46196.535383090275</v>
+        <v>46196.70204975695</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3836,13 +3842,13 @@
         <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46156.46560277778</v>
+        <v>46156.632269444446</v>
       </c>
       <c r="C41" s="9">
-        <v>46196.53311758101</v>
+        <v>46196.699784247685</v>
       </c>
       <c r="D41" s="9">
-        <v>46196.53311966435</v>
+        <v>46196.69978633102</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>94</v>
@@ -3891,11 +3897,11 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46156.465606909725</v>
+        <v>46156.63227357639</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46196.533124027774</v>
+        <v>46196.699790694445</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -3944,11 +3950,11 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46156.4656109375</v>
+        <v>46156.63227760416</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.694850370375</v>
+        <v>46169.86151703703</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -3997,11 +4003,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46156.46561355324</v>
+        <v>46156.63228021991</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.69471401621</v>
+        <v>46169.861380682865</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4060,11 +4066,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46156.46561649306</v>
+        <v>46156.63228315972</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46196.49050579861</v>
+        <v>46196.657172465275</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>91</v>
@@ -4113,11 +4119,11 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46156.46562048611</v>
+        <v>46156.63228715278</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.694761597224</v>
+        <v>46169.86142826389</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4166,11 +4172,11 @@
         <v>172</v>
       </c>
       <c r="B47" s="9">
-        <v>46156.46529826389</v>
+        <v>46156.63196493055</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46184.41412429398</v>
+        <v>46184.58079096065</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>173</v>
@@ -4215,13 +4221,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46156.46562497685</v>
+        <v>46156.63229164352</v>
       </c>
       <c r="C48" s="5">
-        <v>46184.41403015047</v>
+        <v>46184.58069681713</v>
       </c>
       <c r="D48" s="5">
-        <v>46184.41404668981</v>
+        <v>46197.714709479165</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4280,13 +4286,13 @@
         <v>181</v>
       </c>
       <c r="B49" s="9">
-        <v>46156.46562959491</v>
+        <v>46156.632296261574</v>
       </c>
       <c r="C49" s="9">
-        <v>46184.414106516204</v>
+        <v>46184.58077318287</v>
       </c>
       <c r="D49" s="9">
-        <v>46184.414121747686</v>
+        <v>46197.714779409725</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>182</v>
@@ -4345,13 +4351,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46156.4656355787</v>
+        <v>46156.63230224537</v>
       </c>
       <c r="C50" s="5">
-        <v>46184.4141585301</v>
+        <v>46184.58082519676</v>
       </c>
       <c r="D50" s="5">
-        <v>46184.414174375</v>
+        <v>46184.580841041665</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>84</v>
@@ -4360,10 +4366,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4385,7 +4391,7 @@
         <v>182</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q50" s="5">
         <v>46211</v>
@@ -4405,26 +4411,26 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
-        <v>46156.46564869213</v>
+        <v>46156.632315358795</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46156.55922473379</v>
+        <v>46156.72589140046</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I51" s="9">
         <v>46301</v>
@@ -4445,7 +4451,7 @@
         <v>173</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4468,26 +4474,26 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46156.46565230324</v>
+        <v>46156.6323189699</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46156.55929621527</v>
+        <v>46156.725962881945</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>189</v>
-      </c>
       <c r="H52" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I52" s="5">
         <v>46301</v>
@@ -4505,13 +4511,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4521,17 +4527,17 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B53" s="9">
-        <v>46156.46566474537</v>
+        <v>46156.63233141204</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46156.537190312505</v>
+        <v>46156.70385697916</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4555,7 +4561,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4568,26 +4574,26 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B54" s="5">
-        <v>46156.46566793982</v>
+        <v>46156.63233460648</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46156.55939259259</v>
+        <v>46156.72605925926</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I54" s="5">
         <v>46227</v>
@@ -4605,13 +4611,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q54" s="5">
         <v>46227</v>
@@ -4631,17 +4637,17 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B55" s="9">
-        <v>46156.465673032406</v>
+        <v>46156.63233969908</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46156.55945885417</v>
+        <v>46156.72612552083</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4668,13 +4674,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q55" s="9">
         <v>46231</v>
@@ -4694,26 +4700,26 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46156.46568400463</v>
+        <v>46156.632350671294</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46156.55939001158</v>
+        <v>46156.72605667824</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I56" s="5">
         <v>46227</v>
@@ -4731,13 +4737,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>148</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q56" s="5">
         <v>46227</v>
@@ -4757,17 +4763,17 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B57" s="9">
-        <v>46156.46568866898</v>
+        <v>46156.63235533565</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46156.55945584491</v>
+        <v>46156.72612251157</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -4794,13 +4800,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q57" s="9">
         <v>46231</v>
@@ -4820,26 +4826,26 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46156.46569278935</v>
+        <v>46156.63235945602</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46156.559385914356</v>
+        <v>46156.72605258102</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I58" s="5">
         <v>46227</v>
@@ -4857,13 +4863,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>170</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q58" s="5">
         <v>46227</v>
@@ -4883,17 +4889,17 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B59" s="9">
-        <v>46156.4656965625</v>
+        <v>46156.63236322917</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46156.55945299768</v>
+        <v>46156.72611966435</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -4920,13 +4926,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q59" s="9">
         <v>46231</v>
@@ -4946,17 +4952,17 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46156.46570077546</v>
+        <v>46156.63236744213</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46156.5435802662</v>
+        <v>46156.71024693287</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -4980,7 +4986,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -4993,26 +4999,26 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B61" s="9">
-        <v>46156.46570341435</v>
+        <v>46156.63237008102</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46161.410576319446</v>
+        <v>46161.57724298611</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I61" s="9">
         <v>46233</v>
@@ -5030,13 +5036,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q61" s="9">
         <v>46233</v>
@@ -5056,26 +5062,26 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46156.46570917824</v>
+        <v>46156.63237584491</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46156.559578506945</v>
+        <v>46156.72624517361</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I62" s="5">
         <v>46233</v>
@@ -5093,13 +5099,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5109,26 +5115,26 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B63" s="9">
-        <v>46156.46572930556</v>
+        <v>46156.63239597222</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46156.559530266204</v>
+        <v>46156.72619693287</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5146,13 +5152,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q63" s="9">
         <v>46244</v>
@@ -5172,26 +5178,26 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46156.46573340277</v>
+        <v>46156.632400069444</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46184.41417564815</v>
+        <v>46184.58084231481</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I64" s="5">
         <v>46244</v>
@@ -5209,13 +5215,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5225,26 +5231,26 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B65" s="9">
-        <v>46156.46580068287</v>
+        <v>46156.63246734954</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46156.55952659722</v>
+        <v>46156.726193263894</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I65" s="9">
         <v>46262</v>
@@ -5262,13 +5268,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q65" s="9">
         <v>46262</v>
@@ -5288,26 +5294,26 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46156.465805960645</v>
+        <v>46156.632472627316</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46184.41417393518</v>
+        <v>46184.58084060185</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I66" s="5">
         <v>46262</v>
@@ -5325,13 +5331,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5341,17 +5347,17 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B67" s="9">
-        <v>46156.46582619213</v>
+        <v>46156.6324928588</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46156.545767337964</v>
+        <v>46156.71243400463</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>25</v>
@@ -5375,7 +5381,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>26</v>
@@ -5388,26 +5394,26 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B68" s="5">
-        <v>46156.4658296875</v>
+        <v>46156.63249635417</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46156.55978782407</v>
+        <v>46156.72645449074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I68" s="5">
         <v>46154</v>
@@ -5425,13 +5431,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>117</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q68" s="5">
         <v>46154</v>
@@ -5451,26 +5457,26 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B69" s="9">
-        <v>46156.465835625</v>
+        <v>46156.63250229167</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46156.55978502315</v>
+        <v>46156.726451689814</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I69" s="9">
         <v>46268</v>
@@ -5488,13 +5494,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>108</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q69" s="9">
         <v>46268</v>
@@ -5514,26 +5520,26 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B70" s="5">
-        <v>46156.46584185185</v>
+        <v>46156.63250851852</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46156.55978221065</v>
+        <v>46156.726448877314</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I70" s="5">
         <v>46294</v>
@@ -5551,13 +5557,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>126</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q70" s="5">
         <v>46294</v>
@@ -5577,26 +5583,26 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B71" s="9">
-        <v>46156.46584798611</v>
+        <v>46156.63251465278</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46156.55977885416</v>
+        <v>46156.726445520835</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I71" s="9">
         <v>46255</v>
@@ -5614,13 +5620,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>158</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q71" s="9">
         <v>46255</v>
@@ -5640,17 +5646,17 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B72" s="5">
-        <v>46156.46585247685</v>
+        <v>46156.63251914352</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46156.54914844908</v>
+        <v>46156.71581511574</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>25</v>
@@ -5674,7 +5680,7 @@
         <v>26</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>26</v>
@@ -5687,17 +5693,17 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B73" s="9">
-        <v>46156.465855532406</v>
+        <v>46156.63252219907</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46156.55988152778</v>
+        <v>46156.72654819445</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5724,13 +5730,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q73" s="9">
         <v>46266</v>
@@ -5750,17 +5756,17 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B74" s="5">
-        <v>46156.46586267361</v>
+        <v>46156.63252934028</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46156.55990940973</v>
+        <v>46156.726576076384</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5787,10 +5793,10 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5803,17 +5809,17 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B75" s="9">
-        <v>46156.465879201394</v>
+        <v>46156.63254586805</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46156.559878541666</v>
+        <v>46156.72654520834</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5840,13 +5846,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q75" s="9">
         <v>46288</v>
@@ -5866,17 +5872,17 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B76" s="5">
-        <v>46156.465883807876</v>
+        <v>46156.63255047453</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46184.414174606485</v>
+        <v>46184.58084127315</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5903,13 +5909,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5919,17 +5925,17 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B77" s="9">
-        <v>46156.465912071755</v>
+        <v>46156.63257873843</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46156.55987570602</v>
+        <v>46156.726542372686</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5956,13 +5962,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q77" s="9">
         <v>46290</v>
@@ -5982,17 +5988,17 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B78" s="5">
-        <v>46156.465916319445</v>
+        <v>46156.632582986116</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46184.41417528935</v>
+        <v>46184.58084195602</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6019,13 +6025,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O78" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="P78" s="6" t="s">
         <v>262</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>260</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6035,17 +6041,17 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B79" s="9">
-        <v>46156.46598900463</v>
+        <v>46156.632655671296</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46156.55987254629</v>
+        <v>46156.72653921296</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6072,13 +6078,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q79" s="9">
         <v>46296</v>
@@ -6098,17 +6104,17 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B80" s="5">
-        <v>46156.46599484954</v>
+        <v>46156.6326615162</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46184.41417643518</v>
+        <v>46184.58084310185</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6135,13 +6141,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6151,17 +6157,17 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B81" s="9">
-        <v>46156.46601900463</v>
+        <v>46156.6326856713</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46156.559869062505</v>
+        <v>46156.72653572916</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6188,13 +6194,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q81" s="9">
         <v>46300</v>
@@ -6214,17 +6220,17 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B82" s="5">
-        <v>46156.46602746528</v>
+        <v>46156.63269413194</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46156.560094942135</v>
+        <v>46156.72676160879</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6251,13 +6257,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6267,17 +6273,17 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B83" s="9">
-        <v>46156.46604914352</v>
+        <v>46156.632715810185</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46156.55986508101</v>
+        <v>46156.726531747685</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6304,13 +6310,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q83" s="9">
         <v>46302</v>
@@ -6330,17 +6336,17 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B84" s="5">
-        <v>46156.46605503472</v>
+        <v>46156.63272170139</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46156.56013622685</v>
+        <v>46156.72680289352</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6367,13 +6373,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6383,17 +6389,17 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B85" s="9">
-        <v>46156.46607326389</v>
+        <v>46156.63273993056</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46156.550152615746</v>
+        <v>46156.7168192824</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>25</v>
@@ -6417,7 +6423,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6430,26 +6436,26 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B86" s="5">
-        <v>46156.46607689815</v>
+        <v>46156.63274356481</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46156.56020984954</v>
+        <v>46156.7268765162</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I86" s="5">
         <v>46303</v>
@@ -6467,13 +6473,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="O86" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="O86" s="6" t="s">
-        <v>276</v>
-      </c>
       <c r="P86" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q86" s="5">
         <v>46303</v>
@@ -6493,26 +6499,26 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B87" s="9">
-        <v>46156.46608248843</v>
+        <v>46156.63274915509</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46156.56025369213</v>
+        <v>46156.72692035879</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I87" s="9">
         <v>46303</v>
@@ -6530,13 +6536,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6546,17 +6552,17 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B88" s="5">
-        <v>46156.46609966435</v>
+        <v>46156.63276633102</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46156.56033458334</v>
+        <v>46156.72700125</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6581,13 +6587,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q88" s="5">
         <v>46304</v>
@@ -6607,17 +6613,17 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B89" s="9">
-        <v>46156.46610417824</v>
+        <v>46156.63277084491</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46156.56030546296</v>
+        <v>46156.72697212963</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6644,13 +6650,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6660,26 +6666,26 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B90" s="5">
-        <v>46156.466167314815</v>
+        <v>46156.63283398148</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46156.56042763889</v>
+        <v>46156.727094305556</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I90" s="5">
         <v>46307</v>
@@ -6697,13 +6703,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q90" s="5">
         <v>46307</v>
@@ -6723,26 +6729,26 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B91" s="9">
-        <v>46156.46617347222</v>
+        <v>46156.63284013889</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46156.56038800926</v>
+        <v>46156.727054675925</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I91" s="9">
         <v>46307</v>
@@ -6760,13 +6766,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6776,26 +6782,26 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B92" s="5">
-        <v>46156.466201979165</v>
+        <v>46156.63286864583</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46156.56055357639</v>
+        <v>46156.727220243054</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I92" s="5">
         <v>46308</v>
@@ -6813,13 +6819,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q92" s="5">
         <v>46308</v>
@@ -6839,26 +6845,26 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B93" s="9">
-        <v>46156.46620930555</v>
+        <v>46156.632875972224</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46156.56051700232</v>
+        <v>46156.727183668976</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="9">
@@ -6874,13 +6880,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6890,17 +6896,17 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B94" s="5">
-        <v>46156.466237534725</v>
+        <v>46156.63290420139</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46156.5506479051</v>
+        <v>46156.71731457176</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>25</v>
@@ -6924,7 +6930,7 @@
         <v>26</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>26</v>
@@ -6937,26 +6943,26 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B95" s="9">
-        <v>46156.46624121528</v>
+        <v>46156.63290788194</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46156.560622523146</v>
+        <v>46156.72728918982</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I95" s="9">
         <v>46309</v>
@@ -6974,13 +6980,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q95" s="9">
         <v>46309</v>
@@ -7000,17 +7006,17 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B96" s="5">
-        <v>46156.466247476856</v>
+        <v>46156.63291414352</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46156.56067673611</v>
+        <v>46156.727343402774</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7037,13 +7043,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q96" s="5">
         <v>46309</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46195.92957673611</v>
+        <v>46197.783559131945</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3372,9 +3372,11 @@
       <c r="B33" s="9">
         <v>46156.63218368056</v>
       </c>
-      <c r="C33" s="10"/>
+      <c r="C33" s="9">
+        <v>46197.78355179398</v>
+      </c>
       <c r="D33" s="9">
-        <v>46195.929578923606</v>
+        <v>46197.78355364583</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>129</v>
@@ -4292,7 +4294,7 @@
         <v>46184.58077318287</v>
       </c>
       <c r="D49" s="9">
-        <v>46197.714779409725</v>
+        <v>46197.78357092592</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>182</v>
@@ -4342,8 +4344,8 @@
       <c r="T49" s="10">
         <v>1</v>
       </c>
-      <c r="U49" s="7" t="s">
-        <v>27</v>
+      <c r="U49" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -5240,7 +5240,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46156.726193263894</v>
+        <v>46197.83505042824</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>235</v>
@@ -5249,10 +5249,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>223</v>
+        <v>162</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>224</v>
+        <v>163</v>
       </c>
       <c r="I65" s="9">
         <v>46262</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46184.58084060185</v>
+        <v>46197.83511621528</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>195</v>
@@ -5312,10 +5312,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>223</v>
+        <v>162</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>224</v>
+        <v>163</v>
       </c>
       <c r="I66" s="5">
         <v>46262</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -1595,13 +1595,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46156.6319474537</v>
+        <v>46156.46528078704</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.87352961805</v>
+        <v>46175.70686295139</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.87354112268</v>
+        <v>46175.706874456024</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46156.63206733797</v>
+        <v>46156.465400671295</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.87350086805</v>
+        <v>46175.70683420139</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.873530763885</v>
+        <v>46175.70686409722</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1711,13 +1711,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46156.63207047454</v>
+        <v>46156.46540380787</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.87350159722</v>
+        <v>46175.706834930555</v>
       </c>
       <c r="D6" s="5">
-        <v>46184.57987159722</v>
+        <v>46184.413204930555</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1774,13 +1774,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46156.632073217595</v>
+        <v>46156.465406550924</v>
       </c>
       <c r="C7" s="9">
-        <v>46184.58116133102</v>
+        <v>46184.41449466435</v>
       </c>
       <c r="D7" s="9">
-        <v>46184.58116259259</v>
+        <v>46184.41449592593</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -1837,13 +1837,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46156.63207597222</v>
+        <v>46156.46540930556</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.87350255787</v>
+        <v>46175.70683589121</v>
       </c>
       <c r="D8" s="5">
-        <v>46184.57963962963</v>
+        <v>46184.412972962964</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1900,13 +1900,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46156.63207924768</v>
+        <v>46156.46541258102</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.87350324074</v>
+        <v>46175.70683657407</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.87353033565</v>
+        <v>46175.70686366898</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -1963,11 +1963,11 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46156.63195149305</v>
+        <v>46156.465284826394</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46184.58046658565</v>
+        <v>46184.413799918984</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2010,13 +2010,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46156.63208246528</v>
+        <v>46156.46541579861</v>
       </c>
       <c r="C11" s="9">
-        <v>46184.58031472222</v>
+        <v>46184.41364805556</v>
       </c>
       <c r="D11" s="9">
-        <v>46184.58033075232</v>
+        <v>46184.413664085645</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2075,13 +2075,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46156.63208759259</v>
+        <v>46156.465420925924</v>
       </c>
       <c r="C12" s="5">
-        <v>46184.580324097224</v>
+        <v>46184.41365743056</v>
       </c>
       <c r="D12" s="5">
-        <v>46184.58034085648</v>
+        <v>46184.41367418981</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2140,13 +2140,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46156.63209254629</v>
+        <v>46156.46542587963</v>
       </c>
       <c r="C13" s="9">
-        <v>46184.580456111114</v>
+        <v>46184.41378944444</v>
       </c>
       <c r="D13" s="9">
-        <v>46184.58047240741</v>
+        <v>46184.41380574074</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2205,11 +2205,11 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46156.632097615744</v>
+        <v>46156.46543094907</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46184.58047240741</v>
+        <v>46184.41380574074</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2268,13 +2268,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46156.631956365745</v>
+        <v>46156.465289699074</v>
       </c>
       <c r="C15" s="9">
-        <v>46197.50205516204</v>
+        <v>46197.33538849537</v>
       </c>
       <c r="D15" s="9">
-        <v>46197.50206623843</v>
+        <v>46197.33539957176</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2321,13 +2321,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46156.63210516203</v>
+        <v>46156.465438495376</v>
       </c>
       <c r="C16" s="5">
-        <v>46184.58048224537</v>
+        <v>46184.41381557871</v>
       </c>
       <c r="D16" s="5">
-        <v>46184.58049826389</v>
+        <v>46184.41383159722</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2386,13 +2386,13 @@
         <v>73</v>
       </c>
       <c r="B17" s="9">
-        <v>46156.63211037037</v>
+        <v>46156.4654437037</v>
       </c>
       <c r="C17" s="9">
-        <v>46184.58049662037</v>
+        <v>46184.4138299537</v>
       </c>
       <c r="D17" s="9">
-        <v>46184.58051194444</v>
+        <v>46184.41384527778</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>74</v>
@@ -2451,13 +2451,13 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46156.63211564815</v>
+        <v>46156.465448981486</v>
       </c>
       <c r="C18" s="5">
-        <v>46197.50203898148</v>
+        <v>46197.33537231482</v>
       </c>
       <c r="D18" s="5">
-        <v>46197.5020416551</v>
+        <v>46197.335374988426</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2516,13 +2516,13 @@
         <v>80</v>
       </c>
       <c r="B19" s="9">
-        <v>46156.632121504634</v>
+        <v>46156.46545483796</v>
       </c>
       <c r="C19" s="9">
-        <v>46196.656259456024</v>
+        <v>46196.48959278935</v>
       </c>
       <c r="D19" s="9">
-        <v>46196.65627553241</v>
+        <v>46196.48960886574</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>81</v>
@@ -2581,13 +2581,13 @@
         <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46156.63212631944</v>
+        <v>46156.465459652776</v>
       </c>
       <c r="C20" s="5">
-        <v>46196.65655393519</v>
+        <v>46196.489887268515</v>
       </c>
       <c r="D20" s="5">
-        <v>46196.656567858794</v>
+        <v>46196.48990119213</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2646,13 +2646,13 @@
         <v>89</v>
       </c>
       <c r="B21" s="9">
-        <v>46156.63213005787</v>
+        <v>46156.4654633912</v>
       </c>
       <c r="C21" s="9">
-        <v>46196.65716653936</v>
+        <v>46196.490499872685</v>
       </c>
       <c r="D21" s="9">
-        <v>46196.65718306713</v>
+        <v>46196.49051640046</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2711,13 +2711,13 @@
         <v>92</v>
       </c>
       <c r="B22" s="5">
-        <v>46156.632133692125</v>
+        <v>46156.46546702547</v>
       </c>
       <c r="C22" s="5">
-        <v>46196.65766008102</v>
+        <v>46196.49099341435</v>
       </c>
       <c r="D22" s="5">
-        <v>46196.657674409726</v>
+        <v>46196.491007743054</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2776,11 +2776,11 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46156.6319605787</v>
+        <v>46156.46529391204</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46156.69832805556</v>
+        <v>46156.531661388886</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2823,11 +2823,11 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46156.63213814815</v>
+        <v>46156.46547148148</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46195.929228946756</v>
+        <v>46195.76256228009</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2886,13 +2886,13 @@
         <v>104</v>
       </c>
       <c r="B25" s="9">
-        <v>46156.63214259259</v>
+        <v>46156.46547592593</v>
       </c>
       <c r="C25" s="9">
-        <v>46195.92922075231</v>
+        <v>46195.76255408565</v>
       </c>
       <c r="D25" s="9">
-        <v>46195.92922337963</v>
+        <v>46195.76255671296</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>105</v>
@@ -2947,11 +2947,11 @@
         <v>107</v>
       </c>
       <c r="B26" s="5">
-        <v>46156.63214717593</v>
+        <v>46156.46548050926</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46195.92922835649</v>
+        <v>46195.762561689815</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>108</v>
@@ -3006,11 +3006,11 @@
         <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46156.6321521412</v>
+        <v>46156.46548547454</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46169.86132256944</v>
+        <v>46169.69465590278</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3069,11 +3069,11 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46156.63215657407</v>
+        <v>46156.46548990741</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46197.502050625</v>
+        <v>46197.33538395833</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3128,11 +3128,11 @@
         <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46156.63216167824</v>
+        <v>46156.46549501157</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46169.86172537037</v>
+        <v>46169.6950587037</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3187,11 +3187,11 @@
         <v>119</v>
       </c>
       <c r="B30" s="5">
-        <v>46156.63216756945</v>
+        <v>46156.46550090278</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46197.783559131945</v>
+        <v>46197.616892465274</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3250,13 +3250,13 @@
         <v>122</v>
       </c>
       <c r="B31" s="9">
-        <v>46156.63217278935</v>
+        <v>46156.46550612268</v>
       </c>
       <c r="C31" s="9">
-        <v>46195.929570740744</v>
+        <v>46195.76290407407</v>
       </c>
       <c r="D31" s="9">
-        <v>46195.92957241899</v>
+        <v>46195.762905752315</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>123</v>
@@ -3311,11 +3311,11 @@
         <v>125</v>
       </c>
       <c r="B32" s="5">
-        <v>46156.63217837963</v>
+        <v>46156.46551171296</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46195.92957792824</v>
+        <v>46195.76291126157</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -3370,13 +3370,13 @@
         <v>128</v>
       </c>
       <c r="B33" s="9">
-        <v>46156.63218368056</v>
+        <v>46156.46551701389</v>
       </c>
       <c r="C33" s="9">
-        <v>46197.78355179398</v>
+        <v>46197.61688512731</v>
       </c>
       <c r="D33" s="9">
-        <v>46197.78355364583</v>
+        <v>46197.616886979165</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>129</v>
@@ -3431,11 +3431,11 @@
         <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46156.632188240736</v>
+        <v>46156.46552157408</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.861346631944</v>
+        <v>46169.69467996528</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3494,11 +3494,11 @@
         <v>136</v>
       </c>
       <c r="B35" s="9">
-        <v>46156.63219359954</v>
+        <v>46156.465526932865</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46196.656266342594</v>
+        <v>46196.48959967593</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3553,11 +3553,11 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46156.63219844908</v>
+        <v>46156.46553178241</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.86161818287</v>
+        <v>46169.694951516205</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3612,11 +3612,11 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46156.63225444444</v>
+        <v>46156.46558777778</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.86135784722</v>
+        <v>46169.69469118056</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3675,11 +3675,11 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46156.632258206024</v>
+        <v>46156.46559153935</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46196.65655980324</v>
+        <v>46196.489893136575</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>88</v>
@@ -3728,11 +3728,11 @@
         <v>147</v>
       </c>
       <c r="B39" s="9">
-        <v>46156.63226241898</v>
+        <v>46156.465595752314</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.86156158565</v>
+        <v>46169.69489491898</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>148</v>
@@ -3781,11 +3781,11 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46156.63226644676</v>
+        <v>46156.46559978009</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46196.70204975695</v>
+        <v>46196.535383090275</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3844,13 +3844,13 @@
         <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46156.632269444446</v>
+        <v>46156.46560277778</v>
       </c>
       <c r="C41" s="9">
-        <v>46196.699784247685</v>
+        <v>46196.53311758101</v>
       </c>
       <c r="D41" s="9">
-        <v>46196.69978633102</v>
+        <v>46196.53311966435</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>94</v>
@@ -3899,11 +3899,11 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46156.63227357639</v>
+        <v>46156.465606909725</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46196.699790694445</v>
+        <v>46196.533124027774</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -3952,11 +3952,11 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46156.63227760416</v>
+        <v>46156.4656109375</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.86151703703</v>
+        <v>46169.694850370375</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -4005,11 +4005,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46156.63228021991</v>
+        <v>46156.46561355324</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.861380682865</v>
+        <v>46169.69471401621</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4068,11 +4068,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46156.63228315972</v>
+        <v>46156.46561649306</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46196.657172465275</v>
+        <v>46196.49050579861</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>91</v>
@@ -4121,11 +4121,11 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46156.63228715278</v>
+        <v>46156.46562048611</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.86142826389</v>
+        <v>46169.694761597224</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4174,11 +4174,11 @@
         <v>172</v>
       </c>
       <c r="B47" s="9">
-        <v>46156.63196493055</v>
+        <v>46156.46529826389</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46184.58079096065</v>
+        <v>46184.41412429398</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>173</v>
@@ -4223,13 +4223,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46156.63229164352</v>
+        <v>46156.46562497685</v>
       </c>
       <c r="C48" s="5">
-        <v>46184.58069681713</v>
+        <v>46184.41403015047</v>
       </c>
       <c r="D48" s="5">
-        <v>46197.714709479165</v>
+        <v>46197.5480428125</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4288,13 +4288,13 @@
         <v>181</v>
       </c>
       <c r="B49" s="9">
-        <v>46156.632296261574</v>
+        <v>46156.46562959491</v>
       </c>
       <c r="C49" s="9">
-        <v>46184.58077318287</v>
+        <v>46184.414106516204</v>
       </c>
       <c r="D49" s="9">
-        <v>46197.78357092592</v>
+        <v>46197.61690425926</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>182</v>
@@ -4353,13 +4353,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46156.63230224537</v>
+        <v>46156.4656355787</v>
       </c>
       <c r="C50" s="5">
-        <v>46184.58082519676</v>
+        <v>46184.4141585301</v>
       </c>
       <c r="D50" s="5">
-        <v>46184.580841041665</v>
+        <v>46184.414174375</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>84</v>
@@ -4416,11 +4416,11 @@
         <v>189</v>
       </c>
       <c r="B51" s="9">
-        <v>46156.632315358795</v>
+        <v>46156.46564869213</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46156.72589140046</v>
+        <v>46156.55922473379</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -4479,11 +4479,11 @@
         <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46156.6323189699</v>
+        <v>46156.46565230324</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46156.725962881945</v>
+        <v>46156.55929621527</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4532,11 +4532,11 @@
         <v>197</v>
       </c>
       <c r="B53" s="9">
-        <v>46156.63233141204</v>
+        <v>46156.46566474537</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46156.70385697916</v>
+        <v>46156.537190312505</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>198</v>
@@ -4579,11 +4579,11 @@
         <v>200</v>
       </c>
       <c r="B54" s="5">
-        <v>46156.63233460648</v>
+        <v>46156.46566793982</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46156.72605925926</v>
+        <v>46156.55939259259</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>201</v>
@@ -4642,11 +4642,11 @@
         <v>205</v>
       </c>
       <c r="B55" s="9">
-        <v>46156.63233969908</v>
+        <v>46156.465673032406</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46156.72612552083</v>
+        <v>46156.55945885417</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>206</v>
@@ -4705,11 +4705,11 @@
         <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46156.632350671294</v>
+        <v>46156.46568400463</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46156.72605667824</v>
+        <v>46156.55939001158</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4768,11 +4768,11 @@
         <v>212</v>
       </c>
       <c r="B57" s="9">
-        <v>46156.63235533565</v>
+        <v>46156.46568866898</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46156.72612251157</v>
+        <v>46156.55945584491</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>213</v>
@@ -4831,11 +4831,11 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46156.63235945602</v>
+        <v>46156.46569278935</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46156.72605258102</v>
+        <v>46156.559385914356</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4894,11 +4894,11 @@
         <v>217</v>
       </c>
       <c r="B59" s="9">
-        <v>46156.63236322917</v>
+        <v>46156.4656965625</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46156.72611966435</v>
+        <v>46156.55945299768</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>216</v>
@@ -4957,11 +4957,11 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46156.63236744213</v>
+        <v>46156.46570077546</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46156.71024693287</v>
+        <v>46156.5435802662</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5004,11 +5004,11 @@
         <v>221</v>
       </c>
       <c r="B61" s="9">
-        <v>46156.63237008102</v>
+        <v>46156.46570341435</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46161.57724298611</v>
+        <v>46161.410576319446</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>
@@ -5067,11 +5067,11 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46156.63237584491</v>
+        <v>46156.46570917824</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46156.72624517361</v>
+        <v>46156.559578506945</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>195</v>
@@ -5120,11 +5120,11 @@
         <v>229</v>
       </c>
       <c r="B63" s="9">
-        <v>46156.63239597222</v>
+        <v>46156.46572930556</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46156.72619693287</v>
+        <v>46156.559530266204</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>230</v>
@@ -5183,11 +5183,11 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46156.632400069444</v>
+        <v>46156.46573340277</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46184.58084231481</v>
+        <v>46184.41417564815</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>195</v>
@@ -5236,11 +5236,11 @@
         <v>234</v>
       </c>
       <c r="B65" s="9">
-        <v>46156.63246734954</v>
+        <v>46156.46580068287</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46197.83505042824</v>
+        <v>46197.66838376157</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>235</v>
@@ -5299,11 +5299,11 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46156.632472627316</v>
+        <v>46156.465805960645</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46197.83511621528</v>
+        <v>46197.66844954861</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>195</v>
@@ -5352,11 +5352,11 @@
         <v>238</v>
       </c>
       <c r="B67" s="9">
-        <v>46156.6324928588</v>
+        <v>46156.46582619213</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46156.71243400463</v>
+        <v>46156.545767337964</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>198</v>
@@ -5399,11 +5399,11 @@
         <v>240</v>
       </c>
       <c r="B68" s="5">
-        <v>46156.63249635417</v>
+        <v>46156.4658296875</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46156.72645449074</v>
+        <v>46156.55978782407</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>241</v>
@@ -5462,11 +5462,11 @@
         <v>242</v>
       </c>
       <c r="B69" s="9">
-        <v>46156.63250229167</v>
+        <v>46156.465835625</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46156.726451689814</v>
+        <v>46156.55978502315</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>243</v>
@@ -5525,11 +5525,11 @@
         <v>244</v>
       </c>
       <c r="B70" s="5">
-        <v>46156.63250851852</v>
+        <v>46156.46584185185</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46156.726448877314</v>
+        <v>46156.55978221065</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>245</v>
@@ -5588,11 +5588,11 @@
         <v>246</v>
       </c>
       <c r="B71" s="9">
-        <v>46156.63251465278</v>
+        <v>46156.46584798611</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46156.726445520835</v>
+        <v>46156.55977885416</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>247</v>
@@ -5651,11 +5651,11 @@
         <v>249</v>
       </c>
       <c r="B72" s="5">
-        <v>46156.63251914352</v>
+        <v>46156.46585247685</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46156.71581511574</v>
+        <v>46156.54914844908</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>250</v>
@@ -5698,11 +5698,11 @@
         <v>252</v>
       </c>
       <c r="B73" s="9">
-        <v>46156.63252219907</v>
+        <v>46156.465855532406</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46156.72654819445</v>
+        <v>46156.55988152778</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>253</v>
@@ -5761,11 +5761,11 @@
         <v>255</v>
       </c>
       <c r="B74" s="5">
-        <v>46156.63252934028</v>
+        <v>46156.46586267361</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46156.726576076384</v>
+        <v>46156.55990940973</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>195</v>
@@ -5814,11 +5814,11 @@
         <v>256</v>
       </c>
       <c r="B75" s="9">
-        <v>46156.63254586805</v>
+        <v>46156.465879201394</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46156.72654520834</v>
+        <v>46156.559878541666</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>257</v>
@@ -5877,11 +5877,11 @@
         <v>258</v>
       </c>
       <c r="B76" s="5">
-        <v>46156.63255047453</v>
+        <v>46156.465883807876</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46184.58084127315</v>
+        <v>46184.414174606485</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>195</v>
@@ -5930,11 +5930,11 @@
         <v>261</v>
       </c>
       <c r="B77" s="9">
-        <v>46156.63257873843</v>
+        <v>46156.465912071755</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46156.726542372686</v>
+        <v>46156.55987570602</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>262</v>
@@ -5993,11 +5993,11 @@
         <v>263</v>
       </c>
       <c r="B78" s="5">
-        <v>46156.632582986116</v>
+        <v>46156.465916319445</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46184.58084195602</v>
+        <v>46184.41417528935</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>195</v>
@@ -6046,11 +6046,11 @@
         <v>265</v>
       </c>
       <c r="B79" s="9">
-        <v>46156.632655671296</v>
+        <v>46156.46598900463</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46156.72653921296</v>
+        <v>46156.55987254629</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>266</v>
@@ -6109,11 +6109,11 @@
         <v>267</v>
       </c>
       <c r="B80" s="5">
-        <v>46156.6326615162</v>
+        <v>46156.46599484954</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46184.58084310185</v>
+        <v>46184.41417643518</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>195</v>
@@ -6162,11 +6162,11 @@
         <v>270</v>
       </c>
       <c r="B81" s="9">
-        <v>46156.6326856713</v>
+        <v>46156.46601900463</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46156.72653572916</v>
+        <v>46156.559869062505</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>271</v>
@@ -6225,11 +6225,11 @@
         <v>272</v>
       </c>
       <c r="B82" s="5">
-        <v>46156.63269413194</v>
+        <v>46156.46602746528</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46156.72676160879</v>
+        <v>46156.560094942135</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>195</v>
@@ -6278,11 +6278,11 @@
         <v>274</v>
       </c>
       <c r="B83" s="9">
-        <v>46156.632715810185</v>
+        <v>46156.46604914352</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46156.726531747685</v>
+        <v>46156.55986508101</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>275</v>
@@ -6341,11 +6341,11 @@
         <v>277</v>
       </c>
       <c r="B84" s="5">
-        <v>46156.63272170139</v>
+        <v>46156.46605503472</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46156.72680289352</v>
+        <v>46156.56013622685</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>195</v>
@@ -6394,11 +6394,11 @@
         <v>279</v>
       </c>
       <c r="B85" s="9">
-        <v>46156.63273993056</v>
+        <v>46156.46607326389</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46156.7168192824</v>
+        <v>46156.550152615746</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>280</v>
@@ -6441,11 +6441,11 @@
         <v>282</v>
       </c>
       <c r="B86" s="5">
-        <v>46156.63274356481</v>
+        <v>46156.46607689815</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46156.7268765162</v>
+        <v>46156.56020984954</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>283</v>
@@ -6504,11 +6504,11 @@
         <v>286</v>
       </c>
       <c r="B87" s="9">
-        <v>46156.63274915509</v>
+        <v>46156.46608248843</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46156.72692035879</v>
+        <v>46156.56025369213</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>195</v>
@@ -6557,11 +6557,11 @@
         <v>288</v>
       </c>
       <c r="B88" s="5">
-        <v>46156.63276633102</v>
+        <v>46156.46609966435</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46156.72700125</v>
+        <v>46156.56033458334</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>289</v>
@@ -6618,11 +6618,11 @@
         <v>290</v>
       </c>
       <c r="B89" s="9">
-        <v>46156.63277084491</v>
+        <v>46156.46610417824</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46156.72697212963</v>
+        <v>46156.56030546296</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>195</v>
@@ -6671,11 +6671,11 @@
         <v>292</v>
       </c>
       <c r="B90" s="5">
-        <v>46156.63283398148</v>
+        <v>46156.466167314815</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46156.727094305556</v>
+        <v>46156.56042763889</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>293</v>
@@ -6734,11 +6734,11 @@
         <v>294</v>
       </c>
       <c r="B91" s="9">
-        <v>46156.63284013889</v>
+        <v>46156.46617347222</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46156.727054675925</v>
+        <v>46156.56038800926</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>195</v>
@@ -6787,11 +6787,11 @@
         <v>296</v>
       </c>
       <c r="B92" s="5">
-        <v>46156.63286864583</v>
+        <v>46156.466201979165</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46156.727220243054</v>
+        <v>46156.56055357639</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>297</v>
@@ -6850,11 +6850,11 @@
         <v>299</v>
       </c>
       <c r="B93" s="9">
-        <v>46156.632875972224</v>
+        <v>46156.46620930555</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46156.727183668976</v>
+        <v>46156.56051700232</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>195</v>
@@ -6901,11 +6901,11 @@
         <v>300</v>
       </c>
       <c r="B94" s="5">
-        <v>46156.63290420139</v>
+        <v>46156.466237534725</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46156.71731457176</v>
+        <v>46156.5506479051</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>301</v>
@@ -6948,11 +6948,11 @@
         <v>303</v>
       </c>
       <c r="B95" s="9">
-        <v>46156.63290788194</v>
+        <v>46156.46624121528</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46156.72728918982</v>
+        <v>46156.560622523146</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>304</v>
@@ -7011,11 +7011,11 @@
         <v>307</v>
       </c>
       <c r="B96" s="5">
-        <v>46156.63291414352</v>
+        <v>46156.466247476856</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46156.727343402774</v>
+        <v>46156.56067673611</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>308</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -1595,13 +1595,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46156.46528078704</v>
+        <v>46156.6319474537</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70686295139</v>
+        <v>46175.87352961805</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.706874456024</v>
+        <v>46175.87354112268</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46156.465400671295</v>
+        <v>46156.63206733797</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.70683420139</v>
+        <v>46175.87350086805</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.70686409722</v>
+        <v>46175.873530763885</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1711,13 +1711,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46156.46540380787</v>
+        <v>46156.63207047454</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.706834930555</v>
+        <v>46175.87350159722</v>
       </c>
       <c r="D6" s="5">
-        <v>46184.413204930555</v>
+        <v>46184.57987159722</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1774,13 +1774,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46156.465406550924</v>
+        <v>46156.632073217595</v>
       </c>
       <c r="C7" s="9">
-        <v>46184.41449466435</v>
+        <v>46184.58116133102</v>
       </c>
       <c r="D7" s="9">
-        <v>46184.41449592593</v>
+        <v>46184.58116259259</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -1837,13 +1837,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46156.46540930556</v>
+        <v>46156.63207597222</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.70683589121</v>
+        <v>46175.87350255787</v>
       </c>
       <c r="D8" s="5">
-        <v>46184.412972962964</v>
+        <v>46184.57963962963</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1900,13 +1900,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46156.46541258102</v>
+        <v>46156.63207924768</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.70683657407</v>
+        <v>46175.87350324074</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.70686366898</v>
+        <v>46175.87353033565</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -1963,11 +1963,11 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46156.465284826394</v>
+        <v>46156.63195149305</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46184.413799918984</v>
+        <v>46184.58046658565</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2010,13 +2010,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46156.46541579861</v>
+        <v>46156.63208246528</v>
       </c>
       <c r="C11" s="9">
-        <v>46184.41364805556</v>
+        <v>46184.58031472222</v>
       </c>
       <c r="D11" s="9">
-        <v>46184.413664085645</v>
+        <v>46184.58033075232</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2075,13 +2075,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46156.465420925924</v>
+        <v>46156.63208759259</v>
       </c>
       <c r="C12" s="5">
-        <v>46184.41365743056</v>
+        <v>46184.580324097224</v>
       </c>
       <c r="D12" s="5">
-        <v>46184.41367418981</v>
+        <v>46184.58034085648</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2140,13 +2140,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46156.46542587963</v>
+        <v>46156.63209254629</v>
       </c>
       <c r="C13" s="9">
-        <v>46184.41378944444</v>
+        <v>46184.580456111114</v>
       </c>
       <c r="D13" s="9">
-        <v>46184.41380574074</v>
+        <v>46184.58047240741</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2205,11 +2205,11 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46156.46543094907</v>
+        <v>46156.632097615744</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46184.41380574074</v>
+        <v>46184.58047240741</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2268,13 +2268,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46156.465289699074</v>
+        <v>46156.631956365745</v>
       </c>
       <c r="C15" s="9">
-        <v>46197.33538849537</v>
+        <v>46197.50205516204</v>
       </c>
       <c r="D15" s="9">
-        <v>46197.33539957176</v>
+        <v>46197.50206623843</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2321,13 +2321,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46156.465438495376</v>
+        <v>46156.63210516203</v>
       </c>
       <c r="C16" s="5">
-        <v>46184.41381557871</v>
+        <v>46184.58048224537</v>
       </c>
       <c r="D16" s="5">
-        <v>46184.41383159722</v>
+        <v>46184.58049826389</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2386,13 +2386,13 @@
         <v>73</v>
       </c>
       <c r="B17" s="9">
-        <v>46156.4654437037</v>
+        <v>46156.63211037037</v>
       </c>
       <c r="C17" s="9">
-        <v>46184.4138299537</v>
+        <v>46184.58049662037</v>
       </c>
       <c r="D17" s="9">
-        <v>46184.41384527778</v>
+        <v>46184.58051194444</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>74</v>
@@ -2451,13 +2451,13 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46156.465448981486</v>
+        <v>46156.63211564815</v>
       </c>
       <c r="C18" s="5">
-        <v>46197.33537231482</v>
+        <v>46197.50203898148</v>
       </c>
       <c r="D18" s="5">
-        <v>46197.335374988426</v>
+        <v>46197.5020416551</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2516,13 +2516,13 @@
         <v>80</v>
       </c>
       <c r="B19" s="9">
-        <v>46156.46545483796</v>
+        <v>46156.632121504634</v>
       </c>
       <c r="C19" s="9">
-        <v>46196.48959278935</v>
+        <v>46196.656259456024</v>
       </c>
       <c r="D19" s="9">
-        <v>46196.48960886574</v>
+        <v>46196.65627553241</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>81</v>
@@ -2581,13 +2581,13 @@
         <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46156.465459652776</v>
+        <v>46156.63212631944</v>
       </c>
       <c r="C20" s="5">
-        <v>46196.489887268515</v>
+        <v>46196.65655393519</v>
       </c>
       <c r="D20" s="5">
-        <v>46196.48990119213</v>
+        <v>46196.656567858794</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2646,13 +2646,13 @@
         <v>89</v>
       </c>
       <c r="B21" s="9">
-        <v>46156.4654633912</v>
+        <v>46156.63213005787</v>
       </c>
       <c r="C21" s="9">
-        <v>46196.490499872685</v>
+        <v>46196.65716653936</v>
       </c>
       <c r="D21" s="9">
-        <v>46196.49051640046</v>
+        <v>46196.65718306713</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2711,13 +2711,13 @@
         <v>92</v>
       </c>
       <c r="B22" s="5">
-        <v>46156.46546702547</v>
+        <v>46156.632133692125</v>
       </c>
       <c r="C22" s="5">
-        <v>46196.49099341435</v>
+        <v>46196.65766008102</v>
       </c>
       <c r="D22" s="5">
-        <v>46196.491007743054</v>
+        <v>46196.657674409726</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2776,11 +2776,11 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46156.46529391204</v>
+        <v>46156.6319605787</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46156.531661388886</v>
+        <v>46156.69832805556</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2823,11 +2823,11 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46156.46547148148</v>
+        <v>46156.63213814815</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46195.76256228009</v>
+        <v>46195.929228946756</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2886,13 +2886,13 @@
         <v>104</v>
       </c>
       <c r="B25" s="9">
-        <v>46156.46547592593</v>
+        <v>46156.63214259259</v>
       </c>
       <c r="C25" s="9">
-        <v>46195.76255408565</v>
+        <v>46195.92922075231</v>
       </c>
       <c r="D25" s="9">
-        <v>46195.76255671296</v>
+        <v>46195.92922337963</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>105</v>
@@ -2947,11 +2947,11 @@
         <v>107</v>
       </c>
       <c r="B26" s="5">
-        <v>46156.46548050926</v>
+        <v>46156.63214717593</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46195.762561689815</v>
+        <v>46195.92922835649</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>108</v>
@@ -3006,11 +3006,11 @@
         <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46156.46548547454</v>
+        <v>46156.6321521412</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46169.69465590278</v>
+        <v>46169.86132256944</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3069,11 +3069,11 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46156.46548990741</v>
+        <v>46156.63215657407</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46197.33538395833</v>
+        <v>46197.502050625</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3128,11 +3128,11 @@
         <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46156.46549501157</v>
+        <v>46156.63216167824</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46169.6950587037</v>
+        <v>46169.86172537037</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3187,11 +3187,11 @@
         <v>119</v>
       </c>
       <c r="B30" s="5">
-        <v>46156.46550090278</v>
+        <v>46156.63216756945</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46197.616892465274</v>
+        <v>46197.783559131945</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3250,13 +3250,13 @@
         <v>122</v>
       </c>
       <c r="B31" s="9">
-        <v>46156.46550612268</v>
+        <v>46156.63217278935</v>
       </c>
       <c r="C31" s="9">
-        <v>46195.76290407407</v>
+        <v>46195.929570740744</v>
       </c>
       <c r="D31" s="9">
-        <v>46195.762905752315</v>
+        <v>46195.92957241899</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>123</v>
@@ -3311,11 +3311,11 @@
         <v>125</v>
       </c>
       <c r="B32" s="5">
-        <v>46156.46551171296</v>
+        <v>46156.63217837963</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46195.76291126157</v>
+        <v>46195.92957792824</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -3370,13 +3370,13 @@
         <v>128</v>
       </c>
       <c r="B33" s="9">
-        <v>46156.46551701389</v>
+        <v>46156.63218368056</v>
       </c>
       <c r="C33" s="9">
-        <v>46197.61688512731</v>
+        <v>46197.78355179398</v>
       </c>
       <c r="D33" s="9">
-        <v>46197.616886979165</v>
+        <v>46197.78355364583</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>129</v>
@@ -3431,11 +3431,11 @@
         <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46156.46552157408</v>
+        <v>46156.632188240736</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.69467996528</v>
+        <v>46169.861346631944</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3494,11 +3494,11 @@
         <v>136</v>
       </c>
       <c r="B35" s="9">
-        <v>46156.465526932865</v>
+        <v>46156.63219359954</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46196.48959967593</v>
+        <v>46196.656266342594</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3553,11 +3553,11 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46156.46553178241</v>
+        <v>46156.63219844908</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.694951516205</v>
+        <v>46169.86161818287</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3612,11 +3612,11 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46156.46558777778</v>
+        <v>46156.63225444444</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46169.69469118056</v>
+        <v>46169.86135784722</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3675,11 +3675,11 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46156.46559153935</v>
+        <v>46156.632258206024</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46196.489893136575</v>
+        <v>46196.65655980324</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>88</v>
@@ -3728,11 +3728,11 @@
         <v>147</v>
       </c>
       <c r="B39" s="9">
-        <v>46156.465595752314</v>
+        <v>46156.63226241898</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46169.69489491898</v>
+        <v>46169.86156158565</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>148</v>
@@ -3781,11 +3781,11 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46156.46559978009</v>
+        <v>46156.63226644676</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46196.535383090275</v>
+        <v>46196.70204975695</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3844,13 +3844,13 @@
         <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46156.46560277778</v>
+        <v>46156.632269444446</v>
       </c>
       <c r="C41" s="9">
-        <v>46196.53311758101</v>
+        <v>46196.699784247685</v>
       </c>
       <c r="D41" s="9">
-        <v>46196.53311966435</v>
+        <v>46196.69978633102</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>94</v>
@@ -3899,11 +3899,11 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46156.465606909725</v>
+        <v>46156.63227357639</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46196.533124027774</v>
+        <v>46196.699790694445</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -3952,11 +3952,11 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46156.4656109375</v>
+        <v>46156.63227760416</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.694850370375</v>
+        <v>46169.86151703703</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -4005,11 +4005,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46156.46561355324</v>
+        <v>46156.63228021991</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.69471401621</v>
+        <v>46169.861380682865</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4068,11 +4068,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46156.46561649306</v>
+        <v>46156.63228315972</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46196.49050579861</v>
+        <v>46196.657172465275</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>91</v>
@@ -4121,11 +4121,11 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46156.46562048611</v>
+        <v>46156.63228715278</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.694761597224</v>
+        <v>46169.86142826389</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4174,11 +4174,11 @@
         <v>172</v>
       </c>
       <c r="B47" s="9">
-        <v>46156.46529826389</v>
+        <v>46156.63196493055</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46184.41412429398</v>
+        <v>46184.58079096065</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>173</v>
@@ -4223,13 +4223,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46156.46562497685</v>
+        <v>46156.63229164352</v>
       </c>
       <c r="C48" s="5">
-        <v>46184.41403015047</v>
+        <v>46184.58069681713</v>
       </c>
       <c r="D48" s="5">
-        <v>46197.5480428125</v>
+        <v>46197.714709479165</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4288,13 +4288,13 @@
         <v>181</v>
       </c>
       <c r="B49" s="9">
-        <v>46156.46562959491</v>
+        <v>46156.632296261574</v>
       </c>
       <c r="C49" s="9">
-        <v>46184.414106516204</v>
+        <v>46184.58077318287</v>
       </c>
       <c r="D49" s="9">
-        <v>46197.61690425926</v>
+        <v>46197.78357092592</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>182</v>
@@ -4353,13 +4353,13 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46156.4656355787</v>
+        <v>46156.63230224537</v>
       </c>
       <c r="C50" s="5">
-        <v>46184.4141585301</v>
+        <v>46184.58082519676</v>
       </c>
       <c r="D50" s="5">
-        <v>46184.414174375</v>
+        <v>46184.580841041665</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>84</v>
@@ -4416,11 +4416,11 @@
         <v>189</v>
       </c>
       <c r="B51" s="9">
-        <v>46156.46564869213</v>
+        <v>46156.632315358795</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46156.55922473379</v>
+        <v>46156.72589140046</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -4479,11 +4479,11 @@
         <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46156.46565230324</v>
+        <v>46156.6323189699</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46156.55929621527</v>
+        <v>46156.725962881945</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4532,11 +4532,11 @@
         <v>197</v>
       </c>
       <c r="B53" s="9">
-        <v>46156.46566474537</v>
+        <v>46156.63233141204</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46156.537190312505</v>
+        <v>46156.70385697916</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>198</v>
@@ -4579,11 +4579,11 @@
         <v>200</v>
       </c>
       <c r="B54" s="5">
-        <v>46156.46566793982</v>
+        <v>46156.63233460648</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46156.55939259259</v>
+        <v>46156.72605925926</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>201</v>
@@ -4642,11 +4642,11 @@
         <v>205</v>
       </c>
       <c r="B55" s="9">
-        <v>46156.465673032406</v>
+        <v>46156.63233969908</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46156.55945885417</v>
+        <v>46156.72612552083</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>206</v>
@@ -4705,11 +4705,11 @@
         <v>209</v>
       </c>
       <c r="B56" s="5">
-        <v>46156.46568400463</v>
+        <v>46156.632350671294</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46156.55939001158</v>
+        <v>46156.72605667824</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4768,11 +4768,11 @@
         <v>212</v>
       </c>
       <c r="B57" s="9">
-        <v>46156.46568866898</v>
+        <v>46156.63235533565</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46156.55945584491</v>
+        <v>46156.72612251157</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>213</v>
@@ -4831,11 +4831,11 @@
         <v>214</v>
       </c>
       <c r="B58" s="5">
-        <v>46156.46569278935</v>
+        <v>46156.63235945602</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46156.559385914356</v>
+        <v>46156.72605258102</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4894,11 +4894,11 @@
         <v>217</v>
       </c>
       <c r="B59" s="9">
-        <v>46156.4656965625</v>
+        <v>46156.63236322917</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46156.55945299768</v>
+        <v>46156.72611966435</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>216</v>
@@ -4957,11 +4957,11 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46156.46570077546</v>
+        <v>46156.63236744213</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46156.5435802662</v>
+        <v>46156.71024693287</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5004,11 +5004,11 @@
         <v>221</v>
       </c>
       <c r="B61" s="9">
-        <v>46156.46570341435</v>
+        <v>46156.63237008102</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46161.410576319446</v>
+        <v>46161.57724298611</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>222</v>
@@ -5067,11 +5067,11 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46156.46570917824</v>
+        <v>46156.63237584491</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46156.559578506945</v>
+        <v>46156.72624517361</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>195</v>
@@ -5120,11 +5120,11 @@
         <v>229</v>
       </c>
       <c r="B63" s="9">
-        <v>46156.46572930556</v>
+        <v>46156.63239597222</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46156.559530266204</v>
+        <v>46156.72619693287</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>230</v>
@@ -5183,11 +5183,11 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46156.46573340277</v>
+        <v>46156.632400069444</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46184.41417564815</v>
+        <v>46184.58084231481</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>195</v>
@@ -5236,11 +5236,11 @@
         <v>234</v>
       </c>
       <c r="B65" s="9">
-        <v>46156.46580068287</v>
+        <v>46156.63246734954</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46197.66838376157</v>
+        <v>46197.83505042824</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>235</v>
@@ -5299,11 +5299,11 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46156.465805960645</v>
+        <v>46156.632472627316</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46197.66844954861</v>
+        <v>46197.83511621528</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>195</v>
@@ -5352,11 +5352,11 @@
         <v>238</v>
       </c>
       <c r="B67" s="9">
-        <v>46156.46582619213</v>
+        <v>46156.6324928588</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46156.545767337964</v>
+        <v>46156.71243400463</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>198</v>
@@ -5399,11 +5399,11 @@
         <v>240</v>
       </c>
       <c r="B68" s="5">
-        <v>46156.4658296875</v>
+        <v>46156.63249635417</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46156.55978782407</v>
+        <v>46156.72645449074</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>241</v>
@@ -5462,11 +5462,11 @@
         <v>242</v>
       </c>
       <c r="B69" s="9">
-        <v>46156.465835625</v>
+        <v>46156.63250229167</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46156.55978502315</v>
+        <v>46156.726451689814</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>243</v>
@@ -5525,11 +5525,11 @@
         <v>244</v>
       </c>
       <c r="B70" s="5">
-        <v>46156.46584185185</v>
+        <v>46156.63250851852</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46156.55978221065</v>
+        <v>46156.726448877314</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>245</v>
@@ -5588,11 +5588,11 @@
         <v>246</v>
       </c>
       <c r="B71" s="9">
-        <v>46156.46584798611</v>
+        <v>46156.63251465278</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46156.55977885416</v>
+        <v>46156.726445520835</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>247</v>
@@ -5651,11 +5651,11 @@
         <v>249</v>
       </c>
       <c r="B72" s="5">
-        <v>46156.46585247685</v>
+        <v>46156.63251914352</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46156.54914844908</v>
+        <v>46156.71581511574</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>250</v>
@@ -5698,11 +5698,11 @@
         <v>252</v>
       </c>
       <c r="B73" s="9">
-        <v>46156.465855532406</v>
+        <v>46156.63252219907</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46156.55988152778</v>
+        <v>46156.72654819445</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>253</v>
@@ -5761,11 +5761,11 @@
         <v>255</v>
       </c>
       <c r="B74" s="5">
-        <v>46156.46586267361</v>
+        <v>46156.63252934028</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46156.55990940973</v>
+        <v>46156.726576076384</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>195</v>
@@ -5814,11 +5814,11 @@
         <v>256</v>
       </c>
       <c r="B75" s="9">
-        <v>46156.465879201394</v>
+        <v>46156.63254586805</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46156.559878541666</v>
+        <v>46156.72654520834</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>257</v>
@@ -5877,11 +5877,11 @@
         <v>258</v>
       </c>
       <c r="B76" s="5">
-        <v>46156.465883807876</v>
+        <v>46156.63255047453</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46184.414174606485</v>
+        <v>46184.58084127315</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>195</v>
@@ -5930,11 +5930,11 @@
         <v>261</v>
       </c>
       <c r="B77" s="9">
-        <v>46156.465912071755</v>
+        <v>46156.63257873843</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46156.55987570602</v>
+        <v>46156.726542372686</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>262</v>
@@ -5993,11 +5993,11 @@
         <v>263</v>
       </c>
       <c r="B78" s="5">
-        <v>46156.465916319445</v>
+        <v>46156.632582986116</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46184.41417528935</v>
+        <v>46184.58084195602</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>195</v>
@@ -6046,11 +6046,11 @@
         <v>265</v>
       </c>
       <c r="B79" s="9">
-        <v>46156.46598900463</v>
+        <v>46156.632655671296</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46156.55987254629</v>
+        <v>46156.72653921296</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>266</v>
@@ -6109,11 +6109,11 @@
         <v>267</v>
       </c>
       <c r="B80" s="5">
-        <v>46156.46599484954</v>
+        <v>46156.6326615162</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46184.41417643518</v>
+        <v>46184.58084310185</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>195</v>
@@ -6162,11 +6162,11 @@
         <v>270</v>
       </c>
       <c r="B81" s="9">
-        <v>46156.46601900463</v>
+        <v>46156.6326856713</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46156.559869062505</v>
+        <v>46156.72653572916</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>271</v>
@@ -6225,11 +6225,11 @@
         <v>272</v>
       </c>
       <c r="B82" s="5">
-        <v>46156.46602746528</v>
+        <v>46156.63269413194</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46156.560094942135</v>
+        <v>46156.72676160879</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>195</v>
@@ -6278,11 +6278,11 @@
         <v>274</v>
       </c>
       <c r="B83" s="9">
-        <v>46156.46604914352</v>
+        <v>46156.632715810185</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46156.55986508101</v>
+        <v>46156.726531747685</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>275</v>
@@ -6341,11 +6341,11 @@
         <v>277</v>
       </c>
       <c r="B84" s="5">
-        <v>46156.46605503472</v>
+        <v>46156.63272170139</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46156.56013622685</v>
+        <v>46156.72680289352</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>195</v>
@@ -6394,11 +6394,11 @@
         <v>279</v>
       </c>
       <c r="B85" s="9">
-        <v>46156.46607326389</v>
+        <v>46156.63273993056</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46156.550152615746</v>
+        <v>46156.7168192824</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>280</v>
@@ -6441,11 +6441,11 @@
         <v>282</v>
       </c>
       <c r="B86" s="5">
-        <v>46156.46607689815</v>
+        <v>46156.63274356481</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46156.56020984954</v>
+        <v>46156.7268765162</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>283</v>
@@ -6504,11 +6504,11 @@
         <v>286</v>
       </c>
       <c r="B87" s="9">
-        <v>46156.46608248843</v>
+        <v>46156.63274915509</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46156.56025369213</v>
+        <v>46156.72692035879</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>195</v>
@@ -6557,11 +6557,11 @@
         <v>288</v>
       </c>
       <c r="B88" s="5">
-        <v>46156.46609966435</v>
+        <v>46156.63276633102</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46156.56033458334</v>
+        <v>46156.72700125</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>289</v>
@@ -6618,11 +6618,11 @@
         <v>290</v>
       </c>
       <c r="B89" s="9">
-        <v>46156.46610417824</v>
+        <v>46156.63277084491</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46156.56030546296</v>
+        <v>46156.72697212963</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>195</v>
@@ -6671,11 +6671,11 @@
         <v>292</v>
       </c>
       <c r="B90" s="5">
-        <v>46156.466167314815</v>
+        <v>46156.63283398148</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46156.56042763889</v>
+        <v>46156.727094305556</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>293</v>
@@ -6734,11 +6734,11 @@
         <v>294</v>
       </c>
       <c r="B91" s="9">
-        <v>46156.46617347222</v>
+        <v>46156.63284013889</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46156.56038800926</v>
+        <v>46156.727054675925</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>195</v>
@@ -6787,11 +6787,11 @@
         <v>296</v>
       </c>
       <c r="B92" s="5">
-        <v>46156.466201979165</v>
+        <v>46156.63286864583</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46156.56055357639</v>
+        <v>46156.727220243054</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>297</v>
@@ -6850,11 +6850,11 @@
         <v>299</v>
       </c>
       <c r="B93" s="9">
-        <v>46156.46620930555</v>
+        <v>46156.632875972224</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46156.56051700232</v>
+        <v>46156.727183668976</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>195</v>
@@ -6901,11 +6901,11 @@
         <v>300</v>
       </c>
       <c r="B94" s="5">
-        <v>46156.466237534725</v>
+        <v>46156.63290420139</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46156.5506479051</v>
+        <v>46156.71731457176</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>301</v>
@@ -6948,11 +6948,11 @@
         <v>303</v>
       </c>
       <c r="B95" s="9">
-        <v>46156.46624121528</v>
+        <v>46156.63290788194</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46156.560622523146</v>
+        <v>46156.72728918982</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>304</v>
@@ -7011,11 +7011,11 @@
         <v>307</v>
       </c>
       <c r="B96" s="5">
-        <v>46156.466247476856</v>
+        <v>46156.63291414352</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46156.56067673611</v>
+        <v>46156.727343402774</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>308</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46156.69832805556</v>
+        <v>46199.559805983794</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -3433,9 +3433,11 @@
       <c r="B34" s="5">
         <v>46156.632188240736</v>
       </c>
-      <c r="C34" s="6"/>
+      <c r="C34" s="5">
+        <v>46199.55979506944</v>
+      </c>
       <c r="D34" s="5">
-        <v>46169.861346631944</v>
+        <v>46199.55980914352</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3483,10 +3485,10 @@
         <v>33</v>
       </c>
       <c r="T34" s="6">
-        <v>0</v>
-      </c>
-      <c r="U34" s="12" t="s">
-        <v>103</v>
+        <v>1</v>
+      </c>
+      <c r="U34" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3496,9 +3498,11 @@
       <c r="B35" s="9">
         <v>46156.63219359954</v>
       </c>
-      <c r="C35" s="10"/>
+      <c r="C35" s="9">
+        <v>46199.55916827546</v>
+      </c>
       <c r="D35" s="9">
-        <v>46196.656266342594</v>
+        <v>46199.55917045139</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3555,9 +3559,11 @@
       <c r="B36" s="5">
         <v>46156.63219844908</v>
       </c>
-      <c r="C36" s="6"/>
+      <c r="C36" s="5">
+        <v>46199.55978109954</v>
+      </c>
       <c r="D36" s="5">
-        <v>46169.86161818287</v>
+        <v>46199.5597825</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3614,9 +3620,11 @@
       <c r="B37" s="9">
         <v>46156.63225444444</v>
       </c>
-      <c r="C37" s="10"/>
+      <c r="C37" s="9">
+        <v>46199.55997423611</v>
+      </c>
       <c r="D37" s="9">
-        <v>46169.86135784722</v>
+        <v>46199.55998701389</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3664,10 +3672,10 @@
         <v>33</v>
       </c>
       <c r="T37" s="10">
-        <v>0</v>
-      </c>
-      <c r="U37" s="12" t="s">
-        <v>103</v>
+        <v>1</v>
+      </c>
+      <c r="U37" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -3677,9 +3685,11 @@
       <c r="B38" s="5">
         <v>46156.632258206024</v>
       </c>
-      <c r="C38" s="6"/>
+      <c r="C38" s="5">
+        <v>46199.55990923611</v>
+      </c>
       <c r="D38" s="5">
-        <v>46196.65655980324</v>
+        <v>46199.55991087963</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>88</v>
@@ -3730,9 +3740,11 @@
       <c r="B39" s="9">
         <v>46156.63226241898</v>
       </c>
-      <c r="C39" s="10"/>
+      <c r="C39" s="9">
+        <v>46199.55995880787</v>
+      </c>
       <c r="D39" s="9">
-        <v>46169.86156158565</v>
+        <v>46199.55996042824</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>148</v>
@@ -4007,9 +4019,11 @@
       <c r="B44" s="5">
         <v>46156.63228021991</v>
       </c>
-      <c r="C44" s="6"/>
+      <c r="C44" s="5">
+        <v>46199.56230621527</v>
+      </c>
       <c r="D44" s="5">
-        <v>46169.861380682865</v>
+        <v>46199.562315937495</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4057,10 +4071,10 @@
         <v>33</v>
       </c>
       <c r="T44" s="6">
-        <v>0</v>
-      </c>
-      <c r="U44" s="12" t="s">
-        <v>103</v>
+        <v>1</v>
+      </c>
+      <c r="U44" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4070,9 +4084,11 @@
       <c r="B45" s="9">
         <v>46156.63228315972</v>
       </c>
-      <c r="C45" s="10"/>
+      <c r="C45" s="9">
+        <v>46199.562242835644</v>
+      </c>
       <c r="D45" s="9">
-        <v>46196.657172465275</v>
+        <v>46199.56224427083</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>91</v>
@@ -4123,9 +4139,11 @@
       <c r="B46" s="5">
         <v>46156.63228715278</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46199.56229306713</v>
+      </c>
       <c r="D46" s="5">
-        <v>46169.86142826389</v>
+        <v>46199.56229454861</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4583,7 +4601,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46156.72605925926</v>
+        <v>46199.559799317125</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>201</v>
@@ -4633,8 +4651,8 @@
       <c r="T54" s="6">
         <v>0</v>
       </c>
-      <c r="U54" s="12" t="s">
-        <v>103</v>
+      <c r="U54" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4709,7 +4727,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46156.72605667824</v>
+        <v>46199.559976840275</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>210</v>
@@ -4759,8 +4777,8 @@
       <c r="T56" s="6">
         <v>0</v>
       </c>
-      <c r="U56" s="12" t="s">
-        <v>103</v>
+      <c r="U56" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4835,7 +4853,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46156.72605258102</v>
+        <v>46199.56230880787</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>215</v>
@@ -4885,8 +4903,8 @@
       <c r="T58" s="6">
         <v>0</v>
       </c>
-      <c r="U58" s="12" t="s">
-        <v>103</v>
+      <c r="U58" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="311">
   <si>
     <t>50001547 - XEMORTIZ (AMERICAS GOLD)</t>
   </si>
@@ -594,6 +594,9 @@
   </si>
   <si>
     <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1214809528759377</t>
@@ -4312,7 +4315,7 @@
         <v>46184.58077318287</v>
       </c>
       <c r="D49" s="9">
-        <v>46197.78357092592</v>
+        <v>46203.19706542824</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>182</v>
@@ -4356,8 +4359,8 @@
       <c r="R49" s="9">
         <v>46210</v>
       </c>
-      <c r="S49" s="7" t="s">
-        <v>33</v>
+      <c r="S49" s="11" t="s">
+        <v>185</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>
@@ -4368,7 +4371,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B50" s="5">
         <v>46156.63230224537</v>
@@ -4386,10 +4389,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="5">
@@ -4411,7 +4414,7 @@
         <v>182</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q50" s="5">
         <v>46211</v>
@@ -4431,7 +4434,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46156.632315358795</v>
@@ -4441,16 +4444,16 @@
         <v>46156.72589140046</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I51" s="9">
         <v>46301</v>
@@ -4471,7 +4474,7 @@
         <v>173</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>26</v>
@@ -4494,7 +4497,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B52" s="5">
         <v>46156.6323189699</v>
@@ -4504,16 +4507,16 @@
         <v>46156.725962881945</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="I52" s="5">
         <v>46301</v>
@@ -4531,13 +4534,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4547,7 +4550,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B53" s="9">
         <v>46156.63233141204</v>
@@ -4557,7 +4560,7 @@
         <v>46156.70385697916</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4581,7 +4584,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4594,7 +4597,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B54" s="5">
         <v>46156.63233460648</v>
@@ -4604,16 +4607,16 @@
         <v>46199.559799317125</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I54" s="5">
         <v>46227</v>
@@ -4631,13 +4634,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q54" s="5">
         <v>46227</v>
@@ -4657,7 +4660,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B55" s="9">
         <v>46156.63233969908</v>
@@ -4667,7 +4670,7 @@
         <v>46156.72612552083</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4694,13 +4697,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q55" s="9">
         <v>46231</v>
@@ -4720,7 +4723,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B56" s="5">
         <v>46156.632350671294</v>
@@ -4730,16 +4733,16 @@
         <v>46199.559976840275</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I56" s="5">
         <v>46227</v>
@@ -4757,13 +4760,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>148</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q56" s="5">
         <v>46227</v>
@@ -4783,7 +4786,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B57" s="9">
         <v>46156.63235533565</v>
@@ -4793,7 +4796,7 @@
         <v>46156.72612251157</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -4820,13 +4823,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q57" s="9">
         <v>46231</v>
@@ -4846,7 +4849,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B58" s="5">
         <v>46156.63235945602</v>
@@ -4856,16 +4859,16 @@
         <v>46199.56230880787</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I58" s="5">
         <v>46227</v>
@@ -4883,13 +4886,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>170</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q58" s="5">
         <v>46227</v>
@@ -4909,7 +4912,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B59" s="9">
         <v>46156.63236322917</v>
@@ -4919,7 +4922,7 @@
         <v>46156.72611966435</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -4946,13 +4949,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q59" s="9">
         <v>46231</v>
@@ -4972,17 +4975,17 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B60" s="5">
         <v>46156.63236744213</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46156.71024693287</v>
+        <v>46203.5014815162</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5006,7 +5009,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5019,26 +5022,28 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B61" s="9">
         <v>46156.63237008102</v>
       </c>
-      <c r="C61" s="10"/>
+      <c r="C61" s="9">
+        <v>46203.50147394676</v>
+      </c>
       <c r="D61" s="9">
-        <v>46161.57724298611</v>
+        <v>46203.50149189815</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I61" s="9">
         <v>46233</v>
@@ -5056,13 +5061,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q61" s="9">
         <v>46233</v>
@@ -5074,15 +5079,15 @@
         <v>33</v>
       </c>
       <c r="T61" s="10">
-        <v>0</v>
-      </c>
-      <c r="U61" s="12" t="s">
-        <v>103</v>
+        <v>1</v>
+      </c>
+      <c r="U61" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B62" s="5">
         <v>46156.63237584491</v>
@@ -5092,16 +5097,16 @@
         <v>46156.72624517361</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I62" s="5">
         <v>46233</v>
@@ -5119,13 +5124,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5135,7 +5140,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B63" s="9">
         <v>46156.63239597222</v>
@@ -5145,16 +5150,16 @@
         <v>46156.72619693287</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5172,13 +5177,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q63" s="9">
         <v>46244</v>
@@ -5198,7 +5203,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B64" s="5">
         <v>46156.632400069444</v>
@@ -5208,16 +5213,16 @@
         <v>46184.58084231481</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I64" s="5">
         <v>46244</v>
@@ -5235,13 +5240,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5251,7 +5256,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B65" s="9">
         <v>46156.63246734954</v>
@@ -5261,7 +5266,7 @@
         <v>46197.83505042824</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5288,13 +5293,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q65" s="9">
         <v>46262</v>
@@ -5314,7 +5319,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B66" s="5">
         <v>46156.632472627316</v>
@@ -5324,7 +5329,7 @@
         <v>46197.83511621528</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5351,13 +5356,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5367,7 +5372,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B67" s="9">
         <v>46156.6324928588</v>
@@ -5377,7 +5382,7 @@
         <v>46156.71243400463</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>25</v>
@@ -5401,7 +5406,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>26</v>
@@ -5414,7 +5419,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B68" s="5">
         <v>46156.63249635417</v>
@@ -5424,16 +5429,16 @@
         <v>46156.72645449074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I68" s="5">
         <v>46154</v>
@@ -5451,13 +5456,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>117</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q68" s="5">
         <v>46154</v>
@@ -5477,7 +5482,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B69" s="9">
         <v>46156.63250229167</v>
@@ -5487,16 +5492,16 @@
         <v>46156.726451689814</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I69" s="9">
         <v>46268</v>
@@ -5514,13 +5519,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>108</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q69" s="9">
         <v>46268</v>
@@ -5540,7 +5545,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B70" s="5">
         <v>46156.63250851852</v>
@@ -5550,16 +5555,16 @@
         <v>46156.726448877314</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I70" s="5">
         <v>46294</v>
@@ -5577,13 +5582,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>126</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q70" s="5">
         <v>46294</v>
@@ -5603,7 +5608,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B71" s="9">
         <v>46156.63251465278</v>
@@ -5613,16 +5618,16 @@
         <v>46156.726445520835</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I71" s="9">
         <v>46255</v>
@@ -5640,13 +5645,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>158</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q71" s="9">
         <v>46255</v>
@@ -5666,7 +5671,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B72" s="5">
         <v>46156.63251914352</v>
@@ -5676,7 +5681,7 @@
         <v>46156.71581511574</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>25</v>
@@ -5700,7 +5705,7 @@
         <v>26</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>26</v>
@@ -5713,7 +5718,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B73" s="9">
         <v>46156.63252219907</v>
@@ -5723,7 +5728,7 @@
         <v>46156.72654819445</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5750,13 +5755,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q73" s="9">
         <v>46266</v>
@@ -5776,7 +5781,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B74" s="5">
         <v>46156.63252934028</v>
@@ -5786,7 +5791,7 @@
         <v>46156.726576076384</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5813,10 +5818,10 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5829,7 +5834,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B75" s="9">
         <v>46156.63254586805</v>
@@ -5839,7 +5844,7 @@
         <v>46156.72654520834</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5866,13 +5871,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q75" s="9">
         <v>46288</v>
@@ -5892,7 +5897,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B76" s="5">
         <v>46156.63255047453</v>
@@ -5902,7 +5907,7 @@
         <v>46184.58084127315</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5929,13 +5934,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5945,7 +5950,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B77" s="9">
         <v>46156.63257873843</v>
@@ -5955,7 +5960,7 @@
         <v>46156.726542372686</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5982,13 +5987,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q77" s="9">
         <v>46290</v>
@@ -6008,7 +6013,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B78" s="5">
         <v>46156.632582986116</v>
@@ -6018,7 +6023,7 @@
         <v>46184.58084195602</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6045,13 +6050,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6061,7 +6066,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B79" s="9">
         <v>46156.632655671296</v>
@@ -6071,7 +6076,7 @@
         <v>46156.72653921296</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6098,13 +6103,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q79" s="9">
         <v>46296</v>
@@ -6124,7 +6129,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B80" s="5">
         <v>46156.6326615162</v>
@@ -6134,7 +6139,7 @@
         <v>46184.58084310185</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6161,13 +6166,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6177,7 +6182,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B81" s="9">
         <v>46156.6326856713</v>
@@ -6187,7 +6192,7 @@
         <v>46156.72653572916</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6214,13 +6219,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q81" s="9">
         <v>46300</v>
@@ -6240,7 +6245,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B82" s="5">
         <v>46156.63269413194</v>
@@ -6250,7 +6255,7 @@
         <v>46156.72676160879</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6277,13 +6282,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6293,7 +6298,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B83" s="9">
         <v>46156.632715810185</v>
@@ -6303,7 +6308,7 @@
         <v>46156.726531747685</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6330,13 +6335,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q83" s="9">
         <v>46302</v>
@@ -6356,7 +6361,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B84" s="5">
         <v>46156.63272170139</v>
@@ -6366,7 +6371,7 @@
         <v>46156.72680289352</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6393,13 +6398,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6409,7 +6414,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B85" s="9">
         <v>46156.63273993056</v>
@@ -6419,7 +6424,7 @@
         <v>46156.7168192824</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>25</v>
@@ -6443,7 +6448,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6456,7 +6461,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B86" s="5">
         <v>46156.63274356481</v>
@@ -6466,16 +6471,16 @@
         <v>46156.7268765162</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I86" s="5">
         <v>46303</v>
@@ -6493,13 +6498,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q86" s="5">
         <v>46303</v>
@@ -6519,7 +6524,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B87" s="9">
         <v>46156.63274915509</v>
@@ -6529,16 +6534,16 @@
         <v>46156.72692035879</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I87" s="9">
         <v>46303</v>
@@ -6556,13 +6561,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6572,7 +6577,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B88" s="5">
         <v>46156.63276633102</v>
@@ -6582,7 +6587,7 @@
         <v>46156.72700125</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6607,13 +6612,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q88" s="5">
         <v>46304</v>
@@ -6633,7 +6638,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B89" s="9">
         <v>46156.63277084491</v>
@@ -6643,7 +6648,7 @@
         <v>46156.72697212963</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6670,13 +6675,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6686,7 +6691,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B90" s="5">
         <v>46156.63283398148</v>
@@ -6696,16 +6701,16 @@
         <v>46156.727094305556</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I90" s="5">
         <v>46307</v>
@@ -6723,13 +6728,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q90" s="5">
         <v>46307</v>
@@ -6749,7 +6754,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B91" s="9">
         <v>46156.63284013889</v>
@@ -6759,16 +6764,16 @@
         <v>46156.727054675925</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I91" s="9">
         <v>46307</v>
@@ -6786,13 +6791,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6802,7 +6807,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B92" s="5">
         <v>46156.63286864583</v>
@@ -6812,16 +6817,16 @@
         <v>46156.727220243054</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I92" s="5">
         <v>46308</v>
@@ -6839,13 +6844,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q92" s="5">
         <v>46308</v>
@@ -6865,7 +6870,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B93" s="9">
         <v>46156.632875972224</v>
@@ -6875,16 +6880,16 @@
         <v>46156.727183668976</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="9">
@@ -6900,13 +6905,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6916,7 +6921,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B94" s="5">
         <v>46156.63290420139</v>
@@ -6926,7 +6931,7 @@
         <v>46156.71731457176</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>25</v>
@@ -6950,7 +6955,7 @@
         <v>26</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>26</v>
@@ -6963,7 +6968,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B95" s="9">
         <v>46156.63290788194</v>
@@ -6973,16 +6978,16 @@
         <v>46156.72728918982</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I95" s="9">
         <v>46309</v>
@@ -7000,13 +7005,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q95" s="9">
         <v>46309</v>
@@ -7026,7 +7031,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B96" s="5">
         <v>46156.63291414352</v>
@@ -7036,7 +7041,7 @@
         <v>46156.727343402774</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7063,13 +7068,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q96" s="5">
         <v>46309</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -4380,7 +4380,7 @@
         <v>46184.58082519676</v>
       </c>
       <c r="D50" s="5">
-        <v>46184.580841041665</v>
+        <v>46204.18267401621</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>84</v>
@@ -4422,8 +4422,8 @@
       <c r="R50" s="5">
         <v>46211</v>
       </c>
-      <c r="S50" s="7" t="s">
-        <v>33</v>
+      <c r="S50" s="11" t="s">
+        <v>185</v>
       </c>
       <c r="T50" s="6">
         <v>1</v>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46156.72619693287</v>
+        <v>46203.92734233796</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>231</v>
@@ -5197,8 +5197,8 @@
       <c r="T63" s="10">
         <v>0</v>
       </c>
-      <c r="U63" s="12" t="s">
-        <v>103</v>
+      <c r="U63" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -3800,7 +3800,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46196.70204975695</v>
+        <v>46204.860021458335</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3850,8 +3850,8 @@
       <c r="T40" s="6">
         <v>0</v>
       </c>
-      <c r="U40" s="12" t="s">
-        <v>103</v>
+      <c r="U40" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -3916,9 +3916,11 @@
       <c r="B42" s="5">
         <v>46156.63227357639</v>
       </c>
-      <c r="C42" s="6"/>
+      <c r="C42" s="5">
+        <v>46204.86000005787</v>
+      </c>
       <c r="D42" s="5">
-        <v>46196.699790694445</v>
+        <v>46204.86000238426</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -3971,7 +3973,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46169.86151703703</v>
+        <v>46204.86001229167</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -5615,7 +5617,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46156.726445520835</v>
+        <v>46204.86002143519</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>248</v>
@@ -5665,8 +5667,8 @@
       <c r="T71" s="10">
         <v>0</v>
       </c>
-      <c r="U71" s="12" t="s">
-        <v>103</v>
+      <c r="U71" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -3798,9 +3798,11 @@
       <c r="B40" s="5">
         <v>46156.63226644676</v>
       </c>
-      <c r="C40" s="6"/>
+      <c r="C40" s="5">
+        <v>46204.87072556713</v>
+      </c>
       <c r="D40" s="5">
-        <v>46204.860021458335</v>
+        <v>46204.87074320602</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3848,10 +3850,10 @@
         <v>33</v>
       </c>
       <c r="T40" s="6">
-        <v>0</v>
-      </c>
-      <c r="U40" s="11" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U40" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -1598,13 +1598,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46156.6319474537</v>
+        <v>46156.46528078704</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.87352961805</v>
+        <v>46175.70686295139</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.87354112268</v>
+        <v>46175.706874456024</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1651,13 +1651,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46156.63206733797</v>
+        <v>46156.465400671295</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.87350086805</v>
+        <v>46175.70683420139</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.873530763885</v>
+        <v>46175.70686409722</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1714,13 +1714,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46156.63207047454</v>
+        <v>46156.46540380787</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.87350159722</v>
+        <v>46175.706834930555</v>
       </c>
       <c r="D6" s="5">
-        <v>46184.57987159722</v>
+        <v>46184.413204930555</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1777,13 +1777,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46156.632073217595</v>
+        <v>46156.465406550924</v>
       </c>
       <c r="C7" s="9">
-        <v>46184.58116133102</v>
+        <v>46184.41449466435</v>
       </c>
       <c r="D7" s="9">
-        <v>46184.58116259259</v>
+        <v>46184.41449592593</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -1840,13 +1840,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46156.63207597222</v>
+        <v>46156.46540930556</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.87350255787</v>
+        <v>46175.70683589121</v>
       </c>
       <c r="D8" s="5">
-        <v>46184.57963962963</v>
+        <v>46184.412972962964</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1903,13 +1903,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46156.63207924768</v>
+        <v>46156.46541258102</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.87350324074</v>
+        <v>46175.70683657407</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.87353033565</v>
+        <v>46175.70686366898</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -1966,11 +1966,11 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46156.63195149305</v>
+        <v>46156.465284826394</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46184.58046658565</v>
+        <v>46184.413799918984</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2013,13 +2013,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46156.63208246528</v>
+        <v>46156.46541579861</v>
       </c>
       <c r="C11" s="9">
-        <v>46184.58031472222</v>
+        <v>46184.41364805556</v>
       </c>
       <c r="D11" s="9">
-        <v>46184.58033075232</v>
+        <v>46184.413664085645</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2078,13 +2078,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46156.63208759259</v>
+        <v>46156.465420925924</v>
       </c>
       <c r="C12" s="5">
-        <v>46184.580324097224</v>
+        <v>46184.41365743056</v>
       </c>
       <c r="D12" s="5">
-        <v>46184.58034085648</v>
+        <v>46184.41367418981</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2143,13 +2143,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46156.63209254629</v>
+        <v>46156.46542587963</v>
       </c>
       <c r="C13" s="9">
-        <v>46184.580456111114</v>
+        <v>46184.41378944444</v>
       </c>
       <c r="D13" s="9">
-        <v>46184.58047240741</v>
+        <v>46184.41380574074</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2208,11 +2208,11 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46156.632097615744</v>
+        <v>46156.46543094907</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46184.58047240741</v>
+        <v>46184.41380574074</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2271,13 +2271,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46156.631956365745</v>
+        <v>46156.465289699074</v>
       </c>
       <c r="C15" s="9">
-        <v>46197.50205516204</v>
+        <v>46197.33538849537</v>
       </c>
       <c r="D15" s="9">
-        <v>46197.50206623843</v>
+        <v>46197.33539957176</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2324,13 +2324,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46156.63210516203</v>
+        <v>46156.465438495376</v>
       </c>
       <c r="C16" s="5">
-        <v>46184.58048224537</v>
+        <v>46184.41381557871</v>
       </c>
       <c r="D16" s="5">
-        <v>46184.58049826389</v>
+        <v>46184.41383159722</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2389,13 +2389,13 @@
         <v>73</v>
       </c>
       <c r="B17" s="9">
-        <v>46156.63211037037</v>
+        <v>46156.4654437037</v>
       </c>
       <c r="C17" s="9">
-        <v>46184.58049662037</v>
+        <v>46184.4138299537</v>
       </c>
       <c r="D17" s="9">
-        <v>46184.58051194444</v>
+        <v>46184.41384527778</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>74</v>
@@ -2454,13 +2454,13 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46156.63211564815</v>
+        <v>46156.465448981486</v>
       </c>
       <c r="C18" s="5">
-        <v>46197.50203898148</v>
+        <v>46197.33537231482</v>
       </c>
       <c r="D18" s="5">
-        <v>46197.5020416551</v>
+        <v>46197.335374988426</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2519,13 +2519,13 @@
         <v>80</v>
       </c>
       <c r="B19" s="9">
-        <v>46156.632121504634</v>
+        <v>46156.46545483796</v>
       </c>
       <c r="C19" s="9">
-        <v>46196.656259456024</v>
+        <v>46196.48959278935</v>
       </c>
       <c r="D19" s="9">
-        <v>46196.65627553241</v>
+        <v>46196.48960886574</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>81</v>
@@ -2584,13 +2584,13 @@
         <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46156.63212631944</v>
+        <v>46156.465459652776</v>
       </c>
       <c r="C20" s="5">
-        <v>46196.65655393519</v>
+        <v>46196.489887268515</v>
       </c>
       <c r="D20" s="5">
-        <v>46196.656567858794</v>
+        <v>46196.48990119213</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2649,13 +2649,13 @@
         <v>89</v>
       </c>
       <c r="B21" s="9">
-        <v>46156.63213005787</v>
+        <v>46156.4654633912</v>
       </c>
       <c r="C21" s="9">
-        <v>46196.65716653936</v>
+        <v>46196.490499872685</v>
       </c>
       <c r="D21" s="9">
-        <v>46196.65718306713</v>
+        <v>46196.49051640046</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2714,13 +2714,13 @@
         <v>92</v>
       </c>
       <c r="B22" s="5">
-        <v>46156.632133692125</v>
+        <v>46156.46546702547</v>
       </c>
       <c r="C22" s="5">
-        <v>46196.65766008102</v>
+        <v>46196.49099341435</v>
       </c>
       <c r="D22" s="5">
-        <v>46196.657674409726</v>
+        <v>46196.491007743054</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2779,11 +2779,11 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46156.6319605787</v>
+        <v>46156.46529391204</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46199.559805983794</v>
+        <v>46199.39313931713</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2826,11 +2826,11 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46156.63213814815</v>
+        <v>46156.46547148148</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46195.929228946756</v>
+        <v>46195.76256228009</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2889,13 +2889,13 @@
         <v>104</v>
       </c>
       <c r="B25" s="9">
-        <v>46156.63214259259</v>
+        <v>46156.46547592593</v>
       </c>
       <c r="C25" s="9">
-        <v>46195.92922075231</v>
+        <v>46195.76255408565</v>
       </c>
       <c r="D25" s="9">
-        <v>46195.92922337963</v>
+        <v>46195.76255671296</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>105</v>
@@ -2950,11 +2950,11 @@
         <v>107</v>
       </c>
       <c r="B26" s="5">
-        <v>46156.63214717593</v>
+        <v>46156.46548050926</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46195.92922835649</v>
+        <v>46195.762561689815</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>108</v>
@@ -3009,11 +3009,11 @@
         <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46156.6321521412</v>
+        <v>46156.46548547454</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46169.86132256944</v>
+        <v>46169.69465590278</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3072,11 +3072,11 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46156.63215657407</v>
+        <v>46156.46548990741</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46197.502050625</v>
+        <v>46197.33538395833</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3131,11 +3131,11 @@
         <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46156.63216167824</v>
+        <v>46156.46549501157</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46169.86172537037</v>
+        <v>46169.6950587037</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3190,11 +3190,11 @@
         <v>119</v>
       </c>
       <c r="B30" s="5">
-        <v>46156.63216756945</v>
+        <v>46156.46550090278</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46197.783559131945</v>
+        <v>46197.616892465274</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3253,13 +3253,13 @@
         <v>122</v>
       </c>
       <c r="B31" s="9">
-        <v>46156.63217278935</v>
+        <v>46156.46550612268</v>
       </c>
       <c r="C31" s="9">
-        <v>46195.929570740744</v>
+        <v>46195.76290407407</v>
       </c>
       <c r="D31" s="9">
-        <v>46195.92957241899</v>
+        <v>46195.762905752315</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>123</v>
@@ -3314,11 +3314,11 @@
         <v>125</v>
       </c>
       <c r="B32" s="5">
-        <v>46156.63217837963</v>
+        <v>46156.46551171296</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46195.92957792824</v>
+        <v>46195.76291126157</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -3373,13 +3373,13 @@
         <v>128</v>
       </c>
       <c r="B33" s="9">
-        <v>46156.63218368056</v>
+        <v>46156.46551701389</v>
       </c>
       <c r="C33" s="9">
-        <v>46197.78355179398</v>
+        <v>46197.61688512731</v>
       </c>
       <c r="D33" s="9">
-        <v>46197.78355364583</v>
+        <v>46197.616886979165</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>129</v>
@@ -3434,13 +3434,13 @@
         <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46156.632188240736</v>
+        <v>46156.46552157408</v>
       </c>
       <c r="C34" s="5">
-        <v>46199.55979506944</v>
+        <v>46199.39312840278</v>
       </c>
       <c r="D34" s="5">
-        <v>46199.55980914352</v>
+        <v>46199.39314247685</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3499,13 +3499,13 @@
         <v>136</v>
       </c>
       <c r="B35" s="9">
-        <v>46156.63219359954</v>
+        <v>46156.465526932865</v>
       </c>
       <c r="C35" s="9">
-        <v>46199.55916827546</v>
+        <v>46199.392501608796</v>
       </c>
       <c r="D35" s="9">
-        <v>46199.55917045139</v>
+        <v>46199.39250378472</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3560,13 +3560,13 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46156.63219844908</v>
+        <v>46156.46553178241</v>
       </c>
       <c r="C36" s="5">
-        <v>46199.55978109954</v>
+        <v>46199.39311443287</v>
       </c>
       <c r="D36" s="5">
-        <v>46199.5597825</v>
+        <v>46199.39311583333</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3621,13 +3621,13 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46156.63225444444</v>
+        <v>46156.46558777778</v>
       </c>
       <c r="C37" s="9">
-        <v>46199.55997423611</v>
+        <v>46199.393307569444</v>
       </c>
       <c r="D37" s="9">
-        <v>46199.55998701389</v>
+        <v>46199.393320347226</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3686,13 +3686,13 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46156.632258206024</v>
+        <v>46156.46559153935</v>
       </c>
       <c r="C38" s="5">
-        <v>46199.55990923611</v>
+        <v>46199.393242569444</v>
       </c>
       <c r="D38" s="5">
-        <v>46199.55991087963</v>
+        <v>46199.39324421296</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>88</v>
@@ -3741,13 +3741,13 @@
         <v>147</v>
       </c>
       <c r="B39" s="9">
-        <v>46156.63226241898</v>
+        <v>46156.465595752314</v>
       </c>
       <c r="C39" s="9">
-        <v>46199.55995880787</v>
+        <v>46199.393292141205</v>
       </c>
       <c r="D39" s="9">
-        <v>46199.55996042824</v>
+        <v>46199.393293761575</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>148</v>
@@ -3796,13 +3796,13 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46156.63226644676</v>
+        <v>46156.46559978009</v>
       </c>
       <c r="C40" s="5">
-        <v>46204.87072556713</v>
+        <v>46204.70405890046</v>
       </c>
       <c r="D40" s="5">
-        <v>46204.87074320602</v>
+        <v>46204.70407653935</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3861,13 +3861,13 @@
         <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46156.632269444446</v>
+        <v>46156.46560277778</v>
       </c>
       <c r="C41" s="9">
-        <v>46196.699784247685</v>
+        <v>46196.53311758101</v>
       </c>
       <c r="D41" s="9">
-        <v>46196.69978633102</v>
+        <v>46196.53311966435</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>94</v>
@@ -3916,13 +3916,13 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46156.63227357639</v>
+        <v>46156.465606909725</v>
       </c>
       <c r="C42" s="5">
-        <v>46204.86000005787</v>
+        <v>46204.6933333912</v>
       </c>
       <c r="D42" s="5">
-        <v>46204.86000238426</v>
+        <v>46204.69333571759</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -3971,11 +3971,11 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46156.63227760416</v>
+        <v>46156.4656109375</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46204.86001229167</v>
+        <v>46204.693345625</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -4024,13 +4024,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46156.63228021991</v>
+        <v>46156.46561355324</v>
       </c>
       <c r="C44" s="5">
-        <v>46199.56230621527</v>
+        <v>46199.39563954861</v>
       </c>
       <c r="D44" s="5">
-        <v>46199.562315937495</v>
+        <v>46199.39564927084</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4089,13 +4089,13 @@
         <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46156.63228315972</v>
+        <v>46156.46561649306</v>
       </c>
       <c r="C45" s="9">
-        <v>46199.562242835644</v>
+        <v>46199.39557616899</v>
       </c>
       <c r="D45" s="9">
-        <v>46199.56224427083</v>
+        <v>46199.39557760417</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>91</v>
@@ -4144,13 +4144,13 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46156.63228715278</v>
+        <v>46156.46562048611</v>
       </c>
       <c r="C46" s="5">
-        <v>46199.56229306713</v>
+        <v>46199.39562640047</v>
       </c>
       <c r="D46" s="5">
-        <v>46199.56229454861</v>
+        <v>46199.395627881946</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4199,11 +4199,11 @@
         <v>172</v>
       </c>
       <c r="B47" s="9">
-        <v>46156.63196493055</v>
+        <v>46156.46529826389</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46184.58079096065</v>
+        <v>46184.41412429398</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>173</v>
@@ -4248,13 +4248,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46156.63229164352</v>
+        <v>46156.46562497685</v>
       </c>
       <c r="C48" s="5">
-        <v>46184.58069681713</v>
+        <v>46184.41403015047</v>
       </c>
       <c r="D48" s="5">
-        <v>46197.714709479165</v>
+        <v>46197.5480428125</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4313,13 +4313,13 @@
         <v>181</v>
       </c>
       <c r="B49" s="9">
-        <v>46156.632296261574</v>
+        <v>46156.46562959491</v>
       </c>
       <c r="C49" s="9">
-        <v>46184.58077318287</v>
+        <v>46184.414106516204</v>
       </c>
       <c r="D49" s="9">
-        <v>46203.19706542824</v>
+        <v>46203.03039876158</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>182</v>
@@ -4378,13 +4378,13 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46156.63230224537</v>
+        <v>46156.4656355787</v>
       </c>
       <c r="C50" s="5">
-        <v>46184.58082519676</v>
+        <v>46184.4141585301</v>
       </c>
       <c r="D50" s="5">
-        <v>46204.18267401621</v>
+        <v>46204.016007349535</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>84</v>
@@ -4441,11 +4441,11 @@
         <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46156.632315358795</v>
+        <v>46156.46564869213</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46156.72589140046</v>
+        <v>46156.55922473379</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>191</v>
@@ -4504,11 +4504,11 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46156.6323189699</v>
+        <v>46156.46565230324</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46156.725962881945</v>
+        <v>46156.55929621527</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>194</v>
@@ -4557,11 +4557,11 @@
         <v>198</v>
       </c>
       <c r="B53" s="9">
-        <v>46156.63233141204</v>
+        <v>46156.46566474537</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46156.70385697916</v>
+        <v>46156.537190312505</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>199</v>
@@ -4604,11 +4604,11 @@
         <v>201</v>
       </c>
       <c r="B54" s="5">
-        <v>46156.63233460648</v>
+        <v>46156.46566793982</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46199.559799317125</v>
+        <v>46199.39313265047</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4667,11 +4667,11 @@
         <v>206</v>
       </c>
       <c r="B55" s="9">
-        <v>46156.63233969908</v>
+        <v>46156.465673032406</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46156.72612552083</v>
+        <v>46156.55945885417</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>207</v>
@@ -4730,11 +4730,11 @@
         <v>210</v>
       </c>
       <c r="B56" s="5">
-        <v>46156.632350671294</v>
+        <v>46156.46568400463</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46199.559976840275</v>
+        <v>46199.39331017361</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>211</v>
@@ -4793,11 +4793,11 @@
         <v>213</v>
       </c>
       <c r="B57" s="9">
-        <v>46156.63235533565</v>
+        <v>46156.46568866898</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46156.72612251157</v>
+        <v>46156.55945584491</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>214</v>
@@ -4856,11 +4856,11 @@
         <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46156.63235945602</v>
+        <v>46156.46569278935</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46199.56230880787</v>
+        <v>46199.3956421412</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>216</v>
@@ -4919,11 +4919,11 @@
         <v>218</v>
       </c>
       <c r="B59" s="9">
-        <v>46156.63236322917</v>
+        <v>46156.4656965625</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46156.72611966435</v>
+        <v>46156.55945299768</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>217</v>
@@ -4982,11 +4982,11 @@
         <v>219</v>
       </c>
       <c r="B60" s="5">
-        <v>46156.63236744213</v>
+        <v>46156.46570077546</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46203.5014815162</v>
+        <v>46203.33481484954</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>220</v>
@@ -5029,13 +5029,13 @@
         <v>222</v>
       </c>
       <c r="B61" s="9">
-        <v>46156.63237008102</v>
+        <v>46156.46570341435</v>
       </c>
       <c r="C61" s="9">
-        <v>46203.50147394676</v>
+        <v>46203.33480728009</v>
       </c>
       <c r="D61" s="9">
-        <v>46203.50149189815</v>
+        <v>46203.33482523148</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>223</v>
@@ -5094,11 +5094,11 @@
         <v>227</v>
       </c>
       <c r="B62" s="5">
-        <v>46156.63237584491</v>
+        <v>46156.46570917824</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46156.72624517361</v>
+        <v>46156.559578506945</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>196</v>
@@ -5147,11 +5147,11 @@
         <v>230</v>
       </c>
       <c r="B63" s="9">
-        <v>46156.63239597222</v>
+        <v>46156.46572930556</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46203.92734233796</v>
+        <v>46203.76067567129</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>231</v>
@@ -5210,11 +5210,11 @@
         <v>232</v>
       </c>
       <c r="B64" s="5">
-        <v>46156.632400069444</v>
+        <v>46156.46573340277</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46184.58084231481</v>
+        <v>46184.41417564815</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>196</v>
@@ -5263,11 +5263,11 @@
         <v>235</v>
       </c>
       <c r="B65" s="9">
-        <v>46156.63246734954</v>
+        <v>46156.46580068287</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46197.83505042824</v>
+        <v>46197.66838376157</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>236</v>
@@ -5326,11 +5326,11 @@
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46156.632472627316</v>
+        <v>46156.465805960645</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46197.83511621528</v>
+        <v>46197.66844954861</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>196</v>
@@ -5379,11 +5379,11 @@
         <v>239</v>
       </c>
       <c r="B67" s="9">
-        <v>46156.6324928588</v>
+        <v>46156.46582619213</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46156.71243400463</v>
+        <v>46156.545767337964</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>199</v>
@@ -5426,11 +5426,11 @@
         <v>241</v>
       </c>
       <c r="B68" s="5">
-        <v>46156.63249635417</v>
+        <v>46156.4658296875</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46156.72645449074</v>
+        <v>46156.55978782407</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>242</v>
@@ -5489,11 +5489,11 @@
         <v>243</v>
       </c>
       <c r="B69" s="9">
-        <v>46156.63250229167</v>
+        <v>46156.465835625</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46156.726451689814</v>
+        <v>46156.55978502315</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>244</v>
@@ -5552,11 +5552,11 @@
         <v>245</v>
       </c>
       <c r="B70" s="5">
-        <v>46156.63250851852</v>
+        <v>46156.46584185185</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46156.726448877314</v>
+        <v>46156.55978221065</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>246</v>
@@ -5615,11 +5615,11 @@
         <v>247</v>
       </c>
       <c r="B71" s="9">
-        <v>46156.63251465278</v>
+        <v>46156.46584798611</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46204.86002143519</v>
+        <v>46204.69335476852</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>248</v>
@@ -5678,11 +5678,11 @@
         <v>250</v>
       </c>
       <c r="B72" s="5">
-        <v>46156.63251914352</v>
+        <v>46156.46585247685</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46156.71581511574</v>
+        <v>46156.54914844908</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>251</v>
@@ -5725,11 +5725,11 @@
         <v>253</v>
       </c>
       <c r="B73" s="9">
-        <v>46156.63252219907</v>
+        <v>46156.465855532406</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46156.72654819445</v>
+        <v>46156.55988152778</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>254</v>
@@ -5788,11 +5788,11 @@
         <v>256</v>
       </c>
       <c r="B74" s="5">
-        <v>46156.63252934028</v>
+        <v>46156.46586267361</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46156.726576076384</v>
+        <v>46156.55990940973</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>196</v>
@@ -5841,11 +5841,11 @@
         <v>257</v>
       </c>
       <c r="B75" s="9">
-        <v>46156.63254586805</v>
+        <v>46156.465879201394</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46156.72654520834</v>
+        <v>46156.559878541666</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>258</v>
@@ -5904,11 +5904,11 @@
         <v>259</v>
       </c>
       <c r="B76" s="5">
-        <v>46156.63255047453</v>
+        <v>46156.465883807876</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46184.58084127315</v>
+        <v>46184.414174606485</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>196</v>
@@ -5957,11 +5957,11 @@
         <v>262</v>
       </c>
       <c r="B77" s="9">
-        <v>46156.63257873843</v>
+        <v>46156.465912071755</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46156.726542372686</v>
+        <v>46156.55987570602</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>263</v>
@@ -6020,11 +6020,11 @@
         <v>264</v>
       </c>
       <c r="B78" s="5">
-        <v>46156.632582986116</v>
+        <v>46156.465916319445</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46184.58084195602</v>
+        <v>46184.41417528935</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>196</v>
@@ -6073,11 +6073,11 @@
         <v>266</v>
       </c>
       <c r="B79" s="9">
-        <v>46156.632655671296</v>
+        <v>46156.46598900463</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46156.72653921296</v>
+        <v>46156.55987254629</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>267</v>
@@ -6136,11 +6136,11 @@
         <v>268</v>
       </c>
       <c r="B80" s="5">
-        <v>46156.6326615162</v>
+        <v>46156.46599484954</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46184.58084310185</v>
+        <v>46184.41417643518</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>196</v>
@@ -6189,11 +6189,11 @@
         <v>271</v>
       </c>
       <c r="B81" s="9">
-        <v>46156.6326856713</v>
+        <v>46156.46601900463</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46156.72653572916</v>
+        <v>46156.559869062505</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>272</v>
@@ -6252,11 +6252,11 @@
         <v>273</v>
       </c>
       <c r="B82" s="5">
-        <v>46156.63269413194</v>
+        <v>46156.46602746528</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46156.72676160879</v>
+        <v>46156.560094942135</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>196</v>
@@ -6305,11 +6305,11 @@
         <v>275</v>
       </c>
       <c r="B83" s="9">
-        <v>46156.632715810185</v>
+        <v>46156.46604914352</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46156.726531747685</v>
+        <v>46156.55986508101</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>276</v>
@@ -6368,11 +6368,11 @@
         <v>278</v>
       </c>
       <c r="B84" s="5">
-        <v>46156.63272170139</v>
+        <v>46156.46605503472</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46156.72680289352</v>
+        <v>46156.56013622685</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>196</v>
@@ -6421,11 +6421,11 @@
         <v>280</v>
       </c>
       <c r="B85" s="9">
-        <v>46156.63273993056</v>
+        <v>46156.46607326389</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46156.7168192824</v>
+        <v>46156.550152615746</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>281</v>
@@ -6468,11 +6468,11 @@
         <v>283</v>
       </c>
       <c r="B86" s="5">
-        <v>46156.63274356481</v>
+        <v>46156.46607689815</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46156.7268765162</v>
+        <v>46156.56020984954</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>284</v>
@@ -6531,11 +6531,11 @@
         <v>287</v>
       </c>
       <c r="B87" s="9">
-        <v>46156.63274915509</v>
+        <v>46156.46608248843</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46156.72692035879</v>
+        <v>46156.56025369213</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>196</v>
@@ -6584,11 +6584,11 @@
         <v>289</v>
       </c>
       <c r="B88" s="5">
-        <v>46156.63276633102</v>
+        <v>46156.46609966435</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46156.72700125</v>
+        <v>46156.56033458334</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>290</v>
@@ -6645,11 +6645,11 @@
         <v>291</v>
       </c>
       <c r="B89" s="9">
-        <v>46156.63277084491</v>
+        <v>46156.46610417824</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46156.72697212963</v>
+        <v>46156.56030546296</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>196</v>
@@ -6698,11 +6698,11 @@
         <v>293</v>
       </c>
       <c r="B90" s="5">
-        <v>46156.63283398148</v>
+        <v>46156.466167314815</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46156.727094305556</v>
+        <v>46156.56042763889</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>294</v>
@@ -6761,11 +6761,11 @@
         <v>295</v>
       </c>
       <c r="B91" s="9">
-        <v>46156.63284013889</v>
+        <v>46156.46617347222</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46156.727054675925</v>
+        <v>46156.56038800926</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>196</v>
@@ -6814,11 +6814,11 @@
         <v>297</v>
       </c>
       <c r="B92" s="5">
-        <v>46156.63286864583</v>
+        <v>46156.466201979165</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46156.727220243054</v>
+        <v>46156.56055357639</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>298</v>
@@ -6877,11 +6877,11 @@
         <v>300</v>
       </c>
       <c r="B93" s="9">
-        <v>46156.632875972224</v>
+        <v>46156.46620930555</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46156.727183668976</v>
+        <v>46156.56051700232</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>196</v>
@@ -6928,11 +6928,11 @@
         <v>301</v>
       </c>
       <c r="B94" s="5">
-        <v>46156.63290420139</v>
+        <v>46156.466237534725</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46156.71731457176</v>
+        <v>46156.5506479051</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>302</v>
@@ -6975,11 +6975,11 @@
         <v>304</v>
       </c>
       <c r="B95" s="9">
-        <v>46156.63290788194</v>
+        <v>46156.46624121528</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46156.72728918982</v>
+        <v>46156.560622523146</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>305</v>
@@ -7038,11 +7038,11 @@
         <v>308</v>
       </c>
       <c r="B96" s="5">
-        <v>46156.63291414352</v>
+        <v>46156.466247476856</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46156.727343402774</v>
+        <v>46156.56067673611</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>309</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -1598,13 +1598,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46156.46528078704</v>
+        <v>46156.6319474537</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.70686295139</v>
+        <v>46175.87352961805</v>
       </c>
       <c r="D4" s="5">
-        <v>46175.706874456024</v>
+        <v>46175.87354112268</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1651,13 +1651,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46156.465400671295</v>
+        <v>46156.63206733797</v>
       </c>
       <c r="C5" s="9">
-        <v>46175.70683420139</v>
+        <v>46175.87350086805</v>
       </c>
       <c r="D5" s="9">
-        <v>46175.70686409722</v>
+        <v>46175.873530763885</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1714,13 +1714,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46156.46540380787</v>
+        <v>46156.63207047454</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.706834930555</v>
+        <v>46175.87350159722</v>
       </c>
       <c r="D6" s="5">
-        <v>46184.413204930555</v>
+        <v>46184.57987159722</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1777,13 +1777,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46156.465406550924</v>
+        <v>46156.632073217595</v>
       </c>
       <c r="C7" s="9">
-        <v>46184.41449466435</v>
+        <v>46184.58116133102</v>
       </c>
       <c r="D7" s="9">
-        <v>46184.41449592593</v>
+        <v>46184.58116259259</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -1840,13 +1840,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46156.46540930556</v>
+        <v>46156.63207597222</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.70683589121</v>
+        <v>46175.87350255787</v>
       </c>
       <c r="D8" s="5">
-        <v>46184.412972962964</v>
+        <v>46184.57963962963</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1903,13 +1903,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46156.46541258102</v>
+        <v>46156.63207924768</v>
       </c>
       <c r="C9" s="9">
-        <v>46175.70683657407</v>
+        <v>46175.87350324074</v>
       </c>
       <c r="D9" s="9">
-        <v>46175.70686366898</v>
+        <v>46175.87353033565</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -1966,11 +1966,11 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46156.465284826394</v>
+        <v>46156.63195149305</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46184.413799918984</v>
+        <v>46184.58046658565</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2013,13 +2013,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46156.46541579861</v>
+        <v>46156.63208246528</v>
       </c>
       <c r="C11" s="9">
-        <v>46184.41364805556</v>
+        <v>46184.58031472222</v>
       </c>
       <c r="D11" s="9">
-        <v>46184.413664085645</v>
+        <v>46184.58033075232</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2078,13 +2078,13 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46156.465420925924</v>
+        <v>46156.63208759259</v>
       </c>
       <c r="C12" s="5">
-        <v>46184.41365743056</v>
+        <v>46184.580324097224</v>
       </c>
       <c r="D12" s="5">
-        <v>46184.41367418981</v>
+        <v>46184.58034085648</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2143,13 +2143,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="9">
-        <v>46156.46542587963</v>
+        <v>46156.63209254629</v>
       </c>
       <c r="C13" s="9">
-        <v>46184.41378944444</v>
+        <v>46184.580456111114</v>
       </c>
       <c r="D13" s="9">
-        <v>46184.41380574074</v>
+        <v>46184.58047240741</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2208,11 +2208,11 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46156.46543094907</v>
+        <v>46156.632097615744</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46184.41380574074</v>
+        <v>46184.58047240741</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2271,13 +2271,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46156.465289699074</v>
+        <v>46156.631956365745</v>
       </c>
       <c r="C15" s="9">
-        <v>46197.33538849537</v>
+        <v>46197.50205516204</v>
       </c>
       <c r="D15" s="9">
-        <v>46197.33539957176</v>
+        <v>46197.50206623843</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2324,13 +2324,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46156.465438495376</v>
+        <v>46156.63210516203</v>
       </c>
       <c r="C16" s="5">
-        <v>46184.41381557871</v>
+        <v>46184.58048224537</v>
       </c>
       <c r="D16" s="5">
-        <v>46184.41383159722</v>
+        <v>46184.58049826389</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2389,13 +2389,13 @@
         <v>73</v>
       </c>
       <c r="B17" s="9">
-        <v>46156.4654437037</v>
+        <v>46156.63211037037</v>
       </c>
       <c r="C17" s="9">
-        <v>46184.4138299537</v>
+        <v>46184.58049662037</v>
       </c>
       <c r="D17" s="9">
-        <v>46184.41384527778</v>
+        <v>46184.58051194444</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>74</v>
@@ -2454,13 +2454,13 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46156.465448981486</v>
+        <v>46156.63211564815</v>
       </c>
       <c r="C18" s="5">
-        <v>46197.33537231482</v>
+        <v>46197.50203898148</v>
       </c>
       <c r="D18" s="5">
-        <v>46197.335374988426</v>
+        <v>46197.5020416551</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2519,13 +2519,13 @@
         <v>80</v>
       </c>
       <c r="B19" s="9">
-        <v>46156.46545483796</v>
+        <v>46156.632121504634</v>
       </c>
       <c r="C19" s="9">
-        <v>46196.48959278935</v>
+        <v>46196.656259456024</v>
       </c>
       <c r="D19" s="9">
-        <v>46196.48960886574</v>
+        <v>46196.65627553241</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>81</v>
@@ -2584,13 +2584,13 @@
         <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46156.465459652776</v>
+        <v>46156.63212631944</v>
       </c>
       <c r="C20" s="5">
-        <v>46196.489887268515</v>
+        <v>46196.65655393519</v>
       </c>
       <c r="D20" s="5">
-        <v>46196.48990119213</v>
+        <v>46196.656567858794</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2649,13 +2649,13 @@
         <v>89</v>
       </c>
       <c r="B21" s="9">
-        <v>46156.4654633912</v>
+        <v>46156.63213005787</v>
       </c>
       <c r="C21" s="9">
-        <v>46196.490499872685</v>
+        <v>46196.65716653936</v>
       </c>
       <c r="D21" s="9">
-        <v>46196.49051640046</v>
+        <v>46196.65718306713</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2714,13 +2714,13 @@
         <v>92</v>
       </c>
       <c r="B22" s="5">
-        <v>46156.46546702547</v>
+        <v>46156.632133692125</v>
       </c>
       <c r="C22" s="5">
-        <v>46196.49099341435</v>
+        <v>46196.65766008102</v>
       </c>
       <c r="D22" s="5">
-        <v>46196.491007743054</v>
+        <v>46196.657674409726</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2779,11 +2779,11 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46156.46529391204</v>
+        <v>46156.6319605787</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46199.39313931713</v>
+        <v>46199.559805983794</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2826,11 +2826,11 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46156.46547148148</v>
+        <v>46156.63213814815</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46195.76256228009</v>
+        <v>46195.929228946756</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2889,13 +2889,13 @@
         <v>104</v>
       </c>
       <c r="B25" s="9">
-        <v>46156.46547592593</v>
+        <v>46156.63214259259</v>
       </c>
       <c r="C25" s="9">
-        <v>46195.76255408565</v>
+        <v>46195.92922075231</v>
       </c>
       <c r="D25" s="9">
-        <v>46195.76255671296</v>
+        <v>46195.92922337963</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>105</v>
@@ -2950,11 +2950,11 @@
         <v>107</v>
       </c>
       <c r="B26" s="5">
-        <v>46156.46548050926</v>
+        <v>46156.63214717593</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46195.762561689815</v>
+        <v>46195.92922835649</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>108</v>
@@ -3009,11 +3009,11 @@
         <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46156.46548547454</v>
+        <v>46156.6321521412</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46169.69465590278</v>
+        <v>46169.86132256944</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3072,11 +3072,11 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46156.46548990741</v>
+        <v>46156.63215657407</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46197.33538395833</v>
+        <v>46197.502050625</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3131,11 +3131,11 @@
         <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46156.46549501157</v>
+        <v>46156.63216167824</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46169.6950587037</v>
+        <v>46169.86172537037</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3190,11 +3190,11 @@
         <v>119</v>
       </c>
       <c r="B30" s="5">
-        <v>46156.46550090278</v>
+        <v>46156.63216756945</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46197.616892465274</v>
+        <v>46197.783559131945</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3253,13 +3253,13 @@
         <v>122</v>
       </c>
       <c r="B31" s="9">
-        <v>46156.46550612268</v>
+        <v>46156.63217278935</v>
       </c>
       <c r="C31" s="9">
-        <v>46195.76290407407</v>
+        <v>46195.929570740744</v>
       </c>
       <c r="D31" s="9">
-        <v>46195.762905752315</v>
+        <v>46195.92957241899</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>123</v>
@@ -3314,11 +3314,11 @@
         <v>125</v>
       </c>
       <c r="B32" s="5">
-        <v>46156.46551171296</v>
+        <v>46156.63217837963</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46195.76291126157</v>
+        <v>46195.92957792824</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -3373,13 +3373,13 @@
         <v>128</v>
       </c>
       <c r="B33" s="9">
-        <v>46156.46551701389</v>
+        <v>46156.63218368056</v>
       </c>
       <c r="C33" s="9">
-        <v>46197.61688512731</v>
+        <v>46197.78355179398</v>
       </c>
       <c r="D33" s="9">
-        <v>46197.616886979165</v>
+        <v>46197.78355364583</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>129</v>
@@ -3434,13 +3434,13 @@
         <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46156.46552157408</v>
+        <v>46156.632188240736</v>
       </c>
       <c r="C34" s="5">
-        <v>46199.39312840278</v>
+        <v>46199.55979506944</v>
       </c>
       <c r="D34" s="5">
-        <v>46199.39314247685</v>
+        <v>46199.55980914352</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3499,13 +3499,13 @@
         <v>136</v>
       </c>
       <c r="B35" s="9">
-        <v>46156.465526932865</v>
+        <v>46156.63219359954</v>
       </c>
       <c r="C35" s="9">
-        <v>46199.392501608796</v>
+        <v>46199.55916827546</v>
       </c>
       <c r="D35" s="9">
-        <v>46199.39250378472</v>
+        <v>46199.55917045139</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3560,13 +3560,13 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46156.46553178241</v>
+        <v>46156.63219844908</v>
       </c>
       <c r="C36" s="5">
-        <v>46199.39311443287</v>
+        <v>46199.55978109954</v>
       </c>
       <c r="D36" s="5">
-        <v>46199.39311583333</v>
+        <v>46199.5597825</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>140</v>
@@ -3621,13 +3621,13 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46156.46558777778</v>
+        <v>46156.63225444444</v>
       </c>
       <c r="C37" s="9">
-        <v>46199.393307569444</v>
+        <v>46199.55997423611</v>
       </c>
       <c r="D37" s="9">
-        <v>46199.393320347226</v>
+        <v>46199.55998701389</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3686,13 +3686,13 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46156.46559153935</v>
+        <v>46156.632258206024</v>
       </c>
       <c r="C38" s="5">
-        <v>46199.393242569444</v>
+        <v>46199.55990923611</v>
       </c>
       <c r="D38" s="5">
-        <v>46199.39324421296</v>
+        <v>46199.55991087963</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>88</v>
@@ -3741,13 +3741,13 @@
         <v>147</v>
       </c>
       <c r="B39" s="9">
-        <v>46156.465595752314</v>
+        <v>46156.63226241898</v>
       </c>
       <c r="C39" s="9">
-        <v>46199.393292141205</v>
+        <v>46199.55995880787</v>
       </c>
       <c r="D39" s="9">
-        <v>46199.393293761575</v>
+        <v>46199.55996042824</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>148</v>
@@ -3796,13 +3796,13 @@
         <v>150</v>
       </c>
       <c r="B40" s="5">
-        <v>46156.46559978009</v>
+        <v>46156.63226644676</v>
       </c>
       <c r="C40" s="5">
-        <v>46204.70405890046</v>
+        <v>46204.87072556713</v>
       </c>
       <c r="D40" s="5">
-        <v>46204.70407653935</v>
+        <v>46204.87074320602</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3861,13 +3861,13 @@
         <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46156.46560277778</v>
+        <v>46156.632269444446</v>
       </c>
       <c r="C41" s="9">
-        <v>46196.53311758101</v>
+        <v>46196.699784247685</v>
       </c>
       <c r="D41" s="9">
-        <v>46196.53311966435</v>
+        <v>46196.69978633102</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>94</v>
@@ -3916,13 +3916,13 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46156.465606909725</v>
+        <v>46156.63227357639</v>
       </c>
       <c r="C42" s="5">
-        <v>46204.6933333912</v>
+        <v>46204.86000005787</v>
       </c>
       <c r="D42" s="5">
-        <v>46204.69333571759</v>
+        <v>46204.86000238426</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -3971,11 +3971,11 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46156.4656109375</v>
+        <v>46156.63227760416</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46204.693345625</v>
+        <v>46204.86001229167</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -4024,13 +4024,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46156.46561355324</v>
+        <v>46156.63228021991</v>
       </c>
       <c r="C44" s="5">
-        <v>46199.39563954861</v>
+        <v>46199.56230621527</v>
       </c>
       <c r="D44" s="5">
-        <v>46199.39564927084</v>
+        <v>46199.562315937495</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4089,13 +4089,13 @@
         <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46156.46561649306</v>
+        <v>46156.63228315972</v>
       </c>
       <c r="C45" s="9">
-        <v>46199.39557616899</v>
+        <v>46199.562242835644</v>
       </c>
       <c r="D45" s="9">
-        <v>46199.39557760417</v>
+        <v>46199.56224427083</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>91</v>
@@ -4144,13 +4144,13 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46156.46562048611</v>
+        <v>46156.63228715278</v>
       </c>
       <c r="C46" s="5">
-        <v>46199.39562640047</v>
+        <v>46199.56229306713</v>
       </c>
       <c r="D46" s="5">
-        <v>46199.395627881946</v>
+        <v>46199.56229454861</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4199,11 +4199,11 @@
         <v>172</v>
       </c>
       <c r="B47" s="9">
-        <v>46156.46529826389</v>
+        <v>46156.63196493055</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46184.41412429398</v>
+        <v>46184.58079096065</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>173</v>
@@ -4248,13 +4248,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46156.46562497685</v>
+        <v>46156.63229164352</v>
       </c>
       <c r="C48" s="5">
-        <v>46184.41403015047</v>
+        <v>46184.58069681713</v>
       </c>
       <c r="D48" s="5">
-        <v>46197.5480428125</v>
+        <v>46197.714709479165</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4313,13 +4313,13 @@
         <v>181</v>
       </c>
       <c r="B49" s="9">
-        <v>46156.46562959491</v>
+        <v>46156.632296261574</v>
       </c>
       <c r="C49" s="9">
-        <v>46184.414106516204</v>
+        <v>46184.58077318287</v>
       </c>
       <c r="D49" s="9">
-        <v>46203.03039876158</v>
+        <v>46203.19706542824</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>182</v>
@@ -4378,13 +4378,13 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46156.4656355787</v>
+        <v>46156.63230224537</v>
       </c>
       <c r="C50" s="5">
-        <v>46184.4141585301</v>
+        <v>46184.58082519676</v>
       </c>
       <c r="D50" s="5">
-        <v>46204.016007349535</v>
+        <v>46204.18267401621</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>84</v>
@@ -4441,11 +4441,11 @@
         <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46156.46564869213</v>
+        <v>46156.632315358795</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46156.55922473379</v>
+        <v>46156.72589140046</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>191</v>
@@ -4504,11 +4504,11 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46156.46565230324</v>
+        <v>46156.6323189699</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46156.55929621527</v>
+        <v>46156.725962881945</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>194</v>
@@ -4557,11 +4557,11 @@
         <v>198</v>
       </c>
       <c r="B53" s="9">
-        <v>46156.46566474537</v>
+        <v>46156.63233141204</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46156.537190312505</v>
+        <v>46156.70385697916</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>199</v>
@@ -4604,11 +4604,11 @@
         <v>201</v>
       </c>
       <c r="B54" s="5">
-        <v>46156.46566793982</v>
+        <v>46156.63233460648</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46199.39313265047</v>
+        <v>46199.559799317125</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4667,11 +4667,11 @@
         <v>206</v>
       </c>
       <c r="B55" s="9">
-        <v>46156.465673032406</v>
+        <v>46156.63233969908</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46156.55945885417</v>
+        <v>46156.72612552083</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>207</v>
@@ -4730,11 +4730,11 @@
         <v>210</v>
       </c>
       <c r="B56" s="5">
-        <v>46156.46568400463</v>
+        <v>46156.632350671294</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46199.39331017361</v>
+        <v>46199.559976840275</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>211</v>
@@ -4793,11 +4793,11 @@
         <v>213</v>
       </c>
       <c r="B57" s="9">
-        <v>46156.46568866898</v>
+        <v>46156.63235533565</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46156.55945584491</v>
+        <v>46156.72612251157</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>214</v>
@@ -4856,11 +4856,11 @@
         <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46156.46569278935</v>
+        <v>46156.63235945602</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46199.3956421412</v>
+        <v>46199.56230880787</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>216</v>
@@ -4919,11 +4919,11 @@
         <v>218</v>
       </c>
       <c r="B59" s="9">
-        <v>46156.4656965625</v>
+        <v>46156.63236322917</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46156.55945299768</v>
+        <v>46156.72611966435</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>217</v>
@@ -4982,11 +4982,11 @@
         <v>219</v>
       </c>
       <c r="B60" s="5">
-        <v>46156.46570077546</v>
+        <v>46156.63236744213</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46203.33481484954</v>
+        <v>46203.5014815162</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>220</v>
@@ -5029,13 +5029,13 @@
         <v>222</v>
       </c>
       <c r="B61" s="9">
-        <v>46156.46570341435</v>
+        <v>46156.63237008102</v>
       </c>
       <c r="C61" s="9">
-        <v>46203.33480728009</v>
+        <v>46203.50147394676</v>
       </c>
       <c r="D61" s="9">
-        <v>46203.33482523148</v>
+        <v>46203.50149189815</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>223</v>
@@ -5094,11 +5094,11 @@
         <v>227</v>
       </c>
       <c r="B62" s="5">
-        <v>46156.46570917824</v>
+        <v>46156.63237584491</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46156.559578506945</v>
+        <v>46156.72624517361</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>196</v>
@@ -5147,11 +5147,11 @@
         <v>230</v>
       </c>
       <c r="B63" s="9">
-        <v>46156.46572930556</v>
+        <v>46156.63239597222</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46203.76067567129</v>
+        <v>46203.92734233796</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>231</v>
@@ -5210,11 +5210,11 @@
         <v>232</v>
       </c>
       <c r="B64" s="5">
-        <v>46156.46573340277</v>
+        <v>46156.632400069444</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46184.41417564815</v>
+        <v>46184.58084231481</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>196</v>
@@ -5263,11 +5263,11 @@
         <v>235</v>
       </c>
       <c r="B65" s="9">
-        <v>46156.46580068287</v>
+        <v>46156.63246734954</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46197.66838376157</v>
+        <v>46197.83505042824</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>236</v>
@@ -5326,11 +5326,11 @@
         <v>237</v>
       </c>
       <c r="B66" s="5">
-        <v>46156.465805960645</v>
+        <v>46156.632472627316</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46197.66844954861</v>
+        <v>46197.83511621528</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>196</v>
@@ -5379,11 +5379,11 @@
         <v>239</v>
       </c>
       <c r="B67" s="9">
-        <v>46156.46582619213</v>
+        <v>46156.6324928588</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46156.545767337964</v>
+        <v>46156.71243400463</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>199</v>
@@ -5426,11 +5426,11 @@
         <v>241</v>
       </c>
       <c r="B68" s="5">
-        <v>46156.4658296875</v>
+        <v>46156.63249635417</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46156.55978782407</v>
+        <v>46156.72645449074</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>242</v>
@@ -5489,11 +5489,11 @@
         <v>243</v>
       </c>
       <c r="B69" s="9">
-        <v>46156.465835625</v>
+        <v>46156.63250229167</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46156.55978502315</v>
+        <v>46156.726451689814</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>244</v>
@@ -5552,11 +5552,11 @@
         <v>245</v>
       </c>
       <c r="B70" s="5">
-        <v>46156.46584185185</v>
+        <v>46156.63250851852</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46156.55978221065</v>
+        <v>46156.726448877314</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>246</v>
@@ -5615,11 +5615,11 @@
         <v>247</v>
       </c>
       <c r="B71" s="9">
-        <v>46156.46584798611</v>
+        <v>46156.63251465278</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46204.69335476852</v>
+        <v>46204.86002143519</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>248</v>
@@ -5678,11 +5678,11 @@
         <v>250</v>
       </c>
       <c r="B72" s="5">
-        <v>46156.46585247685</v>
+        <v>46156.63251914352</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46156.54914844908</v>
+        <v>46156.71581511574</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>251</v>
@@ -5725,11 +5725,11 @@
         <v>253</v>
       </c>
       <c r="B73" s="9">
-        <v>46156.465855532406</v>
+        <v>46156.63252219907</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46156.55988152778</v>
+        <v>46156.72654819445</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>254</v>
@@ -5788,11 +5788,11 @@
         <v>256</v>
       </c>
       <c r="B74" s="5">
-        <v>46156.46586267361</v>
+        <v>46156.63252934028</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46156.55990940973</v>
+        <v>46156.726576076384</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>196</v>
@@ -5841,11 +5841,11 @@
         <v>257</v>
       </c>
       <c r="B75" s="9">
-        <v>46156.465879201394</v>
+        <v>46156.63254586805</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46156.559878541666</v>
+        <v>46156.72654520834</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>258</v>
@@ -5904,11 +5904,11 @@
         <v>259</v>
       </c>
       <c r="B76" s="5">
-        <v>46156.465883807876</v>
+        <v>46156.63255047453</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46184.414174606485</v>
+        <v>46184.58084127315</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>196</v>
@@ -5957,11 +5957,11 @@
         <v>262</v>
       </c>
       <c r="B77" s="9">
-        <v>46156.465912071755</v>
+        <v>46156.63257873843</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46156.55987570602</v>
+        <v>46156.726542372686</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>263</v>
@@ -6020,11 +6020,11 @@
         <v>264</v>
       </c>
       <c r="B78" s="5">
-        <v>46156.465916319445</v>
+        <v>46156.632582986116</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46184.41417528935</v>
+        <v>46184.58084195602</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>196</v>
@@ -6073,11 +6073,11 @@
         <v>266</v>
       </c>
       <c r="B79" s="9">
-        <v>46156.46598900463</v>
+        <v>46156.632655671296</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46156.55987254629</v>
+        <v>46156.72653921296</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>267</v>
@@ -6136,11 +6136,11 @@
         <v>268</v>
       </c>
       <c r="B80" s="5">
-        <v>46156.46599484954</v>
+        <v>46156.6326615162</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46184.41417643518</v>
+        <v>46184.58084310185</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>196</v>
@@ -6189,11 +6189,11 @@
         <v>271</v>
       </c>
       <c r="B81" s="9">
-        <v>46156.46601900463</v>
+        <v>46156.6326856713</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46156.559869062505</v>
+        <v>46156.72653572916</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>272</v>
@@ -6252,11 +6252,11 @@
         <v>273</v>
       </c>
       <c r="B82" s="5">
-        <v>46156.46602746528</v>
+        <v>46156.63269413194</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46156.560094942135</v>
+        <v>46156.72676160879</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>196</v>
@@ -6305,11 +6305,11 @@
         <v>275</v>
       </c>
       <c r="B83" s="9">
-        <v>46156.46604914352</v>
+        <v>46156.632715810185</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46156.55986508101</v>
+        <v>46156.726531747685</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>276</v>
@@ -6368,11 +6368,11 @@
         <v>278</v>
       </c>
       <c r="B84" s="5">
-        <v>46156.46605503472</v>
+        <v>46156.63272170139</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46156.56013622685</v>
+        <v>46156.72680289352</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>196</v>
@@ -6421,11 +6421,11 @@
         <v>280</v>
       </c>
       <c r="B85" s="9">
-        <v>46156.46607326389</v>
+        <v>46156.63273993056</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46156.550152615746</v>
+        <v>46156.7168192824</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>281</v>
@@ -6468,11 +6468,11 @@
         <v>283</v>
       </c>
       <c r="B86" s="5">
-        <v>46156.46607689815</v>
+        <v>46156.63274356481</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46156.56020984954</v>
+        <v>46156.7268765162</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>284</v>
@@ -6531,11 +6531,11 @@
         <v>287</v>
       </c>
       <c r="B87" s="9">
-        <v>46156.46608248843</v>
+        <v>46156.63274915509</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46156.56025369213</v>
+        <v>46156.72692035879</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>196</v>
@@ -6584,11 +6584,11 @@
         <v>289</v>
       </c>
       <c r="B88" s="5">
-        <v>46156.46609966435</v>
+        <v>46156.63276633102</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46156.56033458334</v>
+        <v>46156.72700125</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>290</v>
@@ -6645,11 +6645,11 @@
         <v>291</v>
       </c>
       <c r="B89" s="9">
-        <v>46156.46610417824</v>
+        <v>46156.63277084491</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46156.56030546296</v>
+        <v>46156.72697212963</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>196</v>
@@ -6698,11 +6698,11 @@
         <v>293</v>
       </c>
       <c r="B90" s="5">
-        <v>46156.466167314815</v>
+        <v>46156.63283398148</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46156.56042763889</v>
+        <v>46156.727094305556</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>294</v>
@@ -6761,11 +6761,11 @@
         <v>295</v>
       </c>
       <c r="B91" s="9">
-        <v>46156.46617347222</v>
+        <v>46156.63284013889</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46156.56038800926</v>
+        <v>46156.727054675925</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>196</v>
@@ -6814,11 +6814,11 @@
         <v>297</v>
       </c>
       <c r="B92" s="5">
-        <v>46156.466201979165</v>
+        <v>46156.63286864583</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46156.56055357639</v>
+        <v>46156.727220243054</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>298</v>
@@ -6877,11 +6877,11 @@
         <v>300</v>
       </c>
       <c r="B93" s="9">
-        <v>46156.46620930555</v>
+        <v>46156.632875972224</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46156.56051700232</v>
+        <v>46156.727183668976</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>196</v>
@@ -6928,11 +6928,11 @@
         <v>301</v>
       </c>
       <c r="B94" s="5">
-        <v>46156.466237534725</v>
+        <v>46156.63290420139</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46156.5506479051</v>
+        <v>46156.71731457176</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>302</v>
@@ -6975,11 +6975,11 @@
         <v>304</v>
       </c>
       <c r="B95" s="9">
-        <v>46156.46624121528</v>
+        <v>46156.63290788194</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46156.560622523146</v>
+        <v>46156.72728918982</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>305</v>
@@ -7038,11 +7038,11 @@
         <v>308</v>
       </c>
       <c r="B96" s="5">
-        <v>46156.466247476856</v>
+        <v>46156.63291414352</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46156.56067673611</v>
+        <v>46156.727343402774</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>309</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -5151,7 +5151,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46203.92734233796</v>
+        <v>46205.904521226854</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>231</v>
@@ -5199,7 +5199,7 @@
         <v>33</v>
       </c>
       <c r="T63" s="10">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="U63" s="11" t="s">
         <v>66</v>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46156.7168192824</v>
+        <v>46205.90465030093</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>281</v>
@@ -6700,9 +6700,11 @@
       <c r="B90" s="5">
         <v>46156.63283398148</v>
       </c>
-      <c r="C90" s="6"/>
+      <c r="C90" s="5">
+        <v>46205.90464569445</v>
+      </c>
       <c r="D90" s="5">
-        <v>46156.727094305556</v>
+        <v>46205.904737627316</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>294</v>
@@ -6750,10 +6752,10 @@
         <v>33</v>
       </c>
       <c r="T90" s="6">
-        <v>0</v>
-      </c>
-      <c r="U90" s="12" t="s">
-        <v>103</v>
+        <v>1</v>
+      </c>
+      <c r="U90" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
@@ -6763,9 +6765,11 @@
       <c r="B91" s="9">
         <v>46156.63284013889</v>
       </c>
-      <c r="C91" s="10"/>
+      <c r="C91" s="9">
+        <v>46205.90471993056</v>
+      </c>
       <c r="D91" s="9">
-        <v>46156.727054675925</v>
+        <v>46205.90481071759</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>196</v>
@@ -6881,7 +6885,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46156.727183668976</v>
+        <v>46205.9047287037</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>196</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -299,6 +299,9 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser OT 4317</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1214809660718675</t>
   </si>
   <si>
@@ -594,9 +597,6 @@
   </si>
   <si>
     <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214809528759377</t>
@@ -2525,7 +2525,7 @@
         <v>46196.656259456024</v>
       </c>
       <c r="D19" s="9">
-        <v>46196.65627553241</v>
+        <v>46206.193739560185</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>81</v>
@@ -2569,8 +2569,8 @@
       <c r="R19" s="9">
         <v>46213</v>
       </c>
-      <c r="S19" s="7" t="s">
-        <v>33</v>
+      <c r="S19" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="T19" s="10">
         <v>1</v>
@@ -2581,7 +2581,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B20" s="5">
         <v>46156.63212631944</v>
@@ -2590,10 +2590,10 @@
         <v>46196.65655393519</v>
       </c>
       <c r="D20" s="5">
-        <v>46196.656567858794</v>
+        <v>46206.193739560185</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2626,7 +2626,7 @@
         <v>84</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q20" s="5">
         <v>46212</v>
@@ -2634,8 +2634,8 @@
       <c r="R20" s="5">
         <v>46213</v>
       </c>
-      <c r="S20" s="7" t="s">
-        <v>33</v>
+      <c r="S20" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -2646,7 +2646,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B21" s="9">
         <v>46156.63213005787</v>
@@ -2655,10 +2655,10 @@
         <v>46196.65716653936</v>
       </c>
       <c r="D21" s="9">
-        <v>46196.65718306713</v>
+        <v>46206.193739571754</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2691,7 +2691,7 @@
         <v>84</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q21" s="9">
         <v>46212</v>
@@ -2699,8 +2699,8 @@
       <c r="R21" s="9">
         <v>46213</v>
       </c>
-      <c r="S21" s="7" t="s">
-        <v>33</v>
+      <c r="S21" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="T21" s="10">
         <v>1</v>
@@ -2711,7 +2711,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B22" s="5">
         <v>46156.632133692125</v>
@@ -2720,10 +2720,10 @@
         <v>46196.65766008102</v>
       </c>
       <c r="D22" s="5">
-        <v>46196.657674409726</v>
+        <v>46206.193739571754</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2756,7 +2756,7 @@
         <v>84</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q22" s="5">
         <v>46212</v>
@@ -2764,8 +2764,8 @@
       <c r="R22" s="5">
         <v>46213</v>
       </c>
-      <c r="S22" s="7" t="s">
-        <v>33</v>
+      <c r="S22" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B23" s="9">
         <v>46156.6319605787</v>
@@ -2786,7 +2786,7 @@
         <v>46199.559805983794</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>25</v>
@@ -2810,7 +2810,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>26</v>
@@ -2823,7 +2823,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B24" s="5">
         <v>46156.63213814815</v>
@@ -2833,16 +2833,16 @@
         <v>46195.929228946756</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I24" s="5">
         <v>46154</v>
@@ -2860,13 +2860,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q24" s="5">
         <v>46154</v>
@@ -2881,12 +2881,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B25" s="9">
         <v>46156.63214259259</v>
@@ -2898,16 +2898,16 @@
         <v>46195.92922337963</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I25" s="9">
         <v>46154</v>
@@ -2925,13 +2925,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>74</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -2942,12 +2942,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B26" s="5">
         <v>46156.63214717593</v>
@@ -2957,16 +2957,16 @@
         <v>46195.92922835649</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I26" s="5">
         <v>46156</v>
@@ -2984,13 +2984,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3001,12 +3001,12 @@
         <v>0</v>
       </c>
       <c r="U26" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B27" s="9">
         <v>46156.6321521412</v>
@@ -3016,16 +3016,16 @@
         <v>46169.86132256944</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I27" s="9">
         <v>46150</v>
@@ -3043,13 +3043,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q27" s="9">
         <v>46150</v>
@@ -3064,12 +3064,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B28" s="5">
         <v>46156.63215657407</v>
@@ -3079,16 +3079,16 @@
         <v>46197.502050625</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I28" s="5">
         <v>46150</v>
@@ -3106,13 +3106,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3123,12 +3123,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B29" s="9">
         <v>46156.63216167824</v>
@@ -3138,16 +3138,16 @@
         <v>46169.86172537037</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I29" s="9">
         <v>46150</v>
@@ -3165,13 +3165,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3182,12 +3182,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5">
         <v>46156.63216756945</v>
@@ -3197,16 +3197,16 @@
         <v>46197.783559131945</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I30" s="5">
         <v>46142</v>
@@ -3224,13 +3224,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q30" s="5">
         <v>46172</v>
@@ -3245,12 +3245,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" s="9">
         <v>46156.63217278935</v>
@@ -3262,16 +3262,16 @@
         <v>46195.92957241899</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I31" s="9">
         <v>46142</v>
@@ -3289,13 +3289,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>71</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3306,12 +3306,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5">
         <v>46156.63217837963</v>
@@ -3321,16 +3321,16 @@
         <v>46195.92957792824</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I32" s="5">
         <v>46164</v>
@@ -3348,13 +3348,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3365,12 +3365,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B33" s="9">
         <v>46156.63218368056</v>
@@ -3382,16 +3382,16 @@
         <v>46197.78355364583</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I33" s="9">
         <v>46164</v>
@@ -3409,13 +3409,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3426,12 +3426,12 @@
         <v>0</v>
       </c>
       <c r="U33" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46156.632188240736</v>
@@ -3443,16 +3443,16 @@
         <v>46199.55980914352</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I34" s="5">
         <v>46216</v>
@@ -3470,13 +3470,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q34" s="5">
         <v>46216</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B35" s="9">
         <v>46156.63219359954</v>
@@ -3508,16 +3508,16 @@
         <v>46199.55917045139</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I35" s="9">
         <v>46216</v>
@@ -3535,13 +3535,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>81</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3552,12 +3552,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46156.63219844908</v>
@@ -3569,16 +3569,16 @@
         <v>46199.5597825</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I36" s="5">
         <v>46218</v>
@@ -3596,13 +3596,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3613,12 +3613,12 @@
         <v>0</v>
       </c>
       <c r="U36" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B37" s="9">
         <v>46156.63225444444</v>
@@ -3630,16 +3630,16 @@
         <v>46199.55998701389</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I37" s="9">
         <v>46216</v>
@@ -3657,10 +3657,10 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>26</v>
@@ -3683,7 +3683,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B38" s="5">
         <v>46156.632258206024</v>
@@ -3695,16 +3695,16 @@
         <v>46199.55991087963</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I38" s="5">
         <v>46216</v>
@@ -3722,13 +3722,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3738,7 +3738,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B39" s="9">
         <v>46156.63226241898</v>
@@ -3750,16 +3750,16 @@
         <v>46199.55996042824</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I39" s="9">
         <v>46218</v>
@@ -3777,13 +3777,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46156.63226644676</v>
@@ -3805,16 +3805,16 @@
         <v>46204.87074320602</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I40" s="5">
         <v>46216</v>
@@ -3832,10 +3832,10 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3858,7 +3858,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B41" s="9">
         <v>46156.632269444446</v>
@@ -3870,16 +3870,16 @@
         <v>46196.69978633102</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I41" s="9">
         <v>46216</v>
@@ -3897,13 +3897,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3913,7 +3913,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B42" s="5">
         <v>46156.63227357639</v>
@@ -3925,16 +3925,16 @@
         <v>46204.86000238426</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I42" s="5">
         <v>46225</v>
@@ -3952,13 +3952,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3968,7 +3968,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B43" s="9">
         <v>46156.63227760416</v>
@@ -3978,16 +3978,16 @@
         <v>46204.86001229167</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I43" s="9">
         <v>46254</v>
@@ -4005,10 +4005,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4021,7 +4021,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B44" s="5">
         <v>46156.63228021991</v>
@@ -4033,16 +4033,16 @@
         <v>46199.562315937495</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I44" s="5">
         <v>46216</v>
@@ -4060,10 +4060,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4086,7 +4086,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" s="9">
         <v>46156.63228315972</v>
@@ -4098,16 +4098,16 @@
         <v>46199.56224427083</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I45" s="9">
         <v>46216</v>
@@ -4125,13 +4125,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4141,7 +4141,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46156.63228715278</v>
@@ -4153,16 +4153,16 @@
         <v>46199.56229454861</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I46" s="5">
         <v>46218</v>
@@ -4180,13 +4180,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B47" s="9">
         <v>46156.63196493055</v>
@@ -4206,7 +4206,7 @@
         <v>46184.58079096065</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>25</v>
@@ -4230,7 +4230,7 @@
         <v>26</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>26</v>
@@ -4245,7 +4245,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46156.63229164352</v>
@@ -4257,16 +4257,16 @@
         <v>46197.714709479165</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I48" s="5">
         <v>46150</v>
@@ -4284,13 +4284,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46150</v>
@@ -4299,7 +4299,7 @@
         <v>46156</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T48" s="6">
         <v>1</v>
@@ -4310,7 +4310,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46156.632296261574</v>
@@ -4322,16 +4322,16 @@
         <v>46203.19706542824</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I49" s="9">
         <v>46204</v>
@@ -4349,13 +4349,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q49" s="9">
         <v>46204</v>
@@ -4364,7 +4364,7 @@
         <v>46210</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>
@@ -4412,10 +4412,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>189</v>
@@ -4427,7 +4427,7 @@
         <v>46211</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="T50" s="6">
         <v>1</v>
@@ -4475,7 +4475,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>194</v>
@@ -4496,7 +4496,7 @@
         <v>0</v>
       </c>
       <c r="U51" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4641,7 +4641,7 @@
         <v>199</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>205</v>
@@ -4680,10 +4680,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I55" s="9">
         <v>46231</v>
@@ -4722,7 +4722,7 @@
         <v>0</v>
       </c>
       <c r="U55" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4767,7 +4767,7 @@
         <v>199</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>212</v>
@@ -4806,10 +4806,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I57" s="9">
         <v>46231</v>
@@ -4848,7 +4848,7 @@
         <v>0</v>
       </c>
       <c r="U57" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4893,7 +4893,7 @@
         <v>199</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>217</v>
@@ -4932,10 +4932,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I59" s="9">
         <v>46231</v>
@@ -4974,7 +4974,7 @@
         <v>0</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5276,10 +5276,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I65" s="9">
         <v>46262</v>
@@ -5318,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5339,10 +5339,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I66" s="5">
         <v>46262</v>
@@ -5463,7 +5463,7 @@
         <v>199</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>209</v>
@@ -5481,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="U68" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5526,7 +5526,7 @@
         <v>199</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>209</v>
@@ -5544,7 +5544,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5589,7 +5589,7 @@
         <v>199</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>209</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5652,7 +5652,7 @@
         <v>199</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>249</v>
@@ -5780,7 +5780,7 @@
         <v>0</v>
       </c>
       <c r="U73" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -5896,7 +5896,7 @@
         <v>0</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6012,7 +6012,7 @@
         <v>0</v>
       </c>
       <c r="U77" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6128,7 +6128,7 @@
         <v>0</v>
       </c>
       <c r="U79" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6244,7 +6244,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6360,7 +6360,7 @@
         <v>0</v>
       </c>
       <c r="U83" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6523,7 +6523,7 @@
         <v>0</v>
       </c>
       <c r="U86" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -6637,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="U88" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6873,7 +6873,7 @@
         <v>0</v>
       </c>
       <c r="U92" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -7034,7 +7034,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7097,7 +7097,7 @@
         <v>0</v>
       </c>
       <c r="U96" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -2655,7 +2655,7 @@
         <v>46196.65716653936</v>
       </c>
       <c r="D21" s="9">
-        <v>46206.193739571754</v>
+        <v>46206.56335621528</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>91</v>
@@ -2720,7 +2720,7 @@
         <v>46196.65766008102</v>
       </c>
       <c r="D22" s="5">
-        <v>46206.193739571754</v>
+        <v>46206.563520752316</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>94</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="305">
   <si>
     <t>50001547 - XEMORTIZ (AMERICAS GOLD)</t>
   </si>
@@ -179,7 +179,7 @@
     <t>Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
-    <t>Ingenieria Basica Motor,Ingenieria basica Rodete,Analisis de costeo,Ingenieria Detalle</t>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214809660705231</t>
@@ -197,7 +197,7 @@
     <t>MOTOR DE STOCK WEG - 02 POLOS - IE3 FRAME 280</t>
   </si>
   <si>
-    <t>Ingenieria Jefe de proyecto:,Analisis de costeo,propuesta motor OT 4317</t>
+    <t>Ingenieria Jefe de proyecto:,propuesta motor OT 4317</t>
   </si>
   <si>
     <t>1214809416473931</t>
@@ -215,7 +215,7 @@
 </t>
   </si>
   <si>
-    <t>Ingenieria Jefe de proyecto:,propuesta nucleo rodete OT 4317,propuesta alabes OT 4317,Analisis de costeo</t>
+    <t>Ingenieria Jefe de proyecto:,propuesta nucleo rodete OT 4317,propuesta alabes OT 4317</t>
   </si>
   <si>
     <t>1214809660709713</t>
@@ -224,22 +224,7 @@
     <t>Ingenieria Detalle</t>
   </si>
   <si>
-    <t>Planos preliminar,Analisis de costeo,Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>1214809660709733</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Costos,Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
+    <t>Planos preliminar,Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
     <t>1214787972061375</t>
@@ -969,9 +954,6 @@
   </si>
   <si>
     <t>Costos</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Despacho</t>
   </si>
 </sst>
 </file>
@@ -1495,7 +1477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U96"/>
+  <dimension ref="A1:U95"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -1970,7 +1952,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46184.58046658565</v>
+        <v>46209.55906222222</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -1997,7 +1979,7 @@
         <v>26</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>26</v>
@@ -2006,7 +1988,9 @@
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
       <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
+      <c r="U10" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
@@ -2019,7 +2003,7 @@
         <v>46184.58031472222</v>
       </c>
       <c r="D11" s="9">
-        <v>46184.58033075232</v>
+        <v>46209.55905150463</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2084,7 +2068,7 @@
         <v>46184.580324097224</v>
       </c>
       <c r="D12" s="5">
-        <v>46184.58034085648</v>
+        <v>46209.55905152777</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2149,7 +2133,7 @@
         <v>46184.580456111114</v>
       </c>
       <c r="D13" s="9">
-        <v>46184.58047240741</v>
+        <v>46209.55905167824</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>60</v>
@@ -2208,30 +2192,26 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46156.632097615744</v>
-      </c>
-      <c r="C14" s="6"/>
+        <v>46156.631956365745</v>
+      </c>
+      <c r="C14" s="5">
+        <v>46197.50205516204</v>
+      </c>
       <c r="D14" s="5">
-        <v>46184.58047240741</v>
+        <v>46197.50206623843</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="5">
-        <v>46140</v>
-      </c>
-      <c r="J14" s="5">
-        <v>46149</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
       <c r="K14" s="6" t="s">
         <v>26</v>
       </c>
@@ -2239,79 +2219,85 @@
         <v>26</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q14" s="5">
-        <v>46140</v>
-      </c>
-      <c r="R14" s="5">
-        <v>46149</v>
-      </c>
-      <c r="S14" s="7" t="s">
-        <v>33</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
       <c r="T14" s="6">
-        <v>0</v>
-      </c>
-      <c r="U14" s="11" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="U14" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="9">
+        <v>46156.63210516203</v>
+      </c>
+      <c r="C15" s="9">
+        <v>46184.58048224537</v>
+      </c>
+      <c r="D15" s="9">
+        <v>46184.58049826389</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="9">
+        <v>46142</v>
+      </c>
+      <c r="J15" s="9">
+        <v>46146</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="O15" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="P15" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="9">
-        <v>46156.631956365745</v>
-      </c>
-      <c r="C15" s="9">
-        <v>46197.50205516204</v>
-      </c>
-      <c r="D15" s="9">
-        <v>46197.50206623843</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O15" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
+      <c r="Q15" s="9">
+        <v>46142</v>
+      </c>
+      <c r="R15" s="9">
+        <v>46146</v>
+      </c>
+      <c r="S15" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="T15" s="10">
         <v>1</v>
       </c>
@@ -2321,19 +2307,19 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46156.63210516203</v>
+        <v>46156.63211037037</v>
       </c>
       <c r="C16" s="5">
-        <v>46184.58048224537</v>
+        <v>46184.58049662037</v>
       </c>
       <c r="D16" s="5">
-        <v>46184.58049826389</v>
+        <v>46184.58051194444</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2345,10 +2331,10 @@
         <v>52</v>
       </c>
       <c r="I16" s="5">
-        <v>46142</v>
+        <v>46150</v>
       </c>
       <c r="J16" s="5">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>26</v>
@@ -2360,19 +2346,19 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Q16" s="5">
-        <v>46142</v>
+        <v>46150</v>
       </c>
       <c r="R16" s="5">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="S16" s="7" t="s">
         <v>33</v>
@@ -2386,28 +2372,28 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="9">
+        <v>46156.63211564815</v>
+      </c>
+      <c r="C17" s="9">
+        <v>46197.50203898148</v>
+      </c>
+      <c r="D17" s="9">
+        <v>46197.5020416551</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="9">
-        <v>46156.63211037037</v>
-      </c>
-      <c r="C17" s="9">
-        <v>46184.58049662037</v>
-      </c>
-      <c r="D17" s="9">
-        <v>46184.58051194444</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="H17" s="10" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="I17" s="9">
         <v>46150</v>
@@ -2425,13 +2411,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="9">
         <v>46150</v>
@@ -2451,34 +2437,34 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46156.632121504634</v>
+      </c>
+      <c r="C18" s="5">
+        <v>46196.656259456024</v>
+      </c>
+      <c r="D18" s="5">
+        <v>46206.193739560185</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B18" s="5">
-        <v>46156.63211564815</v>
-      </c>
-      <c r="C18" s="5">
-        <v>46197.50203898148</v>
-      </c>
-      <c r="D18" s="5">
-        <v>46197.5020416551</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="F18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>78</v>
       </c>
       <c r="I18" s="5">
-        <v>46150</v>
+        <v>46212</v>
       </c>
       <c r="J18" s="5">
-        <v>46153</v>
+        <v>46213</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>26</v>
@@ -2490,22 +2476,22 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="5">
-        <v>46150</v>
+        <v>46212</v>
       </c>
       <c r="R18" s="5">
-        <v>46153</v>
-      </c>
-      <c r="S18" s="7" t="s">
-        <v>33</v>
+        <v>46213</v>
+      </c>
+      <c r="S18" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2516,28 +2502,28 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B19" s="9">
-        <v>46156.632121504634</v>
+        <v>46156.63212631944</v>
       </c>
       <c r="C19" s="9">
-        <v>46196.656259456024</v>
+        <v>46196.65655393519</v>
       </c>
       <c r="D19" s="9">
         <v>46206.193739560185</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I19" s="9">
         <v>46212</v>
@@ -2555,13 +2541,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="O19" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="P19" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="P19" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="Q19" s="9">
         <v>46212</v>
@@ -2570,7 +2556,7 @@
         <v>46213</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="T19" s="10">
         <v>1</v>
@@ -2581,28 +2567,28 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46156.63212631944</v>
+        <v>46156.63213005787</v>
       </c>
       <c r="C20" s="5">
-        <v>46196.65655393519</v>
+        <v>46196.65716653936</v>
       </c>
       <c r="D20" s="5">
-        <v>46206.193739560185</v>
+        <v>46206.56335621528</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I20" s="5">
         <v>46212</v>
@@ -2620,13 +2606,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="5">
         <v>46212</v>
@@ -2635,7 +2621,7 @@
         <v>46213</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -2646,28 +2632,28 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B21" s="9">
-        <v>46156.63213005787</v>
+        <v>46156.632133692125</v>
       </c>
       <c r="C21" s="9">
-        <v>46196.65716653936</v>
+        <v>46196.65766008102</v>
       </c>
       <c r="D21" s="9">
-        <v>46206.56335621528</v>
+        <v>46206.563520752316</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I21" s="9">
         <v>46212</v>
@@ -2685,13 +2671,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="Q21" s="9">
         <v>46212</v>
@@ -2700,7 +2686,7 @@
         <v>46213</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="T21" s="10">
         <v>1</v>
@@ -2711,92 +2697,80 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46156.6319605787</v>
+      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="5">
+        <v>46199.559805983794</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O22" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B22" s="5">
-        <v>46156.632133692125</v>
-      </c>
-      <c r="C22" s="5">
-        <v>46196.65766008102</v>
-      </c>
-      <c r="D22" s="5">
-        <v>46206.563520752316</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I22" s="5">
-        <v>46212</v>
-      </c>
-      <c r="J22" s="5">
-        <v>46213</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N22" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="O22" s="6" t="s">
-        <v>84</v>
-      </c>
       <c r="P22" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q22" s="5">
-        <v>46212</v>
-      </c>
-      <c r="R22" s="5">
-        <v>46213</v>
-      </c>
-      <c r="S22" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="T22" s="6">
-        <v>1</v>
-      </c>
-      <c r="U22" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B23" s="9">
-        <v>46156.6319605787</v>
+        <v>46156.63213814815</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46199.559805983794</v>
+        <v>46195.929228946756</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
+      <c r="I23" s="9">
+        <v>46154</v>
+      </c>
+      <c r="J23" s="9">
+        <v>46267</v>
+      </c>
       <c r="K23" s="10" t="s">
         <v>26</v>
       </c>
@@ -2804,51 +2778,63 @@
         <v>26</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>98</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10"/>
-      <c r="S23" s="10"/>
-      <c r="T23" s="10"/>
-      <c r="U23" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="Q23" s="9">
+        <v>46154</v>
+      </c>
+      <c r="R23" s="9">
+        <v>46267</v>
+      </c>
+      <c r="S23" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T23" s="10">
+        <v>0</v>
+      </c>
+      <c r="U23" s="12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B24" s="5">
-        <v>46156.63213814815</v>
-      </c>
-      <c r="C24" s="6"/>
+        <v>46156.63214259259</v>
+      </c>
+      <c r="C24" s="5">
+        <v>46195.92922075231</v>
+      </c>
       <c r="D24" s="5">
-        <v>46195.929228946756</v>
+        <v>46195.92922337963</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="I24" s="5">
         <v>46154</v>
       </c>
       <c r="J24" s="5">
-        <v>46267</v>
+        <v>46155</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>26</v>
@@ -2860,20 +2846,16 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q24" s="5">
-        <v>46154</v>
-      </c>
-      <c r="R24" s="5">
-        <v>46267</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
         <v>33</v>
       </c>
@@ -2881,57 +2863,55 @@
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" s="9">
+        <v>46156.63214717593</v>
+      </c>
+      <c r="C25" s="10"/>
+      <c r="D25" s="9">
+        <v>46195.92922835649</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I25" s="9">
+        <v>46156</v>
+      </c>
+      <c r="J25" s="9">
+        <v>46267</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="O25" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="P25" s="10" t="s">
         <v>105</v>
-      </c>
-      <c r="B25" s="9">
-        <v>46156.63214259259</v>
-      </c>
-      <c r="C25" s="9">
-        <v>46195.92922075231</v>
-      </c>
-      <c r="D25" s="9">
-        <v>46195.92922337963</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="I25" s="9">
-        <v>46154</v>
-      </c>
-      <c r="J25" s="9">
-        <v>46155</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N25" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="O25" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="P25" s="10" t="s">
-        <v>107</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -2942,37 +2922,37 @@
         <v>0</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46156.63214717593</v>
+        <v>46156.6321521412</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46195.92922835649</v>
+        <v>46169.86132256944</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="I26" s="5">
-        <v>46156</v>
+        <v>46150</v>
       </c>
       <c r="J26" s="5">
-        <v>46267</v>
+        <v>46153</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>26</v>
@@ -2984,16 +2964,20 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
+        <v>92</v>
+      </c>
+      <c r="Q26" s="5">
+        <v>46150</v>
+      </c>
+      <c r="R26" s="5">
+        <v>46153</v>
+      </c>
       <c r="S26" s="7" t="s">
         <v>33</v>
       </c>
@@ -3001,31 +2985,31 @@
         <v>0</v>
       </c>
       <c r="U26" s="12" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B27" s="9">
-        <v>46156.6321521412</v>
+        <v>46156.63215657407</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46169.86132256944</v>
+        <v>46197.502050625</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="I27" s="9">
         <v>46150</v>
@@ -3043,20 +3027,16 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q27" s="9">
-        <v>46150</v>
-      </c>
-      <c r="R27" s="9">
-        <v>46153</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
         <v>33</v>
       </c>
@@ -3064,31 +3044,31 @@
         <v>0</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46156.63215657407</v>
+        <v>46156.63216167824</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46197.502050625</v>
+        <v>46169.86172537037</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="I28" s="5">
         <v>46150</v>
@@ -3106,13 +3086,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3123,37 +3103,37 @@
         <v>0</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B29" s="9">
-        <v>46156.63216167824</v>
+        <v>46156.63216756945</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46169.86172537037</v>
+        <v>46197.783559131945</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="I29" s="9">
-        <v>46150</v>
+        <v>46142</v>
       </c>
       <c r="J29" s="9">
-        <v>46153</v>
+        <v>46293</v>
       </c>
       <c r="K29" s="10" t="s">
         <v>26</v>
@@ -3165,16 +3145,20 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="Q29" s="9">
+        <v>46172</v>
+      </c>
+      <c r="R29" s="9">
+        <v>46293</v>
+      </c>
       <c r="S29" s="7" t="s">
         <v>33</v>
       </c>
@@ -3182,37 +3166,39 @@
         <v>0</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
-        <v>46156.63216756945</v>
-      </c>
-      <c r="C30" s="6"/>
+        <v>46156.63217278935</v>
+      </c>
+      <c r="C30" s="5">
+        <v>46195.929570740744</v>
+      </c>
       <c r="D30" s="5">
-        <v>46197.783559131945</v>
+        <v>46195.92957241899</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="I30" s="5">
         <v>46142</v>
       </c>
       <c r="J30" s="5">
-        <v>46293</v>
+        <v>46162</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>26</v>
@@ -3224,20 +3210,16 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q30" s="5">
-        <v>46172</v>
-      </c>
-      <c r="R30" s="5">
-        <v>46293</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
         <v>33</v>
       </c>
@@ -3245,57 +3227,55 @@
         <v>0</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="9">
+        <v>46156.63217837963</v>
+      </c>
+      <c r="C31" s="10"/>
+      <c r="D31" s="9">
+        <v>46195.92957792824</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I31" s="9">
+        <v>46164</v>
+      </c>
+      <c r="J31" s="9">
+        <v>46293</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N31" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="O31" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="P31" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="B31" s="9">
-        <v>46156.63217278935</v>
-      </c>
-      <c r="C31" s="9">
-        <v>46195.929570740744</v>
-      </c>
-      <c r="D31" s="9">
-        <v>46195.92957241899</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="I31" s="9">
-        <v>46142</v>
-      </c>
-      <c r="J31" s="9">
-        <v>46162</v>
-      </c>
-      <c r="K31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N31" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="O31" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="P31" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3306,37 +3286,39 @@
         <v>0</v>
       </c>
       <c r="U31" s="12" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
-        <v>46156.63217837963</v>
-      </c>
-      <c r="C32" s="6"/>
+        <v>46156.63218368056</v>
+      </c>
+      <c r="C32" s="5">
+        <v>46197.78355179398</v>
+      </c>
       <c r="D32" s="5">
-        <v>46195.92957792824</v>
+        <v>46197.78355364583</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="I32" s="5">
         <v>46164</v>
       </c>
       <c r="J32" s="5">
-        <v>46293</v>
+        <v>46203</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>26</v>
@@ -3348,13 +3330,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3365,39 +3347,39 @@
         <v>0</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B33" s="9">
+        <v>46156.632188240736</v>
+      </c>
+      <c r="C33" s="9">
+        <v>46199.55979506944</v>
+      </c>
+      <c r="D33" s="9">
+        <v>46199.55980914352</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B33" s="9">
-        <v>46156.63218368056</v>
-      </c>
-      <c r="C33" s="9">
-        <v>46197.78355179398</v>
-      </c>
-      <c r="D33" s="9">
-        <v>46197.78355364583</v>
-      </c>
-      <c r="E33" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>102</v>
-      </c>
       <c r="I33" s="9">
-        <v>46164</v>
+        <v>46216</v>
       </c>
       <c r="J33" s="9">
-        <v>46203</v>
+        <v>46226</v>
       </c>
       <c r="K33" s="10" t="s">
         <v>26</v>
@@ -3409,24 +3391,28 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="Q33" s="9">
+        <v>46216</v>
+      </c>
+      <c r="R33" s="9">
+        <v>46226</v>
+      </c>
       <c r="S33" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T33" s="10">
-        <v>0</v>
-      </c>
-      <c r="U33" s="12" t="s">
-        <v>104</v>
+        <v>1</v>
+      </c>
+      <c r="U33" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3434,13 +3420,13 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46156.632188240736</v>
+        <v>46156.63219359954</v>
       </c>
       <c r="C34" s="5">
-        <v>46199.55979506944</v>
+        <v>46199.55916827546</v>
       </c>
       <c r="D34" s="5">
-        <v>46199.55980914352</v>
+        <v>46199.55917045139</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3449,16 +3435,16 @@
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I34" s="5">
         <v>46216</v>
       </c>
       <c r="J34" s="5">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>26</v>
@@ -3470,78 +3456,74 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q34" s="5">
-        <v>46216</v>
-      </c>
-      <c r="R34" s="5">
-        <v>46226</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T34" s="6">
-        <v>1</v>
-      </c>
-      <c r="U34" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U34" s="12" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B35" s="9">
+        <v>46156.63219844908</v>
+      </c>
+      <c r="C35" s="9">
+        <v>46199.55978109954</v>
+      </c>
+      <c r="D35" s="9">
+        <v>46199.5597825</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="I35" s="9">
+        <v>46218</v>
+      </c>
+      <c r="J35" s="9">
+        <v>46226</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="O35" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="P35" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="B35" s="9">
-        <v>46156.63219359954</v>
-      </c>
-      <c r="C35" s="9">
-        <v>46199.55916827546</v>
-      </c>
-      <c r="D35" s="9">
-        <v>46199.55917045139</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="I35" s="9">
-        <v>46216</v>
-      </c>
-      <c r="J35" s="9">
-        <v>46217</v>
-      </c>
-      <c r="K35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N35" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="O35" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="P35" s="10" t="s">
-        <v>139</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3552,36 +3534,36 @@
         <v>0</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
-        <v>46156.63219844908</v>
+        <v>46156.63225444444</v>
       </c>
       <c r="C36" s="5">
-        <v>46199.55978109954</v>
+        <v>46199.55997423611</v>
       </c>
       <c r="D36" s="5">
-        <v>46199.5597825</v>
+        <v>46199.55998701389</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I36" s="5">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="J36" s="5">
         <v>46226</v>
@@ -3596,56 +3578,60 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="Q36" s="5">
+        <v>46216</v>
+      </c>
+      <c r="R36" s="5">
+        <v>46226</v>
+      </c>
       <c r="S36" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T36" s="6">
-        <v>0</v>
-      </c>
-      <c r="U36" s="12" t="s">
-        <v>104</v>
+        <v>1</v>
+      </c>
+      <c r="U36" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46156.63225444444</v>
+        <v>46156.632258206024</v>
       </c>
       <c r="C37" s="9">
-        <v>46199.55997423611</v>
+        <v>46199.55990923611</v>
       </c>
       <c r="D37" s="9">
-        <v>46199.55998701389</v>
+        <v>46199.55991087963</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I37" s="9">
         <v>46216</v>
       </c>
       <c r="J37" s="9">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="K37" s="10" t="s">
         <v>26</v>
@@ -3657,60 +3643,50 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q37" s="9">
-        <v>46216</v>
-      </c>
-      <c r="R37" s="9">
-        <v>46226</v>
-      </c>
-      <c r="S37" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T37" s="10">
-        <v>1</v>
-      </c>
-      <c r="U37" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
+      <c r="U37" s="10"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
-        <v>46156.632258206024</v>
+        <v>46156.63226241898</v>
       </c>
       <c r="C38" s="5">
-        <v>46199.55990923611</v>
+        <v>46199.55995880787</v>
       </c>
       <c r="D38" s="5">
-        <v>46199.55991087963</v>
+        <v>46199.55996042824</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>89</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I38" s="5">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="J38" s="5">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>26</v>
@@ -3722,13 +3698,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3738,34 +3714,34 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B39" s="9">
+        <v>46156.63226644676</v>
+      </c>
+      <c r="C39" s="9">
+        <v>46204.87072556713</v>
+      </c>
+      <c r="D39" s="9">
+        <v>46204.87074320602</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B39" s="9">
-        <v>46156.63226241898</v>
-      </c>
-      <c r="C39" s="9">
-        <v>46199.55995880787</v>
-      </c>
-      <c r="D39" s="9">
-        <v>46199.55996042824</v>
-      </c>
-      <c r="E39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>135</v>
-      </c>
       <c r="I39" s="9">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="J39" s="9">
-        <v>46226</v>
+        <v>46254</v>
       </c>
       <c r="K39" s="10" t="s">
         <v>26</v>
@@ -3777,50 +3753,60 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>89</v>
+        <v>150</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="10"/>
-      <c r="S39" s="10"/>
-      <c r="T39" s="10"/>
-      <c r="U39" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="Q39" s="9">
+        <v>46216</v>
+      </c>
+      <c r="R39" s="9">
+        <v>46254</v>
+      </c>
+      <c r="S39" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T39" s="10">
+        <v>1</v>
+      </c>
+      <c r="U39" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46156.63226644676</v>
+        <v>46156.632269444446</v>
       </c>
       <c r="C40" s="5">
-        <v>46204.87072556713</v>
+        <v>46196.699784247685</v>
       </c>
       <c r="D40" s="5">
-        <v>46204.87074320602</v>
+        <v>46196.69978633102</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>152</v>
+        <v>90</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46216</v>
       </c>
       <c r="J40" s="5">
-        <v>46254</v>
+        <v>46224</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>26</v>
@@ -3832,60 +3818,50 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>155</v>
+        <v>89</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q40" s="5">
-        <v>46216</v>
-      </c>
-      <c r="R40" s="5">
-        <v>46254</v>
-      </c>
-      <c r="S40" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T40" s="6">
-        <v>1</v>
-      </c>
-      <c r="U40" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="Q40" s="6"/>
+      <c r="R40" s="6"/>
+      <c r="S40" s="6"/>
+      <c r="T40" s="6"/>
+      <c r="U40" s="6"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
-        <v>46156.632269444446</v>
+        <v>46156.63227357639</v>
       </c>
       <c r="C41" s="9">
-        <v>46196.699784247685</v>
+        <v>46204.86000005787</v>
       </c>
       <c r="D41" s="9">
-        <v>46196.69978633102</v>
+        <v>46204.86000238426</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="I41" s="9">
-        <v>46216</v>
+        <v>46225</v>
       </c>
       <c r="J41" s="9">
-        <v>46224</v>
+        <v>46253</v>
       </c>
       <c r="K41" s="10" t="s">
         <v>26</v>
@@ -3897,13 +3873,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3913,52 +3889,50 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B42" s="5">
+        <v>46156.63227760416</v>
+      </c>
+      <c r="C42" s="6"/>
+      <c r="D42" s="5">
+        <v>46204.86001229167</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="B42" s="5">
-        <v>46156.63227357639</v>
-      </c>
-      <c r="C42" s="5">
-        <v>46204.86000005787</v>
-      </c>
-      <c r="D42" s="5">
-        <v>46204.86000238426</v>
-      </c>
-      <c r="E42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="H42" s="6" t="s">
+      <c r="I42" s="5">
+        <v>46254</v>
+      </c>
+      <c r="J42" s="5">
+        <v>46254</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="O42" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="I42" s="5">
-        <v>46225</v>
-      </c>
-      <c r="J42" s="5">
-        <v>46253</v>
-      </c>
-      <c r="K42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N42" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O42" s="6" t="s">
-        <v>95</v>
-      </c>
       <c r="P42" s="6" t="s">
-        <v>160</v>
+        <v>26</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3968,87 +3942,99 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B43" s="9">
+        <v>46156.63228021991</v>
+      </c>
+      <c r="C43" s="9">
+        <v>46199.56230621527</v>
+      </c>
+      <c r="D43" s="9">
+        <v>46199.562315937495</v>
+      </c>
+      <c r="E43" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B43" s="9">
-        <v>46156.63227760416</v>
-      </c>
-      <c r="C43" s="10"/>
-      <c r="D43" s="9">
-        <v>46204.86001229167</v>
-      </c>
-      <c r="E43" s="10" t="s">
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="I43" s="9">
+        <v>46216</v>
+      </c>
+      <c r="J43" s="9">
+        <v>46226</v>
+      </c>
+      <c r="K43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="O43" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="I43" s="9">
-        <v>46254</v>
-      </c>
-      <c r="J43" s="9">
-        <v>46254</v>
-      </c>
-      <c r="K43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N43" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="O43" s="10" t="s">
-        <v>159</v>
-      </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="Q43" s="10"/>
-      <c r="R43" s="10"/>
-      <c r="S43" s="10"/>
-      <c r="T43" s="10"/>
-      <c r="U43" s="10"/>
+      <c r="Q43" s="9">
+        <v>46216</v>
+      </c>
+      <c r="R43" s="9">
+        <v>46226</v>
+      </c>
+      <c r="S43" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T43" s="10">
+        <v>1</v>
+      </c>
+      <c r="U43" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46156.63228021991</v>
+        <v>46156.63228315972</v>
       </c>
       <c r="C44" s="5">
-        <v>46199.56230621527</v>
+        <v>46199.562242835644</v>
       </c>
       <c r="D44" s="5">
-        <v>46199.562315937495</v>
+        <v>46199.56224427083</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>166</v>
+        <v>87</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I44" s="5">
         <v>46216</v>
       </c>
       <c r="J44" s="5">
-        <v>46226</v>
+        <v>46217</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>26</v>
@@ -4060,60 +4046,50 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>97</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>167</v>
+        <v>86</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q44" s="5">
-        <v>46216</v>
-      </c>
-      <c r="R44" s="5">
-        <v>46226</v>
-      </c>
-      <c r="S44" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T44" s="6">
-        <v>1</v>
-      </c>
-      <c r="U44" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Q44" s="6"/>
+      <c r="R44" s="6"/>
+      <c r="S44" s="6"/>
+      <c r="T44" s="6"/>
+      <c r="U44" s="6"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B45" s="9">
-        <v>46156.63228315972</v>
+        <v>46156.63228715278</v>
       </c>
       <c r="C45" s="9">
-        <v>46199.562242835644</v>
+        <v>46199.56229306713</v>
       </c>
       <c r="D45" s="9">
-        <v>46199.56224427083</v>
+        <v>46199.56229454861</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I45" s="9">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="J45" s="9">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="K45" s="10" t="s">
         <v>26</v>
@@ -4125,13 +4101,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4141,82 +4117,84 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B46" s="5">
+        <v>46156.63196493055</v>
+      </c>
+      <c r="C46" s="6"/>
+      <c r="D46" s="5">
+        <v>46184.58079096065</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O46" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="B46" s="5">
-        <v>46156.63228715278</v>
-      </c>
-      <c r="C46" s="5">
-        <v>46199.56229306713</v>
-      </c>
-      <c r="D46" s="5">
-        <v>46199.56229454861</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="I46" s="5">
-        <v>46218</v>
-      </c>
-      <c r="J46" s="5">
-        <v>46226</v>
-      </c>
-      <c r="K46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N46" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="O46" s="6" t="s">
-        <v>92</v>
-      </c>
       <c r="P46" s="6" t="s">
-        <v>172</v>
+        <v>26</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
+      <c r="U46" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B47" s="9">
+        <v>46156.63229164352</v>
+      </c>
+      <c r="C47" s="9">
+        <v>46184.58069681713</v>
+      </c>
+      <c r="D47" s="9">
+        <v>46197.714709479165</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="B47" s="9">
-        <v>46156.63196493055</v>
-      </c>
-      <c r="C47" s="10"/>
-      <c r="D47" s="9">
-        <v>46184.58079096065</v>
-      </c>
-      <c r="E47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
+      <c r="I47" s="9">
+        <v>46150</v>
+      </c>
+      <c r="J47" s="9">
+        <v>46156</v>
+      </c>
       <c r="K47" s="10" t="s">
         <v>26</v>
       </c>
@@ -4224,170 +4202,174 @@
         <v>26</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>26</v>
+        <v>169</v>
       </c>
       <c r="O47" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="P47" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="P47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q47" s="10"/>
-      <c r="R47" s="10"/>
-      <c r="S47" s="10"/>
-      <c r="T47" s="10"/>
-      <c r="U47" s="11" t="s">
-        <v>66</v>
+      <c r="Q47" s="9">
+        <v>46150</v>
+      </c>
+      <c r="R47" s="9">
+        <v>46156</v>
+      </c>
+      <c r="S47" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="T47" s="10">
+        <v>1</v>
+      </c>
+      <c r="U47" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
-        <v>46156.63229164352</v>
+        <v>46156.632296261574</v>
       </c>
       <c r="C48" s="5">
-        <v>46184.58069681713</v>
+        <v>46184.58077318287</v>
       </c>
       <c r="D48" s="5">
-        <v>46197.714709479165</v>
+        <v>46203.19706542824</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H48" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="I48" s="5">
+        <v>46204</v>
+      </c>
+      <c r="J48" s="5">
+        <v>46210</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="O48" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="I48" s="5">
-        <v>46150</v>
-      </c>
-      <c r="J48" s="5">
-        <v>46156</v>
-      </c>
-      <c r="K48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N48" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="O48" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>180</v>
       </c>
       <c r="Q48" s="5">
-        <v>46150</v>
+        <v>46204</v>
       </c>
       <c r="R48" s="5">
-        <v>46156</v>
-      </c>
-      <c r="S48" s="12" t="s">
-        <v>181</v>
+        <v>46210</v>
+      </c>
+      <c r="S48" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="T48" s="6">
         <v>1</v>
       </c>
-      <c r="U48" s="7" t="s">
-        <v>27</v>
+      <c r="U48" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B49" s="9">
+        <v>46156.63230224537</v>
+      </c>
+      <c r="C49" s="9">
+        <v>46184.58082519676</v>
+      </c>
+      <c r="D49" s="9">
+        <v>46204.18267401621</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B49" s="9">
-        <v>46156.632296261574</v>
-      </c>
-      <c r="C49" s="9">
-        <v>46184.58077318287</v>
-      </c>
-      <c r="D49" s="9">
-        <v>46203.19706542824</v>
-      </c>
-      <c r="E49" s="10" t="s">
+      <c r="H49" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="10" t="s">
+      <c r="I49" s="10"/>
+      <c r="J49" s="9">
+        <v>46211</v>
+      </c>
+      <c r="K49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N49" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="O49" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="H49" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I49" s="9">
-        <v>46204</v>
-      </c>
-      <c r="J49" s="9">
-        <v>46210</v>
-      </c>
-      <c r="K49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N49" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="O49" s="10" t="s">
+      <c r="P49" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="P49" s="10" t="s">
-        <v>185</v>
-      </c>
       <c r="Q49" s="9">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="R49" s="9">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>
       </c>
-      <c r="U49" s="11" t="s">
-        <v>66</v>
+      <c r="U49" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B50" s="5">
+        <v>46156.632315358795</v>
+      </c>
+      <c r="C50" s="6"/>
+      <c r="D50" s="5">
+        <v>46156.72589140046</v>
+      </c>
+      <c r="E50" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="B50" s="5">
-        <v>46156.63230224537</v>
-      </c>
-      <c r="C50" s="5">
-        <v>46184.58082519676</v>
-      </c>
-      <c r="D50" s="5">
-        <v>46204.18267401621</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4398,9 +4380,11 @@
       <c r="H50" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="I50" s="6"/>
+      <c r="I50" s="5">
+        <v>46301</v>
+      </c>
       <c r="J50" s="5">
-        <v>46211</v>
+        <v>46301</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>26</v>
@@ -4412,28 +4396,28 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="Q50" s="5">
-        <v>46211</v>
+        <v>46301</v>
       </c>
       <c r="R50" s="5">
-        <v>46211</v>
-      </c>
-      <c r="S50" s="11" t="s">
-        <v>86</v>
+        <v>46301</v>
+      </c>
+      <c r="S50" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T50" s="6">
-        <v>1</v>
-      </c>
-      <c r="U50" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U50" s="12" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4441,23 +4425,23 @@
         <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46156.632315358795</v>
+        <v>46156.6323189699</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46156.72589140046</v>
+        <v>46156.725962881945</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="I51" s="9">
         <v>46301</v>
@@ -4475,59 +4459,43 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q51" s="9">
-        <v>46301</v>
-      </c>
-      <c r="R51" s="9">
-        <v>46301</v>
-      </c>
-      <c r="S51" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T51" s="10">
-        <v>0</v>
-      </c>
-      <c r="U51" s="12" t="s">
-        <v>104</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="10"/>
+      <c r="T51" s="10"/>
+      <c r="U51" s="10"/>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
-        <v>46156.6323189699</v>
+        <v>46156.63233141204</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46156.725962881945</v>
+        <v>46156.70385697916</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>194</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="I52" s="5">
-        <v>46301</v>
-      </c>
-      <c r="J52" s="5">
-        <v>46301</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
       <c r="K52" s="6" t="s">
         <v>26</v>
       </c>
@@ -4535,16 +4503,16 @@
         <v>26</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>191</v>
+        <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>197</v>
+        <v>26</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4554,27 +4522,33 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B53" s="9">
-        <v>46156.63233141204</v>
+        <v>46156.63233460648</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46156.70385697916</v>
+        <v>46199.559799317125</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F53" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
+      <c r="I53" s="9">
+        <v>46227</v>
+      </c>
+      <c r="J53" s="9">
+        <v>46230</v>
+      </c>
       <c r="K53" s="10" t="s">
         <v>26</v>
       </c>
@@ -4582,33 +4556,43 @@
         <v>26</v>
       </c>
       <c r="M53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N53" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="O53" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="P53" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q53" s="9">
+        <v>46227</v>
+      </c>
+      <c r="R53" s="9">
+        <v>46230</v>
+      </c>
+      <c r="S53" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T53" s="10">
         <v>0</v>
       </c>
-      <c r="N53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O53" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="P53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q53" s="10"/>
-      <c r="R53" s="10"/>
-      <c r="S53" s="10"/>
-      <c r="T53" s="10"/>
-      <c r="U53" s="10"/>
+      <c r="U53" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>201</v>
       </c>
       <c r="B54" s="5">
-        <v>46156.63233460648</v>
+        <v>46156.63233969908</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46199.559799317125</v>
+        <v>46156.72612552083</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4617,40 +4601,40 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I54" s="5">
+        <v>46231</v>
+      </c>
+      <c r="J54" s="5">
+        <v>46232</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N54" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="O54" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="H54" s="6" t="s">
+      <c r="P54" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="I54" s="5">
-        <v>46227</v>
-      </c>
-      <c r="J54" s="5">
-        <v>46230</v>
-      </c>
-      <c r="K54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N54" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="O54" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>205</v>
-      </c>
       <c r="Q54" s="5">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="R54" s="5">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="S54" s="7" t="s">
         <v>33</v>
@@ -4658,62 +4642,62 @@
       <c r="T54" s="6">
         <v>0</v>
       </c>
-      <c r="U54" s="11" t="s">
-        <v>66</v>
+      <c r="U54" s="12" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B55" s="9">
-        <v>46156.63233969908</v>
+        <v>46156.632350671294</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46156.72612552083</v>
+        <v>46199.559976840275</v>
       </c>
       <c r="E55" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="I55" s="9">
+        <v>46227</v>
+      </c>
+      <c r="J55" s="9">
+        <v>46230</v>
+      </c>
+      <c r="K55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N55" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="O55" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="P55" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="F55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="I55" s="9">
-        <v>46231</v>
-      </c>
-      <c r="J55" s="9">
-        <v>46232</v>
-      </c>
-      <c r="K55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N55" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="O55" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="P55" s="10" t="s">
-        <v>209</v>
-      </c>
       <c r="Q55" s="9">
-        <v>46231</v>
+        <v>46227</v>
       </c>
       <c r="R55" s="9">
-        <v>46232</v>
+        <v>46230</v>
       </c>
       <c r="S55" s="7" t="s">
         <v>33</v>
@@ -4721,38 +4705,38 @@
       <c r="T55" s="10">
         <v>0</v>
       </c>
-      <c r="U55" s="12" t="s">
-        <v>104</v>
+      <c r="U55" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B56" s="5">
-        <v>46156.632350671294</v>
+        <v>46156.63235533565</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46199.559976840275</v>
+        <v>46156.72612251157</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>204</v>
+        <v>159</v>
       </c>
       <c r="I56" s="5">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="J56" s="5">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>26</v>
@@ -4764,19 +4748,19 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>149</v>
+        <v>206</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="Q56" s="5">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="R56" s="5">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="S56" s="7" t="s">
         <v>33</v>
@@ -4784,38 +4768,38 @@
       <c r="T56" s="6">
         <v>0</v>
       </c>
-      <c r="U56" s="11" t="s">
-        <v>66</v>
+      <c r="U56" s="12" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B57" s="9">
-        <v>46156.63235533565</v>
+        <v>46156.63235945602</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46156.72612251157</v>
+        <v>46199.56230880787</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="I57" s="9">
-        <v>46231</v>
+        <v>46227</v>
       </c>
       <c r="J57" s="9">
-        <v>46232</v>
+        <v>46230</v>
       </c>
       <c r="K57" s="10" t="s">
         <v>26</v>
@@ -4827,19 +4811,19 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>211</v>
+        <v>166</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="Q57" s="9">
-        <v>46231</v>
+        <v>46227</v>
       </c>
       <c r="R57" s="9">
-        <v>46232</v>
+        <v>46230</v>
       </c>
       <c r="S57" s="7" t="s">
         <v>33</v>
@@ -4847,38 +4831,38 @@
       <c r="T57" s="10">
         <v>0</v>
       </c>
-      <c r="U57" s="12" t="s">
-        <v>104</v>
+      <c r="U57" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
-        <v>46156.63235945602</v>
+        <v>46156.63236322917</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46199.56230880787</v>
+        <v>46156.72611966435</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>204</v>
+        <v>159</v>
       </c>
       <c r="I58" s="5">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="J58" s="5">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>26</v>
@@ -4890,19 +4874,19 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
       <c r="Q58" s="5">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="R58" s="5">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="S58" s="7" t="s">
         <v>33</v>
@@ -4910,39 +4894,33 @@
       <c r="T58" s="6">
         <v>0</v>
       </c>
-      <c r="U58" s="11" t="s">
-        <v>66</v>
+      <c r="U58" s="12" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B59" s="9">
-        <v>46156.63236322917</v>
+        <v>46156.63236744213</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46156.72611966435</v>
+        <v>46203.5014815162</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="I59" s="9">
-        <v>46231</v>
-      </c>
-      <c r="J59" s="9">
-        <v>46232</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H59" s="10"/>
+      <c r="I59" s="10"/>
+      <c r="J59" s="10"/>
       <c r="K59" s="10" t="s">
         <v>26</v>
       </c>
@@ -4950,56 +4928,54 @@
         <v>26</v>
       </c>
       <c r="M59" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>199</v>
+        <v>26</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>216</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q59" s="9">
-        <v>46231</v>
-      </c>
-      <c r="R59" s="9">
-        <v>46232</v>
-      </c>
-      <c r="S59" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T59" s="10">
-        <v>0</v>
-      </c>
-      <c r="U59" s="12" t="s">
-        <v>104</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="10"/>
+      <c r="S59" s="10"/>
+      <c r="T59" s="10"/>
+      <c r="U59" s="10"/>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B60" s="5">
+        <v>46156.63237008102</v>
+      </c>
+      <c r="C60" s="5">
+        <v>46203.50147394676</v>
+      </c>
+      <c r="D60" s="5">
+        <v>46203.50149189815</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="B60" s="5">
-        <v>46156.63236744213</v>
-      </c>
-      <c r="C60" s="6"/>
-      <c r="D60" s="5">
-        <v>46203.5014815162</v>
-      </c>
-      <c r="E60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
+      <c r="I60" s="5">
+        <v>46233</v>
+      </c>
+      <c r="J60" s="5">
+        <v>46241</v>
+      </c>
       <c r="K60" s="6" t="s">
         <v>26</v>
       </c>
@@ -5007,47 +4983,55 @@
         <v>26</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>26</v>
+        <v>215</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>221</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q60" s="6"/>
-      <c r="R60" s="6"/>
-      <c r="S60" s="6"/>
-      <c r="T60" s="6"/>
-      <c r="U60" s="6"/>
+        <v>215</v>
+      </c>
+      <c r="Q60" s="5">
+        <v>46233</v>
+      </c>
+      <c r="R60" s="5">
+        <v>46241</v>
+      </c>
+      <c r="S60" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T60" s="6">
+        <v>1</v>
+      </c>
+      <c r="U60" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
         <v>222</v>
       </c>
       <c r="B61" s="9">
-        <v>46156.63237008102</v>
-      </c>
-      <c r="C61" s="9">
-        <v>46203.50147394676</v>
-      </c>
+        <v>46156.63237584491</v>
+      </c>
+      <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46203.50149189815</v>
+        <v>46156.72624517361</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I61" s="9">
         <v>46233</v>
@@ -5065,58 +5049,48 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q61" s="9">
-        <v>46233</v>
-      </c>
-      <c r="R61" s="9">
-        <v>46241</v>
-      </c>
-      <c r="S61" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T61" s="10">
-        <v>1</v>
-      </c>
-      <c r="U61" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
+      <c r="S61" s="10"/>
+      <c r="T61" s="10"/>
+      <c r="U61" s="10"/>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46156.63237584491</v>
+        <v>46156.63239597222</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46156.72624517361</v>
+        <v>46205.904521226854</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I62" s="5">
-        <v>46233</v>
+        <v>46244</v>
       </c>
       <c r="J62" s="5">
-        <v>46241</v>
+        <v>46261</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>26</v>
@@ -5128,42 +5102,52 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="6"/>
-      <c r="S62" s="6"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
+        <v>215</v>
+      </c>
+      <c r="Q62" s="5">
+        <v>46244</v>
+      </c>
+      <c r="R62" s="5">
+        <v>46261</v>
+      </c>
+      <c r="S62" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T62" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="U62" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B63" s="9">
-        <v>46156.63239597222</v>
+        <v>46156.632400069444</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46205.904521226854</v>
+        <v>46184.58084231481</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5181,58 +5165,48 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q63" s="9">
-        <v>46244</v>
-      </c>
-      <c r="R63" s="9">
-        <v>46261</v>
-      </c>
-      <c r="S63" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T63" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="U63" s="11" t="s">
-        <v>66</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="Q63" s="10"/>
+      <c r="R63" s="10"/>
+      <c r="S63" s="10"/>
+      <c r="T63" s="10"/>
+      <c r="U63" s="10"/>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B64" s="5">
-        <v>46156.632400069444</v>
+        <v>46156.63246734954</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46184.58084231481</v>
+        <v>46197.83505042824</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>196</v>
+        <v>231</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>224</v>
+        <v>158</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>225</v>
+        <v>159</v>
       </c>
       <c r="I64" s="5">
-        <v>46244</v>
+        <v>46262</v>
       </c>
       <c r="J64" s="5">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>26</v>
@@ -5244,42 +5218,52 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q64" s="6"/>
-      <c r="R64" s="6"/>
-      <c r="S64" s="6"/>
-      <c r="T64" s="6"/>
-      <c r="U64" s="6"/>
+        <v>215</v>
+      </c>
+      <c r="Q64" s="5">
+        <v>46262</v>
+      </c>
+      <c r="R64" s="5">
+        <v>46265</v>
+      </c>
+      <c r="S64" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T64" s="6">
+        <v>0</v>
+      </c>
+      <c r="U64" s="12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B65" s="9">
-        <v>46156.63246734954</v>
+        <v>46156.632472627316</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46197.83505042824</v>
+        <v>46197.83511621528</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>236</v>
+        <v>191</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="I65" s="9">
         <v>46262</v>
@@ -5297,59 +5281,43 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q65" s="9">
-        <v>46262</v>
-      </c>
-      <c r="R65" s="9">
-        <v>46265</v>
-      </c>
-      <c r="S65" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T65" s="10">
-        <v>0</v>
-      </c>
-      <c r="U65" s="12" t="s">
-        <v>104</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
+      <c r="S65" s="10"/>
+      <c r="T65" s="10"/>
+      <c r="U65" s="10"/>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B66" s="5">
-        <v>46156.632472627316</v>
+        <v>46156.6324928588</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46197.83511621528</v>
+        <v>46156.71243400463</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="I66" s="5">
-        <v>46262</v>
-      </c>
-      <c r="J66" s="5">
-        <v>46265</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
       <c r="K66" s="6" t="s">
         <v>26</v>
       </c>
@@ -5357,16 +5325,16 @@
         <v>26</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>236</v>
+        <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>238</v>
+        <v>26</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5376,27 +5344,33 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B67" s="9">
-        <v>46156.6324928588</v>
+        <v>46156.63249635417</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46156.71243400463</v>
+        <v>46156.72645449074</v>
       </c>
       <c r="E67" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F67" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G67" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H67" s="10"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="10"/>
+      <c r="I67" s="9">
+        <v>46154</v>
+      </c>
+      <c r="J67" s="9">
+        <v>46155</v>
+      </c>
       <c r="K67" s="10" t="s">
         <v>26</v>
       </c>
@@ -5404,75 +5378,85 @@
         <v>26</v>
       </c>
       <c r="M67" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N67" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="O67" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="P67" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q67" s="9">
+        <v>46154</v>
+      </c>
+      <c r="R67" s="9">
+        <v>46155</v>
+      </c>
+      <c r="S67" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T67" s="10">
         <v>0</v>
       </c>
-      <c r="N67" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O67" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="P67" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q67" s="10"/>
-      <c r="R67" s="10"/>
-      <c r="S67" s="10"/>
-      <c r="T67" s="10"/>
-      <c r="U67" s="10"/>
+      <c r="U67" s="12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B68" s="5">
-        <v>46156.63249635417</v>
+        <v>46156.63250229167</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46156.72645449074</v>
+        <v>46156.726451689814</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="H68" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="I68" s="5">
+        <v>46268</v>
+      </c>
+      <c r="J68" s="5">
+        <v>46269</v>
+      </c>
+      <c r="K68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="O68" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="I68" s="5">
-        <v>46154</v>
-      </c>
-      <c r="J68" s="5">
-        <v>46155</v>
-      </c>
-      <c r="K68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N68" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="O68" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>209</v>
-      </c>
       <c r="Q68" s="5">
-        <v>46154</v>
+        <v>46268</v>
       </c>
       <c r="R68" s="5">
-        <v>46155</v>
+        <v>46269</v>
       </c>
       <c r="S68" s="7" t="s">
         <v>33</v>
@@ -5481,61 +5465,61 @@
         <v>0</v>
       </c>
       <c r="U68" s="12" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B69" s="9">
-        <v>46156.63250229167</v>
+        <v>46156.63250851852</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46156.726451689814</v>
+        <v>46156.726448877314</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="H69" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="I69" s="9">
+        <v>46294</v>
+      </c>
+      <c r="J69" s="9">
+        <v>46295</v>
+      </c>
+      <c r="K69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N69" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="O69" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="I69" s="9">
-        <v>46268</v>
-      </c>
-      <c r="J69" s="9">
-        <v>46269</v>
-      </c>
-      <c r="K69" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L69" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M69" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N69" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="O69" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="P69" s="10" t="s">
-        <v>209</v>
-      </c>
       <c r="Q69" s="9">
-        <v>46268</v>
+        <v>46294</v>
       </c>
       <c r="R69" s="9">
-        <v>46269</v>
+        <v>46295</v>
       </c>
       <c r="S69" s="7" t="s">
         <v>33</v>
@@ -5544,37 +5528,37 @@
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B70" s="5">
-        <v>46156.63250851852</v>
+        <v>46156.63251465278</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46156.726448877314</v>
+        <v>46204.86002143519</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="I70" s="5">
-        <v>46294</v>
+        <v>46255</v>
       </c>
       <c r="J70" s="5">
-        <v>46295</v>
+        <v>46258</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>26</v>
@@ -5586,19 +5570,19 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="Q70" s="5">
-        <v>46294</v>
+        <v>46255</v>
       </c>
       <c r="R70" s="5">
-        <v>46295</v>
+        <v>46258</v>
       </c>
       <c r="S70" s="7" t="s">
         <v>33</v>
@@ -5606,39 +5590,33 @@
       <c r="T70" s="6">
         <v>0</v>
       </c>
-      <c r="U70" s="12" t="s">
-        <v>104</v>
+      <c r="U70" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B71" s="9">
-        <v>46156.63251465278</v>
+        <v>46156.63251914352</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46204.86002143519</v>
+        <v>46156.71581511574</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="I71" s="9">
-        <v>46255</v>
-      </c>
-      <c r="J71" s="9">
-        <v>46258</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H71" s="10"/>
+      <c r="I71" s="10"/>
+      <c r="J71" s="10"/>
       <c r="K71" s="10" t="s">
         <v>26</v>
       </c>
@@ -5646,56 +5624,52 @@
         <v>26</v>
       </c>
       <c r="M71" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>199</v>
+        <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q71" s="9">
-        <v>46255</v>
-      </c>
-      <c r="R71" s="9">
-        <v>46258</v>
-      </c>
-      <c r="S71" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T71" s="10">
-        <v>0</v>
-      </c>
-      <c r="U71" s="11" t="s">
-        <v>66</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q71" s="10"/>
+      <c r="R71" s="10"/>
+      <c r="S71" s="10"/>
+      <c r="T71" s="10"/>
+      <c r="U71" s="10"/>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B72" s="5">
-        <v>46156.63251914352</v>
+        <v>46156.63252219907</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46156.71581511574</v>
+        <v>46156.72654819445</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="I72" s="5">
+        <v>46266</v>
+      </c>
+      <c r="J72" s="5">
+        <v>46287</v>
+      </c>
       <c r="K72" s="6" t="s">
         <v>26</v>
       </c>
@@ -5703,45 +5677,55 @@
         <v>26</v>
       </c>
       <c r="M72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N72" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="O72" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="P72" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q72" s="5">
+        <v>46266</v>
+      </c>
+      <c r="R72" s="5">
+        <v>46287</v>
+      </c>
+      <c r="S72" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T72" s="6">
         <v>0</v>
       </c>
-      <c r="N72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O72" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q72" s="6"/>
-      <c r="R72" s="6"/>
-      <c r="S72" s="6"/>
-      <c r="T72" s="6"/>
-      <c r="U72" s="6"/>
+      <c r="U72" s="12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B73" s="9">
-        <v>46156.63252219907</v>
+        <v>46156.63252934028</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46156.72654819445</v>
+        <v>46156.726576076384</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>254</v>
+        <v>191</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I73" s="9">
         <v>46266</v>
@@ -5759,58 +5743,48 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q73" s="9">
-        <v>46266</v>
-      </c>
-      <c r="R73" s="9">
-        <v>46287</v>
-      </c>
-      <c r="S73" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T73" s="10">
-        <v>0</v>
-      </c>
-      <c r="U73" s="12" t="s">
-        <v>104</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="10"/>
+      <c r="S73" s="10"/>
+      <c r="T73" s="10"/>
+      <c r="U73" s="10"/>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B74" s="5">
-        <v>46156.63252934028</v>
+        <v>46156.63254586805</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46156.726576076384</v>
+        <v>46156.72654520834</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>196</v>
+        <v>253</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I74" s="5">
-        <v>46266</v>
+        <v>46288</v>
       </c>
       <c r="J74" s="5">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>26</v>
@@ -5822,42 +5796,52 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>255</v>
+        <v>191</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q74" s="6"/>
-      <c r="R74" s="6"/>
-      <c r="S74" s="6"/>
-      <c r="T74" s="6"/>
-      <c r="U74" s="6"/>
+        <v>246</v>
+      </c>
+      <c r="Q74" s="5">
+        <v>46288</v>
+      </c>
+      <c r="R74" s="5">
+        <v>46289</v>
+      </c>
+      <c r="S74" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T74" s="6">
+        <v>0</v>
+      </c>
+      <c r="U74" s="12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B75" s="9">
-        <v>46156.63254586805</v>
+        <v>46156.63255047453</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46156.72654520834</v>
+        <v>46184.58084127315</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>258</v>
+        <v>191</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I75" s="9">
         <v>46288</v>
@@ -5875,58 +5859,48 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>196</v>
+        <v>255</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q75" s="9">
-        <v>46288</v>
-      </c>
-      <c r="R75" s="9">
-        <v>46289</v>
-      </c>
-      <c r="S75" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T75" s="10">
-        <v>0</v>
-      </c>
-      <c r="U75" s="12" t="s">
-        <v>104</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="Q75" s="10"/>
+      <c r="R75" s="10"/>
+      <c r="S75" s="10"/>
+      <c r="T75" s="10"/>
+      <c r="U75" s="10"/>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B76" s="5">
-        <v>46156.63255047453</v>
+        <v>46156.63257873843</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46184.58084127315</v>
+        <v>46156.726542372686</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>196</v>
+        <v>258</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I76" s="5">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="J76" s="5">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>26</v>
@@ -5938,42 +5912,52 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>260</v>
+        <v>191</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="6"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
+        <v>246</v>
+      </c>
+      <c r="Q76" s="5">
+        <v>46290</v>
+      </c>
+      <c r="R76" s="5">
+        <v>46293</v>
+      </c>
+      <c r="S76" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0</v>
+      </c>
+      <c r="U76" s="12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B77" s="9">
-        <v>46156.63257873843</v>
+        <v>46156.632582986116</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46156.726542372686</v>
+        <v>46184.58084195602</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>263</v>
+        <v>191</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I77" s="9">
         <v>46290</v>
@@ -5991,58 +5975,48 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>196</v>
+        <v>260</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q77" s="9">
-        <v>46290</v>
-      </c>
-      <c r="R77" s="9">
-        <v>46293</v>
-      </c>
-      <c r="S77" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T77" s="10">
-        <v>0</v>
-      </c>
-      <c r="U77" s="12" t="s">
-        <v>104</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="10"/>
+      <c r="S77" s="10"/>
+      <c r="T77" s="10"/>
+      <c r="U77" s="10"/>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B78" s="5">
-        <v>46156.632582986116</v>
+        <v>46156.632655671296</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46184.58084195602</v>
+        <v>46156.72653921296</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>196</v>
+        <v>262</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I78" s="5">
-        <v>46290</v>
+        <v>46296</v>
       </c>
       <c r="J78" s="5">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>26</v>
@@ -6054,42 +6028,52 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>265</v>
+        <v>191</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q78" s="6"/>
-      <c r="R78" s="6"/>
-      <c r="S78" s="6"/>
-      <c r="T78" s="6"/>
-      <c r="U78" s="6"/>
+        <v>246</v>
+      </c>
+      <c r="Q78" s="5">
+        <v>46296</v>
+      </c>
+      <c r="R78" s="5">
+        <v>46297</v>
+      </c>
+      <c r="S78" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T78" s="6">
+        <v>0</v>
+      </c>
+      <c r="U78" s="12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B79" s="9">
-        <v>46156.632655671296</v>
+        <v>46156.6326615162</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46156.72653921296</v>
+        <v>46184.58084310185</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>267</v>
+        <v>191</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I79" s="9">
         <v>46296</v>
@@ -6107,58 +6091,48 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>196</v>
+        <v>264</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q79" s="9">
-        <v>46296</v>
-      </c>
-      <c r="R79" s="9">
-        <v>46297</v>
-      </c>
-      <c r="S79" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T79" s="10">
-        <v>0</v>
-      </c>
-      <c r="U79" s="12" t="s">
-        <v>104</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="10"/>
+      <c r="S79" s="10"/>
+      <c r="T79" s="10"/>
+      <c r="U79" s="10"/>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B80" s="5">
-        <v>46156.6326615162</v>
+        <v>46156.6326856713</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46184.58084310185</v>
+        <v>46156.72653572916</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>196</v>
+        <v>267</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I80" s="5">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="J80" s="5">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>26</v>
@@ -6170,42 +6144,52 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>269</v>
+        <v>191</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q80" s="6"/>
-      <c r="R80" s="6"/>
-      <c r="S80" s="6"/>
-      <c r="T80" s="6"/>
-      <c r="U80" s="6"/>
+        <v>246</v>
+      </c>
+      <c r="Q80" s="5">
+        <v>46300</v>
+      </c>
+      <c r="R80" s="5">
+        <v>46300</v>
+      </c>
+      <c r="S80" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T80" s="6">
+        <v>0</v>
+      </c>
+      <c r="U80" s="12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B81" s="9">
-        <v>46156.6326856713</v>
+        <v>46156.63269413194</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46156.72653572916</v>
+        <v>46156.72676160879</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>272</v>
+        <v>191</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I81" s="9">
         <v>46300</v>
@@ -6223,58 +6207,48 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q81" s="9">
-        <v>46300</v>
-      </c>
-      <c r="R81" s="9">
-        <v>46300</v>
-      </c>
-      <c r="S81" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T81" s="10">
-        <v>0</v>
-      </c>
-      <c r="U81" s="12" t="s">
-        <v>104</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="Q81" s="10"/>
+      <c r="R81" s="10"/>
+      <c r="S81" s="10"/>
+      <c r="T81" s="10"/>
+      <c r="U81" s="10"/>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B82" s="5">
-        <v>46156.63269413194</v>
+        <v>46156.632715810185</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46156.72676160879</v>
+        <v>46156.726531747685</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>196</v>
+        <v>271</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I82" s="5">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="J82" s="5">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>26</v>
@@ -6286,42 +6260,52 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="O82" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q82" s="6"/>
-      <c r="R82" s="6"/>
-      <c r="S82" s="6"/>
-      <c r="T82" s="6"/>
-      <c r="U82" s="6"/>
+      <c r="Q82" s="5">
+        <v>46302</v>
+      </c>
+      <c r="R82" s="5">
+        <v>46302</v>
+      </c>
+      <c r="S82" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T82" s="6">
+        <v>0</v>
+      </c>
+      <c r="U82" s="12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B83" s="9">
-        <v>46156.632715810185</v>
+        <v>46156.63272170139</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46156.726531747685</v>
+        <v>46156.72680289352</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>276</v>
+        <v>191</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I83" s="9">
         <v>46302</v>
@@ -6339,59 +6323,43 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q83" s="9">
-        <v>46302</v>
-      </c>
-      <c r="R83" s="9">
-        <v>46302</v>
-      </c>
-      <c r="S83" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T83" s="10">
-        <v>0</v>
-      </c>
-      <c r="U83" s="12" t="s">
-        <v>104</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="Q83" s="10"/>
+      <c r="R83" s="10"/>
+      <c r="S83" s="10"/>
+      <c r="T83" s="10"/>
+      <c r="U83" s="10"/>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B84" s="5">
-        <v>46156.63272170139</v>
+        <v>46156.63273993056</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46156.72680289352</v>
+        <v>46205.90465030093</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>196</v>
+        <v>276</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I84" s="5">
-        <v>46302</v>
-      </c>
-      <c r="J84" s="5">
-        <v>46302</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H84" s="6"/>
+      <c r="I84" s="6"/>
+      <c r="J84" s="6"/>
       <c r="K84" s="6" t="s">
         <v>26</v>
       </c>
@@ -6399,16 +6367,16 @@
         <v>26</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>276</v>
+        <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>194</v>
+        <v>277</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>279</v>
+        <v>26</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6418,27 +6386,33 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B85" s="9">
-        <v>46156.63273993056</v>
+        <v>46156.63274356481</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46205.90465030093</v>
+        <v>46156.7268765162</v>
       </c>
       <c r="E85" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="F85" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H85" s="10"/>
-      <c r="I85" s="10"/>
-      <c r="J85" s="10"/>
+      <c r="I85" s="9">
+        <v>46303</v>
+      </c>
+      <c r="J85" s="9">
+        <v>46303</v>
+      </c>
       <c r="K85" s="10" t="s">
         <v>26</v>
       </c>
@@ -6446,45 +6420,55 @@
         <v>26</v>
       </c>
       <c r="M85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N85" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="O85" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="P85" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q85" s="9">
+        <v>46303</v>
+      </c>
+      <c r="R85" s="9">
+        <v>46303</v>
+      </c>
+      <c r="S85" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T85" s="10">
         <v>0</v>
       </c>
-      <c r="N85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O85" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="P85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q85" s="10"/>
-      <c r="R85" s="10"/>
-      <c r="S85" s="10"/>
-      <c r="T85" s="10"/>
-      <c r="U85" s="10"/>
+      <c r="U85" s="12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B86" s="5">
-        <v>46156.63274356481</v>
+        <v>46156.63274915509</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46156.7268765162</v>
+        <v>46156.72692035879</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>284</v>
+        <v>191</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="I86" s="5">
         <v>46303</v>
@@ -6502,58 +6486,46 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>279</v>
+        <v>191</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q86" s="5">
-        <v>46303</v>
-      </c>
-      <c r="R86" s="5">
-        <v>46303</v>
-      </c>
-      <c r="S86" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T86" s="6">
-        <v>0</v>
-      </c>
-      <c r="U86" s="12" t="s">
-        <v>104</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="Q86" s="6"/>
+      <c r="R86" s="6"/>
+      <c r="S86" s="6"/>
+      <c r="T86" s="6"/>
+      <c r="U86" s="6"/>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B87" s="9">
-        <v>46156.63274915509</v>
+        <v>46156.63276633102</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46156.72692035879</v>
+        <v>46156.72700125</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>196</v>
+        <v>285</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>285</v>
+        <v>73</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="I87" s="9">
-        <v>46303</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="I87" s="10"/>
       <c r="J87" s="9">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="K87" s="10" t="s">
         <v>26</v>
@@ -6565,44 +6537,56 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q87" s="10"/>
-      <c r="R87" s="10"/>
-      <c r="S87" s="10"/>
-      <c r="T87" s="10"/>
-      <c r="U87" s="10"/>
+        <v>276</v>
+      </c>
+      <c r="Q87" s="9">
+        <v>46304</v>
+      </c>
+      <c r="R87" s="9">
+        <v>46304</v>
+      </c>
+      <c r="S87" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T87" s="10">
+        <v>0</v>
+      </c>
+      <c r="U87" s="12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B88" s="5">
-        <v>46156.63276633102</v>
+        <v>46156.63277084491</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46156.72700125</v>
+        <v>46156.72697212963</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>290</v>
+        <v>191</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I88" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="I88" s="5">
+        <v>46304</v>
+      </c>
       <c r="J88" s="5">
         <v>46304</v>
       </c>
@@ -6616,58 +6600,50 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q88" s="5">
-        <v>46304</v>
-      </c>
-      <c r="R88" s="5">
-        <v>46304</v>
-      </c>
-      <c r="S88" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T88" s="6">
-        <v>0</v>
-      </c>
-      <c r="U88" s="12" t="s">
-        <v>104</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="Q88" s="6"/>
+      <c r="R88" s="6"/>
+      <c r="S88" s="6"/>
+      <c r="T88" s="6"/>
+      <c r="U88" s="6"/>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B89" s="9">
-        <v>46156.63277084491</v>
-      </c>
-      <c r="C89" s="10"/>
+        <v>46156.63283398148</v>
+      </c>
+      <c r="C89" s="9">
+        <v>46205.90464569445</v>
+      </c>
       <c r="D89" s="9">
-        <v>46156.72697212963</v>
+        <v>46205.904737627316</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>196</v>
+        <v>289</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>78</v>
+        <v>220</v>
       </c>
       <c r="I89" s="9">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="J89" s="9">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="K89" s="10" t="s">
         <v>26</v>
@@ -6679,44 +6655,54 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q89" s="10"/>
-      <c r="R89" s="10"/>
-      <c r="S89" s="10"/>
-      <c r="T89" s="10"/>
-      <c r="U89" s="10"/>
+        <v>276</v>
+      </c>
+      <c r="Q89" s="9">
+        <v>46307</v>
+      </c>
+      <c r="R89" s="9">
+        <v>46307</v>
+      </c>
+      <c r="S89" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T89" s="10">
+        <v>1</v>
+      </c>
+      <c r="U89" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B90" s="5">
-        <v>46156.63283398148</v>
+        <v>46156.63284013889</v>
       </c>
       <c r="C90" s="5">
-        <v>46205.90464569445</v>
+        <v>46205.90471993056</v>
       </c>
       <c r="D90" s="5">
-        <v>46205.904737627316</v>
+        <v>46205.90481071759</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>294</v>
+        <v>191</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I90" s="5">
         <v>46307</v>
@@ -6734,60 +6720,48 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q90" s="5">
-        <v>46307</v>
-      </c>
-      <c r="R90" s="5">
-        <v>46307</v>
-      </c>
-      <c r="S90" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T90" s="6">
-        <v>1</v>
-      </c>
-      <c r="U90" s="11" t="s">
-        <v>66</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="Q90" s="6"/>
+      <c r="R90" s="6"/>
+      <c r="S90" s="6"/>
+      <c r="T90" s="6"/>
+      <c r="U90" s="6"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B91" s="9">
-        <v>46156.63284013889</v>
-      </c>
-      <c r="C91" s="9">
-        <v>46205.90471993056</v>
-      </c>
+        <v>46156.63286864583</v>
+      </c>
+      <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46205.90481071759</v>
+        <v>46156.727220243054</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>196</v>
+        <v>293</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I91" s="9">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="J91" s="9">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="K91" s="10" t="s">
         <v>26</v>
@@ -6799,46 +6773,54 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="O91" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="P91" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="O91" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="P91" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="Q91" s="10"/>
-      <c r="R91" s="10"/>
-      <c r="S91" s="10"/>
-      <c r="T91" s="10"/>
-      <c r="U91" s="10"/>
+      <c r="Q91" s="9">
+        <v>46308</v>
+      </c>
+      <c r="R91" s="9">
+        <v>46308</v>
+      </c>
+      <c r="S91" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T91" s="10">
+        <v>0</v>
+      </c>
+      <c r="U91" s="12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B92" s="5">
-        <v>46156.63286864583</v>
+        <v>46156.632875972224</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46156.727220243054</v>
+        <v>46205.9047287037</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>298</v>
+        <v>191</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="I92" s="5">
-        <v>46308</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="I92" s="6"/>
       <c r="J92" s="5">
         <v>46308</v>
       </c>
@@ -6852,57 +6834,43 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q92" s="5">
-        <v>46308</v>
-      </c>
-      <c r="R92" s="5">
-        <v>46308</v>
-      </c>
-      <c r="S92" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T92" s="6">
-        <v>0</v>
-      </c>
-      <c r="U92" s="12" t="s">
-        <v>104</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="Q92" s="6"/>
+      <c r="R92" s="6"/>
+      <c r="S92" s="6"/>
+      <c r="T92" s="6"/>
+      <c r="U92" s="6"/>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B93" s="9">
-        <v>46156.632875972224</v>
+        <v>46156.63290420139</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46205.9047287037</v>
+        <v>46156.71731457176</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>196</v>
+        <v>297</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>225</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H93" s="10"/>
       <c r="I93" s="10"/>
-      <c r="J93" s="9">
-        <v>46308</v>
-      </c>
+      <c r="J93" s="10"/>
       <c r="K93" s="10" t="s">
         <v>26</v>
       </c>
@@ -6910,16 +6878,16 @@
         <v>26</v>
       </c>
       <c r="M93" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N93" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O93" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="O93" s="10" t="s">
-        <v>196</v>
-      </c>
       <c r="P93" s="10" t="s">
-        <v>298</v>
+        <v>26</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6929,27 +6897,33 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B94" s="5">
-        <v>46156.63290420139</v>
+        <v>46156.63290788194</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46156.71731457176</v>
+        <v>46156.72728918982</v>
       </c>
       <c r="E94" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="F94" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
-      <c r="J94" s="6"/>
+      <c r="I94" s="5">
+        <v>46309</v>
+      </c>
+      <c r="J94" s="5">
+        <v>46317</v>
+      </c>
       <c r="K94" s="6" t="s">
         <v>26</v>
       </c>
@@ -6957,45 +6931,55 @@
         <v>26</v>
       </c>
       <c r="M94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N94" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="O94" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="P94" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q94" s="5">
+        <v>46309</v>
+      </c>
+      <c r="R94" s="5">
+        <v>46317</v>
+      </c>
+      <c r="S94" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T94" s="6">
         <v>0</v>
       </c>
-      <c r="N94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O94" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q94" s="6"/>
-      <c r="R94" s="6"/>
-      <c r="S94" s="6"/>
-      <c r="T94" s="6"/>
-      <c r="U94" s="6"/>
+      <c r="U94" s="12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B95" s="9">
-        <v>46156.63290788194</v>
+        <v>46156.63291414352</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46156.72728918982</v>
+        <v>46209.559051539356</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>306</v>
+        <v>51</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>307</v>
+        <v>52</v>
       </c>
       <c r="I95" s="9">
         <v>46309</v>
@@ -7013,13 +6997,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="Q95" s="9">
         <v>46309</v>
@@ -7034,70 +7018,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A96" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B96" s="5">
-        <v>46156.63291414352</v>
-      </c>
-      <c r="C96" s="6"/>
-      <c r="D96" s="5">
-        <v>46156.727343402774</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G96" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="I96" s="5">
-        <v>46309</v>
-      </c>
-      <c r="J96" s="5">
-        <v>46317</v>
-      </c>
-      <c r="K96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N96" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="O96" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="Q96" s="5">
-        <v>46309</v>
-      </c>
-      <c r="R96" s="5">
-        <v>46317</v>
-      </c>
-      <c r="S96" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T96" s="6">
-        <v>0</v>
-      </c>
-      <c r="U96" s="12" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="305">
   <si>
     <t>50001547 - XEMORTIZ (AMERICAS GOLD)</t>
   </si>
@@ -338,16 +338,16 @@
     <t>Fabricación Alabe OT 4317,Generación OC Alabe OT 4317</t>
   </si>
   <si>
+    <t>1214809660726272</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Alabe OT 4317,Alabe OT 4317 </t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214809660726272</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Alabe OT 4317,Alabe OT 4317 </t>
   </si>
   <si>
     <t>1214809612445357</t>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46199.559805983794</v>
+        <v>46210.64699083334</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -2740,7 +2740,9 @@
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
       <c r="T22" s="6"/>
-      <c r="U22" s="6"/>
+      <c r="U22" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
@@ -2749,9 +2751,11 @@
       <c r="B23" s="9">
         <v>46156.63213814815</v>
       </c>
-      <c r="C23" s="10"/>
+      <c r="C23" s="9">
+        <v>46210.646711388894</v>
+      </c>
       <c r="D23" s="9">
-        <v>46195.929228946756</v>
+        <v>46210.6467582176</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>95</v>
@@ -2799,15 +2803,15 @@
         <v>33</v>
       </c>
       <c r="T23" s="10">
-        <v>0</v>
-      </c>
-      <c r="U23" s="12" t="s">
-        <v>99</v>
+        <v>1</v>
+      </c>
+      <c r="U23" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B24" s="5">
         <v>46156.63214259259</v>
@@ -2819,7 +2823,7 @@
         <v>46195.92922337963</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2852,7 +2856,7 @@
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2863,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -2873,9 +2877,11 @@
       <c r="B25" s="9">
         <v>46156.63214717593</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="9">
+        <v>46210.646694560186</v>
+      </c>
       <c r="D25" s="9">
-        <v>46195.92922835649</v>
+        <v>46210.64669667824</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>104</v>
@@ -2908,7 +2914,7 @@
         <v>95</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>105</v>
@@ -2922,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -2932,9 +2938,11 @@
       <c r="B26" s="5">
         <v>46156.6321521412</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="5">
+        <v>46210.64696896991</v>
+      </c>
       <c r="D26" s="5">
-        <v>46169.86132256944</v>
+        <v>46210.64698900463</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -2982,10 +2990,10 @@
         <v>33</v>
       </c>
       <c r="T26" s="6">
-        <v>0</v>
-      </c>
-      <c r="U26" s="12" t="s">
-        <v>99</v>
+        <v>1</v>
+      </c>
+      <c r="U26" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -2995,9 +3003,11 @@
       <c r="B27" s="9">
         <v>46156.63215657407</v>
       </c>
-      <c r="C27" s="10"/>
+      <c r="C27" s="9">
+        <v>46210.646919618055</v>
+      </c>
       <c r="D27" s="9">
-        <v>46197.502050625</v>
+        <v>46210.64692099537</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3044,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3054,9 +3064,11 @@
       <c r="B28" s="5">
         <v>46156.63216167824</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="5">
+        <v>46210.64695491898</v>
+      </c>
       <c r="D28" s="5">
-        <v>46169.86172537037</v>
+        <v>46210.64695642361</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3103,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3113,9 +3125,11 @@
       <c r="B29" s="9">
         <v>46156.63216756945</v>
       </c>
-      <c r="C29" s="10"/>
+      <c r="C29" s="9">
+        <v>46210.645546747684</v>
+      </c>
       <c r="D29" s="9">
-        <v>46197.783559131945</v>
+        <v>46210.645560289355</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3163,10 +3177,10 @@
         <v>33</v>
       </c>
       <c r="T29" s="10">
-        <v>0</v>
-      </c>
-      <c r="U29" s="12" t="s">
-        <v>99</v>
+        <v>1</v>
+      </c>
+      <c r="U29" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3227,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3237,9 +3251,11 @@
       <c r="B31" s="9">
         <v>46156.63217837963</v>
       </c>
-      <c r="C31" s="10"/>
+      <c r="C31" s="9">
+        <v>46210.64553108797</v>
+      </c>
       <c r="D31" s="9">
-        <v>46195.92957792824</v>
+        <v>46210.64553332176</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>122</v>
@@ -3286,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="U31" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3347,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3473,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3534,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3723,7 +3739,7 @@
         <v>46204.87072556713</v>
       </c>
       <c r="D39" s="9">
-        <v>46204.87074320602</v>
+        <v>46210.649648715276</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>147</v>
@@ -3894,9 +3910,11 @@
       <c r="B42" s="5">
         <v>46156.63227760416</v>
       </c>
-      <c r="C42" s="6"/>
+      <c r="C42" s="5">
+        <v>46210.649582847225</v>
+      </c>
       <c r="D42" s="5">
-        <v>46204.86001229167</v>
+        <v>46210.64958435185</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -4417,7 +4435,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4480,9 +4498,11 @@
       <c r="B52" s="5">
         <v>46156.63233141204</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="5">
+        <v>46210.64939368056</v>
+      </c>
       <c r="D52" s="5">
-        <v>46156.70385697916</v>
+        <v>46210.64940796296</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>194</v>
@@ -4517,8 +4537,12 @@
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
       <c r="S52" s="6"/>
-      <c r="T52" s="6"/>
-      <c r="U52" s="6"/>
+      <c r="T52" s="6">
+        <v>1</v>
+      </c>
+      <c r="U52" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
@@ -4527,9 +4551,11 @@
       <c r="B53" s="9">
         <v>46156.63233460648</v>
       </c>
-      <c r="C53" s="10"/>
+      <c r="C53" s="9">
+        <v>46210.648792141204</v>
+      </c>
       <c r="D53" s="9">
-        <v>46199.559799317125</v>
+        <v>46210.64881278935</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>197</v>
@@ -4577,10 +4603,10 @@
         <v>33</v>
       </c>
       <c r="T53" s="10">
-        <v>0</v>
-      </c>
-      <c r="U53" s="11" t="s">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="U53" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4590,9 +4616,11 @@
       <c r="B54" s="5">
         <v>46156.63233969908</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46210.64935451389</v>
+      </c>
       <c r="D54" s="5">
-        <v>46156.72612552083</v>
+        <v>46210.649371875</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4640,10 +4668,10 @@
         <v>33</v>
       </c>
       <c r="T54" s="6">
-        <v>0</v>
-      </c>
-      <c r="U54" s="12" t="s">
-        <v>99</v>
+        <v>1</v>
+      </c>
+      <c r="U54" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4653,9 +4681,11 @@
       <c r="B55" s="9">
         <v>46156.632350671294</v>
       </c>
-      <c r="C55" s="10"/>
+      <c r="C55" s="9">
+        <v>46210.64880347222</v>
+      </c>
       <c r="D55" s="9">
-        <v>46199.559976840275</v>
+        <v>46210.64881809028</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>206</v>
@@ -4703,10 +4733,10 @@
         <v>33</v>
       </c>
       <c r="T55" s="10">
-        <v>0</v>
-      </c>
-      <c r="U55" s="11" t="s">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="U55" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4716,9 +4746,11 @@
       <c r="B56" s="5">
         <v>46156.63235533565</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46210.64936773149</v>
+      </c>
       <c r="D56" s="5">
-        <v>46156.72612251157</v>
+        <v>46210.64938440973</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>209</v>
@@ -4766,10 +4798,10 @@
         <v>33</v>
       </c>
       <c r="T56" s="6">
-        <v>0</v>
-      </c>
-      <c r="U56" s="12" t="s">
-        <v>99</v>
+        <v>1</v>
+      </c>
+      <c r="U56" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4779,9 +4811,11 @@
       <c r="B57" s="9">
         <v>46156.63235945602</v>
       </c>
-      <c r="C57" s="10"/>
+      <c r="C57" s="9">
+        <v>46210.648815740744</v>
+      </c>
       <c r="D57" s="9">
-        <v>46199.56230880787</v>
+        <v>46210.648830949074</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>211</v>
@@ -4829,10 +4863,10 @@
         <v>33</v>
       </c>
       <c r="T57" s="10">
-        <v>0</v>
-      </c>
-      <c r="U57" s="11" t="s">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="U57" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4842,9 +4876,11 @@
       <c r="B58" s="5">
         <v>46156.63236322917</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46210.64937866898</v>
+      </c>
       <c r="D58" s="5">
-        <v>46156.72611966435</v>
+        <v>46210.64939421296</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>212</v>
@@ -4892,10 +4928,10 @@
         <v>33</v>
       </c>
       <c r="T58" s="6">
-        <v>0</v>
-      </c>
-      <c r="U58" s="12" t="s">
-        <v>99</v>
+        <v>1</v>
+      </c>
+      <c r="U58" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5019,7 +5055,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46156.72624517361</v>
+        <v>46210.64938539352</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>191</v>
@@ -5072,7 +5108,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46205.904521226854</v>
+        <v>46210.650037060186</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5239,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5304,7 +5340,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46156.71243400463</v>
+        <v>46210.64710428241</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>194</v>
@@ -5340,7 +5376,9 @@
       <c r="R66" s="6"/>
       <c r="S66" s="6"/>
       <c r="T66" s="6"/>
-      <c r="U66" s="6"/>
+      <c r="U66" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
@@ -5349,9 +5387,11 @@
       <c r="B67" s="9">
         <v>46156.63249635417</v>
       </c>
-      <c r="C67" s="10"/>
+      <c r="C67" s="9">
+        <v>46210.64707274306</v>
+      </c>
       <c r="D67" s="9">
-        <v>46156.72645449074</v>
+        <v>46210.64718186343</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>237</v>
@@ -5399,10 +5439,10 @@
         <v>33</v>
       </c>
       <c r="T67" s="10">
-        <v>0</v>
-      </c>
-      <c r="U67" s="12" t="s">
-        <v>99</v>
+        <v>1</v>
+      </c>
+      <c r="U67" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5412,9 +5452,11 @@
       <c r="B68" s="5">
         <v>46156.63250229167</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46210.647080740746</v>
+      </c>
       <c r="D68" s="5">
-        <v>46156.726451689814</v>
+        <v>46210.64712949074</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>239</v>
@@ -5462,10 +5504,10 @@
         <v>33</v>
       </c>
       <c r="T68" s="6">
-        <v>0</v>
-      </c>
-      <c r="U68" s="12" t="s">
-        <v>99</v>
+        <v>1</v>
+      </c>
+      <c r="U68" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5475,9 +5517,11 @@
       <c r="B69" s="9">
         <v>46156.63250851852</v>
       </c>
-      <c r="C69" s="10"/>
+      <c r="C69" s="9">
+        <v>46210.64568954861</v>
+      </c>
       <c r="D69" s="9">
-        <v>46156.726448877314</v>
+        <v>46210.645706863426</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>241</v>
@@ -5525,10 +5569,10 @@
         <v>33</v>
       </c>
       <c r="T69" s="10">
-        <v>0</v>
-      </c>
-      <c r="U69" s="12" t="s">
-        <v>99</v>
+        <v>1</v>
+      </c>
+      <c r="U69" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5701,7 +5745,7 @@
         <v>0</v>
       </c>
       <c r="U72" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5817,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="U74" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5829,7 +5873,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46184.58084127315</v>
+        <v>46210.647096342596</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>191</v>
@@ -5933,7 +5977,7 @@
         <v>0</v>
       </c>
       <c r="U76" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -5945,7 +5989,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46184.58084195602</v>
+        <v>46210.64708005787</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>191</v>
@@ -6049,7 +6093,7 @@
         <v>0</v>
       </c>
       <c r="U78" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6061,7 +6105,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46184.58084310185</v>
+        <v>46210.645696875</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>191</v>
@@ -6165,7 +6209,7 @@
         <v>0</v>
       </c>
       <c r="U80" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6281,7 +6325,7 @@
         <v>0</v>
       </c>
       <c r="U82" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6444,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="U85" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6558,7 +6602,7 @@
         <v>0</v>
       </c>
       <c r="U87" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -6794,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="U91" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6955,7 +6999,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7018,7 +7062,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -4258,7 +4258,7 @@
         <v>46184.58077318287</v>
       </c>
       <c r="D48" s="5">
-        <v>46203.19706542824</v>
+        <v>46211.19501542824</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4302,8 +4302,8 @@
       <c r="R48" s="5">
         <v>46210</v>
       </c>
-      <c r="S48" s="11" t="s">
-        <v>81</v>
+      <c r="S48" s="12" t="s">
+        <v>176</v>
       </c>
       <c r="T48" s="6">
         <v>1</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -5108,7 +5108,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46210.650037060186</v>
+        <v>46211.65705916667</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -4992,7 +4992,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46203.50149189815</v>
+        <v>46211.68096902777</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>218</v>
@@ -5053,9 +5053,11 @@
       <c r="B61" s="9">
         <v>46156.63237584491</v>
       </c>
-      <c r="C61" s="10"/>
+      <c r="C61" s="9">
+        <v>46211.68096327546</v>
+      </c>
       <c r="D61" s="9">
-        <v>46210.64938539352</v>
+        <v>46211.68096520833</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>191</v>
@@ -5171,7 +5173,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46184.58084231481</v>
+        <v>46211.68097021991</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>191</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -4323,7 +4323,7 @@
         <v>46184.58082519676</v>
       </c>
       <c r="D49" s="9">
-        <v>46204.18267401621</v>
+        <v>46212.1877253125</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>79</v>
@@ -4365,8 +4365,8 @@
       <c r="R49" s="9">
         <v>46211</v>
       </c>
-      <c r="S49" s="11" t="s">
-        <v>81</v>
+      <c r="S49" s="12" t="s">
+        <v>176</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -179,9 +179,6 @@
     <t>Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
     <t>1214809660705231</t>
   </si>
   <si>
@@ -552,6 +549,9 @@
   </si>
   <si>
     <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214809534019503</t>
@@ -1950,9 +1950,11 @@
       <c r="B10" s="5">
         <v>46156.63195149305</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46212.59677549769</v>
+      </c>
       <c r="D10" s="5">
-        <v>46209.55906222222</v>
+        <v>46212.59679202546</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -1987,14 +1989,16 @@
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="11" t="s">
-        <v>48</v>
+      <c r="T10" s="6">
+        <v>1</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" s="9">
         <v>46156.63208246528</v>
@@ -2006,16 +2010,16 @@
         <v>46209.55905150463</v>
       </c>
       <c r="E11" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="10" t="s">
+      <c r="H11" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="I11" s="9">
         <v>46140</v>
@@ -2027,7 +2031,7 @@
         <v>26</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>26</v>
@@ -2039,7 +2043,7 @@
         <v>40</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q11" s="9">
         <v>46140</v>
@@ -2059,7 +2063,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="5">
         <v>46156.63208759259</v>
@@ -2071,16 +2075,16 @@
         <v>46209.55905152777</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="I12" s="5">
         <v>46140</v>
@@ -2092,7 +2096,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
@@ -2104,7 +2108,7 @@
         <v>40</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q12" s="5">
         <v>46140</v>
@@ -2124,7 +2128,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" s="9">
         <v>46156.63209254629</v>
@@ -2136,16 +2140,16 @@
         <v>46209.55905167824</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="I13" s="9">
         <v>46140</v>
@@ -2169,7 +2173,7 @@
         <v>40</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q13" s="9">
         <v>46140</v>
@@ -2189,7 +2193,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B14" s="5">
         <v>46156.631956365745</v>
@@ -2201,7 +2205,7 @@
         <v>46197.50206623843</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2225,7 +2229,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2242,7 +2246,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15" s="9">
         <v>46156.63210516203</v>
@@ -2254,16 +2258,16 @@
         <v>46184.58049826389</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="I15" s="9">
         <v>46142</v>
@@ -2281,13 +2285,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q15" s="9">
         <v>46142</v>
@@ -2307,7 +2311,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B16" s="5">
         <v>46156.63211037037</v>
@@ -2319,16 +2323,16 @@
         <v>46184.58051194444</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="I16" s="5">
         <v>46150</v>
@@ -2346,13 +2350,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q16" s="5">
         <v>46150</v>
@@ -2372,7 +2376,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B17" s="9">
         <v>46156.63211564815</v>
@@ -2384,16 +2388,16 @@
         <v>46197.5020416551</v>
       </c>
       <c r="E17" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>73</v>
-      </c>
       <c r="H17" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I17" s="9">
         <v>46150</v>
@@ -2411,13 +2415,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q17" s="9">
         <v>46150</v>
@@ -2437,7 +2441,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="5">
         <v>46156.632121504634</v>
@@ -2449,16 +2453,16 @@
         <v>46206.193739560185</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I18" s="5">
         <v>46212</v>
@@ -2476,13 +2480,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O18" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="Q18" s="5">
         <v>46212</v>
@@ -2491,7 +2495,7 @@
         <v>46213</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2502,7 +2506,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="9">
         <v>46156.63212631944</v>
@@ -2514,16 +2518,16 @@
         <v>46206.193739560185</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I19" s="9">
         <v>46212</v>
@@ -2541,13 +2545,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="9">
         <v>46212</v>
@@ -2556,7 +2560,7 @@
         <v>46213</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="T19" s="10">
         <v>1</v>
@@ -2567,7 +2571,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5">
         <v>46156.63213005787</v>
@@ -2579,16 +2583,16 @@
         <v>46206.56335621528</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I20" s="5">
         <v>46212</v>
@@ -2606,13 +2610,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>46212</v>
@@ -2621,7 +2625,7 @@
         <v>46213</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -2632,7 +2636,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B21" s="9">
         <v>46156.632133692125</v>
@@ -2644,16 +2648,16 @@
         <v>46206.563520752316</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I21" s="9">
         <v>46212</v>
@@ -2671,13 +2675,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q21" s="9">
         <v>46212</v>
@@ -2686,7 +2690,7 @@
         <v>46213</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="T21" s="10">
         <v>1</v>
@@ -2697,17 +2701,19 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B22" s="5">
         <v>46156.6319605787</v>
       </c>
-      <c r="C22" s="6"/>
+      <c r="C22" s="5">
+        <v>46212.59675680556</v>
+      </c>
       <c r="D22" s="5">
-        <v>46210.64699083334</v>
+        <v>46212.59677189815</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2731,7 +2737,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2739,14 +2745,16 @@
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
-      <c r="T22" s="6"/>
-      <c r="U22" s="11" t="s">
-        <v>48</v>
+      <c r="T22" s="6">
+        <v>1</v>
+      </c>
+      <c r="U22" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B23" s="9">
         <v>46156.63213814815</v>
@@ -2758,16 +2766,16 @@
         <v>46210.6467582176</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="H23" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>97</v>
       </c>
       <c r="I23" s="9">
         <v>46154</v>
@@ -2785,13 +2793,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="9">
         <v>46154</v>
@@ -2811,7 +2819,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5">
         <v>46156.63214259259</v>
@@ -2823,16 +2831,16 @@
         <v>46195.92922337963</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="I24" s="5">
         <v>46154</v>
@@ -2850,13 +2858,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2867,12 +2875,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B25" s="9">
         <v>46156.63214717593</v>
@@ -2884,16 +2892,16 @@
         <v>46210.64669667824</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>97</v>
       </c>
       <c r="I25" s="9">
         <v>46156</v>
@@ -2911,13 +2919,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -2928,12 +2936,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B26" s="5">
         <v>46156.6321521412</v>
@@ -2945,16 +2953,16 @@
         <v>46210.64698900463</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="I26" s="5">
         <v>46150</v>
@@ -2972,13 +2980,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q26" s="5">
         <v>46150</v>
@@ -2998,7 +3006,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B27" s="9">
         <v>46156.63215657407</v>
@@ -3010,16 +3018,16 @@
         <v>46210.64692099537</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>97</v>
       </c>
       <c r="I27" s="9">
         <v>46150</v>
@@ -3037,13 +3045,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3054,12 +3062,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46156.63216167824</v>
@@ -3071,16 +3079,16 @@
         <v>46210.64695642361</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="I28" s="5">
         <v>46150</v>
@@ -3098,13 +3106,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3115,12 +3123,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B29" s="9">
         <v>46156.63216756945</v>
@@ -3132,16 +3140,16 @@
         <v>46210.645560289355</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>97</v>
       </c>
       <c r="I29" s="9">
         <v>46142</v>
@@ -3159,13 +3167,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q29" s="9">
         <v>46172</v>
@@ -3185,7 +3193,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46156.63217278935</v>
@@ -3197,16 +3205,16 @@
         <v>46195.92957241899</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="I30" s="5">
         <v>46142</v>
@@ -3224,13 +3232,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3241,12 +3249,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B31" s="9">
         <v>46156.63217837963</v>
@@ -3258,16 +3266,16 @@
         <v>46210.64553332176</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>97</v>
       </c>
       <c r="I31" s="9">
         <v>46164</v>
@@ -3285,13 +3293,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3302,12 +3310,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46156.63218368056</v>
@@ -3319,16 +3327,16 @@
         <v>46197.78355364583</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="I32" s="5">
         <v>46164</v>
@@ -3346,13 +3354,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3363,12 +3371,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B33" s="9">
         <v>46156.632188240736</v>
@@ -3380,16 +3388,16 @@
         <v>46199.55980914352</v>
       </c>
       <c r="E33" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I33" s="9">
         <v>46216</v>
@@ -3407,13 +3415,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q33" s="9">
         <v>46216</v>
@@ -3433,7 +3441,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46156.63219359954</v>
@@ -3445,16 +3453,16 @@
         <v>46199.55917045139</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I34" s="5">
         <v>46216</v>
@@ -3472,13 +3480,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3489,12 +3497,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B35" s="9">
         <v>46156.63219844908</v>
@@ -3506,16 +3514,16 @@
         <v>46199.5597825</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I35" s="9">
         <v>46218</v>
@@ -3533,13 +3541,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3550,12 +3558,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46156.63225444444</v>
@@ -3567,16 +3575,16 @@
         <v>46199.55998701389</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46216</v>
@@ -3594,10 +3602,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3620,7 +3628,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B37" s="9">
         <v>46156.632258206024</v>
@@ -3632,16 +3640,16 @@
         <v>46199.55991087963</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I37" s="9">
         <v>46216</v>
@@ -3659,13 +3667,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3675,7 +3683,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46156.63226241898</v>
@@ -3687,16 +3695,16 @@
         <v>46199.55996042824</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I38" s="5">
         <v>46218</v>
@@ -3714,13 +3722,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3730,7 +3738,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B39" s="9">
         <v>46156.63226644676</v>
@@ -3742,16 +3750,16 @@
         <v>46210.649648715276</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="I39" s="9">
         <v>46216</v>
@@ -3769,10 +3777,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3795,7 +3803,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46156.632269444446</v>
@@ -3807,16 +3815,16 @@
         <v>46196.69978633102</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46216</v>
@@ -3834,13 +3842,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3850,7 +3858,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B41" s="9">
         <v>46156.63227357639</v>
@@ -3862,16 +3870,16 @@
         <v>46204.86000238426</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="I41" s="9">
         <v>46225</v>
@@ -3889,13 +3897,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3905,7 +3913,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46156.63227760416</v>
@@ -3917,16 +3925,16 @@
         <v>46210.64958435185</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46254</v>
@@ -3944,10 +3952,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3960,7 +3968,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="9">
         <v>46156.63228021991</v>
@@ -3972,16 +3980,16 @@
         <v>46199.562315937495</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I43" s="9">
         <v>46216</v>
@@ -3999,10 +4007,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4025,7 +4033,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46156.63228315972</v>
@@ -4037,16 +4045,16 @@
         <v>46199.56224427083</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I44" s="5">
         <v>46216</v>
@@ -4064,13 +4072,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4080,7 +4088,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B45" s="9">
         <v>46156.63228715278</v>
@@ -4092,16 +4100,16 @@
         <v>46199.56229454861</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I45" s="9">
         <v>46218</v>
@@ -4119,13 +4127,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4135,7 +4143,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46156.63196493055</v>
@@ -4145,7 +4153,7 @@
         <v>46184.58079096065</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4169,7 +4177,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4179,7 +4187,7 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="11" t="s">
-        <v>48</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4223,10 +4231,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>175</v>
@@ -4258,7 +4266,7 @@
         <v>46184.58077318287</v>
       </c>
       <c r="D48" s="5">
-        <v>46211.19501542824</v>
+        <v>46212.59685061342</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4288,7 +4296,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>179</v>
@@ -4308,8 +4316,8 @@
       <c r="T48" s="6">
         <v>1</v>
       </c>
-      <c r="U48" s="11" t="s">
-        <v>48</v>
+      <c r="U48" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4326,7 +4334,7 @@
         <v>46212.1877253125</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
@@ -4351,7 +4359,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>178</v>
@@ -4414,7 +4422,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>189</v>
@@ -4435,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4588,7 +4596,7 @@
         <v>194</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>200</v>
@@ -4629,10 +4637,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I54" s="5">
         <v>46231</v>
@@ -4718,7 +4726,7 @@
         <v>194</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>207</v>
@@ -4759,10 +4767,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I56" s="5">
         <v>46231</v>
@@ -4848,7 +4856,7 @@
         <v>194</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>212</v>
@@ -4889,10 +4897,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I58" s="5">
         <v>46231</v>
@@ -5161,7 +5169,7 @@
         <v>0.5</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>48</v>
+        <v>170</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5235,10 +5243,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I64" s="5">
         <v>46262</v>
@@ -5277,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="U64" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5298,10 +5306,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I65" s="9">
         <v>46262</v>
@@ -5340,9 +5348,11 @@
       <c r="B66" s="5">
         <v>46156.6324928588</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46212.596692673615</v>
+      </c>
       <c r="D66" s="5">
-        <v>46210.64710428241</v>
+        <v>46212.59671021991</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>194</v>
@@ -5377,9 +5387,11 @@
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
       <c r="S66" s="6"/>
-      <c r="T66" s="6"/>
-      <c r="U66" s="11" t="s">
-        <v>48</v>
+      <c r="T66" s="6">
+        <v>1</v>
+      </c>
+      <c r="U66" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5426,7 +5438,7 @@
         <v>194</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>204</v>
@@ -5491,7 +5503,7 @@
         <v>194</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>204</v>
@@ -5556,7 +5568,7 @@
         <v>194</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>204</v>
@@ -5584,9 +5596,11 @@
       <c r="B70" s="5">
         <v>46156.63251465278</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46212.59667254629</v>
+      </c>
       <c r="D70" s="5">
-        <v>46204.86002143519</v>
+        <v>46212.59669387732</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>243</v>
@@ -5619,7 +5633,7 @@
         <v>194</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>244</v>
@@ -5634,10 +5648,10 @@
         <v>33</v>
       </c>
       <c r="T70" s="6">
-        <v>0</v>
-      </c>
-      <c r="U70" s="11" t="s">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="U70" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5696,7 +5710,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46156.72654819445</v>
+        <v>46212.59668103009</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>249</v>
@@ -5705,10 +5719,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I72" s="5">
         <v>46266</v>
@@ -5747,7 +5761,7 @@
         <v>0</v>
       </c>
       <c r="U72" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5759,7 +5773,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46156.726576076384</v>
+        <v>46212.59668166666</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>191</v>
@@ -5768,10 +5782,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I73" s="9">
         <v>46266</v>
@@ -5821,10 +5835,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I74" s="5">
         <v>46288</v>
@@ -5863,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="U74" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5884,10 +5898,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I75" s="9">
         <v>46288</v>
@@ -5937,10 +5951,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I76" s="5">
         <v>46290</v>
@@ -5979,7 +5993,7 @@
         <v>0</v>
       </c>
       <c r="U76" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -6000,10 +6014,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I77" s="9">
         <v>46290</v>
@@ -6053,10 +6067,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I78" s="5">
         <v>46296</v>
@@ -6095,7 +6109,7 @@
         <v>0</v>
       </c>
       <c r="U78" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6116,10 +6130,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I79" s="9">
         <v>46296</v>
@@ -6169,10 +6183,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I80" s="5">
         <v>46300</v>
@@ -6211,7 +6225,7 @@
         <v>0</v>
       </c>
       <c r="U80" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6232,10 +6246,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I81" s="9">
         <v>46300</v>
@@ -6285,10 +6299,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I82" s="5">
         <v>46302</v>
@@ -6327,7 +6341,7 @@
         <v>0</v>
       </c>
       <c r="U82" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6348,10 +6362,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I83" s="9">
         <v>46302</v>
@@ -6490,7 +6504,7 @@
         <v>0</v>
       </c>
       <c r="U85" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6564,10 +6578,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
@@ -6604,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="U87" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -6625,10 +6639,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I88" s="5">
         <v>46304</v>
@@ -6722,7 +6736,7 @@
         <v>1</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>48</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -6840,7 +6854,7 @@
         <v>0</v>
       </c>
       <c r="U91" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -7001,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7022,10 +7036,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="I95" s="9">
         <v>46309</v>
@@ -7064,7 +7078,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -5663,7 +5663,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46156.71581511574</v>
+        <v>46213.50747597222</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>246</v>
@@ -5824,9 +5824,11 @@
       <c r="B74" s="5">
         <v>46156.63254586805</v>
       </c>
-      <c r="C74" s="6"/>
+      <c r="C74" s="5">
+        <v>46213.50741020833</v>
+      </c>
       <c r="D74" s="5">
-        <v>46156.72654520834</v>
+        <v>46213.50742533564</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>253</v>
@@ -5874,10 +5876,10 @@
         <v>33</v>
       </c>
       <c r="T74" s="6">
-        <v>0</v>
-      </c>
-      <c r="U74" s="12" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U74" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5940,9 +5942,11 @@
       <c r="B76" s="5">
         <v>46156.63257873843</v>
       </c>
-      <c r="C76" s="6"/>
+      <c r="C76" s="5">
+        <v>46213.50747125</v>
+      </c>
       <c r="D76" s="5">
-        <v>46156.726542372686</v>
+        <v>46213.5074855787</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>258</v>
@@ -5990,10 +5994,10 @@
         <v>33</v>
       </c>
       <c r="T76" s="6">
-        <v>0</v>
-      </c>
-      <c r="U76" s="12" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U76" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="306">
   <si>
     <t>50001547 - XEMORTIZ (AMERICAS GOLD)</t>
   </si>
@@ -119,6 +119,31 @@
   </si>
   <si>
     <t>Apertura pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buen día,
+Para el pedido 1547, se tiene un ventilador ZVN 1-16-126/4 para Xemortiz (Americas Gold):
+    Planos para:
+        Ventilador ZVN 1-16-126/4 con motor WEG
+        Alcance ZCH: Tobera + Rejilla + Ventilador
+        Plano de fabricación: CH1481
+hugo.isla@zitron.com, pedido listo para realizar propuesta de materiales.
+    Rodete:
+        Alabe s/ plano 2605.01
+        Código:  300007
+        Z10 N900
+        Calaje: 0°
+        Consumo estimado en fabrica: 120kW
+benjamin.bustos@zitron.com, reservar alabes a código.
+    Tratamiento superficial:
+        Estándar Zitrón con 2 capas y color de terminación Blanco RAL 9001.
+    Datos eléctricos para el motor:
+        Motor WEG 126KW, FR315 S/M
+        4P, 460V, 60Hz, IP55.
+benjamin.bustos@zitron.com, se requiere duplicado de placa.
+    Fechas de entrega: 13/07/2026.
+    Nota: hugo.isla@zitron.com, el difusor acústico y la junta flexible es alcance de Zitron México
+ </t>
   </si>
   <si>
     <t>1214809660705201</t>
@@ -1702,7 +1727,7 @@
         <v>46175.87350159722</v>
       </c>
       <c r="D6" s="5">
-        <v>46184.57987159722</v>
+        <v>46213.76905379629</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1724,7 +1749,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>26</v>
@@ -1756,7 +1781,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="9">
         <v>46156.632073217595</v>
@@ -1768,7 +1793,7 @@
         <v>46184.58116259259</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>26</v>
@@ -1787,7 +1812,7 @@
         <v>26</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>26</v>
@@ -1819,7 +1844,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="5">
         <v>46156.63207597222</v>
@@ -1831,7 +1856,7 @@
         <v>46184.57963962963</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>26</v>
@@ -1850,7 +1875,7 @@
         <v>26</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>26</v>
@@ -1862,7 +1887,7 @@
         <v>26</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q8" s="5">
         <v>46139</v>
@@ -1882,7 +1907,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" s="9">
         <v>46156.63207924768</v>
@@ -1894,7 +1919,7 @@
         <v>46175.87353033565</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>26</v>
@@ -1913,7 +1938,7 @@
         <v>26</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M9" s="10" t="s">
         <v>26</v>
@@ -1945,7 +1970,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="5">
         <v>46156.63195149305</v>
@@ -1957,7 +1982,7 @@
         <v>46212.59679202546</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>25</v>
@@ -1981,7 +2006,7 @@
         <v>26</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>26</v>
@@ -1998,7 +2023,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="9">
         <v>46156.63208246528</v>
@@ -2010,16 +2035,16 @@
         <v>46209.55905150463</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I11" s="9">
         <v>46140</v>
@@ -2031,19 +2056,19 @@
         <v>26</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q11" s="9">
         <v>46140</v>
@@ -2063,7 +2088,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" s="5">
         <v>46156.63208759259</v>
@@ -2075,16 +2100,16 @@
         <v>46209.55905152777</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I12" s="5">
         <v>46140</v>
@@ -2096,19 +2121,19 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q12" s="5">
         <v>46140</v>
@@ -2128,7 +2153,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B13" s="9">
         <v>46156.63209254629</v>
@@ -2140,16 +2165,16 @@
         <v>46209.55905167824</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I13" s="9">
         <v>46140</v>
@@ -2167,13 +2192,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q13" s="9">
         <v>46140</v>
@@ -2193,7 +2218,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="5">
         <v>46156.631956365745</v>
@@ -2205,7 +2230,7 @@
         <v>46197.50206623843</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2229,7 +2254,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2246,7 +2271,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" s="9">
         <v>46156.63210516203</v>
@@ -2258,16 +2283,16 @@
         <v>46184.58049826389</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I15" s="9">
         <v>46142</v>
@@ -2285,13 +2310,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q15" s="9">
         <v>46142</v>
@@ -2311,7 +2336,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B16" s="5">
         <v>46156.63211037037</v>
@@ -2323,16 +2348,16 @@
         <v>46184.58051194444</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I16" s="5">
         <v>46150</v>
@@ -2350,13 +2375,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q16" s="5">
         <v>46150</v>
@@ -2376,7 +2401,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" s="9">
         <v>46156.63211564815</v>
@@ -2388,16 +2413,16 @@
         <v>46197.5020416551</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I17" s="9">
         <v>46150</v>
@@ -2415,13 +2440,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="9">
         <v>46150</v>
@@ -2441,7 +2466,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" s="5">
         <v>46156.632121504634</v>
@@ -2453,16 +2478,16 @@
         <v>46206.193739560185</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I18" s="5">
         <v>46212</v>
@@ -2480,13 +2505,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="5">
         <v>46212</v>
@@ -2495,7 +2520,7 @@
         <v>46213</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2506,7 +2531,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B19" s="9">
         <v>46156.63212631944</v>
@@ -2518,16 +2543,16 @@
         <v>46206.193739560185</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I19" s="9">
         <v>46212</v>
@@ -2545,13 +2570,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="9">
         <v>46212</v>
@@ -2560,7 +2585,7 @@
         <v>46213</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T19" s="10">
         <v>1</v>
@@ -2571,7 +2596,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
         <v>46156.63213005787</v>
@@ -2583,16 +2608,16 @@
         <v>46206.56335621528</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I20" s="5">
         <v>46212</v>
@@ -2610,13 +2635,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="5">
         <v>46212</v>
@@ -2625,7 +2650,7 @@
         <v>46213</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -2636,7 +2661,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B21" s="9">
         <v>46156.632133692125</v>
@@ -2648,16 +2673,16 @@
         <v>46206.563520752316</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I21" s="9">
         <v>46212</v>
@@ -2675,13 +2700,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q21" s="9">
         <v>46212</v>
@@ -2690,7 +2715,7 @@
         <v>46213</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T21" s="10">
         <v>1</v>
@@ -2701,7 +2726,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B22" s="5">
         <v>46156.6319605787</v>
@@ -2713,7 +2738,7 @@
         <v>46212.59677189815</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2737,7 +2762,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2754,7 +2779,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B23" s="9">
         <v>46156.63213814815</v>
@@ -2766,16 +2791,16 @@
         <v>46210.6467582176</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I23" s="9">
         <v>46154</v>
@@ -2793,13 +2818,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="9">
         <v>46154</v>
@@ -2819,7 +2844,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B24" s="5">
         <v>46156.63214259259</v>
@@ -2831,16 +2856,16 @@
         <v>46195.92922337963</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I24" s="5">
         <v>46154</v>
@@ -2858,13 +2883,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2875,12 +2900,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B25" s="9">
         <v>46156.63214717593</v>
@@ -2892,16 +2917,16 @@
         <v>46210.64669667824</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I25" s="9">
         <v>46156</v>
@@ -2919,13 +2944,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -2936,12 +2961,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5">
         <v>46156.6321521412</v>
@@ -2953,16 +2978,16 @@
         <v>46210.64698900463</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I26" s="5">
         <v>46150</v>
@@ -2980,13 +3005,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q26" s="5">
         <v>46150</v>
@@ -3006,7 +3031,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B27" s="9">
         <v>46156.63215657407</v>
@@ -3018,16 +3043,16 @@
         <v>46210.64692099537</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I27" s="9">
         <v>46150</v>
@@ -3045,13 +3070,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3062,12 +3087,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46156.63216167824</v>
@@ -3079,16 +3104,16 @@
         <v>46210.64695642361</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I28" s="5">
         <v>46150</v>
@@ -3106,13 +3131,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3123,12 +3148,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="9">
         <v>46156.63216756945</v>
@@ -3140,16 +3165,16 @@
         <v>46210.645560289355</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I29" s="9">
         <v>46142</v>
@@ -3167,13 +3192,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q29" s="9">
         <v>46172</v>
@@ -3193,7 +3218,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46156.63217278935</v>
@@ -3205,16 +3230,16 @@
         <v>46195.92957241899</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I30" s="5">
         <v>46142</v>
@@ -3232,13 +3257,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3249,12 +3274,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" s="9">
         <v>46156.63217837963</v>
@@ -3266,16 +3291,16 @@
         <v>46210.64553332176</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I31" s="9">
         <v>46164</v>
@@ -3293,13 +3318,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3310,12 +3335,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46156.63218368056</v>
@@ -3327,16 +3352,16 @@
         <v>46197.78355364583</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I32" s="5">
         <v>46164</v>
@@ -3354,13 +3379,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3371,12 +3396,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="9">
         <v>46156.632188240736</v>
@@ -3388,16 +3413,16 @@
         <v>46199.55980914352</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I33" s="9">
         <v>46216</v>
@@ -3415,13 +3440,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q33" s="9">
         <v>46216</v>
@@ -3441,7 +3466,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46156.63219359954</v>
@@ -3453,16 +3478,16 @@
         <v>46199.55917045139</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I34" s="5">
         <v>46216</v>
@@ -3480,13 +3505,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3497,12 +3522,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B35" s="9">
         <v>46156.63219844908</v>
@@ -3514,16 +3539,16 @@
         <v>46199.5597825</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I35" s="9">
         <v>46218</v>
@@ -3541,13 +3566,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3558,12 +3583,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46156.63225444444</v>
@@ -3575,16 +3600,16 @@
         <v>46199.55998701389</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46216</v>
@@ -3602,10 +3627,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3628,7 +3653,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46156.632258206024</v>
@@ -3640,16 +3665,16 @@
         <v>46199.55991087963</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I37" s="9">
         <v>46216</v>
@@ -3667,13 +3692,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3683,7 +3708,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46156.63226241898</v>
@@ -3695,16 +3720,16 @@
         <v>46199.55996042824</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I38" s="5">
         <v>46218</v>
@@ -3722,13 +3747,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3738,7 +3763,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B39" s="9">
         <v>46156.63226644676</v>
@@ -3750,16 +3775,16 @@
         <v>46210.649648715276</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I39" s="9">
         <v>46216</v>
@@ -3777,10 +3802,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3803,7 +3828,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46156.632269444446</v>
@@ -3815,16 +3840,16 @@
         <v>46196.69978633102</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46216</v>
@@ -3842,13 +3867,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3858,7 +3883,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46156.63227357639</v>
@@ -3870,16 +3895,16 @@
         <v>46204.86000238426</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I41" s="9">
         <v>46225</v>
@@ -3897,13 +3922,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3913,7 +3938,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46156.63227760416</v>
@@ -3925,16 +3950,16 @@
         <v>46210.64958435185</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46254</v>
@@ -3952,10 +3977,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3968,7 +3993,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46156.63228021991</v>
@@ -3980,16 +4005,16 @@
         <v>46199.562315937495</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I43" s="9">
         <v>46216</v>
@@ -4007,10 +4032,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4033,7 +4058,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46156.63228315972</v>
@@ -4045,16 +4070,16 @@
         <v>46199.56224427083</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I44" s="5">
         <v>46216</v>
@@ -4072,13 +4097,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4088,7 +4113,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B45" s="9">
         <v>46156.63228715278</v>
@@ -4100,16 +4125,16 @@
         <v>46199.56229454861</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I45" s="9">
         <v>46218</v>
@@ -4127,13 +4152,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4143,7 +4168,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46156.63196493055</v>
@@ -4153,7 +4178,7 @@
         <v>46184.58079096065</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4177,7 +4202,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4187,12 +4212,12 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" s="9">
         <v>46156.63229164352</v>
@@ -4204,16 +4229,16 @@
         <v>46197.714709479165</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I47" s="9">
         <v>46150</v>
@@ -4231,13 +4256,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="9">
         <v>46150</v>
@@ -4246,7 +4271,7 @@
         <v>46156</v>
       </c>
       <c r="S47" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T47" s="10">
         <v>1</v>
@@ -4257,7 +4282,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
         <v>46156.632296261574</v>
@@ -4269,16 +4294,16 @@
         <v>46212.59685061342</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46204</v>
@@ -4296,13 +4321,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="5">
         <v>46204</v>
@@ -4311,7 +4336,7 @@
         <v>46210</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T48" s="6">
         <v>1</v>
@@ -4322,7 +4347,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46156.63230224537</v>
@@ -4334,16 +4359,16 @@
         <v>46212.1877253125</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4359,13 +4384,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q49" s="9">
         <v>46211</v>
@@ -4374,7 +4399,7 @@
         <v>46211</v>
       </c>
       <c r="S49" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>
@@ -4385,7 +4410,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B50" s="5">
         <v>46156.632315358795</v>
@@ -4395,16 +4420,16 @@
         <v>46156.72589140046</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I50" s="5">
         <v>46301</v>
@@ -4422,10 +4447,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4443,12 +4468,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B51" s="9">
         <v>46156.6323189699</v>
@@ -4458,16 +4483,16 @@
         <v>46156.725962881945</v>
       </c>
       <c r="E51" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I51" s="9">
         <v>46301</v>
@@ -4485,13 +4510,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4501,7 +4526,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B52" s="5">
         <v>46156.63233141204</v>
@@ -4513,7 +4538,7 @@
         <v>46210.64940796296</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4537,7 +4562,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4554,7 +4579,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B53" s="9">
         <v>46156.63233460648</v>
@@ -4566,16 +4591,16 @@
         <v>46210.64881278935</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I53" s="9">
         <v>46227</v>
@@ -4593,13 +4618,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q53" s="9">
         <v>46227</v>
@@ -4619,7 +4644,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B54" s="5">
         <v>46156.63233969908</v>
@@ -4631,16 +4656,16 @@
         <v>46210.649371875</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I54" s="5">
         <v>46231</v>
@@ -4658,13 +4683,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q54" s="5">
         <v>46231</v>
@@ -4684,7 +4709,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B55" s="9">
         <v>46156.632350671294</v>
@@ -4696,16 +4721,16 @@
         <v>46210.64881809028</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I55" s="9">
         <v>46227</v>
@@ -4723,13 +4748,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q55" s="9">
         <v>46227</v>
@@ -4749,7 +4774,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B56" s="5">
         <v>46156.63235533565</v>
@@ -4761,16 +4786,16 @@
         <v>46210.64938440973</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I56" s="5">
         <v>46231</v>
@@ -4788,13 +4813,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q56" s="5">
         <v>46231</v>
@@ -4814,7 +4839,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B57" s="9">
         <v>46156.63235945602</v>
@@ -4826,16 +4851,16 @@
         <v>46210.648830949074</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I57" s="9">
         <v>46227</v>
@@ -4853,13 +4878,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q57" s="9">
         <v>46227</v>
@@ -4879,7 +4904,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
         <v>46156.63236322917</v>
@@ -4891,16 +4916,16 @@
         <v>46210.64939421296</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I58" s="5">
         <v>46231</v>
@@ -4918,13 +4943,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q58" s="5">
         <v>46231</v>
@@ -4944,7 +4969,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B59" s="9">
         <v>46156.63236744213</v>
@@ -4954,7 +4979,7 @@
         <v>46203.5014815162</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>25</v>
@@ -4978,7 +5003,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -4991,7 +5016,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B60" s="5">
         <v>46156.63237008102</v>
@@ -5003,16 +5028,16 @@
         <v>46211.68096902777</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I60" s="5">
         <v>46233</v>
@@ -5030,13 +5055,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q60" s="5">
         <v>46233</v>
@@ -5056,7 +5081,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B61" s="9">
         <v>46156.63237584491</v>
@@ -5068,16 +5093,16 @@
         <v>46211.68096520833</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I61" s="9">
         <v>46233</v>
@@ -5095,13 +5120,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5111,7 +5136,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B62" s="5">
         <v>46156.63239597222</v>
@@ -5121,16 +5146,16 @@
         <v>46211.65705916667</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I62" s="5">
         <v>46244</v>
@@ -5148,13 +5173,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q62" s="5">
         <v>46244</v>
@@ -5169,12 +5194,12 @@
         <v>0.5</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B63" s="9">
         <v>46156.632400069444</v>
@@ -5184,16 +5209,16 @@
         <v>46211.68097021991</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5211,13 +5236,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5227,7 +5252,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B64" s="5">
         <v>46156.63246734954</v>
@@ -5237,16 +5262,16 @@
         <v>46197.83505042824</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I64" s="5">
         <v>46262</v>
@@ -5264,13 +5289,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5285,12 +5310,12 @@
         <v>0</v>
       </c>
       <c r="U64" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B65" s="9">
         <v>46156.632472627316</v>
@@ -5300,16 +5325,16 @@
         <v>46197.83511621528</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I65" s="9">
         <v>46262</v>
@@ -5327,13 +5352,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5343,7 +5368,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B66" s="5">
         <v>46156.6324928588</v>
@@ -5355,7 +5380,7 @@
         <v>46212.59671021991</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5379,7 +5404,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5396,7 +5421,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B67" s="9">
         <v>46156.63249635417</v>
@@ -5408,16 +5433,16 @@
         <v>46210.64718186343</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I67" s="9">
         <v>46154</v>
@@ -5435,13 +5460,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q67" s="9">
         <v>46154</v>
@@ -5461,7 +5486,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B68" s="5">
         <v>46156.63250229167</v>
@@ -5473,16 +5498,16 @@
         <v>46210.64712949074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I68" s="5">
         <v>46268</v>
@@ -5500,13 +5525,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q68" s="5">
         <v>46268</v>
@@ -5526,7 +5551,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B69" s="9">
         <v>46156.63250851852</v>
@@ -5538,16 +5563,16 @@
         <v>46210.645706863426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I69" s="9">
         <v>46294</v>
@@ -5565,13 +5590,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q69" s="9">
         <v>46294</v>
@@ -5591,7 +5616,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B70" s="5">
         <v>46156.63251465278</v>
@@ -5603,16 +5628,16 @@
         <v>46212.59669387732</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I70" s="5">
         <v>46255</v>
@@ -5630,13 +5655,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q70" s="5">
         <v>46255</v>
@@ -5656,7 +5681,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B71" s="9">
         <v>46156.63251914352</v>
@@ -5666,7 +5691,7 @@
         <v>46213.50747597222</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5690,7 +5715,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5703,7 +5728,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B72" s="5">
         <v>46156.63252219907</v>
@@ -5713,16 +5738,16 @@
         <v>46212.59668103009</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I72" s="5">
         <v>46266</v>
@@ -5740,13 +5765,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q72" s="5">
         <v>46266</v>
@@ -5761,12 +5786,12 @@
         <v>0</v>
       </c>
       <c r="U72" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B73" s="9">
         <v>46156.63252934028</v>
@@ -5776,16 +5801,16 @@
         <v>46212.59668166666</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I73" s="9">
         <v>46266</v>
@@ -5803,10 +5828,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5819,7 +5844,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B74" s="5">
         <v>46156.63254586805</v>
@@ -5831,16 +5856,16 @@
         <v>46213.50742533564</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I74" s="5">
         <v>46288</v>
@@ -5858,13 +5883,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q74" s="5">
         <v>46288</v>
@@ -5884,7 +5909,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B75" s="9">
         <v>46156.63255047453</v>
@@ -5894,16 +5919,16 @@
         <v>46210.647096342596</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I75" s="9">
         <v>46288</v>
@@ -5921,13 +5946,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5937,7 +5962,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B76" s="5">
         <v>46156.63257873843</v>
@@ -5949,16 +5974,16 @@
         <v>46213.5074855787</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I76" s="5">
         <v>46290</v>
@@ -5976,13 +6001,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q76" s="5">
         <v>46290</v>
@@ -6002,7 +6027,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B77" s="9">
         <v>46156.632582986116</v>
@@ -6012,16 +6037,16 @@
         <v>46210.64708005787</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I77" s="9">
         <v>46290</v>
@@ -6039,13 +6064,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6055,7 +6080,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B78" s="5">
         <v>46156.632655671296</v>
@@ -6065,16 +6090,16 @@
         <v>46156.72653921296</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I78" s="5">
         <v>46296</v>
@@ -6092,13 +6117,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q78" s="5">
         <v>46296</v>
@@ -6113,12 +6138,12 @@
         <v>0</v>
       </c>
       <c r="U78" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B79" s="9">
         <v>46156.6326615162</v>
@@ -6128,16 +6153,16 @@
         <v>46210.645696875</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I79" s="9">
         <v>46296</v>
@@ -6155,13 +6180,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6171,7 +6196,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B80" s="5">
         <v>46156.6326856713</v>
@@ -6181,16 +6206,16 @@
         <v>46156.72653572916</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I80" s="5">
         <v>46300</v>
@@ -6208,13 +6233,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q80" s="5">
         <v>46300</v>
@@ -6229,12 +6254,12 @@
         <v>0</v>
       </c>
       <c r="U80" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B81" s="9">
         <v>46156.63269413194</v>
@@ -6244,16 +6269,16 @@
         <v>46156.72676160879</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I81" s="9">
         <v>46300</v>
@@ -6271,13 +6296,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6287,7 +6312,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B82" s="5">
         <v>46156.632715810185</v>
@@ -6297,16 +6322,16 @@
         <v>46156.726531747685</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I82" s="5">
         <v>46302</v>
@@ -6324,13 +6349,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q82" s="5">
         <v>46302</v>
@@ -6345,12 +6370,12 @@
         <v>0</v>
       </c>
       <c r="U82" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B83" s="9">
         <v>46156.63272170139</v>
@@ -6360,16 +6385,16 @@
         <v>46156.72680289352</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I83" s="9">
         <v>46302</v>
@@ -6387,13 +6412,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6403,7 +6428,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B84" s="5">
         <v>46156.63273993056</v>
@@ -6413,7 +6438,7 @@
         <v>46205.90465030093</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6437,7 +6462,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6450,7 +6475,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B85" s="9">
         <v>46156.63274356481</v>
@@ -6460,16 +6485,16 @@
         <v>46156.7268765162</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I85" s="9">
         <v>46303</v>
@@ -6487,13 +6512,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q85" s="9">
         <v>46303</v>
@@ -6508,12 +6533,12 @@
         <v>0</v>
       </c>
       <c r="U85" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B86" s="5">
         <v>46156.63274915509</v>
@@ -6523,16 +6548,16 @@
         <v>46156.72692035879</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I86" s="5">
         <v>46303</v>
@@ -6550,13 +6575,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6566,7 +6591,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B87" s="9">
         <v>46156.63276633102</v>
@@ -6576,16 +6601,16 @@
         <v>46156.72700125</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
@@ -6601,13 +6626,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q87" s="9">
         <v>46304</v>
@@ -6622,12 +6647,12 @@
         <v>0</v>
       </c>
       <c r="U87" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B88" s="5">
         <v>46156.63277084491</v>
@@ -6637,16 +6662,16 @@
         <v>46156.72697212963</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I88" s="5">
         <v>46304</v>
@@ -6664,13 +6689,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6680,7 +6705,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B89" s="9">
         <v>46156.63283398148</v>
@@ -6692,16 +6717,16 @@
         <v>46205.904737627316</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I89" s="9">
         <v>46307</v>
@@ -6719,13 +6744,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q89" s="9">
         <v>46307</v>
@@ -6740,12 +6765,12 @@
         <v>1</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B90" s="5">
         <v>46156.63284013889</v>
@@ -6757,16 +6782,16 @@
         <v>46205.90481071759</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I90" s="5">
         <v>46307</v>
@@ -6784,13 +6809,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6800,7 +6825,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B91" s="9">
         <v>46156.63286864583</v>
@@ -6810,16 +6835,16 @@
         <v>46156.727220243054</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I91" s="9">
         <v>46308</v>
@@ -6837,13 +6862,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q91" s="9">
         <v>46308</v>
@@ -6858,12 +6883,12 @@
         <v>0</v>
       </c>
       <c r="U91" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B92" s="5">
         <v>46156.632875972224</v>
@@ -6873,16 +6898,16 @@
         <v>46205.9047287037</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -6898,13 +6923,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6914,7 +6939,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B93" s="9">
         <v>46156.63290420139</v>
@@ -6924,7 +6949,7 @@
         <v>46156.71731457176</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>25</v>
@@ -6948,7 +6973,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>26</v>
@@ -6961,7 +6986,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B94" s="5">
         <v>46156.63290788194</v>
@@ -6971,16 +6996,16 @@
         <v>46156.72728918982</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I94" s="5">
         <v>46309</v>
@@ -6998,13 +7023,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q94" s="5">
         <v>46309</v>
@@ -7019,12 +7044,12 @@
         <v>0</v>
       </c>
       <c r="U94" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B95" s="9">
         <v>46156.63291414352</v>
@@ -7034,16 +7059,16 @@
         <v>46209.559051539356</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I95" s="9">
         <v>46309</v>
@@ -7061,13 +7086,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q95" s="9">
         <v>46309</v>
@@ -7082,7 +7107,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="305">
   <si>
     <t>50001547 - XEMORTIZ (AMERICAS GOLD)</t>
   </si>
@@ -306,7 +306,7 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser OT 4317</t>
   </si>
   <si>
-    <t>Media</t>
+    <t>Alta</t>
   </si>
   <si>
     <t>1214809660718675</t>
@@ -592,9 +592,6 @@
   </si>
   <si>
     <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>Alta</t>
   </si>
   <si>
     <t>1214809534019523</t>
@@ -1047,12 +1044,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -2475,7 +2472,7 @@
         <v>46196.656259456024</v>
       </c>
       <c r="D18" s="5">
-        <v>46206.193739560185</v>
+        <v>46214.206295462965</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>76</v>
@@ -2540,7 +2537,7 @@
         <v>46196.65655393519</v>
       </c>
       <c r="D19" s="9">
-        <v>46206.193739560185</v>
+        <v>46214.20629638889</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>83</v>
@@ -2605,7 +2602,7 @@
         <v>46196.65716653936</v>
       </c>
       <c r="D20" s="5">
-        <v>46206.56335621528</v>
+        <v>46214.20629671296</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2670,7 +2667,7 @@
         <v>46196.65766008102</v>
       </c>
       <c r="D21" s="9">
-        <v>46206.563520752316</v>
+        <v>46214.20629545139</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>89</v>
@@ -2899,7 +2896,7 @@
       <c r="T24" s="6">
         <v>0</v>
       </c>
-      <c r="U24" s="12" t="s">
+      <c r="U24" s="11" t="s">
         <v>102</v>
       </c>
     </row>
@@ -2960,7 +2957,7 @@
       <c r="T25" s="10">
         <v>0</v>
       </c>
-      <c r="U25" s="12" t="s">
+      <c r="U25" s="11" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3086,7 +3083,7 @@
       <c r="T27" s="10">
         <v>0</v>
       </c>
-      <c r="U27" s="12" t="s">
+      <c r="U27" s="11" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3147,7 +3144,7 @@
       <c r="T28" s="6">
         <v>0</v>
       </c>
-      <c r="U28" s="12" t="s">
+      <c r="U28" s="11" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3273,7 +3270,7 @@
       <c r="T30" s="6">
         <v>0</v>
       </c>
-      <c r="U30" s="12" t="s">
+      <c r="U30" s="11" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3334,7 +3331,7 @@
       <c r="T31" s="10">
         <v>0</v>
       </c>
-      <c r="U31" s="12" t="s">
+      <c r="U31" s="11" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3395,7 +3392,7 @@
       <c r="T32" s="6">
         <v>0</v>
       </c>
-      <c r="U32" s="12" t="s">
+      <c r="U32" s="11" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3521,7 +3518,7 @@
       <c r="T34" s="6">
         <v>0</v>
       </c>
-      <c r="U34" s="12" t="s">
+      <c r="U34" s="11" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3582,7 +3579,7 @@
       <c r="T35" s="10">
         <v>0</v>
       </c>
-      <c r="U35" s="12" t="s">
+      <c r="U35" s="11" t="s">
         <v>102</v>
       </c>
     </row>
@@ -4211,7 +4208,7 @@
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
-      <c r="U46" s="11" t="s">
+      <c r="U46" s="12" t="s">
         <v>171</v>
       </c>
     </row>
@@ -4270,8 +4267,8 @@
       <c r="R47" s="9">
         <v>46156</v>
       </c>
-      <c r="S47" s="12" t="s">
-        <v>177</v>
+      <c r="S47" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="T47" s="10">
         <v>1</v>
@@ -4282,7 +4279,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46156.632296261574</v>
@@ -4294,7 +4291,7 @@
         <v>46212.59685061342</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4324,10 +4321,10 @@
         <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="Q48" s="5">
         <v>46204</v>
@@ -4335,8 +4332,8 @@
       <c r="R48" s="5">
         <v>46210</v>
       </c>
-      <c r="S48" s="12" t="s">
-        <v>177</v>
+      <c r="S48" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="T48" s="6">
         <v>1</v>
@@ -4347,7 +4344,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46156.63230224537</v>
@@ -4365,10 +4362,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4387,10 +4384,10 @@
         <v>169</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="9">
         <v>46211</v>
@@ -4398,8 +4395,8 @@
       <c r="R49" s="9">
         <v>46211</v>
       </c>
-      <c r="S49" s="12" t="s">
-        <v>177</v>
+      <c r="S49" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>
@@ -4410,7 +4407,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46156.632315358795</v>
@@ -4420,16 +4417,16 @@
         <v>46156.72589140046</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="I50" s="5">
         <v>46301</v>
@@ -4450,7 +4447,7 @@
         <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4467,13 +4464,13 @@
       <c r="T50" s="6">
         <v>0</v>
       </c>
-      <c r="U50" s="12" t="s">
+      <c r="U50" s="11" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46156.6323189699</v>
@@ -4483,16 +4480,16 @@
         <v>46156.725962881945</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>189</v>
       </c>
       <c r="I51" s="9">
         <v>46301</v>
@@ -4510,13 +4507,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>192</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4526,7 +4523,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46156.63233141204</v>
@@ -4538,7 +4535,7 @@
         <v>46210.64940796296</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4562,7 +4559,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4579,7 +4576,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B53" s="9">
         <v>46156.63233460648</v>
@@ -4591,16 +4588,16 @@
         <v>46210.64881278935</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="10" t="s">
+      <c r="H53" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I53" s="9">
         <v>46227</v>
@@ -4618,13 +4615,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>136</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q53" s="9">
         <v>46227</v>
@@ -4644,7 +4641,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B54" s="5">
         <v>46156.63233969908</v>
@@ -4656,7 +4653,7 @@
         <v>46210.649371875</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4683,13 +4680,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q54" s="5">
         <v>46231</v>
@@ -4709,7 +4706,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B55" s="9">
         <v>46156.632350671294</v>
@@ -4721,16 +4718,16 @@
         <v>46210.64881809028</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I55" s="9">
         <v>46227</v>
@@ -4748,13 +4745,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>144</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q55" s="9">
         <v>46227</v>
@@ -4774,7 +4771,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B56" s="5">
         <v>46156.63235533565</v>
@@ -4786,7 +4783,7 @@
         <v>46210.64938440973</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4813,13 +4810,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q56" s="5">
         <v>46231</v>
@@ -4839,7 +4836,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B57" s="9">
         <v>46156.63235945602</v>
@@ -4851,16 +4848,16 @@
         <v>46210.648830949074</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I57" s="9">
         <v>46227</v>
@@ -4878,13 +4875,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>166</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q57" s="9">
         <v>46227</v>
@@ -4904,7 +4901,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46156.63236322917</v>
@@ -4916,7 +4913,7 @@
         <v>46210.64939421296</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4943,13 +4940,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q58" s="5">
         <v>46231</v>
@@ -4969,7 +4966,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B59" s="9">
         <v>46156.63236744213</v>
@@ -4979,7 +4976,7 @@
         <v>46203.5014815162</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>25</v>
@@ -5003,7 +5000,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -5016,7 +5013,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B60" s="5">
         <v>46156.63237008102</v>
@@ -5028,16 +5025,16 @@
         <v>46211.68096902777</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="I60" s="5">
         <v>46233</v>
@@ -5055,13 +5052,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="5">
         <v>46233</v>
@@ -5081,7 +5078,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B61" s="9">
         <v>46156.63237584491</v>
@@ -5093,16 +5090,16 @@
         <v>46211.68096520833</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>220</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>221</v>
       </c>
       <c r="I61" s="9">
         <v>46233</v>
@@ -5120,13 +5117,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O61" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="P61" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5136,7 +5133,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B62" s="5">
         <v>46156.63239597222</v>
@@ -5146,16 +5143,16 @@
         <v>46211.65705916667</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="I62" s="5">
         <v>46244</v>
@@ -5173,13 +5170,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q62" s="5">
         <v>46244</v>
@@ -5193,13 +5190,13 @@
       <c r="T62" s="6">
         <v>0.5</v>
       </c>
-      <c r="U62" s="11" t="s">
+      <c r="U62" s="12" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B63" s="9">
         <v>46156.632400069444</v>
@@ -5209,16 +5206,16 @@
         <v>46211.68097021991</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>220</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>221</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5236,13 +5233,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5252,7 +5249,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B64" s="5">
         <v>46156.63246734954</v>
@@ -5262,7 +5259,7 @@
         <v>46197.83505042824</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5289,13 +5286,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5309,13 +5306,13 @@
       <c r="T64" s="6">
         <v>0</v>
       </c>
-      <c r="U64" s="12" t="s">
+      <c r="U64" s="11" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B65" s="9">
         <v>46156.632472627316</v>
@@ -5325,7 +5322,7 @@
         <v>46197.83511621528</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5352,13 +5349,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5368,7 +5365,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B66" s="5">
         <v>46156.6324928588</v>
@@ -5380,7 +5377,7 @@
         <v>46212.59671021991</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5404,7 +5401,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5421,7 +5418,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B67" s="9">
         <v>46156.63249635417</v>
@@ -5433,16 +5430,16 @@
         <v>46210.64718186343</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I67" s="9">
         <v>46154</v>
@@ -5460,13 +5457,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>113</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q67" s="9">
         <v>46154</v>
@@ -5486,7 +5483,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B68" s="5">
         <v>46156.63250229167</v>
@@ -5498,16 +5495,16 @@
         <v>46210.64712949074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I68" s="5">
         <v>46268</v>
@@ -5525,13 +5522,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>104</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q68" s="5">
         <v>46268</v>
@@ -5551,7 +5548,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B69" s="9">
         <v>46156.63250851852</v>
@@ -5563,16 +5560,16 @@
         <v>46210.645706863426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I69" s="9">
         <v>46294</v>
@@ -5590,13 +5587,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>122</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q69" s="9">
         <v>46294</v>
@@ -5616,7 +5613,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B70" s="5">
         <v>46156.63251465278</v>
@@ -5628,16 +5625,16 @@
         <v>46212.59669387732</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I70" s="5">
         <v>46255</v>
@@ -5655,13 +5652,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>154</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q70" s="5">
         <v>46255</v>
@@ -5681,7 +5678,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B71" s="9">
         <v>46156.63251914352</v>
@@ -5691,7 +5688,7 @@
         <v>46213.50747597222</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5715,7 +5712,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5728,7 +5725,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B72" s="5">
         <v>46156.63252219907</v>
@@ -5738,7 +5735,7 @@
         <v>46212.59668103009</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5765,13 +5762,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q72" s="5">
         <v>46266</v>
@@ -5785,13 +5782,13 @@
       <c r="T72" s="6">
         <v>0</v>
       </c>
-      <c r="U72" s="12" t="s">
+      <c r="U72" s="11" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B73" s="9">
         <v>46156.63252934028</v>
@@ -5801,7 +5798,7 @@
         <v>46212.59668166666</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5828,10 +5825,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="O73" s="10" t="s">
         <v>250</v>
-      </c>
-      <c r="O73" s="10" t="s">
-        <v>251</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5844,7 +5841,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B74" s="5">
         <v>46156.63254586805</v>
@@ -5856,7 +5853,7 @@
         <v>46213.50742533564</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5883,13 +5880,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q74" s="5">
         <v>46288</v>
@@ -5909,7 +5906,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B75" s="9">
         <v>46156.63255047453</v>
@@ -5919,7 +5916,7 @@
         <v>46210.647096342596</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5946,13 +5943,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O75" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="P75" s="10" t="s">
         <v>256</v>
-      </c>
-      <c r="P75" s="10" t="s">
-        <v>257</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5962,7 +5959,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B76" s="5">
         <v>46156.63257873843</v>
@@ -5974,7 +5971,7 @@
         <v>46213.5074855787</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6001,13 +5998,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q76" s="5">
         <v>46290</v>
@@ -6027,7 +6024,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B77" s="9">
         <v>46156.632582986116</v>
@@ -6037,7 +6034,7 @@
         <v>46210.64708005787</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6064,13 +6061,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6080,7 +6077,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B78" s="5">
         <v>46156.632655671296</v>
@@ -6090,7 +6087,7 @@
         <v>46156.72653921296</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6117,13 +6114,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q78" s="5">
         <v>46296</v>
@@ -6137,13 +6134,13 @@
       <c r="T78" s="6">
         <v>0</v>
       </c>
-      <c r="U78" s="12" t="s">
+      <c r="U78" s="11" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B79" s="9">
         <v>46156.6326615162</v>
@@ -6153,7 +6150,7 @@
         <v>46210.645696875</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6180,13 +6177,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O79" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="P79" s="10" t="s">
         <v>265</v>
-      </c>
-      <c r="P79" s="10" t="s">
-        <v>266</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6196,7 +6193,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B80" s="5">
         <v>46156.6326856713</v>
@@ -6206,7 +6203,7 @@
         <v>46156.72653572916</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6233,13 +6230,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q80" s="5">
         <v>46300</v>
@@ -6253,13 +6250,13 @@
       <c r="T80" s="6">
         <v>0</v>
       </c>
-      <c r="U80" s="12" t="s">
+      <c r="U80" s="11" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B81" s="9">
         <v>46156.63269413194</v>
@@ -6269,7 +6266,7 @@
         <v>46156.72676160879</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6296,13 +6293,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6312,7 +6309,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B82" s="5">
         <v>46156.632715810185</v>
@@ -6322,7 +6319,7 @@
         <v>46156.726531747685</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6349,13 +6346,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q82" s="5">
         <v>46302</v>
@@ -6369,13 +6366,13 @@
       <c r="T82" s="6">
         <v>0</v>
       </c>
-      <c r="U82" s="12" t="s">
+      <c r="U82" s="11" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B83" s="9">
         <v>46156.63272170139</v>
@@ -6385,7 +6382,7 @@
         <v>46156.72680289352</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6412,13 +6409,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6428,7 +6425,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B84" s="5">
         <v>46156.63273993056</v>
@@ -6438,7 +6435,7 @@
         <v>46205.90465030093</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6462,7 +6459,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6475,7 +6472,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B85" s="9">
         <v>46156.63274356481</v>
@@ -6485,16 +6482,16 @@
         <v>46156.7268765162</v>
       </c>
       <c r="E85" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="F85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" s="10" t="s">
+      <c r="H85" s="10" t="s">
         <v>281</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>282</v>
       </c>
       <c r="I85" s="9">
         <v>46303</v>
@@ -6512,13 +6509,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q85" s="9">
         <v>46303</v>
@@ -6532,13 +6529,13 @@
       <c r="T85" s="10">
         <v>0</v>
       </c>
-      <c r="U85" s="12" t="s">
+      <c r="U85" s="11" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B86" s="5">
         <v>46156.63274915509</v>
@@ -6548,16 +6545,16 @@
         <v>46156.72692035879</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>281</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>282</v>
       </c>
       <c r="I86" s="5">
         <v>46303</v>
@@ -6575,13 +6572,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6591,7 +6588,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B87" s="9">
         <v>46156.63276633102</v>
@@ -6601,7 +6598,7 @@
         <v>46156.72700125</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6626,13 +6623,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q87" s="9">
         <v>46304</v>
@@ -6646,13 +6643,13 @@
       <c r="T87" s="10">
         <v>0</v>
       </c>
-      <c r="U87" s="12" t="s">
+      <c r="U87" s="11" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B88" s="5">
         <v>46156.63277084491</v>
@@ -6662,7 +6659,7 @@
         <v>46156.72697212963</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6689,13 +6686,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6705,7 +6702,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B89" s="9">
         <v>46156.63283398148</v>
@@ -6717,16 +6714,16 @@
         <v>46205.904737627316</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>220</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>221</v>
       </c>
       <c r="I89" s="9">
         <v>46307</v>
@@ -6744,13 +6741,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q89" s="9">
         <v>46307</v>
@@ -6764,13 +6761,13 @@
       <c r="T89" s="10">
         <v>1</v>
       </c>
-      <c r="U89" s="11" t="s">
+      <c r="U89" s="12" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B90" s="5">
         <v>46156.63284013889</v>
@@ -6782,16 +6779,16 @@
         <v>46205.90481071759</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="I90" s="5">
         <v>46307</v>
@@ -6809,13 +6806,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6825,7 +6822,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B91" s="9">
         <v>46156.63286864583</v>
@@ -6835,16 +6832,16 @@
         <v>46156.727220243054</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>220</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>221</v>
       </c>
       <c r="I91" s="9">
         <v>46308</v>
@@ -6862,13 +6859,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q91" s="9">
         <v>46308</v>
@@ -6882,13 +6879,13 @@
       <c r="T91" s="10">
         <v>0</v>
       </c>
-      <c r="U91" s="12" t="s">
+      <c r="U91" s="11" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B92" s="5">
         <v>46156.632875972224</v>
@@ -6898,16 +6895,16 @@
         <v>46205.9047287037</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -6923,13 +6920,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6939,7 +6936,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B93" s="9">
         <v>46156.63290420139</v>
@@ -6949,7 +6946,7 @@
         <v>46156.71731457176</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>25</v>
@@ -6973,7 +6970,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>26</v>
@@ -6986,7 +6983,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B94" s="5">
         <v>46156.63290788194</v>
@@ -6996,16 +6993,16 @@
         <v>46156.72728918982</v>
       </c>
       <c r="E94" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G94" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="F94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G94" s="6" t="s">
+      <c r="H94" s="6" t="s">
         <v>302</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>303</v>
       </c>
       <c r="I94" s="5">
         <v>46309</v>
@@ -7023,13 +7020,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q94" s="5">
         <v>46309</v>
@@ -7043,13 +7040,13 @@
       <c r="T94" s="6">
         <v>0</v>
       </c>
-      <c r="U94" s="12" t="s">
+      <c r="U94" s="11" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B95" s="9">
         <v>46156.63291414352</v>
@@ -7059,7 +7056,7 @@
         <v>46209.559051539356</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7086,13 +7083,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q95" s="9">
         <v>46309</v>
@@ -7106,7 +7103,7 @@
       <c r="T95" s="10">
         <v>0</v>
       </c>
-      <c r="U95" s="12" t="s">
+      <c r="U95" s="11" t="s">
         <v>102</v>
       </c>
     </row>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="302">
   <si>
     <t>50001547 - XEMORTIZ (AMERICAS GOLD)</t>
   </si>
@@ -282,9 +282,6 @@
     <t>propuesta nucleo rodete OT 4317</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Generación OC Rodete OT 4317</t>
   </si>
   <si>
@@ -292,12 +289,6 @@
   </si>
   <si>
     <t>propuesta Corte Laser OT 4317</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>check planos</t>
@@ -2416,11 +2407,9 @@
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H17" s="10"/>
       <c r="I17" s="9">
         <v>46150</v>
       </c>
@@ -2443,7 +2432,7 @@
         <v>56</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q17" s="9">
         <v>46150</v>
@@ -2463,7 +2452,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="5">
         <v>46156.632121504634</v>
@@ -2475,17 +2464,15 @@
         <v>46214.206295462965</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H18" s="6"/>
       <c r="I18" s="5">
         <v>46212</v>
       </c>
@@ -2505,10 +2492,10 @@
         <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="Q18" s="5">
         <v>46212</v>
@@ -2517,7 +2504,7 @@
         <v>46213</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2528,7 +2515,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B19" s="9">
         <v>46156.63212631944</v>
@@ -2540,17 +2527,15 @@
         <v>46214.20629638889</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H19" s="10"/>
       <c r="I19" s="9">
         <v>46212</v>
       </c>
@@ -2570,10 +2555,10 @@
         <v>63</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q19" s="9">
         <v>46212</v>
@@ -2582,7 +2567,7 @@
         <v>46213</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="T19" s="10">
         <v>1</v>
@@ -2593,7 +2578,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B20" s="5">
         <v>46156.63213005787</v>
@@ -2605,17 +2590,15 @@
         <v>46214.20629671296</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H20" s="6"/>
       <c r="I20" s="5">
         <v>46212</v>
       </c>
@@ -2635,10 +2618,10 @@
         <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="Q20" s="5">
         <v>46212</v>
@@ -2647,7 +2630,7 @@
         <v>46213</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -2658,7 +2641,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B21" s="9">
         <v>46156.632133692125</v>
@@ -2670,17 +2653,15 @@
         <v>46214.20629545139</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H21" s="10"/>
       <c r="I21" s="9">
         <v>46212</v>
       </c>
@@ -2700,10 +2681,10 @@
         <v>63</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Q21" s="9">
         <v>46212</v>
@@ -2712,7 +2693,7 @@
         <v>46213</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="T21" s="10">
         <v>1</v>
@@ -2723,7 +2704,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5">
         <v>46156.6319605787</v>
@@ -2735,7 +2716,7 @@
         <v>46212.59677189815</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2759,7 +2740,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2776,7 +2757,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B23" s="9">
         <v>46156.63213814815</v>
@@ -2788,16 +2769,16 @@
         <v>46210.6467582176</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I23" s="9">
         <v>46154</v>
@@ -2815,13 +2796,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="Q23" s="9">
         <v>46154</v>
@@ -2841,7 +2822,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B24" s="5">
         <v>46156.63214259259</v>
@@ -2853,16 +2834,16 @@
         <v>46195.92922337963</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I24" s="5">
         <v>46154</v>
@@ -2880,13 +2861,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2897,12 +2878,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B25" s="9">
         <v>46156.63214717593</v>
@@ -2914,16 +2895,16 @@
         <v>46210.64669667824</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I25" s="9">
         <v>46156</v>
@@ -2941,13 +2922,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -2958,12 +2939,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B26" s="5">
         <v>46156.6321521412</v>
@@ -2975,16 +2956,16 @@
         <v>46210.64698900463</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I26" s="5">
         <v>46150</v>
@@ -3002,13 +2983,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="Q26" s="5">
         <v>46150</v>
@@ -3028,7 +3009,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B27" s="9">
         <v>46156.63215657407</v>
@@ -3040,16 +3021,16 @@
         <v>46210.64692099537</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I27" s="9">
         <v>46150</v>
@@ -3067,13 +3048,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3084,12 +3065,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B28" s="5">
         <v>46156.63216167824</v>
@@ -3101,16 +3082,16 @@
         <v>46210.64695642361</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I28" s="5">
         <v>46150</v>
@@ -3128,13 +3109,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="O28" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="O28" s="6" t="s">
-        <v>110</v>
-      </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3145,12 +3126,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B29" s="9">
         <v>46156.63216756945</v>
@@ -3162,16 +3143,16 @@
         <v>46210.645560289355</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I29" s="9">
         <v>46142</v>
@@ -3189,13 +3170,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="Q29" s="9">
         <v>46172</v>
@@ -3215,7 +3196,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5">
         <v>46156.63217278935</v>
@@ -3227,16 +3208,16 @@
         <v>46195.92957241899</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I30" s="5">
         <v>46142</v>
@@ -3254,13 +3235,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3271,12 +3252,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B31" s="9">
         <v>46156.63217837963</v>
@@ -3288,16 +3269,16 @@
         <v>46210.64553332176</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I31" s="9">
         <v>46164</v>
@@ -3315,13 +3296,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="O31" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="O31" s="10" t="s">
-        <v>119</v>
-      </c>
       <c r="P31" s="10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3332,12 +3313,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46156.63218368056</v>
@@ -3349,16 +3330,16 @@
         <v>46197.78355364583</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I32" s="5">
         <v>46164</v>
@@ -3376,13 +3357,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="O32" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="O32" s="6" t="s">
-        <v>119</v>
-      </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3393,12 +3374,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B33" s="9">
         <v>46156.632188240736</v>
@@ -3410,16 +3391,16 @@
         <v>46199.55980914352</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I33" s="9">
         <v>46216</v>
@@ -3437,13 +3418,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="Q33" s="9">
         <v>46216</v>
@@ -3463,7 +3444,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46156.63219359954</v>
@@ -3475,16 +3456,16 @@
         <v>46199.55917045139</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I34" s="5">
         <v>46216</v>
@@ -3502,13 +3483,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3519,12 +3500,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B35" s="9">
         <v>46156.63219844908</v>
@@ -3536,16 +3517,16 @@
         <v>46199.5597825</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I35" s="9">
         <v>46218</v>
@@ -3563,13 +3544,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3580,12 +3561,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B36" s="5">
         <v>46156.63225444444</v>
@@ -3597,16 +3578,16 @@
         <v>46199.55998701389</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I36" s="5">
         <v>46216</v>
@@ -3624,10 +3605,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3650,7 +3631,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B37" s="9">
         <v>46156.632258206024</v>
@@ -3662,16 +3643,16 @@
         <v>46199.55991087963</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I37" s="9">
         <v>46216</v>
@@ -3689,13 +3670,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="O37" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="P37" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="O37" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="P37" s="10" t="s">
-        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3705,7 +3686,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46156.63226241898</v>
@@ -3717,16 +3698,16 @@
         <v>46199.55996042824</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I38" s="5">
         <v>46218</v>
@@ -3744,13 +3725,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3760,7 +3741,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B39" s="9">
         <v>46156.63226644676</v>
@@ -3772,16 +3753,16 @@
         <v>46210.649648715276</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I39" s="9">
         <v>46216</v>
@@ -3799,10 +3780,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3825,7 +3806,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46156.632269444446</v>
@@ -3837,16 +3818,16 @@
         <v>46196.69978633102</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I40" s="5">
         <v>46216</v>
@@ -3864,13 +3845,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3880,7 +3861,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B41" s="9">
         <v>46156.63227357639</v>
@@ -3892,16 +3873,16 @@
         <v>46204.86000238426</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I41" s="9">
         <v>46225</v>
@@ -3919,13 +3900,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3935,7 +3916,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46156.63227760416</v>
@@ -3947,16 +3928,16 @@
         <v>46210.64958435185</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I42" s="5">
         <v>46254</v>
@@ -3974,10 +3955,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3990,7 +3971,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B43" s="9">
         <v>46156.63228021991</v>
@@ -4002,16 +3983,16 @@
         <v>46199.562315937495</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I43" s="9">
         <v>46216</v>
@@ -4029,10 +4010,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4055,7 +4036,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B44" s="5">
         <v>46156.63228315972</v>
@@ -4067,16 +4048,16 @@
         <v>46199.56224427083</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I44" s="5">
         <v>46216</v>
@@ -4094,13 +4075,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="O44" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4110,7 +4091,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B45" s="9">
         <v>46156.63228715278</v>
@@ -4122,16 +4103,16 @@
         <v>46199.56229454861</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I45" s="9">
         <v>46218</v>
@@ -4149,13 +4130,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4165,7 +4146,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B46" s="5">
         <v>46156.63196493055</v>
@@ -4175,7 +4156,7 @@
         <v>46184.58079096065</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4199,7 +4180,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4209,12 +4190,12 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B47" s="9">
         <v>46156.63229164352</v>
@@ -4226,16 +4207,16 @@
         <v>46197.714709479165</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I47" s="9">
         <v>46150</v>
@@ -4253,13 +4234,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q47" s="9">
         <v>46150</v>
@@ -4268,7 +4249,7 @@
         <v>46156</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="T47" s="10">
         <v>1</v>
@@ -4279,7 +4260,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B48" s="5">
         <v>46156.632296261574</v>
@@ -4291,16 +4272,16 @@
         <v>46212.59685061342</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I48" s="5">
         <v>46204</v>
@@ -4318,13 +4299,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Q48" s="5">
         <v>46204</v>
@@ -4333,7 +4314,7 @@
         <v>46210</v>
       </c>
       <c r="S48" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="T48" s="6">
         <v>1</v>
@@ -4344,7 +4325,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B49" s="9">
         <v>46156.63230224537</v>
@@ -4356,16 +4337,16 @@
         <v>46212.1877253125</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4381,13 +4362,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="Q49" s="9">
         <v>46211</v>
@@ -4396,7 +4377,7 @@
         <v>46211</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>
@@ -4407,7 +4388,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46156.632315358795</v>
@@ -4417,16 +4398,16 @@
         <v>46156.72589140046</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I50" s="5">
         <v>46301</v>
@@ -4444,10 +4425,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4465,12 +4446,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B51" s="9">
         <v>46156.6323189699</v>
@@ -4480,16 +4461,16 @@
         <v>46156.725962881945</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I51" s="9">
         <v>46301</v>
@@ -4507,13 +4488,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4523,7 +4504,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B52" s="5">
         <v>46156.63233141204</v>
@@ -4535,7 +4516,7 @@
         <v>46210.64940796296</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4559,7 +4540,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4576,7 +4557,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
         <v>46156.63233460648</v>
@@ -4588,16 +4569,16 @@
         <v>46210.64881278935</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I53" s="9">
         <v>46227</v>
@@ -4615,13 +4596,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="Q53" s="9">
         <v>46227</v>
@@ -4641,7 +4622,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46156.63233969908</v>
@@ -4653,16 +4634,16 @@
         <v>46210.649371875</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I54" s="5">
         <v>46231</v>
@@ -4680,13 +4661,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="5">
         <v>46231</v>
@@ -4706,7 +4687,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B55" s="9">
         <v>46156.632350671294</v>
@@ -4718,16 +4699,16 @@
         <v>46210.64881809028</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I55" s="9">
         <v>46227</v>
@@ -4745,13 +4726,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Q55" s="9">
         <v>46227</v>
@@ -4771,7 +4752,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B56" s="5">
         <v>46156.63235533565</v>
@@ -4783,16 +4764,16 @@
         <v>46210.64938440973</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I56" s="5">
         <v>46231</v>
@@ -4810,13 +4791,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q56" s="5">
         <v>46231</v>
@@ -4836,7 +4817,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B57" s="9">
         <v>46156.63235945602</v>
@@ -4848,16 +4829,16 @@
         <v>46210.648830949074</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I57" s="9">
         <v>46227</v>
@@ -4875,13 +4856,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="Q57" s="9">
         <v>46227</v>
@@ -4901,7 +4882,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B58" s="5">
         <v>46156.63236322917</v>
@@ -4913,16 +4894,16 @@
         <v>46210.64939421296</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I58" s="5">
         <v>46231</v>
@@ -4940,13 +4921,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q58" s="5">
         <v>46231</v>
@@ -4966,7 +4947,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B59" s="9">
         <v>46156.63236744213</v>
@@ -4976,7 +4957,7 @@
         <v>46203.5014815162</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>25</v>
@@ -5000,7 +4981,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -5013,7 +4994,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B60" s="5">
         <v>46156.63237008102</v>
@@ -5025,16 +5006,16 @@
         <v>46211.68096902777</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I60" s="5">
         <v>46233</v>
@@ -5052,13 +5033,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q60" s="5">
         <v>46233</v>
@@ -5078,7 +5059,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B61" s="9">
         <v>46156.63237584491</v>
@@ -5090,16 +5071,16 @@
         <v>46211.68096520833</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I61" s="9">
         <v>46233</v>
@@ -5117,13 +5098,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5133,7 +5114,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B62" s="5">
         <v>46156.63239597222</v>
@@ -5143,16 +5124,16 @@
         <v>46211.65705916667</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I62" s="5">
         <v>46244</v>
@@ -5170,13 +5151,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q62" s="5">
         <v>46244</v>
@@ -5191,12 +5172,12 @@
         <v>0.5</v>
       </c>
       <c r="U62" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B63" s="9">
         <v>46156.632400069444</v>
@@ -5206,16 +5187,16 @@
         <v>46211.68097021991</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5233,13 +5214,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="O63" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>226</v>
-      </c>
-      <c r="O63" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>229</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5249,7 +5230,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B64" s="5">
         <v>46156.63246734954</v>
@@ -5259,16 +5240,16 @@
         <v>46197.83505042824</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I64" s="5">
         <v>46262</v>
@@ -5286,13 +5267,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5307,12 +5288,12 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B65" s="9">
         <v>46156.632472627316</v>
@@ -5322,16 +5303,16 @@
         <v>46197.83511621528</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I65" s="9">
         <v>46262</v>
@@ -5349,13 +5330,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5365,7 +5346,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
         <v>46156.6324928588</v>
@@ -5377,7 +5358,7 @@
         <v>46212.59671021991</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5401,7 +5382,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5418,7 +5399,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B67" s="9">
         <v>46156.63249635417</v>
@@ -5430,16 +5411,16 @@
         <v>46210.64718186343</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I67" s="9">
         <v>46154</v>
@@ -5457,13 +5438,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Q67" s="9">
         <v>46154</v>
@@ -5483,7 +5464,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B68" s="5">
         <v>46156.63250229167</v>
@@ -5495,16 +5476,16 @@
         <v>46210.64712949074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I68" s="5">
         <v>46268</v>
@@ -5522,13 +5503,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Q68" s="5">
         <v>46268</v>
@@ -5548,7 +5529,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B69" s="9">
         <v>46156.63250851852</v>
@@ -5560,16 +5541,16 @@
         <v>46210.645706863426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I69" s="9">
         <v>46294</v>
@@ -5587,13 +5568,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Q69" s="9">
         <v>46294</v>
@@ -5613,7 +5594,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B70" s="5">
         <v>46156.63251465278</v>
@@ -5625,16 +5606,16 @@
         <v>46212.59669387732</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I70" s="5">
         <v>46255</v>
@@ -5652,13 +5633,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="Q70" s="5">
         <v>46255</v>
@@ -5678,7 +5659,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B71" s="9">
         <v>46156.63251914352</v>
@@ -5688,7 +5669,7 @@
         <v>46213.50747597222</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5712,7 +5693,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5725,7 +5706,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B72" s="5">
         <v>46156.63252219907</v>
@@ -5735,17 +5716,15 @@
         <v>46212.59668103009</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H72" s="6"/>
       <c r="I72" s="5">
         <v>46266</v>
       </c>
@@ -5762,13 +5741,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q72" s="5">
         <v>46266</v>
@@ -5783,12 +5762,12 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B73" s="9">
         <v>46156.63252934028</v>
@@ -5798,17 +5777,15 @@
         <v>46212.59668166666</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H73" s="10"/>
       <c r="I73" s="9">
         <v>46266</v>
       </c>
@@ -5825,10 +5802,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5841,7 +5818,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B74" s="5">
         <v>46156.63254586805</v>
@@ -5853,17 +5830,15 @@
         <v>46213.50742533564</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H74" s="6"/>
       <c r="I74" s="5">
         <v>46288</v>
       </c>
@@ -5880,13 +5855,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q74" s="5">
         <v>46288</v>
@@ -5906,7 +5881,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B75" s="9">
         <v>46156.63255047453</v>
@@ -5916,17 +5891,15 @@
         <v>46210.647096342596</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H75" s="10"/>
       <c r="I75" s="9">
         <v>46288</v>
       </c>
@@ -5943,13 +5916,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="O75" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="P75" s="10" t="s">
         <v>253</v>
-      </c>
-      <c r="O75" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="P75" s="10" t="s">
-        <v>256</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5959,7 +5932,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B76" s="5">
         <v>46156.63257873843</v>
@@ -5971,17 +5944,15 @@
         <v>46213.5074855787</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H76" s="6"/>
       <c r="I76" s="5">
         <v>46290</v>
       </c>
@@ -5998,13 +5969,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q76" s="5">
         <v>46290</v>
@@ -6024,7 +5995,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B77" s="9">
         <v>46156.632582986116</v>
@@ -6034,17 +6005,15 @@
         <v>46210.64708005787</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H77" s="10"/>
       <c r="I77" s="9">
         <v>46290</v>
       </c>
@@ -6061,13 +6030,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6077,7 +6046,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B78" s="5">
         <v>46156.632655671296</v>
@@ -6087,17 +6056,15 @@
         <v>46156.72653921296</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H78" s="6"/>
       <c r="I78" s="5">
         <v>46296</v>
       </c>
@@ -6114,13 +6081,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q78" s="5">
         <v>46296</v>
@@ -6135,12 +6102,12 @@
         <v>0</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B79" s="9">
         <v>46156.6326615162</v>
@@ -6150,17 +6117,15 @@
         <v>46210.645696875</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H79" s="10"/>
       <c r="I79" s="9">
         <v>46296</v>
       </c>
@@ -6177,13 +6142,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="O79" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="P79" s="10" t="s">
         <v>262</v>
-      </c>
-      <c r="O79" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="P79" s="10" t="s">
-        <v>265</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6193,7 +6158,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B80" s="5">
         <v>46156.6326856713</v>
@@ -6203,17 +6168,15 @@
         <v>46156.72653572916</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H80" s="6"/>
       <c r="I80" s="5">
         <v>46300</v>
       </c>
@@ -6230,13 +6193,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q80" s="5">
         <v>46300</v>
@@ -6251,12 +6214,12 @@
         <v>0</v>
       </c>
       <c r="U80" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B81" s="9">
         <v>46156.63269413194</v>
@@ -6266,17 +6229,15 @@
         <v>46156.72676160879</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H81" s="10"/>
       <c r="I81" s="9">
         <v>46300</v>
       </c>
@@ -6293,13 +6254,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6309,7 +6270,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B82" s="5">
         <v>46156.632715810185</v>
@@ -6319,17 +6280,15 @@
         <v>46156.726531747685</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H82" s="6"/>
       <c r="I82" s="5">
         <v>46302</v>
       </c>
@@ -6346,13 +6305,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Q82" s="5">
         <v>46302</v>
@@ -6367,12 +6326,12 @@
         <v>0</v>
       </c>
       <c r="U82" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B83" s="9">
         <v>46156.63272170139</v>
@@ -6382,17 +6341,15 @@
         <v>46156.72680289352</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H83" s="10"/>
       <c r="I83" s="9">
         <v>46302</v>
       </c>
@@ -6409,13 +6366,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="O83" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="P83" s="10" t="s">
         <v>271</v>
-      </c>
-      <c r="O83" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="P83" s="10" t="s">
-        <v>274</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6425,7 +6382,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B84" s="5">
         <v>46156.63273993056</v>
@@ -6435,7 +6392,7 @@
         <v>46205.90465030093</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6459,7 +6416,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6472,7 +6429,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B85" s="9">
         <v>46156.63274356481</v>
@@ -6482,16 +6439,16 @@
         <v>46156.7268765162</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I85" s="9">
         <v>46303</v>
@@ -6509,13 +6466,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="Q85" s="9">
         <v>46303</v>
@@ -6530,12 +6487,12 @@
         <v>0</v>
       </c>
       <c r="U85" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B86" s="5">
         <v>46156.63274915509</v>
@@ -6545,16 +6502,16 @@
         <v>46156.72692035879</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I86" s="5">
         <v>46303</v>
@@ -6572,13 +6529,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6588,7 +6545,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B87" s="9">
         <v>46156.63276633102</v>
@@ -6598,17 +6555,15 @@
         <v>46156.72700125</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H87" s="10"/>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
         <v>46304</v>
@@ -6623,13 +6578,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="Q87" s="9">
         <v>46304</v>
@@ -6644,12 +6599,12 @@
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B88" s="5">
         <v>46156.63277084491</v>
@@ -6659,17 +6614,15 @@
         <v>46156.72697212963</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H88" s="6"/>
       <c r="I88" s="5">
         <v>46304</v>
       </c>
@@ -6686,13 +6639,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6702,7 +6655,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B89" s="9">
         <v>46156.63283398148</v>
@@ -6714,16 +6667,16 @@
         <v>46205.904737627316</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I89" s="9">
         <v>46307</v>
@@ -6741,13 +6694,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="Q89" s="9">
         <v>46307</v>
@@ -6762,12 +6715,12 @@
         <v>1</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B90" s="5">
         <v>46156.63284013889</v>
@@ -6779,16 +6732,16 @@
         <v>46205.90481071759</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I90" s="5">
         <v>46307</v>
@@ -6806,13 +6759,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6822,7 +6775,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B91" s="9">
         <v>46156.63286864583</v>
@@ -6832,16 +6785,16 @@
         <v>46156.727220243054</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I91" s="9">
         <v>46308</v>
@@ -6859,13 +6812,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Q91" s="9">
         <v>46308</v>
@@ -6880,12 +6833,12 @@
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B92" s="5">
         <v>46156.632875972224</v>
@@ -6895,16 +6848,16 @@
         <v>46205.9047287037</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -6920,13 +6873,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6936,7 +6889,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B93" s="9">
         <v>46156.63290420139</v>
@@ -6946,7 +6899,7 @@
         <v>46156.71731457176</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>25</v>
@@ -6970,7 +6923,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>26</v>
@@ -6983,7 +6936,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B94" s="5">
         <v>46156.63290788194</v>
@@ -6993,16 +6946,16 @@
         <v>46156.72728918982</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="I94" s="5">
         <v>46309</v>
@@ -7020,13 +6973,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="Q94" s="5">
         <v>46309</v>
@@ -7041,12 +6994,12 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B95" s="9">
         <v>46156.63291414352</v>
@@ -7056,7 +7009,7 @@
         <v>46209.559051539356</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7083,13 +7036,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="Q95" s="9">
         <v>46309</v>
@@ -7104,7 +7057,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="303">
   <si>
     <t>50001547 - XEMORTIZ (AMERICAS GOLD)</t>
   </si>
@@ -448,6 +448,9 @@
   </si>
   <si>
     <t xml:space="preserve">Generación OC materiales corte Laser OT 4317,Fabricacion Corte Laser OT 4317 </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1214809416559849</t>
@@ -3388,7 +3391,7 @@
         <v>46199.55979506944</v>
       </c>
       <c r="D33" s="9">
-        <v>46199.55980914352</v>
+        <v>46219.184870613426</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>125</v>
@@ -3432,8 +3435,8 @@
       <c r="R33" s="9">
         <v>46226</v>
       </c>
-      <c r="S33" s="7" t="s">
-        <v>33</v>
+      <c r="S33" s="12" t="s">
+        <v>129</v>
       </c>
       <c r="T33" s="10">
         <v>1</v>
@@ -3444,7 +3447,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46156.63219359954</v>
@@ -3456,7 +3459,7 @@
         <v>46199.55917045139</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3489,7 +3492,7 @@
         <v>75</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3505,7 +3508,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B35" s="9">
         <v>46156.63219844908</v>
@@ -3517,7 +3520,7 @@
         <v>46199.5597825</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
@@ -3547,10 +3550,10 @@
         <v>125</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3566,7 +3569,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46156.63225444444</v>
@@ -3575,10 +3578,10 @@
         <v>46199.55997423611</v>
       </c>
       <c r="D36" s="5">
-        <v>46199.55998701389</v>
+        <v>46219.18487111111</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3608,7 +3611,7 @@
         <v>89</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3619,8 +3622,8 @@
       <c r="R36" s="5">
         <v>46226</v>
       </c>
-      <c r="S36" s="7" t="s">
-        <v>33</v>
+      <c r="S36" s="12" t="s">
+        <v>129</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -3631,7 +3634,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B37" s="9">
         <v>46156.632258206024</v>
@@ -3670,13 +3673,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>80</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3686,7 +3689,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46156.63226241898</v>
@@ -3698,7 +3701,7 @@
         <v>46199.55996042824</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3725,13 +3728,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>81</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3741,7 +3744,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B39" s="9">
         <v>46156.63226644676</v>
@@ -3753,16 +3756,16 @@
         <v>46210.649648715276</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I39" s="9">
         <v>46216</v>
@@ -3783,7 +3786,7 @@
         <v>89</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3806,7 +3809,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46156.632269444446</v>
@@ -3824,10 +3827,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I40" s="5">
         <v>46216</v>
@@ -3845,13 +3848,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3861,7 +3864,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" s="9">
         <v>46156.63227357639</v>
@@ -3873,16 +3876,16 @@
         <v>46204.86000238426</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I41" s="9">
         <v>46225</v>
@@ -3900,13 +3903,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>87</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3916,7 +3919,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46156.63227760416</v>
@@ -3928,16 +3931,16 @@
         <v>46210.64958435185</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I42" s="5">
         <v>46254</v>
@@ -3955,10 +3958,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3971,7 +3974,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B43" s="9">
         <v>46156.63228021991</v>
@@ -3980,10 +3983,10 @@
         <v>46199.56230621527</v>
       </c>
       <c r="D43" s="9">
-        <v>46199.562315937495</v>
+        <v>46219.1848712963</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
@@ -4013,7 +4016,7 @@
         <v>89</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4024,8 +4027,8 @@
       <c r="R43" s="9">
         <v>46226</v>
       </c>
-      <c r="S43" s="7" t="s">
-        <v>33</v>
+      <c r="S43" s="12" t="s">
+        <v>129</v>
       </c>
       <c r="T43" s="10">
         <v>1</v>
@@ -4036,7 +4039,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46156.63228315972</v>
@@ -4075,13 +4078,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4091,7 +4094,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B45" s="9">
         <v>46156.63228715278</v>
@@ -4103,7 +4106,7 @@
         <v>46199.56229454861</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4130,13 +4133,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>84</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4146,7 +4149,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>46156.63196493055</v>
@@ -4156,7 +4159,7 @@
         <v>46184.58079096065</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4180,7 +4183,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4190,12 +4193,12 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" s="9">
         <v>46156.63229164352</v>
@@ -4207,16 +4210,16 @@
         <v>46197.714709479165</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I47" s="9">
         <v>46150</v>
@@ -4234,13 +4237,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q47" s="9">
         <v>46150</v>
@@ -4260,7 +4263,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46156.632296261574</v>
@@ -4272,16 +4275,16 @@
         <v>46212.59685061342</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I48" s="5">
         <v>46204</v>
@@ -4299,13 +4302,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="5">
         <v>46204</v>
@@ -4325,7 +4328,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B49" s="9">
         <v>46156.63230224537</v>
@@ -4343,10 +4346,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4362,13 +4365,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q49" s="9">
         <v>46211</v>
@@ -4388,7 +4391,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46156.632315358795</v>
@@ -4398,16 +4401,16 @@
         <v>46156.72589140046</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I50" s="5">
         <v>46301</v>
@@ -4425,10 +4428,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4451,7 +4454,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B51" s="9">
         <v>46156.6323189699</v>
@@ -4461,16 +4464,16 @@
         <v>46156.725962881945</v>
       </c>
       <c r="E51" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I51" s="9">
         <v>46301</v>
@@ -4488,13 +4491,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4504,7 +4507,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46156.63233141204</v>
@@ -4516,7 +4519,7 @@
         <v>46210.64940796296</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4540,7 +4543,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4557,7 +4560,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
         <v>46156.63233460648</v>
@@ -4569,16 +4572,16 @@
         <v>46210.64881278935</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I53" s="9">
         <v>46227</v>
@@ -4596,13 +4599,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q53" s="9">
         <v>46227</v>
@@ -4622,7 +4625,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46156.63233969908</v>
@@ -4634,16 +4637,16 @@
         <v>46210.649371875</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I54" s="5">
         <v>46231</v>
@@ -4661,13 +4664,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q54" s="5">
         <v>46231</v>
@@ -4687,7 +4690,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B55" s="9">
         <v>46156.632350671294</v>
@@ -4699,16 +4702,16 @@
         <v>46210.64881809028</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I55" s="9">
         <v>46227</v>
@@ -4726,13 +4729,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q55" s="9">
         <v>46227</v>
@@ -4752,7 +4755,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B56" s="5">
         <v>46156.63235533565</v>
@@ -4764,16 +4767,16 @@
         <v>46210.64938440973</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I56" s="5">
         <v>46231</v>
@@ -4791,13 +4794,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q56" s="5">
         <v>46231</v>
@@ -4817,7 +4820,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B57" s="9">
         <v>46156.63235945602</v>
@@ -4829,16 +4832,16 @@
         <v>46210.648830949074</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I57" s="9">
         <v>46227</v>
@@ -4856,13 +4859,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q57" s="9">
         <v>46227</v>
@@ -4882,7 +4885,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B58" s="5">
         <v>46156.63236322917</v>
@@ -4894,16 +4897,16 @@
         <v>46210.64939421296</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I58" s="5">
         <v>46231</v>
@@ -4921,13 +4924,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q58" s="5">
         <v>46231</v>
@@ -4947,7 +4950,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B59" s="9">
         <v>46156.63236744213</v>
@@ -4957,7 +4960,7 @@
         <v>46203.5014815162</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>25</v>
@@ -4981,7 +4984,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -4994,7 +4997,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B60" s="5">
         <v>46156.63237008102</v>
@@ -5006,16 +5009,16 @@
         <v>46211.68096902777</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I60" s="5">
         <v>46233</v>
@@ -5033,13 +5036,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q60" s="5">
         <v>46233</v>
@@ -5059,7 +5062,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B61" s="9">
         <v>46156.63237584491</v>
@@ -5071,16 +5074,16 @@
         <v>46211.68096520833</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I61" s="9">
         <v>46233</v>
@@ -5098,13 +5101,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5114,7 +5117,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B62" s="5">
         <v>46156.63239597222</v>
@@ -5124,16 +5127,16 @@
         <v>46211.65705916667</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I62" s="5">
         <v>46244</v>
@@ -5151,13 +5154,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q62" s="5">
         <v>46244</v>
@@ -5172,12 +5175,12 @@
         <v>0.5</v>
       </c>
       <c r="U62" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B63" s="9">
         <v>46156.632400069444</v>
@@ -5187,16 +5190,16 @@
         <v>46211.68097021991</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5214,13 +5217,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5230,7 +5233,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B64" s="5">
         <v>46156.63246734954</v>
@@ -5240,16 +5243,16 @@
         <v>46197.83505042824</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I64" s="5">
         <v>46262</v>
@@ -5267,13 +5270,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5293,7 +5296,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B65" s="9">
         <v>46156.632472627316</v>
@@ -5303,16 +5306,16 @@
         <v>46197.83511621528</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I65" s="9">
         <v>46262</v>
@@ -5330,13 +5333,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5346,7 +5349,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B66" s="5">
         <v>46156.6324928588</v>
@@ -5358,7 +5361,7 @@
         <v>46212.59671021991</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5382,7 +5385,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5399,7 +5402,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B67" s="9">
         <v>46156.63249635417</v>
@@ -5411,16 +5414,16 @@
         <v>46210.64718186343</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I67" s="9">
         <v>46154</v>
@@ -5438,13 +5441,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>110</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q67" s="9">
         <v>46154</v>
@@ -5464,7 +5467,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B68" s="5">
         <v>46156.63250229167</v>
@@ -5476,16 +5479,16 @@
         <v>46210.64712949074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I68" s="5">
         <v>46268</v>
@@ -5503,13 +5506,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>101</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q68" s="5">
         <v>46268</v>
@@ -5529,7 +5532,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B69" s="9">
         <v>46156.63250851852</v>
@@ -5541,16 +5544,16 @@
         <v>46210.645706863426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I69" s="9">
         <v>46294</v>
@@ -5568,13 +5571,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>119</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q69" s="9">
         <v>46294</v>
@@ -5594,7 +5597,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B70" s="5">
         <v>46156.63251465278</v>
@@ -5606,16 +5609,16 @@
         <v>46212.59669387732</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I70" s="5">
         <v>46255</v>
@@ -5633,13 +5636,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q70" s="5">
         <v>46255</v>
@@ -5659,7 +5662,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B71" s="9">
         <v>46156.63251914352</v>
@@ -5669,7 +5672,7 @@
         <v>46213.50747597222</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5693,7 +5696,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5706,7 +5709,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B72" s="5">
         <v>46156.63252219907</v>
@@ -5716,7 +5719,7 @@
         <v>46212.59668103009</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5741,13 +5744,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q72" s="5">
         <v>46266</v>
@@ -5767,7 +5770,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B73" s="9">
         <v>46156.63252934028</v>
@@ -5777,7 +5780,7 @@
         <v>46212.59668166666</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5802,10 +5805,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5818,7 +5821,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B74" s="5">
         <v>46156.63254586805</v>
@@ -5830,7 +5833,7 @@
         <v>46213.50742533564</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5855,13 +5858,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q74" s="5">
         <v>46288</v>
@@ -5881,7 +5884,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B75" s="9">
         <v>46156.63255047453</v>
@@ -5891,7 +5894,7 @@
         <v>46210.647096342596</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5916,13 +5919,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5932,7 +5935,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B76" s="5">
         <v>46156.63257873843</v>
@@ -5944,7 +5947,7 @@
         <v>46213.5074855787</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5969,13 +5972,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q76" s="5">
         <v>46290</v>
@@ -5995,7 +5998,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B77" s="9">
         <v>46156.632582986116</v>
@@ -6005,7 +6008,7 @@
         <v>46210.64708005787</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6030,13 +6033,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6046,7 +6049,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B78" s="5">
         <v>46156.632655671296</v>
@@ -6056,7 +6059,7 @@
         <v>46156.72653921296</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6081,13 +6084,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q78" s="5">
         <v>46296</v>
@@ -6107,7 +6110,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B79" s="9">
         <v>46156.6326615162</v>
@@ -6117,7 +6120,7 @@
         <v>46210.645696875</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6142,13 +6145,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6158,7 +6161,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B80" s="5">
         <v>46156.6326856713</v>
@@ -6168,7 +6171,7 @@
         <v>46156.72653572916</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6193,13 +6196,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q80" s="5">
         <v>46300</v>
@@ -6219,7 +6222,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B81" s="9">
         <v>46156.63269413194</v>
@@ -6229,7 +6232,7 @@
         <v>46156.72676160879</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6254,13 +6257,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6270,7 +6273,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B82" s="5">
         <v>46156.632715810185</v>
@@ -6280,7 +6283,7 @@
         <v>46156.726531747685</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6305,13 +6308,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q82" s="5">
         <v>46302</v>
@@ -6331,7 +6334,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B83" s="9">
         <v>46156.63272170139</v>
@@ -6341,7 +6344,7 @@
         <v>46156.72680289352</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6366,13 +6369,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6382,7 +6385,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B84" s="5">
         <v>46156.63273993056</v>
@@ -6392,7 +6395,7 @@
         <v>46205.90465030093</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6416,7 +6419,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6429,7 +6432,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B85" s="9">
         <v>46156.63274356481</v>
@@ -6439,16 +6442,16 @@
         <v>46156.7268765162</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I85" s="9">
         <v>46303</v>
@@ -6466,13 +6469,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q85" s="9">
         <v>46303</v>
@@ -6492,7 +6495,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B86" s="5">
         <v>46156.63274915509</v>
@@ -6502,16 +6505,16 @@
         <v>46156.72692035879</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I86" s="5">
         <v>46303</v>
@@ -6529,13 +6532,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6545,7 +6548,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B87" s="9">
         <v>46156.63276633102</v>
@@ -6555,7 +6558,7 @@
         <v>46156.72700125</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6578,13 +6581,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q87" s="9">
         <v>46304</v>
@@ -6604,7 +6607,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B88" s="5">
         <v>46156.63277084491</v>
@@ -6614,7 +6617,7 @@
         <v>46156.72697212963</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6639,13 +6642,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6655,7 +6658,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B89" s="9">
         <v>46156.63283398148</v>
@@ -6667,16 +6670,16 @@
         <v>46205.904737627316</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I89" s="9">
         <v>46307</v>
@@ -6694,13 +6697,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q89" s="9">
         <v>46307</v>
@@ -6715,12 +6718,12 @@
         <v>1</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B90" s="5">
         <v>46156.63284013889</v>
@@ -6732,16 +6735,16 @@
         <v>46205.90481071759</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I90" s="5">
         <v>46307</v>
@@ -6759,13 +6762,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6775,7 +6778,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B91" s="9">
         <v>46156.63286864583</v>
@@ -6785,16 +6788,16 @@
         <v>46156.727220243054</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I91" s="9">
         <v>46308</v>
@@ -6812,13 +6815,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q91" s="9">
         <v>46308</v>
@@ -6838,7 +6841,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B92" s="5">
         <v>46156.632875972224</v>
@@ -6848,16 +6851,16 @@
         <v>46205.9047287037</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -6873,13 +6876,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6889,7 +6892,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B93" s="9">
         <v>46156.63290420139</v>
@@ -6899,7 +6902,7 @@
         <v>46156.71731457176</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>25</v>
@@ -6923,7 +6926,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>26</v>
@@ -6936,7 +6939,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B94" s="5">
         <v>46156.63290788194</v>
@@ -6946,16 +6949,16 @@
         <v>46156.72728918982</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I94" s="5">
         <v>46309</v>
@@ -6973,13 +6976,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q94" s="5">
         <v>46309</v>
@@ -6999,7 +7002,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B95" s="9">
         <v>46156.63291414352</v>
@@ -7009,7 +7012,7 @@
         <v>46209.559051539356</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7036,13 +7039,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q95" s="9">
         <v>46309</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="304">
   <si>
     <t>50001547 - XEMORTIZ (AMERICAS GOLD)</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete OT 4317</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Rodete OT 4317</t>
@@ -2401,7 +2404,7 @@
         <v>46197.50203898148</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.5020416551</v>
+        <v>46223.586521875</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>72</v>
@@ -2410,9 +2413,11 @@
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I17" s="9">
         <v>46150</v>
       </c>
@@ -2435,7 +2440,7 @@
         <v>56</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="9">
         <v>46150</v>
@@ -2455,7 +2460,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" s="5">
         <v>46156.632121504634</v>
@@ -2464,18 +2469,20 @@
         <v>46196.656259456024</v>
       </c>
       <c r="D18" s="5">
-        <v>46214.206295462965</v>
+        <v>46223.586517777774</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I18" s="5">
         <v>46212</v>
       </c>
@@ -2495,10 +2502,10 @@
         <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q18" s="5">
         <v>46212</v>
@@ -2507,7 +2514,7 @@
         <v>46213</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2518,7 +2525,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="9">
         <v>46156.63212631944</v>
@@ -2527,18 +2534,20 @@
         <v>46196.65655393519</v>
       </c>
       <c r="D19" s="9">
-        <v>46214.20629638889</v>
+        <v>46223.58651417824</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I19" s="9">
         <v>46212</v>
       </c>
@@ -2558,10 +2567,10 @@
         <v>63</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q19" s="9">
         <v>46212</v>
@@ -2570,7 +2579,7 @@
         <v>46213</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T19" s="10">
         <v>1</v>
@@ -2581,7 +2590,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B20" s="5">
         <v>46156.63213005787</v>
@@ -2590,18 +2599,20 @@
         <v>46196.65716653936</v>
       </c>
       <c r="D20" s="5">
-        <v>46214.20629671296</v>
+        <v>46223.58651050926</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I20" s="5">
         <v>46212</v>
       </c>
@@ -2621,10 +2632,10 @@
         <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="5">
         <v>46212</v>
@@ -2633,7 +2644,7 @@
         <v>46213</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -2644,7 +2655,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B21" s="9">
         <v>46156.632133692125</v>
@@ -2653,18 +2664,20 @@
         <v>46196.65766008102</v>
       </c>
       <c r="D21" s="9">
-        <v>46214.20629545139</v>
+        <v>46223.586505706015</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I21" s="9">
         <v>46212</v>
       </c>
@@ -2684,10 +2697,10 @@
         <v>63</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q21" s="9">
         <v>46212</v>
@@ -2696,7 +2709,7 @@
         <v>46213</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T21" s="10">
         <v>1</v>
@@ -2707,7 +2720,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5">
         <v>46156.6319605787</v>
@@ -2719,7 +2732,7 @@
         <v>46212.59677189815</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2743,7 +2756,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2760,7 +2773,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" s="9">
         <v>46156.63213814815</v>
@@ -2772,16 +2785,16 @@
         <v>46210.6467582176</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I23" s="9">
         <v>46154</v>
@@ -2799,13 +2812,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q23" s="9">
         <v>46154</v>
@@ -2825,7 +2838,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5">
         <v>46156.63214259259</v>
@@ -2837,16 +2850,16 @@
         <v>46195.92922337963</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I24" s="5">
         <v>46154</v>
@@ -2864,13 +2877,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2881,12 +2894,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B25" s="9">
         <v>46156.63214717593</v>
@@ -2898,16 +2911,16 @@
         <v>46210.64669667824</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I25" s="9">
         <v>46156</v>
@@ -2925,13 +2938,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -2942,12 +2955,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5">
         <v>46156.6321521412</v>
@@ -2959,16 +2972,16 @@
         <v>46210.64698900463</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I26" s="5">
         <v>46150</v>
@@ -2986,13 +2999,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q26" s="5">
         <v>46150</v>
@@ -3012,7 +3025,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B27" s="9">
         <v>46156.63215657407</v>
@@ -3024,16 +3037,16 @@
         <v>46210.64692099537</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I27" s="9">
         <v>46150</v>
@@ -3051,13 +3064,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3068,12 +3081,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5">
         <v>46156.63216167824</v>
@@ -3085,16 +3098,16 @@
         <v>46210.64695642361</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I28" s="5">
         <v>46150</v>
@@ -3112,13 +3125,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3129,12 +3142,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B29" s="9">
         <v>46156.63216756945</v>
@@ -3146,16 +3159,16 @@
         <v>46210.645560289355</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I29" s="9">
         <v>46142</v>
@@ -3173,13 +3186,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q29" s="9">
         <v>46172</v>
@@ -3199,7 +3212,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46156.63217278935</v>
@@ -3211,16 +3224,16 @@
         <v>46195.92957241899</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I30" s="5">
         <v>46142</v>
@@ -3238,13 +3251,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3255,12 +3268,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31" s="9">
         <v>46156.63217837963</v>
@@ -3272,16 +3285,16 @@
         <v>46210.64553332176</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I31" s="9">
         <v>46164</v>
@@ -3299,13 +3312,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3316,12 +3329,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46156.63218368056</v>
@@ -3333,16 +3346,16 @@
         <v>46197.78355364583</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I32" s="5">
         <v>46164</v>
@@ -3360,13 +3373,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3377,12 +3390,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B33" s="9">
         <v>46156.632188240736</v>
@@ -3394,16 +3407,16 @@
         <v>46219.184870613426</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I33" s="9">
         <v>46216</v>
@@ -3421,13 +3434,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q33" s="9">
         <v>46216</v>
@@ -3436,7 +3449,7 @@
         <v>46226</v>
       </c>
       <c r="S33" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T33" s="10">
         <v>1</v>
@@ -3447,7 +3460,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46156.63219359954</v>
@@ -3459,16 +3472,16 @@
         <v>46199.55917045139</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I34" s="5">
         <v>46216</v>
@@ -3486,13 +3499,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3503,12 +3516,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B35" s="9">
         <v>46156.63219844908</v>
@@ -3520,16 +3533,16 @@
         <v>46199.5597825</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I35" s="9">
         <v>46218</v>
@@ -3547,13 +3560,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3564,12 +3577,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46156.63225444444</v>
@@ -3581,16 +3594,16 @@
         <v>46219.18487111111</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I36" s="5">
         <v>46216</v>
@@ -3608,10 +3621,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3623,7 +3636,7 @@
         <v>46226</v>
       </c>
       <c r="S36" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -3634,7 +3647,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B37" s="9">
         <v>46156.632258206024</v>
@@ -3646,16 +3659,16 @@
         <v>46199.55991087963</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I37" s="9">
         <v>46216</v>
@@ -3673,13 +3686,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3689,7 +3702,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46156.63226241898</v>
@@ -3701,16 +3714,16 @@
         <v>46199.55996042824</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I38" s="5">
         <v>46218</v>
@@ -3728,13 +3741,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3744,7 +3757,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="9">
         <v>46156.63226644676</v>
@@ -3756,16 +3769,16 @@
         <v>46210.649648715276</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I39" s="9">
         <v>46216</v>
@@ -3783,10 +3796,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3809,7 +3822,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46156.632269444446</v>
@@ -3821,16 +3834,16 @@
         <v>46196.69978633102</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46216</v>
@@ -3848,13 +3861,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3864,7 +3877,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" s="9">
         <v>46156.63227357639</v>
@@ -3876,16 +3889,16 @@
         <v>46204.86000238426</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I41" s="9">
         <v>46225</v>
@@ -3903,13 +3916,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3919,7 +3932,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46156.63227760416</v>
@@ -3931,16 +3944,16 @@
         <v>46210.64958435185</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I42" s="5">
         <v>46254</v>
@@ -3958,10 +3971,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3974,7 +3987,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" s="9">
         <v>46156.63228021991</v>
@@ -3986,16 +3999,16 @@
         <v>46219.1848712963</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I43" s="9">
         <v>46216</v>
@@ -4013,10 +4026,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4028,7 +4041,7 @@
         <v>46226</v>
       </c>
       <c r="S43" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T43" s="10">
         <v>1</v>
@@ -4039,7 +4052,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46156.63228315972</v>
@@ -4051,16 +4064,16 @@
         <v>46199.56224427083</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I44" s="5">
         <v>46216</v>
@@ -4078,13 +4091,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4094,7 +4107,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B45" s="9">
         <v>46156.63228715278</v>
@@ -4106,16 +4119,16 @@
         <v>46199.56229454861</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I45" s="9">
         <v>46218</v>
@@ -4133,13 +4146,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4149,7 +4162,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46156.63196493055</v>
@@ -4159,7 +4172,7 @@
         <v>46184.58079096065</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4183,7 +4196,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4193,12 +4206,12 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="9">
         <v>46156.63229164352</v>
@@ -4210,16 +4223,16 @@
         <v>46197.714709479165</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I47" s="9">
         <v>46150</v>
@@ -4237,13 +4250,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="9">
         <v>46150</v>
@@ -4252,7 +4265,7 @@
         <v>46156</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T47" s="10">
         <v>1</v>
@@ -4263,7 +4276,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46156.632296261574</v>
@@ -4275,16 +4288,16 @@
         <v>46212.59685061342</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46204</v>
@@ -4302,13 +4315,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46204</v>
@@ -4317,7 +4330,7 @@
         <v>46210</v>
       </c>
       <c r="S48" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T48" s="6">
         <v>1</v>
@@ -4328,7 +4341,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46156.63230224537</v>
@@ -4340,16 +4353,16 @@
         <v>46212.1877253125</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4365,13 +4378,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="9">
         <v>46211</v>
@@ -4380,7 +4393,7 @@
         <v>46211</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>
@@ -4391,7 +4404,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46156.632315358795</v>
@@ -4401,16 +4414,16 @@
         <v>46156.72589140046</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I50" s="5">
         <v>46301</v>
@@ -4428,10 +4441,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4449,12 +4462,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46156.6323189699</v>
@@ -4464,16 +4477,16 @@
         <v>46156.725962881945</v>
       </c>
       <c r="E51" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="I51" s="9">
         <v>46301</v>
@@ -4491,13 +4504,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4507,7 +4520,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46156.63233141204</v>
@@ -4519,7 +4532,7 @@
         <v>46210.64940796296</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4543,7 +4556,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4560,7 +4573,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="9">
         <v>46156.63233460648</v>
@@ -4569,19 +4582,19 @@
         <v>46210.648792141204</v>
       </c>
       <c r="D53" s="9">
-        <v>46210.64881278935</v>
+        <v>46223.20114935185</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I53" s="9">
         <v>46227</v>
@@ -4599,13 +4612,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q53" s="9">
         <v>46227</v>
@@ -4613,8 +4626,8 @@
       <c r="R53" s="9">
         <v>46230</v>
       </c>
-      <c r="S53" s="7" t="s">
-        <v>33</v>
+      <c r="S53" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="T53" s="10">
         <v>1</v>
@@ -4625,7 +4638,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B54" s="5">
         <v>46156.63233969908</v>
@@ -4637,16 +4650,16 @@
         <v>46210.649371875</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I54" s="5">
         <v>46231</v>
@@ -4664,13 +4677,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q54" s="5">
         <v>46231</v>
@@ -4690,7 +4703,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B55" s="9">
         <v>46156.632350671294</v>
@@ -4699,19 +4712,19 @@
         <v>46210.64880347222</v>
       </c>
       <c r="D55" s="9">
-        <v>46210.64881809028</v>
+        <v>46223.201149155095</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I55" s="9">
         <v>46227</v>
@@ -4729,13 +4742,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q55" s="9">
         <v>46227</v>
@@ -4743,8 +4756,8 @@
       <c r="R55" s="9">
         <v>46230</v>
       </c>
-      <c r="S55" s="7" t="s">
-        <v>33</v>
+      <c r="S55" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="T55" s="10">
         <v>1</v>
@@ -4755,7 +4768,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B56" s="5">
         <v>46156.63235533565</v>
@@ -4767,16 +4780,16 @@
         <v>46210.64938440973</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I56" s="5">
         <v>46231</v>
@@ -4794,13 +4807,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q56" s="5">
         <v>46231</v>
@@ -4820,7 +4833,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B57" s="9">
         <v>46156.63235945602</v>
@@ -4829,19 +4842,19 @@
         <v>46210.648815740744</v>
       </c>
       <c r="D57" s="9">
-        <v>46210.648830949074</v>
+        <v>46223.20114922454</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I57" s="9">
         <v>46227</v>
@@ -4859,13 +4872,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q57" s="9">
         <v>46227</v>
@@ -4873,8 +4886,8 @@
       <c r="R57" s="9">
         <v>46230</v>
       </c>
-      <c r="S57" s="7" t="s">
-        <v>33</v>
+      <c r="S57" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="T57" s="10">
         <v>1</v>
@@ -4885,7 +4898,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B58" s="5">
         <v>46156.63236322917</v>
@@ -4897,16 +4910,16 @@
         <v>46210.64939421296</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I58" s="5">
         <v>46231</v>
@@ -4924,13 +4937,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q58" s="5">
         <v>46231</v>
@@ -4950,7 +4963,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B59" s="9">
         <v>46156.63236744213</v>
@@ -4960,7 +4973,7 @@
         <v>46203.5014815162</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>25</v>
@@ -4984,7 +4997,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -4997,7 +5010,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B60" s="5">
         <v>46156.63237008102</v>
@@ -5009,16 +5022,16 @@
         <v>46211.68096902777</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I60" s="5">
         <v>46233</v>
@@ -5036,13 +5049,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="5">
         <v>46233</v>
@@ -5062,7 +5075,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B61" s="9">
         <v>46156.63237584491</v>
@@ -5074,16 +5087,16 @@
         <v>46211.68096520833</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I61" s="9">
         <v>46233</v>
@@ -5101,13 +5114,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5117,7 +5130,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B62" s="5">
         <v>46156.63239597222</v>
@@ -5127,16 +5140,16 @@
         <v>46211.65705916667</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I62" s="5">
         <v>46244</v>
@@ -5154,13 +5167,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="5">
         <v>46244</v>
@@ -5175,12 +5188,12 @@
         <v>0.5</v>
       </c>
       <c r="U62" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B63" s="9">
         <v>46156.632400069444</v>
@@ -5190,16 +5203,16 @@
         <v>46211.68097021991</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5217,13 +5230,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5233,7 +5246,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B64" s="5">
         <v>46156.63246734954</v>
@@ -5243,16 +5256,16 @@
         <v>46197.83505042824</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I64" s="5">
         <v>46262</v>
@@ -5270,13 +5283,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5291,12 +5304,12 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B65" s="9">
         <v>46156.632472627316</v>
@@ -5306,16 +5319,16 @@
         <v>46197.83511621528</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I65" s="9">
         <v>46262</v>
@@ -5333,13 +5346,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5349,7 +5362,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B66" s="5">
         <v>46156.6324928588</v>
@@ -5361,7 +5374,7 @@
         <v>46212.59671021991</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5385,7 +5398,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5402,7 +5415,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B67" s="9">
         <v>46156.63249635417</v>
@@ -5414,16 +5427,16 @@
         <v>46210.64718186343</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I67" s="9">
         <v>46154</v>
@@ -5441,13 +5454,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q67" s="9">
         <v>46154</v>
@@ -5467,7 +5480,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B68" s="5">
         <v>46156.63250229167</v>
@@ -5479,16 +5492,16 @@
         <v>46210.64712949074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I68" s="5">
         <v>46268</v>
@@ -5506,13 +5519,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q68" s="5">
         <v>46268</v>
@@ -5532,7 +5545,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B69" s="9">
         <v>46156.63250851852</v>
@@ -5544,16 +5557,16 @@
         <v>46210.645706863426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I69" s="9">
         <v>46294</v>
@@ -5571,13 +5584,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q69" s="9">
         <v>46294</v>
@@ -5597,7 +5610,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B70" s="5">
         <v>46156.63251465278</v>
@@ -5609,16 +5622,16 @@
         <v>46212.59669387732</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I70" s="5">
         <v>46255</v>
@@ -5636,13 +5649,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q70" s="5">
         <v>46255</v>
@@ -5662,7 +5675,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B71" s="9">
         <v>46156.63251914352</v>
@@ -5672,7 +5685,7 @@
         <v>46213.50747597222</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5696,7 +5709,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5709,25 +5722,27 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B72" s="5">
         <v>46156.63252219907</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46212.59668103009</v>
+        <v>46223.587171493054</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H72" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I72" s="5">
         <v>46266</v>
       </c>
@@ -5744,13 +5759,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q72" s="5">
         <v>46266</v>
@@ -5765,30 +5780,32 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B73" s="9">
         <v>46156.63252934028</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46212.59668166666</v>
+        <v>46223.58665680556</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H73" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I73" s="9">
         <v>46266</v>
       </c>
@@ -5805,10 +5822,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5821,7 +5838,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B74" s="5">
         <v>46156.63254586805</v>
@@ -5830,18 +5847,20 @@
         <v>46213.50741020833</v>
       </c>
       <c r="D74" s="5">
-        <v>46213.50742533564</v>
+        <v>46223.58718354166</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H74" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I74" s="5">
         <v>46288</v>
       </c>
@@ -5858,13 +5877,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q74" s="5">
         <v>46288</v>
@@ -5884,25 +5903,27 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B75" s="9">
         <v>46156.63255047453</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46210.647096342596</v>
+        <v>46223.5867387037</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H75" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I75" s="9">
         <v>46288</v>
       </c>
@@ -5919,13 +5940,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5935,7 +5956,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B76" s="5">
         <v>46156.63257873843</v>
@@ -5944,18 +5965,20 @@
         <v>46213.50747125</v>
       </c>
       <c r="D76" s="5">
-        <v>46213.5074855787</v>
+        <v>46223.587179571754</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H76" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I76" s="5">
         <v>46290</v>
       </c>
@@ -5972,13 +5995,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q76" s="5">
         <v>46290</v>
@@ -5998,25 +6021,27 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B77" s="9">
         <v>46156.632582986116</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46210.64708005787</v>
+        <v>46223.58682719908</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H77" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I77" s="9">
         <v>46290</v>
       </c>
@@ -6033,13 +6058,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6049,25 +6074,27 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B78" s="5">
         <v>46156.632655671296</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46156.72653921296</v>
+        <v>46223.58716953704</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H78" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I78" s="5">
         <v>46296</v>
       </c>
@@ -6084,13 +6111,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q78" s="5">
         <v>46296</v>
@@ -6105,30 +6132,32 @@
         <v>0</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B79" s="9">
         <v>46156.6326615162</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46210.645696875</v>
+        <v>46223.58691267361</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H79" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I79" s="9">
         <v>46296</v>
       </c>
@@ -6145,13 +6174,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6161,25 +6190,27 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B80" s="5">
         <v>46156.6326856713</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46156.72653572916</v>
+        <v>46223.58716885417</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H80" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I80" s="5">
         <v>46300</v>
       </c>
@@ -6196,13 +6227,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q80" s="5">
         <v>46300</v>
@@ -6217,30 +6248,32 @@
         <v>0</v>
       </c>
       <c r="U80" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B81" s="9">
         <v>46156.63269413194</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46156.72676160879</v>
+        <v>46223.586982106484</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H81" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H81" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I81" s="9">
         <v>46300</v>
       </c>
@@ -6257,13 +6290,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6273,25 +6306,27 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B82" s="5">
         <v>46156.632715810185</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46156.726531747685</v>
+        <v>46223.58716818287</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H82" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I82" s="5">
         <v>46302</v>
       </c>
@@ -6308,13 +6343,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q82" s="5">
         <v>46302</v>
@@ -6329,30 +6364,32 @@
         <v>0</v>
       </c>
       <c r="U82" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B83" s="9">
         <v>46156.63272170139</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46156.72680289352</v>
+        <v>46223.5870543287</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H83" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I83" s="9">
         <v>46302</v>
       </c>
@@ -6369,13 +6406,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6385,7 +6422,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B84" s="5">
         <v>46156.63273993056</v>
@@ -6395,7 +6432,7 @@
         <v>46205.90465030093</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6419,7 +6456,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6432,7 +6469,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B85" s="9">
         <v>46156.63274356481</v>
@@ -6442,16 +6479,16 @@
         <v>46156.7268765162</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I85" s="9">
         <v>46303</v>
@@ -6469,13 +6506,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q85" s="9">
         <v>46303</v>
@@ -6490,12 +6527,12 @@
         <v>0</v>
       </c>
       <c r="U85" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B86" s="5">
         <v>46156.63274915509</v>
@@ -6505,16 +6542,16 @@
         <v>46156.72692035879</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I86" s="5">
         <v>46303</v>
@@ -6532,13 +6569,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6548,25 +6585,27 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B87" s="9">
         <v>46156.63276633102</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46156.72700125</v>
+        <v>46223.587295798614</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H87" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
         <v>46304</v>
@@ -6581,13 +6620,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q87" s="9">
         <v>46304</v>
@@ -6602,30 +6641,32 @@
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B88" s="5">
         <v>46156.63277084491</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46156.72697212963</v>
+        <v>46223.587235150466</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I88" s="5">
         <v>46304</v>
       </c>
@@ -6642,13 +6683,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6658,7 +6699,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B89" s="9">
         <v>46156.63283398148</v>
@@ -6670,16 +6711,16 @@
         <v>46205.904737627316</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I89" s="9">
         <v>46307</v>
@@ -6697,13 +6738,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q89" s="9">
         <v>46307</v>
@@ -6718,12 +6759,12 @@
         <v>1</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B90" s="5">
         <v>46156.63284013889</v>
@@ -6735,16 +6776,16 @@
         <v>46205.90481071759</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I90" s="5">
         <v>46307</v>
@@ -6762,13 +6803,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6778,7 +6819,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B91" s="9">
         <v>46156.63286864583</v>
@@ -6788,16 +6829,16 @@
         <v>46156.727220243054</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I91" s="9">
         <v>46308</v>
@@ -6815,13 +6856,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q91" s="9">
         <v>46308</v>
@@ -6836,12 +6877,12 @@
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B92" s="5">
         <v>46156.632875972224</v>
@@ -6851,16 +6892,16 @@
         <v>46205.9047287037</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -6876,13 +6917,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6892,7 +6933,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B93" s="9">
         <v>46156.63290420139</v>
@@ -6902,7 +6943,7 @@
         <v>46156.71731457176</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>25</v>
@@ -6926,7 +6967,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>26</v>
@@ -6939,7 +6980,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B94" s="5">
         <v>46156.63290788194</v>
@@ -6949,16 +6990,16 @@
         <v>46156.72728918982</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I94" s="5">
         <v>46309</v>
@@ -6976,13 +7017,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q94" s="5">
         <v>46309</v>
@@ -6997,12 +7038,12 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B95" s="9">
         <v>46156.63291414352</v>
@@ -7012,7 +7053,7 @@
         <v>46209.559051539356</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7039,13 +7080,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q95" s="9">
         <v>46309</v>
@@ -7060,7 +7101,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -723,7 +723,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 </t>
+    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1214809612627656</t>
@@ -5019,7 +5019,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46211.68096902777</v>
+        <v>46224.87838520833</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -723,7 +723,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
   </si>
   <si>
     <t>1214809612627656</t>
@@ -4647,7 +4647,7 @@
         <v>46210.64935451389</v>
       </c>
       <c r="D54" s="5">
-        <v>46210.649371875</v>
+        <v>46225.19134815972</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>201</v>
@@ -4691,8 +4691,8 @@
       <c r="R54" s="5">
         <v>46232</v>
       </c>
-      <c r="S54" s="7" t="s">
-        <v>33</v>
+      <c r="S54" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
@@ -4777,7 +4777,7 @@
         <v>46210.64936773149</v>
       </c>
       <c r="D56" s="5">
-        <v>46210.64938440973</v>
+        <v>46225.191348333334</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>208</v>
@@ -4821,8 +4821,8 @@
       <c r="R56" s="5">
         <v>46232</v>
       </c>
-      <c r="S56" s="7" t="s">
-        <v>33</v>
+      <c r="S56" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -4907,7 +4907,7 @@
         <v>46210.64937866898</v>
       </c>
       <c r="D58" s="5">
-        <v>46210.64939421296</v>
+        <v>46225.191348541666</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>211</v>
@@ -4951,8 +4951,8 @@
       <c r="R58" s="5">
         <v>46232</v>
       </c>
-      <c r="S58" s="7" t="s">
-        <v>33</v>
+      <c r="S58" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5019,7 +5019,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46224.87838520833</v>
+        <v>46225.009609016204</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -723,7 +723,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
   </si>
   <si>
     <t>1214809612627656</t>
@@ -5019,7 +5019,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46225.009609016204</v>
+        <v>46225.589453356486</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="305">
   <si>
     <t>50001547 - XEMORTIZ (AMERICAS GOLD)</t>
   </si>
@@ -282,6 +282,9 @@
     <t>propuesta nucleo rodete OT 4317</t>
   </si>
   <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
     <t>nespinoza@zitron.com</t>
   </si>
   <si>
@@ -723,7 +726,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1214809612627656</t>
@@ -2416,7 +2419,7 @@
         <v>73</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I17" s="9">
         <v>46150</v>
@@ -2440,7 +2443,7 @@
         <v>56</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q17" s="9">
         <v>46150</v>
@@ -2460,7 +2463,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" s="5">
         <v>46156.632121504634</v>
@@ -2472,7 +2475,7 @@
         <v>46223.586517777774</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2481,7 +2484,7 @@
         <v>73</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I18" s="5">
         <v>46212</v>
@@ -2502,10 +2505,10 @@
         <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q18" s="5">
         <v>46212</v>
@@ -2514,7 +2517,7 @@
         <v>46213</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2525,7 +2528,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B19" s="9">
         <v>46156.63212631944</v>
@@ -2537,7 +2540,7 @@
         <v>46223.58651417824</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2546,7 +2549,7 @@
         <v>73</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I19" s="9">
         <v>46212</v>
@@ -2567,10 +2570,10 @@
         <v>63</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="9">
         <v>46212</v>
@@ -2579,7 +2582,7 @@
         <v>46213</v>
       </c>
       <c r="S19" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T19" s="10">
         <v>1</v>
@@ -2590,7 +2593,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5">
         <v>46156.63213005787</v>
@@ -2602,7 +2605,7 @@
         <v>46223.58651050926</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2611,7 +2614,7 @@
         <v>73</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I20" s="5">
         <v>46212</v>
@@ -2632,10 +2635,10 @@
         <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>46212</v>
@@ -2644,7 +2647,7 @@
         <v>46213</v>
       </c>
       <c r="S20" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -2655,7 +2658,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B21" s="9">
         <v>46156.632133692125</v>
@@ -2667,7 +2670,7 @@
         <v>46223.586505706015</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2676,7 +2679,7 @@
         <v>73</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I21" s="9">
         <v>46212</v>
@@ -2697,10 +2700,10 @@
         <v>63</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q21" s="9">
         <v>46212</v>
@@ -2709,7 +2712,7 @@
         <v>46213</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T21" s="10">
         <v>1</v>
@@ -2720,7 +2723,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B22" s="5">
         <v>46156.6319605787</v>
@@ -2732,7 +2735,7 @@
         <v>46212.59677189815</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2756,7 +2759,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2773,7 +2776,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B23" s="9">
         <v>46156.63213814815</v>
@@ -2785,16 +2788,16 @@
         <v>46210.6467582176</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I23" s="9">
         <v>46154</v>
@@ -2812,13 +2815,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="9">
         <v>46154</v>
@@ -2838,7 +2841,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5">
         <v>46156.63214259259</v>
@@ -2850,16 +2853,16 @@
         <v>46195.92922337963</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I24" s="5">
         <v>46154</v>
@@ -2877,13 +2880,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2894,12 +2897,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B25" s="9">
         <v>46156.63214717593</v>
@@ -2911,16 +2914,16 @@
         <v>46210.64669667824</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I25" s="9">
         <v>46156</v>
@@ -2938,13 +2941,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -2955,12 +2958,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B26" s="5">
         <v>46156.6321521412</v>
@@ -2972,16 +2975,16 @@
         <v>46210.64698900463</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I26" s="5">
         <v>46150</v>
@@ -2999,13 +3002,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q26" s="5">
         <v>46150</v>
@@ -3025,7 +3028,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B27" s="9">
         <v>46156.63215657407</v>
@@ -3037,16 +3040,16 @@
         <v>46210.64692099537</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I27" s="9">
         <v>46150</v>
@@ -3064,13 +3067,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3081,12 +3084,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46156.63216167824</v>
@@ -3098,16 +3101,16 @@
         <v>46210.64695642361</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I28" s="5">
         <v>46150</v>
@@ -3125,13 +3128,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3142,12 +3145,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B29" s="9">
         <v>46156.63216756945</v>
@@ -3159,16 +3162,16 @@
         <v>46210.645560289355</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I29" s="9">
         <v>46142</v>
@@ -3186,13 +3189,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q29" s="9">
         <v>46172</v>
@@ -3212,7 +3215,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46156.63217278935</v>
@@ -3224,16 +3227,16 @@
         <v>46195.92957241899</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I30" s="5">
         <v>46142</v>
@@ -3251,13 +3254,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3268,12 +3271,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B31" s="9">
         <v>46156.63217837963</v>
@@ -3285,16 +3288,16 @@
         <v>46210.64553332176</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I31" s="9">
         <v>46164</v>
@@ -3312,13 +3315,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3329,12 +3332,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46156.63218368056</v>
@@ -3346,16 +3349,16 @@
         <v>46197.78355364583</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I32" s="5">
         <v>46164</v>
@@ -3373,13 +3376,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3390,12 +3393,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="9">
         <v>46156.632188240736</v>
@@ -3407,16 +3410,16 @@
         <v>46219.184870613426</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I33" s="9">
         <v>46216</v>
@@ -3434,13 +3437,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q33" s="9">
         <v>46216</v>
@@ -3449,7 +3452,7 @@
         <v>46226</v>
       </c>
       <c r="S33" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="T33" s="10">
         <v>1</v>
@@ -3460,7 +3463,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46156.63219359954</v>
@@ -3472,16 +3475,16 @@
         <v>46199.55917045139</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I34" s="5">
         <v>46216</v>
@@ -3499,13 +3502,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3516,12 +3519,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B35" s="9">
         <v>46156.63219844908</v>
@@ -3533,16 +3536,16 @@
         <v>46199.5597825</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I35" s="9">
         <v>46218</v>
@@ -3560,13 +3563,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3577,12 +3580,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46156.63225444444</v>
@@ -3594,16 +3597,16 @@
         <v>46219.18487111111</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I36" s="5">
         <v>46216</v>
@@ -3621,10 +3624,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3636,7 +3639,7 @@
         <v>46226</v>
       </c>
       <c r="S36" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -3647,7 +3650,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46156.632258206024</v>
@@ -3659,16 +3662,16 @@
         <v>46199.55991087963</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I37" s="9">
         <v>46216</v>
@@ -3686,13 +3689,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3702,7 +3705,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46156.63226241898</v>
@@ -3714,16 +3717,16 @@
         <v>46199.55996042824</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I38" s="5">
         <v>46218</v>
@@ -3741,13 +3744,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3757,7 +3760,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B39" s="9">
         <v>46156.63226644676</v>
@@ -3769,16 +3772,16 @@
         <v>46210.649648715276</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I39" s="9">
         <v>46216</v>
@@ -3796,10 +3799,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3822,7 +3825,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46156.632269444446</v>
@@ -3834,16 +3837,16 @@
         <v>46196.69978633102</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46216</v>
@@ -3861,13 +3864,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3877,7 +3880,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46156.63227357639</v>
@@ -3889,16 +3892,16 @@
         <v>46204.86000238426</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I41" s="9">
         <v>46225</v>
@@ -3916,13 +3919,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3932,7 +3935,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46156.63227760416</v>
@@ -3944,16 +3947,16 @@
         <v>46210.64958435185</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46254</v>
@@ -3971,10 +3974,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3987,7 +3990,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46156.63228021991</v>
@@ -3999,16 +4002,16 @@
         <v>46219.1848712963</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I43" s="9">
         <v>46216</v>
@@ -4026,10 +4029,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4041,7 +4044,7 @@
         <v>46226</v>
       </c>
       <c r="S43" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="T43" s="10">
         <v>1</v>
@@ -4052,7 +4055,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46156.63228315972</v>
@@ -4064,16 +4067,16 @@
         <v>46199.56224427083</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I44" s="5">
         <v>46216</v>
@@ -4091,13 +4094,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4107,7 +4110,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B45" s="9">
         <v>46156.63228715278</v>
@@ -4119,16 +4122,16 @@
         <v>46199.56229454861</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I45" s="9">
         <v>46218</v>
@@ -4146,13 +4149,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4162,7 +4165,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46156.63196493055</v>
@@ -4172,7 +4175,7 @@
         <v>46184.58079096065</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4196,7 +4199,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4206,12 +4209,12 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" s="9">
         <v>46156.63229164352</v>
@@ -4223,16 +4226,16 @@
         <v>46197.714709479165</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I47" s="9">
         <v>46150</v>
@@ -4250,13 +4253,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="9">
         <v>46150</v>
@@ -4265,7 +4268,7 @@
         <v>46156</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T47" s="10">
         <v>1</v>
@@ -4276,7 +4279,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46156.632296261574</v>
@@ -4288,16 +4291,16 @@
         <v>46212.59685061342</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46204</v>
@@ -4315,13 +4318,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46204</v>
@@ -4330,7 +4333,7 @@
         <v>46210</v>
       </c>
       <c r="S48" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T48" s="6">
         <v>1</v>
@@ -4341,7 +4344,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46156.63230224537</v>
@@ -4353,16 +4356,16 @@
         <v>46212.1877253125</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4378,13 +4381,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="9">
         <v>46211</v>
@@ -4393,7 +4396,7 @@
         <v>46211</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T49" s="10">
         <v>1</v>
@@ -4404,7 +4407,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46156.632315358795</v>
@@ -4414,16 +4417,16 @@
         <v>46156.72589140046</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46301</v>
@@ -4441,10 +4444,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4462,12 +4465,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46156.6323189699</v>
@@ -4477,16 +4480,16 @@
         <v>46156.725962881945</v>
       </c>
       <c r="E51" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I51" s="9">
         <v>46301</v>
@@ -4504,13 +4507,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4520,7 +4523,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46156.63233141204</v>
@@ -4532,7 +4535,7 @@
         <v>46210.64940796296</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4556,7 +4559,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4573,7 +4576,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="9">
         <v>46156.63233460648</v>
@@ -4585,16 +4588,16 @@
         <v>46223.20114935185</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I53" s="9">
         <v>46227</v>
@@ -4612,13 +4615,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q53" s="9">
         <v>46227</v>
@@ -4627,7 +4630,7 @@
         <v>46230</v>
       </c>
       <c r="S53" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="T53" s="10">
         <v>1</v>
@@ -4638,7 +4641,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B54" s="5">
         <v>46156.63233969908</v>
@@ -4650,16 +4653,16 @@
         <v>46225.19134815972</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I54" s="5">
         <v>46231</v>
@@ -4677,13 +4680,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q54" s="5">
         <v>46231</v>
@@ -4692,7 +4695,7 @@
         <v>46232</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
@@ -4703,7 +4706,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B55" s="9">
         <v>46156.632350671294</v>
@@ -4715,16 +4718,16 @@
         <v>46223.201149155095</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I55" s="9">
         <v>46227</v>
@@ -4742,13 +4745,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q55" s="9">
         <v>46227</v>
@@ -4757,7 +4760,7 @@
         <v>46230</v>
       </c>
       <c r="S55" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="T55" s="10">
         <v>1</v>
@@ -4768,7 +4771,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B56" s="5">
         <v>46156.63235533565</v>
@@ -4780,16 +4783,16 @@
         <v>46225.191348333334</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I56" s="5">
         <v>46231</v>
@@ -4807,13 +4810,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q56" s="5">
         <v>46231</v>
@@ -4822,7 +4825,7 @@
         <v>46232</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -4833,7 +4836,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B57" s="9">
         <v>46156.63235945602</v>
@@ -4845,16 +4848,16 @@
         <v>46223.20114922454</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I57" s="9">
         <v>46227</v>
@@ -4872,13 +4875,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q57" s="9">
         <v>46227</v>
@@ -4887,7 +4890,7 @@
         <v>46230</v>
       </c>
       <c r="S57" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="T57" s="10">
         <v>1</v>
@@ -4898,7 +4901,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46156.63236322917</v>
@@ -4910,16 +4913,16 @@
         <v>46225.191348541666</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I58" s="5">
         <v>46231</v>
@@ -4937,13 +4940,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q58" s="5">
         <v>46231</v>
@@ -4952,7 +4955,7 @@
         <v>46232</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -4963,7 +4966,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B59" s="9">
         <v>46156.63236744213</v>
@@ -4973,7 +4976,7 @@
         <v>46203.5014815162</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>25</v>
@@ -4997,7 +5000,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -5010,7 +5013,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B60" s="5">
         <v>46156.63237008102</v>
@@ -5019,19 +5022,19 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46225.589453356486</v>
+        <v>46225.86189023148</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I60" s="5">
         <v>46233</v>
@@ -5049,13 +5052,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="5">
         <v>46233</v>
@@ -5075,7 +5078,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B61" s="9">
         <v>46156.63237584491</v>
@@ -5087,16 +5090,16 @@
         <v>46211.68096520833</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I61" s="9">
         <v>46233</v>
@@ -5114,13 +5117,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5130,7 +5133,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B62" s="5">
         <v>46156.63239597222</v>
@@ -5140,16 +5143,16 @@
         <v>46211.65705916667</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I62" s="5">
         <v>46244</v>
@@ -5167,13 +5170,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q62" s="5">
         <v>46244</v>
@@ -5188,12 +5191,12 @@
         <v>0.5</v>
       </c>
       <c r="U62" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B63" s="9">
         <v>46156.632400069444</v>
@@ -5203,16 +5206,16 @@
         <v>46211.68097021991</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5230,13 +5233,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5246,7 +5249,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B64" s="5">
         <v>46156.63246734954</v>
@@ -5256,16 +5259,16 @@
         <v>46197.83505042824</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I64" s="5">
         <v>46262</v>
@@ -5283,13 +5286,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5304,12 +5307,12 @@
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B65" s="9">
         <v>46156.632472627316</v>
@@ -5319,16 +5322,16 @@
         <v>46197.83511621528</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I65" s="9">
         <v>46262</v>
@@ -5346,13 +5349,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5362,7 +5365,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B66" s="5">
         <v>46156.6324928588</v>
@@ -5374,7 +5377,7 @@
         <v>46212.59671021991</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5398,7 +5401,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5415,7 +5418,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B67" s="9">
         <v>46156.63249635417</v>
@@ -5427,16 +5430,16 @@
         <v>46210.64718186343</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I67" s="9">
         <v>46154</v>
@@ -5454,13 +5457,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q67" s="9">
         <v>46154</v>
@@ -5480,7 +5483,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B68" s="5">
         <v>46156.63250229167</v>
@@ -5492,16 +5495,16 @@
         <v>46210.64712949074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I68" s="5">
         <v>46268</v>
@@ -5519,13 +5522,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q68" s="5">
         <v>46268</v>
@@ -5545,7 +5548,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B69" s="9">
         <v>46156.63250851852</v>
@@ -5557,16 +5560,16 @@
         <v>46210.645706863426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I69" s="9">
         <v>46294</v>
@@ -5584,13 +5587,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q69" s="9">
         <v>46294</v>
@@ -5610,7 +5613,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B70" s="5">
         <v>46156.63251465278</v>
@@ -5622,16 +5625,16 @@
         <v>46212.59669387732</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I70" s="5">
         <v>46255</v>
@@ -5649,13 +5652,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q70" s="5">
         <v>46255</v>
@@ -5675,7 +5678,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B71" s="9">
         <v>46156.63251914352</v>
@@ -5685,7 +5688,7 @@
         <v>46213.50747597222</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5709,7 +5712,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5722,7 +5725,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B72" s="5">
         <v>46156.63252219907</v>
@@ -5732,7 +5735,7 @@
         <v>46223.587171493054</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5741,7 +5744,7 @@
         <v>73</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I72" s="5">
         <v>46266</v>
@@ -5759,13 +5762,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q72" s="5">
         <v>46266</v>
@@ -5780,12 +5783,12 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B73" s="9">
         <v>46156.63252934028</v>
@@ -5795,7 +5798,7 @@
         <v>46223.58665680556</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5804,7 +5807,7 @@
         <v>73</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I73" s="9">
         <v>46266</v>
@@ -5822,10 +5825,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5838,7 +5841,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B74" s="5">
         <v>46156.63254586805</v>
@@ -5850,7 +5853,7 @@
         <v>46223.58718354166</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5859,7 +5862,7 @@
         <v>73</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I74" s="5">
         <v>46288</v>
@@ -5877,13 +5880,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q74" s="5">
         <v>46288</v>
@@ -5903,7 +5906,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B75" s="9">
         <v>46156.63255047453</v>
@@ -5913,7 +5916,7 @@
         <v>46223.5867387037</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5922,7 +5925,7 @@
         <v>73</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I75" s="9">
         <v>46288</v>
@@ -5940,13 +5943,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5956,7 +5959,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B76" s="5">
         <v>46156.63257873843</v>
@@ -5968,7 +5971,7 @@
         <v>46223.587179571754</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5977,7 +5980,7 @@
         <v>73</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I76" s="5">
         <v>46290</v>
@@ -5995,13 +5998,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q76" s="5">
         <v>46290</v>
@@ -6021,7 +6024,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B77" s="9">
         <v>46156.632582986116</v>
@@ -6031,7 +6034,7 @@
         <v>46223.58682719908</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6040,7 +6043,7 @@
         <v>73</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I77" s="9">
         <v>46290</v>
@@ -6058,13 +6061,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6074,7 +6077,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B78" s="5">
         <v>46156.632655671296</v>
@@ -6084,7 +6087,7 @@
         <v>46223.58716953704</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6093,7 +6096,7 @@
         <v>73</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I78" s="5">
         <v>46296</v>
@@ -6111,13 +6114,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q78" s="5">
         <v>46296</v>
@@ -6132,12 +6135,12 @@
         <v>0</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B79" s="9">
         <v>46156.6326615162</v>
@@ -6147,7 +6150,7 @@
         <v>46223.58691267361</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6156,7 +6159,7 @@
         <v>73</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I79" s="9">
         <v>46296</v>
@@ -6174,13 +6177,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6190,7 +6193,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B80" s="5">
         <v>46156.6326856713</v>
@@ -6200,7 +6203,7 @@
         <v>46223.58716885417</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6209,7 +6212,7 @@
         <v>73</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I80" s="5">
         <v>46300</v>
@@ -6227,13 +6230,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q80" s="5">
         <v>46300</v>
@@ -6248,12 +6251,12 @@
         <v>0</v>
       </c>
       <c r="U80" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B81" s="9">
         <v>46156.63269413194</v>
@@ -6263,7 +6266,7 @@
         <v>46223.586982106484</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6272,7 +6275,7 @@
         <v>73</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I81" s="9">
         <v>46300</v>
@@ -6290,13 +6293,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6306,7 +6309,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B82" s="5">
         <v>46156.632715810185</v>
@@ -6316,7 +6319,7 @@
         <v>46223.58716818287</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6325,7 +6328,7 @@
         <v>73</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I82" s="5">
         <v>46302</v>
@@ -6343,13 +6346,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q82" s="5">
         <v>46302</v>
@@ -6364,12 +6367,12 @@
         <v>0</v>
       </c>
       <c r="U82" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B83" s="9">
         <v>46156.63272170139</v>
@@ -6379,7 +6382,7 @@
         <v>46223.5870543287</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6388,7 +6391,7 @@
         <v>73</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I83" s="9">
         <v>46302</v>
@@ -6406,13 +6409,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6422,7 +6425,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B84" s="5">
         <v>46156.63273993056</v>
@@ -6432,7 +6435,7 @@
         <v>46205.90465030093</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6456,7 +6459,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6469,7 +6472,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B85" s="9">
         <v>46156.63274356481</v>
@@ -6479,16 +6482,16 @@
         <v>46156.7268765162</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I85" s="9">
         <v>46303</v>
@@ -6506,13 +6509,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q85" s="9">
         <v>46303</v>
@@ -6527,12 +6530,12 @@
         <v>0</v>
       </c>
       <c r="U85" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B86" s="5">
         <v>46156.63274915509</v>
@@ -6542,16 +6545,16 @@
         <v>46156.72692035879</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I86" s="5">
         <v>46303</v>
@@ -6569,13 +6572,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6585,7 +6588,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B87" s="9">
         <v>46156.63276633102</v>
@@ -6595,7 +6598,7 @@
         <v>46223.587295798614</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6604,7 +6607,7 @@
         <v>73</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
@@ -6620,13 +6623,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q87" s="9">
         <v>46304</v>
@@ -6641,12 +6644,12 @@
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B88" s="5">
         <v>46156.63277084491</v>
@@ -6656,7 +6659,7 @@
         <v>46223.587235150466</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6665,7 +6668,7 @@
         <v>73</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I88" s="5">
         <v>46304</v>
@@ -6683,13 +6686,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6699,7 +6702,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B89" s="9">
         <v>46156.63283398148</v>
@@ -6711,16 +6714,16 @@
         <v>46205.904737627316</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I89" s="9">
         <v>46307</v>
@@ -6738,13 +6741,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q89" s="9">
         <v>46307</v>
@@ -6759,12 +6762,12 @@
         <v>1</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B90" s="5">
         <v>46156.63284013889</v>
@@ -6776,16 +6779,16 @@
         <v>46205.90481071759</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I90" s="5">
         <v>46307</v>
@@ -6803,13 +6806,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6819,7 +6822,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B91" s="9">
         <v>46156.63286864583</v>
@@ -6829,16 +6832,16 @@
         <v>46156.727220243054</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I91" s="9">
         <v>46308</v>
@@ -6856,13 +6859,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q91" s="9">
         <v>46308</v>
@@ -6877,12 +6880,12 @@
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B92" s="5">
         <v>46156.632875972224</v>
@@ -6892,16 +6895,16 @@
         <v>46205.9047287037</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -6917,13 +6920,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6933,7 +6936,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B93" s="9">
         <v>46156.63290420139</v>
@@ -6943,7 +6946,7 @@
         <v>46156.71731457176</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>25</v>
@@ -6967,7 +6970,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>26</v>
@@ -6980,7 +6983,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B94" s="5">
         <v>46156.63290788194</v>
@@ -6990,16 +6993,16 @@
         <v>46156.72728918982</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I94" s="5">
         <v>46309</v>
@@ -7017,13 +7020,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q94" s="5">
         <v>46309</v>
@@ -7038,12 +7041,12 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B95" s="9">
         <v>46156.63291414352</v>
@@ -7053,7 +7056,7 @@
         <v>46209.559051539356</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7080,13 +7083,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q95" s="9">
         <v>46309</v>
@@ -7101,7 +7104,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -456,214 +456,214 @@
     <t xml:space="preserve">Generación OC materiales corte Laser OT 4317,Fabricacion Corte Laser OT 4317 </t>
   </si>
   <si>
+    <t>1214809416559849</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales corte Laser OT 4317,Fabricacion Corte Laser OT 4317 </t>
+  </si>
+  <si>
+    <t>1214809533941481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion Corte Laser OT 4317 </t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4317,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>1214809416517093</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4317</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4317,Fabricación Corte Plasma  OT 4317</t>
+  </si>
+  <si>
+    <t>1214809533981000</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4317,Fabricación Corte Plasma  OT 4317</t>
+  </si>
+  <si>
+    <t>1214809533981015</t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma  OT 4317</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4317,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>1214809612514039</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4317</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4317,Generacion OC Fabricación Externa OT 4317</t>
+  </si>
+  <si>
+    <t>1214809612514049</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4317,Fabricación Externa  OT 4317</t>
+  </si>
+  <si>
+    <t>1214809416604370</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa  OT 4317,Control de calidad fabricación externa  OT 4317,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1214809416604385</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4317</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214809416604395</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4317</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4317,Fabricación Mecanizado OT 4317</t>
+  </si>
+  <si>
+    <t>1214809660839754</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4317,Fabricación Mecanizado OT 4317</t>
+  </si>
+  <si>
+    <t>1214809660839769</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4317</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado,Mecanizado OT 4317</t>
+  </si>
+  <si>
+    <t>1214787972061379</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1214809534019503</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214809534019523</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor OT 4317,Planos preliminar</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214809528759377</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Fabricación externa  OT 4317,propuesta Corte Laser OT 4317,Propuesta Corte plasma  OT 4317,Propuesta Mecanizado OT 4317,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214809528759486</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4317 ZVN 1-16-126/4</t>
+  </si>
+  <si>
+    <t>1214809528759496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">check pruebas FAT,OT 4317 ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214809528761692</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214809534064558</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214809416559849</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales corte Laser OT 4317,Fabricacion Corte Laser OT 4317 </t>
-  </si>
-  <si>
-    <t>1214809533941481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion Corte Laser OT 4317 </t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4317,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>1214809416517093</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4317</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4317,Fabricación Corte Plasma  OT 4317</t>
-  </si>
-  <si>
-    <t>1214809533981000</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4317,Fabricación Corte Plasma  OT 4317</t>
-  </si>
-  <si>
-    <t>1214809533981015</t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma  OT 4317</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4317,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>1214809612514039</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4317</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4317,Generacion OC Fabricación Externa OT 4317</t>
-  </si>
-  <si>
-    <t>1214809612514049</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4317,Fabricación Externa  OT 4317</t>
-  </si>
-  <si>
-    <t>1214809416604370</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa  OT 4317,Control de calidad fabricación externa  OT 4317,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1214809416604385</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4317</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1214809416604395</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4317</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4317,Fabricación Mecanizado OT 4317</t>
-  </si>
-  <si>
-    <t>1214809660839754</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4317,Fabricación Mecanizado OT 4317</t>
-  </si>
-  <si>
-    <t>1214809660839769</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4317</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado,Mecanizado OT 4317</t>
-  </si>
-  <si>
-    <t>1214787972061379</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1214809534019503</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214809534019523</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT 4317,Planos preliminar</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214809528759377</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Fabricación externa  OT 4317,propuesta Corte Laser OT 4317,Propuesta Corte plasma  OT 4317,Propuesta Mecanizado OT 4317,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214809528759486</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4317 ZVN 1-16-126/4</t>
-  </si>
-  <si>
-    <t>1214809528759496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">check pruebas FAT,OT 4317 ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214809528761692</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214809534064558</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
     <t>1214809534064578</t>
@@ -3407,7 +3407,7 @@
         <v>46199.55979506944</v>
       </c>
       <c r="D33" s="9">
-        <v>46219.184870613426</v>
+        <v>46227.16739667824</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>127</v>
@@ -3451,8 +3451,8 @@
       <c r="R33" s="9">
         <v>46226</v>
       </c>
-      <c r="S33" s="12" t="s">
-        <v>131</v>
+      <c r="S33" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T33" s="10">
         <v>1</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46156.63219359954</v>
@@ -3475,7 +3475,7 @@
         <v>46199.55917045139</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3508,7 +3508,7 @@
         <v>77</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B35" s="9">
         <v>46156.63219844908</v>
@@ -3536,7 +3536,7 @@
         <v>46199.5597825</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
@@ -3566,10 +3566,10 @@
         <v>127</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3585,7 +3585,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46156.63225444444</v>
@@ -3594,10 +3594,10 @@
         <v>46199.55997423611</v>
       </c>
       <c r="D36" s="5">
-        <v>46219.18487111111</v>
+        <v>46227.167396689816</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3627,7 +3627,7 @@
         <v>91</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3638,8 +3638,8 @@
       <c r="R36" s="5">
         <v>46226</v>
       </c>
-      <c r="S36" s="12" t="s">
-        <v>131</v>
+      <c r="S36" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B37" s="9">
         <v>46156.632258206024</v>
@@ -3689,13 +3689,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>82</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3705,7 +3705,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46156.63226241898</v>
@@ -3717,7 +3717,7 @@
         <v>46199.55996042824</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3744,13 +3744,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B39" s="9">
         <v>46156.63226644676</v>
@@ -3772,16 +3772,16 @@
         <v>46210.649648715276</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="I39" s="9">
         <v>46216</v>
@@ -3802,7 +3802,7 @@
         <v>91</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3825,7 +3825,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46156.632269444446</v>
@@ -3843,10 +3843,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46216</v>
@@ -3864,13 +3864,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3880,7 +3880,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B41" s="9">
         <v>46156.63227357639</v>
@@ -3892,16 +3892,16 @@
         <v>46204.86000238426</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="I41" s="9">
         <v>46225</v>
@@ -3919,13 +3919,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>89</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3935,7 +3935,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46156.63227760416</v>
@@ -3947,16 +3947,16 @@
         <v>46210.64958435185</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46254</v>
@@ -3974,10 +3974,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3990,7 +3990,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="9">
         <v>46156.63228021991</v>
@@ -3999,10 +3999,10 @@
         <v>46199.56230621527</v>
       </c>
       <c r="D43" s="9">
-        <v>46219.1848712963</v>
+        <v>46227.16739670139</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
@@ -4032,7 +4032,7 @@
         <v>91</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4043,8 +4043,8 @@
       <c r="R43" s="9">
         <v>46226</v>
       </c>
-      <c r="S43" s="12" t="s">
-        <v>131</v>
+      <c r="S43" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T43" s="10">
         <v>1</v>
@@ -4055,7 +4055,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46156.63228315972</v>
@@ -4094,13 +4094,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4110,7 +4110,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B45" s="9">
         <v>46156.63228715278</v>
@@ -4122,7 +4122,7 @@
         <v>46199.56229454861</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4149,13 +4149,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>86</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4165,7 +4165,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46156.63196493055</v>
@@ -4175,7 +4175,7 @@
         <v>46184.58079096065</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4199,7 +4199,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4209,12 +4209,12 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B47" s="9">
         <v>46156.63229164352</v>
@@ -4226,16 +4226,16 @@
         <v>46197.714709479165</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="I47" s="9">
         <v>46150</v>
@@ -4253,13 +4253,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="9">
         <v>46150</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46156.632296261574</v>
@@ -4291,16 +4291,16 @@
         <v>46212.59685061342</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46204</v>
@@ -4318,13 +4318,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46204</v>
@@ -4344,7 +4344,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46156.63230224537</v>
@@ -4362,10 +4362,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4381,13 +4381,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="9">
         <v>46211</v>
@@ -4407,7 +4407,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46156.632315358795</v>
@@ -4417,16 +4417,16 @@
         <v>46156.72589140046</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46301</v>
@@ -4444,10 +4444,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4470,7 +4470,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46156.6323189699</v>
@@ -4480,16 +4480,16 @@
         <v>46156.725962881945</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I51" s="9">
         <v>46301</v>
@@ -4507,13 +4507,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>191</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>192</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4523,7 +4523,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46156.63233141204</v>
@@ -4535,7 +4535,7 @@
         <v>46210.64940796296</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4559,7 +4559,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4576,7 +4576,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B53" s="9">
         <v>46156.63233460648</v>
@@ -4588,16 +4588,16 @@
         <v>46223.20114935185</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="10" t="s">
+      <c r="H53" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="I53" s="9">
         <v>46227</v>
@@ -4615,13 +4615,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q53" s="9">
         <v>46227</v>
@@ -4630,7 +4630,7 @@
         <v>46230</v>
       </c>
       <c r="S53" s="12" t="s">
-        <v>131</v>
+        <v>200</v>
       </c>
       <c r="T53" s="10">
         <v>1</v>
@@ -4659,10 +4659,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I54" s="5">
         <v>46231</v>
@@ -4680,7 +4680,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>203</v>
@@ -4695,7 +4695,7 @@
         <v>46232</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>131</v>
+        <v>200</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
@@ -4724,10 +4724,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="I55" s="9">
         <v>46227</v>
@@ -4745,10 +4745,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>207</v>
@@ -4760,7 +4760,7 @@
         <v>46230</v>
       </c>
       <c r="S55" s="12" t="s">
-        <v>131</v>
+        <v>200</v>
       </c>
       <c r="T55" s="10">
         <v>1</v>
@@ -4789,10 +4789,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I56" s="5">
         <v>46231</v>
@@ -4810,13 +4810,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>206</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q56" s="5">
         <v>46231</v>
@@ -4825,7 +4825,7 @@
         <v>46232</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>131</v>
+        <v>200</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -4854,10 +4854,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="I57" s="9">
         <v>46227</v>
@@ -4875,10 +4875,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>212</v>
@@ -4890,7 +4890,7 @@
         <v>46230</v>
       </c>
       <c r="S57" s="12" t="s">
-        <v>131</v>
+        <v>200</v>
       </c>
       <c r="T57" s="10">
         <v>1</v>
@@ -4919,10 +4919,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I58" s="5">
         <v>46231</v>
@@ -4940,13 +4940,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>211</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q58" s="5">
         <v>46231</v>
@@ -4955,7 +4955,7 @@
         <v>46232</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>131</v>
+        <v>200</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5090,7 +5090,7 @@
         <v>46211.68096520833</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5173,7 +5173,7 @@
         <v>215</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>215</v>
@@ -5191,7 +5191,7 @@
         <v>0.5</v>
       </c>
       <c r="U62" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5206,7 +5206,7 @@
         <v>46211.68097021991</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5265,10 +5265,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I64" s="5">
         <v>46262</v>
@@ -5289,7 +5289,7 @@
         <v>215</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>215</v>
@@ -5322,16 +5322,16 @@
         <v>46197.83511621528</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I65" s="9">
         <v>46262</v>
@@ -5377,7 +5377,7 @@
         <v>46212.59671021991</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5436,10 +5436,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="I67" s="9">
         <v>46154</v>
@@ -5457,7 +5457,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>112</v>
@@ -5501,10 +5501,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="I68" s="5">
         <v>46268</v>
@@ -5522,7 +5522,7 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>103</v>
@@ -5566,10 +5566,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="I69" s="9">
         <v>46294</v>
@@ -5587,7 +5587,7 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>121</v>
@@ -5631,10 +5631,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="I70" s="5">
         <v>46255</v>
@@ -5652,10 +5652,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>244</v>
@@ -5798,7 +5798,7 @@
         <v>46223.58665680556</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5883,7 +5883,7 @@
         <v>246</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>246</v>
@@ -5916,7 +5916,7 @@
         <v>46223.5867387037</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -6001,7 +6001,7 @@
         <v>246</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>246</v>
@@ -6034,7 +6034,7 @@
         <v>46223.58682719908</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6117,7 +6117,7 @@
         <v>246</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>246</v>
@@ -6150,7 +6150,7 @@
         <v>46223.58691267361</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6233,7 +6233,7 @@
         <v>246</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>246</v>
@@ -6266,7 +6266,7 @@
         <v>46223.586982106484</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6296,7 +6296,7 @@
         <v>267</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>269</v>
@@ -6349,7 +6349,7 @@
         <v>246</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>272</v>
@@ -6382,7 +6382,7 @@
         <v>46223.5870543287</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6412,7 +6412,7 @@
         <v>271</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>274</v>
@@ -6545,7 +6545,7 @@
         <v>46156.72692035879</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6575,7 +6575,7 @@
         <v>279</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>283</v>
@@ -6626,7 +6626,7 @@
         <v>276</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>276</v>
@@ -6659,7 +6659,7 @@
         <v>46223.587235150466</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6689,7 +6689,7 @@
         <v>285</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>287</v>
@@ -6744,7 +6744,7 @@
         <v>276</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>276</v>
@@ -6762,7 +6762,7 @@
         <v>1</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -6779,7 +6779,7 @@
         <v>46205.90481071759</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6809,7 +6809,7 @@
         <v>289</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>291</v>
@@ -6862,7 +6862,7 @@
         <v>276</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>294</v>
@@ -6895,7 +6895,7 @@
         <v>46205.9047287037</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6923,7 +6923,7 @@
         <v>293</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>293</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -663,21 +663,21 @@
     <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
+    <t>1214809534064578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,OT 4317 ZVN 1-16-126/4 </t>
+  </si>
+  <si>
     <t>Media</t>
   </si>
   <si>
-    <t>1214809534064578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,OT 4317 ZVN 1-16-126/4 </t>
-  </si>
-  <si>
     <t>1214809534098507</t>
   </si>
   <si>
@@ -726,7 +726,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1214809612627656</t>
@@ -4585,7 +4585,7 @@
         <v>46210.648792141204</v>
       </c>
       <c r="D53" s="9">
-        <v>46223.20114935185</v>
+        <v>46231.1833272338</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>196</v>
@@ -4629,8 +4629,8 @@
       <c r="R53" s="9">
         <v>46230</v>
       </c>
-      <c r="S53" s="12" t="s">
-        <v>200</v>
+      <c r="S53" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T53" s="10">
         <v>1</v>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B54" s="5">
         <v>46156.63233969908</v>
@@ -4653,7 +4653,7 @@
         <v>46225.19134815972</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4683,10 +4683,10 @@
         <v>193</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="Q54" s="5">
         <v>46231</v>
@@ -4695,7 +4695,7 @@
         <v>46232</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
@@ -4715,7 +4715,7 @@
         <v>46210.64880347222</v>
       </c>
       <c r="D55" s="9">
-        <v>46223.201149155095</v>
+        <v>46231.183327164355</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>206</v>
@@ -4759,8 +4759,8 @@
       <c r="R55" s="9">
         <v>46230</v>
       </c>
-      <c r="S55" s="12" t="s">
-        <v>200</v>
+      <c r="S55" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T55" s="10">
         <v>1</v>
@@ -4825,7 +4825,7 @@
         <v>46232</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -4845,7 +4845,7 @@
         <v>46210.648815740744</v>
       </c>
       <c r="D57" s="9">
-        <v>46223.20114922454</v>
+        <v>46231.18332707176</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>211</v>
@@ -4889,8 +4889,8 @@
       <c r="R57" s="9">
         <v>46230</v>
       </c>
-      <c r="S57" s="12" t="s">
-        <v>200</v>
+      <c r="S57" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T57" s="10">
         <v>1</v>
@@ -4955,7 +4955,7 @@
         <v>46232</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5022,7 +5022,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46225.86189023148</v>
+        <v>46231.56037206019</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>218</v>
@@ -5463,7 +5463,7 @@
         <v>112</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q67" s="9">
         <v>46154</v>
@@ -5528,7 +5528,7 @@
         <v>103</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q68" s="5">
         <v>46268</v>
@@ -5593,7 +5593,7 @@
         <v>121</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q69" s="9">
         <v>46294</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -5022,7 +5022,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46231.56037206019</v>
+        <v>46231.65309840278</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>218</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -726,7 +726,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1214809612627656</t>
@@ -5022,7 +5022,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46231.65309840278</v>
+        <v>46232.835990810185</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>218</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="304">
   <si>
     <t>50001547 - XEMORTIZ (AMERICAS GOLD)</t>
   </si>
@@ -675,9 +675,6 @@
     <t xml:space="preserve">Bodega:,OT 4317 ZVN 1-16-126/4 </t>
   </si>
   <si>
-    <t>Media</t>
-  </si>
-  <si>
     <t>1214809534098507</t>
   </si>
   <si>
@@ -726,7 +723,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
   </si>
   <si>
     <t>1214809612627656</t>
@@ -4650,7 +4647,7 @@
         <v>46210.64935451389</v>
       </c>
       <c r="D54" s="5">
-        <v>46225.19134815972</v>
+        <v>46233.16737983796</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>201</v>
@@ -4694,8 +4691,8 @@
       <c r="R54" s="5">
         <v>46232</v>
       </c>
-      <c r="S54" s="12" t="s">
-        <v>204</v>
+      <c r="S54" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
@@ -4706,7 +4703,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B55" s="9">
         <v>46156.632350671294</v>
@@ -4718,7 +4715,7 @@
         <v>46231.183327164355</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4751,7 +4748,7 @@
         <v>143</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q55" s="9">
         <v>46227</v>
@@ -4771,7 +4768,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B56" s="5">
         <v>46156.63235533565</v>
@@ -4780,10 +4777,10 @@
         <v>46210.64936773149</v>
       </c>
       <c r="D56" s="5">
-        <v>46225.191348333334</v>
+        <v>46233.16738262732</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4813,7 +4810,7 @@
         <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>190</v>
@@ -4824,8 +4821,8 @@
       <c r="R56" s="5">
         <v>46232</v>
       </c>
-      <c r="S56" s="12" t="s">
-        <v>204</v>
+      <c r="S56" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -4836,7 +4833,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B57" s="9">
         <v>46156.63235945602</v>
@@ -4848,7 +4845,7 @@
         <v>46231.18332707176</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -4881,7 +4878,7 @@
         <v>165</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q57" s="9">
         <v>46227</v>
@@ -4901,7 +4898,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B58" s="5">
         <v>46156.63236322917</v>
@@ -4910,10 +4907,10 @@
         <v>46210.64937866898</v>
       </c>
       <c r="D58" s="5">
-        <v>46225.191348541666</v>
+        <v>46233.1673805787</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4943,7 +4940,7 @@
         <v>193</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>190</v>
@@ -4954,8 +4951,8 @@
       <c r="R58" s="5">
         <v>46232</v>
       </c>
-      <c r="S58" s="12" t="s">
-        <v>204</v>
+      <c r="S58" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -4966,7 +4963,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B59" s="9">
         <v>46156.63236744213</v>
@@ -4976,7 +4973,7 @@
         <v>46203.5014815162</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>25</v>
@@ -5000,7 +4997,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -5013,7 +5010,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B60" s="5">
         <v>46156.63237008102</v>
@@ -5025,16 +5022,16 @@
         <v>46232.835990810185</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I60" s="5">
         <v>46233</v>
@@ -5052,13 +5049,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="5">
         <v>46233</v>
@@ -5078,7 +5075,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B61" s="9">
         <v>46156.63237584491</v>
@@ -5096,10 +5093,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I61" s="9">
         <v>46233</v>
@@ -5117,13 +5114,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O61" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="P61" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5133,7 +5130,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B62" s="5">
         <v>46156.63239597222</v>
@@ -5143,16 +5140,16 @@
         <v>46211.65705916667</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I62" s="5">
         <v>46244</v>
@@ -5170,13 +5167,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="5">
         <v>46244</v>
@@ -5196,7 +5193,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B63" s="9">
         <v>46156.632400069444</v>
@@ -5212,10 +5209,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5233,13 +5230,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>228</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>229</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5249,7 +5246,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B64" s="5">
         <v>46156.63246734954</v>
@@ -5259,7 +5256,7 @@
         <v>46197.83505042824</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5286,13 +5283,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5312,7 +5309,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B65" s="9">
         <v>46156.632472627316</v>
@@ -5349,13 +5346,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5365,7 +5362,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B66" s="5">
         <v>46156.6324928588</v>
@@ -5401,7 +5398,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5418,7 +5415,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B67" s="9">
         <v>46156.63249635417</v>
@@ -5430,7 +5427,7 @@
         <v>46210.64718186343</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5483,7 +5480,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B68" s="5">
         <v>46156.63250229167</v>
@@ -5495,7 +5492,7 @@
         <v>46210.64712949074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5548,7 +5545,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B69" s="9">
         <v>46156.63250851852</v>
@@ -5560,7 +5557,7 @@
         <v>46210.645706863426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5613,7 +5610,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B70" s="5">
         <v>46156.63251465278</v>
@@ -5625,7 +5622,7 @@
         <v>46212.59669387732</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5658,7 +5655,7 @@
         <v>153</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q70" s="5">
         <v>46255</v>
@@ -5678,7 +5675,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B71" s="9">
         <v>46156.63251914352</v>
@@ -5688,7 +5685,7 @@
         <v>46213.50747597222</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5712,7 +5709,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5725,7 +5722,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B72" s="5">
         <v>46156.63252219907</v>
@@ -5735,7 +5732,7 @@
         <v>46223.587171493054</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5762,13 +5759,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q72" s="5">
         <v>46266</v>
@@ -5788,7 +5785,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B73" s="9">
         <v>46156.63252934028</v>
@@ -5825,10 +5822,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="O73" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="O73" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5841,7 +5838,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B74" s="5">
         <v>46156.63254586805</v>
@@ -5853,7 +5850,7 @@
         <v>46223.58718354166</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5880,13 +5877,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q74" s="5">
         <v>46288</v>
@@ -5906,7 +5903,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B75" s="9">
         <v>46156.63255047453</v>
@@ -5943,13 +5940,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O75" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="P75" s="10" t="s">
         <v>255</v>
-      </c>
-      <c r="P75" s="10" t="s">
-        <v>256</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5959,7 +5956,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B76" s="5">
         <v>46156.63257873843</v>
@@ -5971,7 +5968,7 @@
         <v>46223.587179571754</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5998,13 +5995,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q76" s="5">
         <v>46290</v>
@@ -6024,7 +6021,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B77" s="9">
         <v>46156.632582986116</v>
@@ -6061,13 +6058,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6077,7 +6074,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B78" s="5">
         <v>46156.632655671296</v>
@@ -6087,7 +6084,7 @@
         <v>46223.58716953704</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6114,13 +6111,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q78" s="5">
         <v>46296</v>
@@ -6140,7 +6137,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B79" s="9">
         <v>46156.6326615162</v>
@@ -6177,13 +6174,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O79" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="P79" s="10" t="s">
         <v>264</v>
-      </c>
-      <c r="P79" s="10" t="s">
-        <v>265</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6193,7 +6190,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B80" s="5">
         <v>46156.6326856713</v>
@@ -6203,7 +6200,7 @@
         <v>46223.58716885417</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6230,13 +6227,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q80" s="5">
         <v>46300</v>
@@ -6256,7 +6253,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B81" s="9">
         <v>46156.63269413194</v>
@@ -6293,13 +6290,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6309,7 +6306,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B82" s="5">
         <v>46156.632715810185</v>
@@ -6319,7 +6316,7 @@
         <v>46223.58716818287</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6346,13 +6343,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q82" s="5">
         <v>46302</v>
@@ -6372,7 +6369,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B83" s="9">
         <v>46156.63272170139</v>
@@ -6409,13 +6406,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6425,7 +6422,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B84" s="5">
         <v>46156.63273993056</v>
@@ -6435,7 +6432,7 @@
         <v>46205.90465030093</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6459,7 +6456,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6472,7 +6469,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B85" s="9">
         <v>46156.63274356481</v>
@@ -6482,16 +6479,16 @@
         <v>46156.7268765162</v>
       </c>
       <c r="E85" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="F85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" s="10" t="s">
+      <c r="H85" s="10" t="s">
         <v>280</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>281</v>
       </c>
       <c r="I85" s="9">
         <v>46303</v>
@@ -6509,13 +6506,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q85" s="9">
         <v>46303</v>
@@ -6535,7 +6532,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B86" s="5">
         <v>46156.63274915509</v>
@@ -6551,10 +6548,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>280</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>281</v>
       </c>
       <c r="I86" s="5">
         <v>46303</v>
@@ -6572,13 +6569,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6588,7 +6585,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B87" s="9">
         <v>46156.63276633102</v>
@@ -6598,7 +6595,7 @@
         <v>46223.587295798614</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6623,13 +6620,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q87" s="9">
         <v>46304</v>
@@ -6649,7 +6646,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B88" s="5">
         <v>46156.63277084491</v>
@@ -6686,13 +6683,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6702,7 +6699,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B89" s="9">
         <v>46156.63283398148</v>
@@ -6714,16 +6711,16 @@
         <v>46205.904737627316</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I89" s="9">
         <v>46307</v>
@@ -6741,13 +6738,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O89" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q89" s="9">
         <v>46307</v>
@@ -6767,7 +6764,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B90" s="5">
         <v>46156.63284013889</v>
@@ -6785,10 +6782,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I90" s="5">
         <v>46307</v>
@@ -6806,13 +6803,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6822,7 +6819,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B91" s="9">
         <v>46156.63286864583</v>
@@ -6832,16 +6829,16 @@
         <v>46156.727220243054</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I91" s="9">
         <v>46308</v>
@@ -6859,13 +6856,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O91" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q91" s="9">
         <v>46308</v>
@@ -6885,7 +6882,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B92" s="5">
         <v>46156.632875972224</v>
@@ -6901,10 +6898,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -6920,13 +6917,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6936,7 +6933,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B93" s="9">
         <v>46156.63290420139</v>
@@ -6946,7 +6943,7 @@
         <v>46156.71731457176</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>25</v>
@@ -6970,7 +6967,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>26</v>
@@ -6983,7 +6980,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B94" s="5">
         <v>46156.63290788194</v>
@@ -6993,16 +6990,16 @@
         <v>46156.72728918982</v>
       </c>
       <c r="E94" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G94" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="F94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G94" s="6" t="s">
+      <c r="H94" s="6" t="s">
         <v>301</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>302</v>
       </c>
       <c r="I94" s="5">
         <v>46309</v>
@@ -7020,13 +7017,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q94" s="5">
         <v>46309</v>
@@ -7046,7 +7043,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B95" s="9">
         <v>46156.63291414352</v>
@@ -7056,7 +7053,7 @@
         <v>46209.559051539356</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7083,13 +7080,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q95" s="9">
         <v>46309</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -5019,7 +5019,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46232.835990810185</v>
+        <v>46233.64826130787</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="305">
   <si>
     <t>50001547 - XEMORTIZ (AMERICAS GOLD)</t>
   </si>
@@ -724,6 +724,9 @@
   </si>
   <si>
     <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1214809612627656</t>
@@ -5019,7 +5022,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46233.64826130787</v>
+        <v>46234.20496445602</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -5063,8 +5066,8 @@
       <c r="R60" s="5">
         <v>46241</v>
       </c>
-      <c r="S60" s="7" t="s">
-        <v>33</v>
+      <c r="S60" s="12" t="s">
+        <v>221</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5075,7 +5078,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B61" s="9">
         <v>46156.63237584491</v>
@@ -5117,10 +5120,10 @@
         <v>217</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5130,7 +5133,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B62" s="5">
         <v>46156.63239597222</v>
@@ -5140,7 +5143,7 @@
         <v>46211.65705916667</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5193,7 +5196,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B63" s="9">
         <v>46156.632400069444</v>
@@ -5230,13 +5233,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5246,7 +5249,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B64" s="5">
         <v>46156.63246734954</v>
@@ -5256,7 +5259,7 @@
         <v>46197.83505042824</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5309,7 +5312,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B65" s="9">
         <v>46156.632472627316</v>
@@ -5346,13 +5349,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5362,7 +5365,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B66" s="5">
         <v>46156.6324928588</v>
@@ -5398,7 +5401,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5415,7 +5418,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B67" s="9">
         <v>46156.63249635417</v>
@@ -5427,7 +5430,7 @@
         <v>46210.64718186343</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5480,7 +5483,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B68" s="5">
         <v>46156.63250229167</v>
@@ -5492,7 +5495,7 @@
         <v>46210.64712949074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5545,7 +5548,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B69" s="9">
         <v>46156.63250851852</v>
@@ -5557,7 +5560,7 @@
         <v>46210.645706863426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5610,7 +5613,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B70" s="5">
         <v>46156.63251465278</v>
@@ -5622,7 +5625,7 @@
         <v>46212.59669387732</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5655,7 +5658,7 @@
         <v>153</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q70" s="5">
         <v>46255</v>
@@ -5675,7 +5678,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B71" s="9">
         <v>46156.63251914352</v>
@@ -5685,7 +5688,7 @@
         <v>46213.50747597222</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5709,7 +5712,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5722,7 +5725,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B72" s="5">
         <v>46156.63252219907</v>
@@ -5732,7 +5735,7 @@
         <v>46223.587171493054</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5759,13 +5762,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q72" s="5">
         <v>46266</v>
@@ -5785,7 +5788,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B73" s="9">
         <v>46156.63252934028</v>
@@ -5822,10 +5825,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5838,7 +5841,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B74" s="5">
         <v>46156.63254586805</v>
@@ -5850,7 +5853,7 @@
         <v>46223.58718354166</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5877,13 +5880,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q74" s="5">
         <v>46288</v>
@@ -5903,7 +5906,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B75" s="9">
         <v>46156.63255047453</v>
@@ -5940,13 +5943,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5956,7 +5959,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B76" s="5">
         <v>46156.63257873843</v>
@@ -5968,7 +5971,7 @@
         <v>46223.587179571754</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5995,13 +5998,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q76" s="5">
         <v>46290</v>
@@ -6021,7 +6024,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B77" s="9">
         <v>46156.632582986116</v>
@@ -6058,13 +6061,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6074,7 +6077,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B78" s="5">
         <v>46156.632655671296</v>
@@ -6084,7 +6087,7 @@
         <v>46223.58716953704</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6111,13 +6114,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q78" s="5">
         <v>46296</v>
@@ -6137,7 +6140,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B79" s="9">
         <v>46156.6326615162</v>
@@ -6174,13 +6177,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6190,7 +6193,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B80" s="5">
         <v>46156.6326856713</v>
@@ -6200,7 +6203,7 @@
         <v>46223.58716885417</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6227,13 +6230,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q80" s="5">
         <v>46300</v>
@@ -6253,7 +6256,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B81" s="9">
         <v>46156.63269413194</v>
@@ -6290,13 +6293,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6306,7 +6309,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B82" s="5">
         <v>46156.632715810185</v>
@@ -6316,7 +6319,7 @@
         <v>46223.58716818287</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6343,13 +6346,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q82" s="5">
         <v>46302</v>
@@ -6369,7 +6372,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B83" s="9">
         <v>46156.63272170139</v>
@@ -6406,13 +6409,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6422,7 +6425,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B84" s="5">
         <v>46156.63273993056</v>
@@ -6432,7 +6435,7 @@
         <v>46205.90465030093</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6456,7 +6459,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6469,7 +6472,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B85" s="9">
         <v>46156.63274356481</v>
@@ -6479,16 +6482,16 @@
         <v>46156.7268765162</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I85" s="9">
         <v>46303</v>
@@ -6506,13 +6509,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q85" s="9">
         <v>46303</v>
@@ -6532,7 +6535,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B86" s="5">
         <v>46156.63274915509</v>
@@ -6548,10 +6551,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I86" s="5">
         <v>46303</v>
@@ -6569,13 +6572,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6585,7 +6588,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B87" s="9">
         <v>46156.63276633102</v>
@@ -6595,7 +6598,7 @@
         <v>46223.587295798614</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6620,13 +6623,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q87" s="9">
         <v>46304</v>
@@ -6646,7 +6649,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B88" s="5">
         <v>46156.63277084491</v>
@@ -6683,13 +6686,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6699,7 +6702,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B89" s="9">
         <v>46156.63283398148</v>
@@ -6711,7 +6714,7 @@
         <v>46205.904737627316</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6738,13 +6741,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O89" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q89" s="9">
         <v>46307</v>
@@ -6764,7 +6767,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B90" s="5">
         <v>46156.63284013889</v>
@@ -6803,13 +6806,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6819,7 +6822,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B91" s="9">
         <v>46156.63286864583</v>
@@ -6829,7 +6832,7 @@
         <v>46156.727220243054</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6856,13 +6859,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O91" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q91" s="9">
         <v>46308</v>
@@ -6882,7 +6885,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B92" s="5">
         <v>46156.632875972224</v>
@@ -6917,13 +6920,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6933,7 +6936,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B93" s="9">
         <v>46156.63290420139</v>
@@ -6943,7 +6946,7 @@
         <v>46156.71731457176</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>25</v>
@@ -6967,7 +6970,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>26</v>
@@ -6980,7 +6983,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B94" s="5">
         <v>46156.63290788194</v>
@@ -6990,16 +6993,16 @@
         <v>46156.72728918982</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I94" s="5">
         <v>46309</v>
@@ -7017,13 +7020,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q94" s="5">
         <v>46309</v>
@@ -7043,7 +7046,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B95" s="9">
         <v>46156.63291414352</v>
@@ -7053,7 +7056,7 @@
         <v>46209.559051539356</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7080,13 +7083,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q95" s="9">
         <v>46309</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -5140,7 +5140,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46211.65705916667</v>
+        <v>46237.53857474537</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5190,8 +5190,8 @@
       <c r="T62" s="6">
         <v>0.5</v>
       </c>
-      <c r="U62" s="12" t="s">
-        <v>170</v>
+      <c r="U62" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46223.587171493054</v>
+        <v>46237.53864697917</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>249</v>
@@ -5782,8 +5782,8 @@
       <c r="T72" s="6">
         <v>0</v>
       </c>
-      <c r="U72" s="11" t="s">
-        <v>101</v>
+      <c r="U72" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46223.58716953704</v>
+        <v>46237.538680937505</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>262</v>
@@ -6134,8 +6134,8 @@
       <c r="T78" s="6">
         <v>0</v>
       </c>
-      <c r="U78" s="11" t="s">
-        <v>101</v>
+      <c r="U78" s="12" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -723,7 +723,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
+    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>Media</t>
@@ -5022,7 +5022,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46234.20496445602</v>
+        <v>46237.57050016204</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -5022,7 +5022,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46237.57050016204</v>
+        <v>46237.810159699075</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -723,7 +723,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>Media</t>
@@ -5022,7 +5022,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46237.810159699075</v>
+        <v>46239.57424440973</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -723,7 +723,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
   </si>
   <si>
     <t>Media</t>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -5022,7 +5022,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46239.57424440973</v>
+        <v>46240.58270775463</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="304">
   <si>
     <t>50001547 - XEMORTIZ (AMERICAS GOLD)</t>
   </si>
@@ -724,9 +724,6 @@
   </si>
   <si>
     <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214809612627656</t>
@@ -5022,7 +5019,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46240.58270775463</v>
+        <v>46242.17955945602</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -5066,8 +5063,8 @@
       <c r="R60" s="5">
         <v>46241</v>
       </c>
-      <c r="S60" s="12" t="s">
-        <v>221</v>
+      <c r="S60" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5078,7 +5075,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B61" s="9">
         <v>46156.63237584491</v>
@@ -5120,10 +5117,10 @@
         <v>217</v>
       </c>
       <c r="O61" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="P61" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5133,7 +5130,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B62" s="5">
         <v>46156.63239597222</v>
@@ -5143,7 +5140,7 @@
         <v>46237.53857474537</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5196,7 +5193,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B63" s="9">
         <v>46156.632400069444</v>
@@ -5233,13 +5230,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>228</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>229</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5249,7 +5246,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B64" s="5">
         <v>46156.63246734954</v>
@@ -5259,7 +5256,7 @@
         <v>46197.83505042824</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5312,7 +5309,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B65" s="9">
         <v>46156.632472627316</v>
@@ -5349,13 +5346,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5365,7 +5362,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B66" s="5">
         <v>46156.6324928588</v>
@@ -5401,7 +5398,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5418,7 +5415,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B67" s="9">
         <v>46156.63249635417</v>
@@ -5430,7 +5427,7 @@
         <v>46210.64718186343</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5483,7 +5480,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B68" s="5">
         <v>46156.63250229167</v>
@@ -5495,7 +5492,7 @@
         <v>46210.64712949074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5548,7 +5545,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B69" s="9">
         <v>46156.63250851852</v>
@@ -5560,7 +5557,7 @@
         <v>46210.645706863426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5613,7 +5610,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B70" s="5">
         <v>46156.63251465278</v>
@@ -5625,7 +5622,7 @@
         <v>46212.59669387732</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5658,7 +5655,7 @@
         <v>153</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q70" s="5">
         <v>46255</v>
@@ -5678,7 +5675,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B71" s="9">
         <v>46156.63251914352</v>
@@ -5688,7 +5685,7 @@
         <v>46213.50747597222</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5712,7 +5709,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5725,7 +5722,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B72" s="5">
         <v>46156.63252219907</v>
@@ -5735,7 +5732,7 @@
         <v>46237.53864697917</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5762,13 +5759,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q72" s="5">
         <v>46266</v>
@@ -5788,7 +5785,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B73" s="9">
         <v>46156.63252934028</v>
@@ -5825,10 +5822,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="O73" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="O73" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5841,7 +5838,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B74" s="5">
         <v>46156.63254586805</v>
@@ -5853,7 +5850,7 @@
         <v>46223.58718354166</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5880,13 +5877,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q74" s="5">
         <v>46288</v>
@@ -5906,7 +5903,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B75" s="9">
         <v>46156.63255047453</v>
@@ -5943,13 +5940,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O75" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="P75" s="10" t="s">
         <v>255</v>
-      </c>
-      <c r="P75" s="10" t="s">
-        <v>256</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5959,7 +5956,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B76" s="5">
         <v>46156.63257873843</v>
@@ -5971,7 +5968,7 @@
         <v>46223.587179571754</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5998,13 +5995,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q76" s="5">
         <v>46290</v>
@@ -6024,7 +6021,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B77" s="9">
         <v>46156.632582986116</v>
@@ -6061,13 +6058,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6077,7 +6074,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B78" s="5">
         <v>46156.632655671296</v>
@@ -6087,7 +6084,7 @@
         <v>46237.538680937505</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6114,13 +6111,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q78" s="5">
         <v>46296</v>
@@ -6140,7 +6137,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B79" s="9">
         <v>46156.6326615162</v>
@@ -6177,13 +6174,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O79" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="P79" s="10" t="s">
         <v>264</v>
-      </c>
-      <c r="P79" s="10" t="s">
-        <v>265</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6193,7 +6190,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B80" s="5">
         <v>46156.6326856713</v>
@@ -6203,7 +6200,7 @@
         <v>46223.58716885417</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6230,13 +6227,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q80" s="5">
         <v>46300</v>
@@ -6256,7 +6253,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B81" s="9">
         <v>46156.63269413194</v>
@@ -6293,13 +6290,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6309,7 +6306,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B82" s="5">
         <v>46156.632715810185</v>
@@ -6319,7 +6316,7 @@
         <v>46223.58716818287</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6346,13 +6343,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q82" s="5">
         <v>46302</v>
@@ -6372,7 +6369,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B83" s="9">
         <v>46156.63272170139</v>
@@ -6409,13 +6406,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6425,7 +6422,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B84" s="5">
         <v>46156.63273993056</v>
@@ -6435,7 +6432,7 @@
         <v>46205.90465030093</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6459,7 +6456,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6472,7 +6469,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B85" s="9">
         <v>46156.63274356481</v>
@@ -6482,16 +6479,16 @@
         <v>46156.7268765162</v>
       </c>
       <c r="E85" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="F85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" s="10" t="s">
+      <c r="H85" s="10" t="s">
         <v>280</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>281</v>
       </c>
       <c r="I85" s="9">
         <v>46303</v>
@@ -6509,13 +6506,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q85" s="9">
         <v>46303</v>
@@ -6535,7 +6532,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B86" s="5">
         <v>46156.63274915509</v>
@@ -6551,10 +6548,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>280</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>281</v>
       </c>
       <c r="I86" s="5">
         <v>46303</v>
@@ -6572,13 +6569,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6588,7 +6585,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B87" s="9">
         <v>46156.63276633102</v>
@@ -6598,7 +6595,7 @@
         <v>46223.587295798614</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6623,13 +6620,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q87" s="9">
         <v>46304</v>
@@ -6649,7 +6646,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B88" s="5">
         <v>46156.63277084491</v>
@@ -6686,13 +6683,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6702,7 +6699,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B89" s="9">
         <v>46156.63283398148</v>
@@ -6714,7 +6711,7 @@
         <v>46205.904737627316</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6741,13 +6738,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O89" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q89" s="9">
         <v>46307</v>
@@ -6767,7 +6764,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B90" s="5">
         <v>46156.63284013889</v>
@@ -6806,13 +6803,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6822,7 +6819,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B91" s="9">
         <v>46156.63286864583</v>
@@ -6832,7 +6829,7 @@
         <v>46156.727220243054</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6859,13 +6856,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O91" s="10" t="s">
         <v>190</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q91" s="9">
         <v>46308</v>
@@ -6885,7 +6882,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B92" s="5">
         <v>46156.632875972224</v>
@@ -6920,13 +6917,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>190</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6936,7 +6933,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B93" s="9">
         <v>46156.63290420139</v>
@@ -6946,7 +6943,7 @@
         <v>46156.71731457176</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>25</v>
@@ -6970,7 +6967,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>26</v>
@@ -6983,7 +6980,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B94" s="5">
         <v>46156.63290788194</v>
@@ -6993,16 +6990,16 @@
         <v>46156.72728918982</v>
       </c>
       <c r="E94" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G94" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="F94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G94" s="6" t="s">
+      <c r="H94" s="6" t="s">
         <v>301</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>302</v>
       </c>
       <c r="I94" s="5">
         <v>46309</v>
@@ -7020,13 +7017,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q94" s="5">
         <v>46309</v>
@@ -7046,7 +7043,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B95" s="9">
         <v>46156.63291414352</v>
@@ -7056,7 +7053,7 @@
         <v>46209.559051539356</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7083,13 +7080,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q95" s="9">
         <v>46309</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -2729,7 +2729,7 @@
         <v>46212.59675680556</v>
       </c>
       <c r="D22" s="5">
-        <v>46212.59677189815</v>
+        <v>46243.71324824074</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46156.72589140046</v>
+        <v>46243.72746450231</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -5019,7 +5019,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46242.17955945602</v>
+        <v>46243.72771121528</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46237.53857474537</v>
+        <v>46243.72774834491</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>225</v>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46197.83505042824</v>
+        <v>46243.72779826389</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>230</v>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46213.50747597222</v>
+        <v>46243.73553203704</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>245</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46237.53864697917</v>
+        <v>46243.727824525464</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>248</v>
@@ -5847,7 +5847,7 @@
         <v>46213.50741020833</v>
       </c>
       <c r="D74" s="5">
-        <v>46223.58718354166</v>
+        <v>46243.72785484954</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>252</v>
@@ -5965,7 +5965,7 @@
         <v>46213.50747125</v>
       </c>
       <c r="D76" s="5">
-        <v>46223.587179571754</v>
+        <v>46243.72789628472</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>257</v>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46237.538680937505</v>
+        <v>46243.72800076389</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>261</v>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46223.58716885417</v>
+        <v>46243.728052499995</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>266</v>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46223.58716818287</v>
+        <v>46243.728118784726</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>270</v>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46156.7268765162</v>
+        <v>46243.72816118055</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>278</v>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46223.587295798614</v>
+        <v>46243.72822305556</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>284</v>
@@ -6708,7 +6708,7 @@
         <v>46205.90464569445</v>
       </c>
       <c r="D89" s="9">
-        <v>46205.904737627316</v>
+        <v>46243.72826583333</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>288</v>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46156.727220243054</v>
+        <v>46243.72830107639</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>292</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -723,7 +723,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
+    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
   </si>
   <si>
     <t>1214809612627656</t>
@@ -5019,7 +5019,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46243.72771121528</v>
+        <v>46244.58203484953</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -723,7 +723,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
+    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
   </si>
   <si>
     <t>1214809612627656</t>
@@ -5019,7 +5019,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46244.58203484953</v>
+        <v>46244.81647443287</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -723,7 +723,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
+    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
   </si>
   <si>
     <t>1214809612627656</t>
@@ -5019,7 +5019,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46244.81647443287</v>
+        <v>46244.91622328704</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="305">
   <si>
     <t>50001547 - XEMORTIZ (AMERICAS GOLD)</t>
   </si>
@@ -511,6 +511,9 @@
   </si>
   <si>
     <t>Fabricación estructura proveedor externo OT 4317,Generacion OC Fabricación Externa OT 4317</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1214809612514049</t>
@@ -3766,7 +3769,7 @@
         <v>46204.87072556713</v>
       </c>
       <c r="D39" s="9">
-        <v>46210.649648715276</v>
+        <v>46247.1955693287</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>146</v>
@@ -3810,8 +3813,8 @@
       <c r="R39" s="9">
         <v>46254</v>
       </c>
-      <c r="S39" s="7" t="s">
-        <v>33</v>
+      <c r="S39" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -3822,7 +3825,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46156.632269444446</v>
@@ -3867,7 +3870,7 @@
         <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3877,7 +3880,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46156.63227357639</v>
@@ -3889,7 +3892,7 @@
         <v>46204.86000238426</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -3922,7 +3925,7 @@
         <v>89</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3932,7 +3935,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46156.63227760416</v>
@@ -3944,16 +3947,16 @@
         <v>46210.64958435185</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46254</v>
@@ -3974,7 +3977,7 @@
         <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3987,7 +3990,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46156.63228021991</v>
@@ -3999,7 +4002,7 @@
         <v>46227.16739670139</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
@@ -4029,7 +4032,7 @@
         <v>91</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4052,7 +4055,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46156.63228315972</v>
@@ -4091,13 +4094,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4107,7 +4110,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B45" s="9">
         <v>46156.63228715278</v>
@@ -4119,7 +4122,7 @@
         <v>46199.56229454861</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4146,13 +4149,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>86</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4162,7 +4165,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46156.63196493055</v>
@@ -4172,7 +4175,7 @@
         <v>46184.58079096065</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4196,7 +4199,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4206,12 +4209,12 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" s="9">
         <v>46156.63229164352</v>
@@ -4223,16 +4226,16 @@
         <v>46197.714709479165</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I47" s="9">
         <v>46150</v>
@@ -4250,13 +4253,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="9">
         <v>46150</v>
@@ -4276,7 +4279,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46156.632296261574</v>
@@ -4288,16 +4291,16 @@
         <v>46212.59685061342</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46204</v>
@@ -4315,13 +4318,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46204</v>
@@ -4341,7 +4344,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46156.63230224537</v>
@@ -4359,10 +4362,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4378,13 +4381,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="9">
         <v>46211</v>
@@ -4404,7 +4407,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46156.632315358795</v>
@@ -4414,16 +4417,16 @@
         <v>46243.72746450231</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46301</v>
@@ -4441,10 +4444,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4467,7 +4470,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46156.6323189699</v>
@@ -4477,16 +4480,16 @@
         <v>46156.725962881945</v>
       </c>
       <c r="E51" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I51" s="9">
         <v>46301</v>
@@ -4504,13 +4507,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4520,7 +4523,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46156.63233141204</v>
@@ -4532,7 +4535,7 @@
         <v>46210.64940796296</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4556,7 +4559,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4573,7 +4576,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="9">
         <v>46156.63233460648</v>
@@ -4585,16 +4588,16 @@
         <v>46231.1833272338</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I53" s="9">
         <v>46227</v>
@@ -4612,13 +4615,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>135</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q53" s="9">
         <v>46227</v>
@@ -4638,7 +4641,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B54" s="5">
         <v>46156.63233969908</v>
@@ -4650,16 +4653,16 @@
         <v>46233.16737983796</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I54" s="5">
         <v>46231</v>
@@ -4677,13 +4680,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q54" s="5">
         <v>46231</v>
@@ -4703,7 +4706,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B55" s="9">
         <v>46156.632350671294</v>
@@ -4715,16 +4718,16 @@
         <v>46231.183327164355</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I55" s="9">
         <v>46227</v>
@@ -4742,13 +4745,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>143</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q55" s="9">
         <v>46227</v>
@@ -4768,7 +4771,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B56" s="5">
         <v>46156.63235533565</v>
@@ -4780,16 +4783,16 @@
         <v>46233.16738262732</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I56" s="5">
         <v>46231</v>
@@ -4807,13 +4810,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q56" s="5">
         <v>46231</v>
@@ -4833,7 +4836,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B57" s="9">
         <v>46156.63235945602</v>
@@ -4845,16 +4848,16 @@
         <v>46231.18332707176</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I57" s="9">
         <v>46227</v>
@@ -4872,13 +4875,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q57" s="9">
         <v>46227</v>
@@ -4898,7 +4901,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46156.63236322917</v>
@@ -4910,16 +4913,16 @@
         <v>46233.1673805787</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I58" s="5">
         <v>46231</v>
@@ -4937,13 +4940,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q58" s="5">
         <v>46231</v>
@@ -4963,7 +4966,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B59" s="9">
         <v>46156.63236744213</v>
@@ -4973,7 +4976,7 @@
         <v>46203.5014815162</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>25</v>
@@ -4997,7 +5000,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -5010,7 +5013,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B60" s="5">
         <v>46156.63237008102</v>
@@ -5022,16 +5025,16 @@
         <v>46244.91622328704</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I60" s="5">
         <v>46233</v>
@@ -5049,13 +5052,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="5">
         <v>46233</v>
@@ -5075,7 +5078,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B61" s="9">
         <v>46156.63237584491</v>
@@ -5087,16 +5090,16 @@
         <v>46211.68096520833</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I61" s="9">
         <v>46233</v>
@@ -5114,13 +5117,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5130,7 +5133,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B62" s="5">
         <v>46156.63239597222</v>
@@ -5140,16 +5143,16 @@
         <v>46243.72774834491</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I62" s="5">
         <v>46244</v>
@@ -5167,13 +5170,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q62" s="5">
         <v>46244</v>
@@ -5193,7 +5196,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B63" s="9">
         <v>46156.632400069444</v>
@@ -5203,16 +5206,16 @@
         <v>46211.68097021991</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5230,13 +5233,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5246,7 +5249,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B64" s="5">
         <v>46156.63246734954</v>
@@ -5256,16 +5259,16 @@
         <v>46243.72779826389</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I64" s="5">
         <v>46262</v>
@@ -5283,13 +5286,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5309,7 +5312,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B65" s="9">
         <v>46156.632472627316</v>
@@ -5319,16 +5322,16 @@
         <v>46197.83511621528</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I65" s="9">
         <v>46262</v>
@@ -5346,13 +5349,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5362,7 +5365,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B66" s="5">
         <v>46156.6324928588</v>
@@ -5374,7 +5377,7 @@
         <v>46212.59671021991</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5398,7 +5401,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5415,7 +5418,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B67" s="9">
         <v>46156.63249635417</v>
@@ -5427,16 +5430,16 @@
         <v>46210.64718186343</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I67" s="9">
         <v>46154</v>
@@ -5454,13 +5457,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>112</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q67" s="9">
         <v>46154</v>
@@ -5480,7 +5483,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B68" s="5">
         <v>46156.63250229167</v>
@@ -5492,16 +5495,16 @@
         <v>46210.64712949074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I68" s="5">
         <v>46268</v>
@@ -5519,13 +5522,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q68" s="5">
         <v>46268</v>
@@ -5545,7 +5548,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B69" s="9">
         <v>46156.63250851852</v>
@@ -5557,16 +5560,16 @@
         <v>46210.645706863426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I69" s="9">
         <v>46294</v>
@@ -5584,13 +5587,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>121</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q69" s="9">
         <v>46294</v>
@@ -5610,7 +5613,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B70" s="5">
         <v>46156.63251465278</v>
@@ -5622,16 +5625,16 @@
         <v>46212.59669387732</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I70" s="5">
         <v>46255</v>
@@ -5649,13 +5652,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q70" s="5">
         <v>46255</v>
@@ -5675,7 +5678,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B71" s="9">
         <v>46156.63251914352</v>
@@ -5685,7 +5688,7 @@
         <v>46243.73553203704</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5709,7 +5712,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5722,7 +5725,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B72" s="5">
         <v>46156.63252219907</v>
@@ -5732,7 +5735,7 @@
         <v>46243.727824525464</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5759,13 +5762,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q72" s="5">
         <v>46266</v>
@@ -5785,7 +5788,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B73" s="9">
         <v>46156.63252934028</v>
@@ -5795,7 +5798,7 @@
         <v>46223.58665680556</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5822,10 +5825,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5838,7 +5841,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B74" s="5">
         <v>46156.63254586805</v>
@@ -5850,7 +5853,7 @@
         <v>46243.72785484954</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5877,13 +5880,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q74" s="5">
         <v>46288</v>
@@ -5903,7 +5906,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B75" s="9">
         <v>46156.63255047453</v>
@@ -5913,7 +5916,7 @@
         <v>46223.5867387037</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5940,13 +5943,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5956,7 +5959,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B76" s="5">
         <v>46156.63257873843</v>
@@ -5968,7 +5971,7 @@
         <v>46243.72789628472</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5995,13 +5998,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q76" s="5">
         <v>46290</v>
@@ -6021,7 +6024,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B77" s="9">
         <v>46156.632582986116</v>
@@ -6031,7 +6034,7 @@
         <v>46223.58682719908</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6058,13 +6061,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6074,7 +6077,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B78" s="5">
         <v>46156.632655671296</v>
@@ -6084,7 +6087,7 @@
         <v>46243.72800076389</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6111,13 +6114,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q78" s="5">
         <v>46296</v>
@@ -6132,12 +6135,12 @@
         <v>0</v>
       </c>
       <c r="U78" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B79" s="9">
         <v>46156.6326615162</v>
@@ -6147,7 +6150,7 @@
         <v>46223.58691267361</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6174,13 +6177,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6190,7 +6193,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B80" s="5">
         <v>46156.6326856713</v>
@@ -6200,7 +6203,7 @@
         <v>46243.728052499995</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6227,13 +6230,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q80" s="5">
         <v>46300</v>
@@ -6253,7 +6256,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B81" s="9">
         <v>46156.63269413194</v>
@@ -6263,7 +6266,7 @@
         <v>46223.586982106484</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6290,13 +6293,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6306,7 +6309,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B82" s="5">
         <v>46156.632715810185</v>
@@ -6316,7 +6319,7 @@
         <v>46243.728118784726</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6343,13 +6346,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q82" s="5">
         <v>46302</v>
@@ -6369,7 +6372,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B83" s="9">
         <v>46156.63272170139</v>
@@ -6379,7 +6382,7 @@
         <v>46223.5870543287</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6406,13 +6409,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6422,7 +6425,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B84" s="5">
         <v>46156.63273993056</v>
@@ -6432,7 +6435,7 @@
         <v>46205.90465030093</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6456,7 +6459,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6469,7 +6472,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B85" s="9">
         <v>46156.63274356481</v>
@@ -6479,16 +6482,16 @@
         <v>46243.72816118055</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I85" s="9">
         <v>46303</v>
@@ -6506,13 +6509,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q85" s="9">
         <v>46303</v>
@@ -6532,7 +6535,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B86" s="5">
         <v>46156.63274915509</v>
@@ -6542,16 +6545,16 @@
         <v>46156.72692035879</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I86" s="5">
         <v>46303</v>
@@ -6569,13 +6572,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6585,7 +6588,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B87" s="9">
         <v>46156.63276633102</v>
@@ -6595,7 +6598,7 @@
         <v>46243.72822305556</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6620,13 +6623,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q87" s="9">
         <v>46304</v>
@@ -6646,7 +6649,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B88" s="5">
         <v>46156.63277084491</v>
@@ -6656,7 +6659,7 @@
         <v>46223.587235150466</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6683,13 +6686,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6699,7 +6702,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B89" s="9">
         <v>46156.63283398148</v>
@@ -6711,16 +6714,16 @@
         <v>46243.72826583333</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I89" s="9">
         <v>46307</v>
@@ -6738,13 +6741,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q89" s="9">
         <v>46307</v>
@@ -6759,12 +6762,12 @@
         <v>1</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B90" s="5">
         <v>46156.63284013889</v>
@@ -6776,16 +6779,16 @@
         <v>46205.90481071759</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I90" s="5">
         <v>46307</v>
@@ -6803,13 +6806,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6819,7 +6822,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B91" s="9">
         <v>46156.63286864583</v>
@@ -6829,16 +6832,16 @@
         <v>46243.72830107639</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I91" s="9">
         <v>46308</v>
@@ -6856,13 +6859,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q91" s="9">
         <v>46308</v>
@@ -6882,7 +6885,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B92" s="5">
         <v>46156.632875972224</v>
@@ -6892,16 +6895,16 @@
         <v>46205.9047287037</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -6917,13 +6920,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6933,7 +6936,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B93" s="9">
         <v>46156.63290420139</v>
@@ -6943,7 +6946,7 @@
         <v>46156.71731457176</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>25</v>
@@ -6967,7 +6970,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>26</v>
@@ -6980,7 +6983,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B94" s="5">
         <v>46156.63290788194</v>
@@ -6990,16 +6993,16 @@
         <v>46156.72728918982</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I94" s="5">
         <v>46309</v>
@@ -7017,13 +7020,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q94" s="5">
         <v>46309</v>
@@ -7043,7 +7046,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B95" s="9">
         <v>46156.63291414352</v>
@@ -7053,7 +7056,7 @@
         <v>46209.559051539356</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7080,13 +7083,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q95" s="9">
         <v>46309</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -5622,7 +5622,7 @@
         <v>46212.59667254629</v>
       </c>
       <c r="D70" s="5">
-        <v>46212.59669387732</v>
+        <v>46251.18256594907</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>243</v>
@@ -5666,8 +5666,8 @@
       <c r="R70" s="5">
         <v>46258</v>
       </c>
-      <c r="S70" s="7" t="s">
-        <v>33</v>
+      <c r="S70" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -726,7 +726,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
+    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1214809612627656</t>
@@ -5022,7 +5022,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46244.91622328704</v>
+        <v>46252.55709236111</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>218</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -726,7 +726,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1214809612627656</t>
@@ -5022,7 +5022,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46252.55709236111</v>
+        <v>46252.698030266205</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>218</v>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46243.73553203704</v>
+        <v>46252.60737517361</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>246</v>
@@ -5730,9 +5730,11 @@
       <c r="B72" s="5">
         <v>46156.63252219907</v>
       </c>
-      <c r="C72" s="6"/>
+      <c r="C72" s="5">
+        <v>46252.60736721064</v>
+      </c>
       <c r="D72" s="5">
-        <v>46243.727824525464</v>
+        <v>46252.60738498843</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>249</v>
@@ -5780,7 +5782,7 @@
         <v>33</v>
       </c>
       <c r="T72" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U72" s="7" t="s">
         <v>27</v>
@@ -6432,7 +6434,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46205.90465030093</v>
+        <v>46252.60758673611</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>276</v>
@@ -6707,11 +6709,9 @@
       <c r="B89" s="9">
         <v>46156.63283398148</v>
       </c>
-      <c r="C89" s="9">
-        <v>46205.90464569445</v>
-      </c>
+      <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46243.72826583333</v>
+        <v>46252.60758185185</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>289</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -5140,7 +5140,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46243.72774834491</v>
+        <v>46254.172488854165</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5184,8 +5184,8 @@
       <c r="R62" s="5">
         <v>46261</v>
       </c>
-      <c r="S62" s="7" t="s">
-        <v>33</v>
+      <c r="S62" s="12" t="s">
+        <v>150</v>
       </c>
       <c r="T62" s="6">
         <v>0.5</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -513,235 +513,235 @@
     <t>Fabricación estructura proveedor externo OT 4317,Generacion OC Fabricación Externa OT 4317</t>
   </si>
   <si>
+    <t>1214809612514049</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4317,Fabricación Externa  OT 4317</t>
+  </si>
+  <si>
+    <t>1214809416604370</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa  OT 4317,Control de calidad fabricación externa  OT 4317,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1214809416604385</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4317</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214809416604395</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4317</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4317,Fabricación Mecanizado OT 4317</t>
+  </si>
+  <si>
+    <t>1214809660839754</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4317,Fabricación Mecanizado OT 4317</t>
+  </si>
+  <si>
+    <t>1214809660839769</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4317</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado,Mecanizado OT 4317</t>
+  </si>
+  <si>
+    <t>1214787972061379</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1214809534019503</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214809534019523</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor OT 4317,Planos preliminar</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214809528759377</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Fabricación externa  OT 4317,propuesta Corte Laser OT 4317,Propuesta Corte plasma  OT 4317,Propuesta Mecanizado OT 4317,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214809528759486</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4317 ZVN 1-16-126/4</t>
+  </si>
+  <si>
+    <t>1214809528759496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">check pruebas FAT,OT 4317 ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214809528761692</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214809534064558</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214809534064578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,OT 4317 ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214809534098507</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214809534098527</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214809612618886</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214809612618901</t>
+  </si>
+  <si>
+    <t>1214809660900538</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Preparación Materiales,Armado</t>
+  </si>
+  <si>
+    <t>1214809660900548</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1214809612627656</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparación Materiales,OT 4317 ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214809660921603</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214809612514049</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4317,Fabricación Externa  OT 4317</t>
-  </si>
-  <si>
-    <t>1214809416604370</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa  OT 4317,Control de calidad fabricación externa  OT 4317,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1214809416604385</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4317</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1214809416604395</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4317</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4317,Fabricación Mecanizado OT 4317</t>
-  </si>
-  <si>
-    <t>1214809660839754</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4317,Fabricación Mecanizado OT 4317</t>
-  </si>
-  <si>
-    <t>1214809660839769</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4317</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado,Mecanizado OT 4317</t>
-  </si>
-  <si>
-    <t>1214787972061379</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1214809534019503</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214809534019523</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT 4317,Planos preliminar</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214809528759377</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Fabricación externa  OT 4317,propuesta Corte Laser OT 4317,Propuesta Corte plasma  OT 4317,Propuesta Mecanizado OT 4317,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214809528759486</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4317 ZVN 1-16-126/4</t>
-  </si>
-  <si>
-    <t>1214809528759496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">check pruebas FAT,OT 4317 ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214809528761692</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214809534064558</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214809534064578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,OT 4317 ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214809534098507</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214809534098527</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214809612618886</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214809612618901</t>
-  </si>
-  <si>
-    <t>1214809660900538</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Preparación Materiales,Armado</t>
-  </si>
-  <si>
-    <t>1214809660900548</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1214809612627656</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preparación Materiales,OT 4317 ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214809660921603</t>
-  </si>
-  <si>
-    <t>Armado</t>
   </si>
   <si>
     <t>1214809660937075</t>
@@ -3769,7 +3769,7 @@
         <v>46204.87072556713</v>
       </c>
       <c r="D39" s="9">
-        <v>46247.1955693287</v>
+        <v>46255.203167997686</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>146</v>
@@ -3813,8 +3813,8 @@
       <c r="R39" s="9">
         <v>46254</v>
       </c>
-      <c r="S39" s="12" t="s">
-        <v>150</v>
+      <c r="S39" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -3825,7 +3825,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46156.632269444446</v>
@@ -3870,7 +3870,7 @@
         <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3880,7 +3880,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B41" s="9">
         <v>46156.63227357639</v>
@@ -3892,7 +3892,7 @@
         <v>46204.86000238426</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -3925,7 +3925,7 @@
         <v>89</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3935,7 +3935,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46156.63227760416</v>
@@ -3947,16 +3947,16 @@
         <v>46210.64958435185</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46254</v>
@@ -3977,7 +3977,7 @@
         <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3990,7 +3990,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="9">
         <v>46156.63228021991</v>
@@ -4002,7 +4002,7 @@
         <v>46227.16739670139</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
@@ -4032,7 +4032,7 @@
         <v>91</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4055,7 +4055,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46156.63228315972</v>
@@ -4094,13 +4094,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4110,7 +4110,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B45" s="9">
         <v>46156.63228715278</v>
@@ -4122,7 +4122,7 @@
         <v>46199.56229454861</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4149,13 +4149,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>86</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4165,7 +4165,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46156.63196493055</v>
@@ -4175,7 +4175,7 @@
         <v>46184.58079096065</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4199,7 +4199,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4209,12 +4209,12 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B47" s="9">
         <v>46156.63229164352</v>
@@ -4226,16 +4226,16 @@
         <v>46197.714709479165</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="I47" s="9">
         <v>46150</v>
@@ -4253,13 +4253,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="9">
         <v>46150</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46156.632296261574</v>
@@ -4291,16 +4291,16 @@
         <v>46212.59685061342</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46204</v>
@@ -4318,13 +4318,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46204</v>
@@ -4344,7 +4344,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46156.63230224537</v>
@@ -4362,10 +4362,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4381,13 +4381,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="9">
         <v>46211</v>
@@ -4407,7 +4407,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46156.632315358795</v>
@@ -4417,16 +4417,16 @@
         <v>46243.72746450231</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46301</v>
@@ -4444,10 +4444,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4470,7 +4470,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46156.6323189699</v>
@@ -4480,16 +4480,16 @@
         <v>46156.725962881945</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I51" s="9">
         <v>46301</v>
@@ -4507,13 +4507,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>191</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>192</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4523,7 +4523,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46156.63233141204</v>
@@ -4535,7 +4535,7 @@
         <v>46210.64940796296</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4559,7 +4559,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4576,7 +4576,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B53" s="9">
         <v>46156.63233460648</v>
@@ -4588,16 +4588,16 @@
         <v>46231.1833272338</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="10" t="s">
+      <c r="H53" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="I53" s="9">
         <v>46227</v>
@@ -4615,13 +4615,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>135</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q53" s="9">
         <v>46227</v>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B54" s="5">
         <v>46156.63233969908</v>
@@ -4653,16 +4653,16 @@
         <v>46233.16737983796</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I54" s="5">
         <v>46231</v>
@@ -4680,13 +4680,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="Q54" s="5">
         <v>46231</v>
@@ -4706,7 +4706,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B55" s="9">
         <v>46156.632350671294</v>
@@ -4718,16 +4718,16 @@
         <v>46231.183327164355</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="I55" s="9">
         <v>46227</v>
@@ -4745,13 +4745,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>143</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q55" s="9">
         <v>46227</v>
@@ -4771,7 +4771,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B56" s="5">
         <v>46156.63235533565</v>
@@ -4783,16 +4783,16 @@
         <v>46233.16738262732</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I56" s="5">
         <v>46231</v>
@@ -4810,13 +4810,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q56" s="5">
         <v>46231</v>
@@ -4836,7 +4836,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B57" s="9">
         <v>46156.63235945602</v>
@@ -4848,16 +4848,16 @@
         <v>46231.18332707176</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="I57" s="9">
         <v>46227</v>
@@ -4875,13 +4875,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q57" s="9">
         <v>46227</v>
@@ -4901,7 +4901,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B58" s="5">
         <v>46156.63236322917</v>
@@ -4913,16 +4913,16 @@
         <v>46233.1673805787</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I58" s="5">
         <v>46231</v>
@@ -4940,13 +4940,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q58" s="5">
         <v>46231</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B59" s="9">
         <v>46156.63236744213</v>
@@ -4976,7 +4976,7 @@
         <v>46203.5014815162</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>25</v>
@@ -5000,7 +5000,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -5013,7 +5013,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B60" s="5">
         <v>46156.63237008102</v>
@@ -5025,16 +5025,16 @@
         <v>46252.698030266205</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I60" s="5">
         <v>46233</v>
@@ -5052,13 +5052,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="5">
         <v>46233</v>
@@ -5078,7 +5078,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B61" s="9">
         <v>46156.63237584491</v>
@@ -5090,16 +5090,16 @@
         <v>46211.68096520833</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I61" s="9">
         <v>46233</v>
@@ -5117,13 +5117,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O61" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="P61" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5133,7 +5133,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B62" s="5">
         <v>46156.63239597222</v>
@@ -5143,16 +5143,16 @@
         <v>46254.172488854165</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I62" s="5">
         <v>46244</v>
@@ -5170,13 +5170,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="5">
         <v>46244</v>
@@ -5185,7 +5185,7 @@
         <v>46261</v>
       </c>
       <c r="S62" s="12" t="s">
-        <v>150</v>
+        <v>226</v>
       </c>
       <c r="T62" s="6">
         <v>0.5</v>
@@ -5206,16 +5206,16 @@
         <v>46211.68097021991</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5233,7 +5233,7 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O63" s="10" t="s">
         <v>228</v>
@@ -5265,10 +5265,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I64" s="5">
         <v>46262</v>
@@ -5286,13 +5286,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5322,16 +5322,16 @@
         <v>46197.83511621528</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I65" s="9">
         <v>46262</v>
@@ -5377,7 +5377,7 @@
         <v>46212.59671021991</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5436,10 +5436,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="I67" s="9">
         <v>46154</v>
@@ -5457,13 +5457,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>112</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q67" s="9">
         <v>46154</v>
@@ -5501,10 +5501,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="I68" s="5">
         <v>46268</v>
@@ -5522,13 +5522,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q68" s="5">
         <v>46268</v>
@@ -5566,10 +5566,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="I69" s="9">
         <v>46294</v>
@@ -5587,13 +5587,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>121</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q69" s="9">
         <v>46294</v>
@@ -5631,10 +5631,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="I70" s="5">
         <v>46255</v>
@@ -5652,10 +5652,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>244</v>
@@ -5667,7 +5667,7 @@
         <v>46258</v>
       </c>
       <c r="S70" s="12" t="s">
-        <v>150</v>
+        <v>226</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -5800,7 +5800,7 @@
         <v>46223.58665680556</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5885,7 +5885,7 @@
         <v>246</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>246</v>
@@ -5918,7 +5918,7 @@
         <v>46223.5867387037</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -6003,7 +6003,7 @@
         <v>246</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>246</v>
@@ -6036,7 +6036,7 @@
         <v>46223.58682719908</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6119,7 +6119,7 @@
         <v>246</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>246</v>
@@ -6137,7 +6137,7 @@
         <v>0</v>
       </c>
       <c r="U78" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6152,7 +6152,7 @@
         <v>46223.58691267361</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6235,7 +6235,7 @@
         <v>246</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>246</v>
@@ -6268,7 +6268,7 @@
         <v>46223.586982106484</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6298,7 +6298,7 @@
         <v>267</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>269</v>
@@ -6351,7 +6351,7 @@
         <v>246</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>272</v>
@@ -6384,7 +6384,7 @@
         <v>46223.5870543287</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6414,7 +6414,7 @@
         <v>271</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>274</v>
@@ -6547,7 +6547,7 @@
         <v>46156.72692035879</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6577,7 +6577,7 @@
         <v>279</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>283</v>
@@ -6628,7 +6628,7 @@
         <v>276</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>276</v>
@@ -6661,7 +6661,7 @@
         <v>46223.587235150466</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6691,7 +6691,7 @@
         <v>285</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>287</v>
@@ -6720,10 +6720,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I89" s="9">
         <v>46307</v>
@@ -6744,7 +6744,7 @@
         <v>276</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>276</v>
@@ -6762,7 +6762,7 @@
         <v>1</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -6779,16 +6779,16 @@
         <v>46205.90481071759</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I90" s="5">
         <v>46307</v>
@@ -6809,7 +6809,7 @@
         <v>289</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>291</v>
@@ -6838,10 +6838,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I91" s="9">
         <v>46308</v>
@@ -6862,7 +6862,7 @@
         <v>276</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>294</v>
@@ -6895,16 +6895,16 @@
         <v>46205.9047287037</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -6923,7 +6923,7 @@
         <v>293</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>293</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -5256,7 +5256,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46243.72779826389</v>
+        <v>46258.16750372685</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>231</v>
@@ -5300,8 +5300,8 @@
       <c r="R64" s="5">
         <v>46265</v>
       </c>
-      <c r="S64" s="7" t="s">
-        <v>33</v>
+      <c r="S64" s="12" t="s">
+        <v>226</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -723,7 +723,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
   </si>
   <si>
     <t>1214809612627656</t>
@@ -5022,7 +5022,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46252.698030266205</v>
+        <v>46258.64932003472</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -5622,7 +5622,7 @@
         <v>46212.59667254629</v>
       </c>
       <c r="D70" s="5">
-        <v>46251.18256594907</v>
+        <v>46259.17218527778</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>243</v>
@@ -5666,8 +5666,8 @@
       <c r="R70" s="5">
         <v>46258</v>
       </c>
-      <c r="S70" s="12" t="s">
-        <v>226</v>
+      <c r="S70" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -357,6 +357,9 @@
     <t>Fabricación Alabe OT 4317,Generación OC Alabe OT 4317</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1214809660726272</t>
   </si>
   <si>
@@ -739,9 +742,6 @@
   </si>
   <si>
     <t>Armado</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214809660937075</t>
@@ -2785,7 +2785,7 @@
         <v>46210.646711388894</v>
       </c>
       <c r="D23" s="9">
-        <v>46210.6467582176</v>
+        <v>46260.20709655093</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>94</v>
@@ -2829,8 +2829,8 @@
       <c r="R23" s="9">
         <v>46267</v>
       </c>
-      <c r="S23" s="7" t="s">
-        <v>33</v>
+      <c r="S23" s="12" t="s">
+        <v>98</v>
       </c>
       <c r="T23" s="10">
         <v>1</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B24" s="5">
         <v>46156.63214259259</v>
@@ -2853,7 +2853,7 @@
         <v>46195.92922337963</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2886,7 +2886,7 @@
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2897,12 +2897,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B25" s="9">
         <v>46156.63214717593</v>
@@ -2914,7 +2914,7 @@
         <v>46210.64669667824</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
@@ -2944,10 +2944,10 @@
         <v>94</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -2958,12 +2958,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5">
         <v>46156.6321521412</v>
@@ -2975,7 +2975,7 @@
         <v>46210.64698900463</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3005,7 +3005,7 @@
         <v>91</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>91</v>
@@ -3028,7 +3028,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B27" s="9">
         <v>46156.63215657407</v>
@@ -3040,7 +3040,7 @@
         <v>46210.64692099537</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3067,13 +3067,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3084,12 +3084,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46156.63216167824</v>
@@ -3101,7 +3101,7 @@
         <v>46210.64695642361</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3128,13 +3128,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3145,12 +3145,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="9">
         <v>46156.63216756945</v>
@@ -3162,7 +3162,7 @@
         <v>46210.645560289355</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
@@ -3192,7 +3192,7 @@
         <v>91</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>91</v>
@@ -3215,7 +3215,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46156.63217278935</v>
@@ -3227,7 +3227,7 @@
         <v>46195.92957241899</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3254,13 +3254,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3271,12 +3271,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" s="9">
         <v>46156.63217837963</v>
@@ -3288,7 +3288,7 @@
         <v>46210.64553332176</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3315,13 +3315,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3332,12 +3332,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46156.63218368056</v>
@@ -3349,7 +3349,7 @@
         <v>46197.78355364583</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3376,13 +3376,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3393,12 +3393,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="9">
         <v>46156.632188240736</v>
@@ -3410,16 +3410,16 @@
         <v>46227.16739667824</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I33" s="9">
         <v>46216</v>
@@ -3440,7 +3440,7 @@
         <v>91</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>91</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46156.63219359954</v>
@@ -3475,16 +3475,16 @@
         <v>46199.55917045139</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I34" s="5">
         <v>46216</v>
@@ -3502,13 +3502,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3519,12 +3519,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B35" s="9">
         <v>46156.63219844908</v>
@@ -3536,16 +3536,16 @@
         <v>46199.5597825</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I35" s="9">
         <v>46218</v>
@@ -3563,13 +3563,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3580,12 +3580,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46156.63225444444</v>
@@ -3597,16 +3597,16 @@
         <v>46227.167396689816</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46216</v>
@@ -3627,7 +3627,7 @@
         <v>91</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46156.632258206024</v>
@@ -3668,10 +3668,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I37" s="9">
         <v>46216</v>
@@ -3689,13 +3689,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>82</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3705,7 +3705,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46156.63226241898</v>
@@ -3717,16 +3717,16 @@
         <v>46199.55996042824</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I38" s="5">
         <v>46218</v>
@@ -3744,13 +3744,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B39" s="9">
         <v>46156.63226644676</v>
@@ -3772,16 +3772,16 @@
         <v>46255.203167997686</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I39" s="9">
         <v>46216</v>
@@ -3802,7 +3802,7 @@
         <v>91</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3825,7 +3825,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46156.632269444446</v>
@@ -3843,10 +3843,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46216</v>
@@ -3864,13 +3864,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3880,7 +3880,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46156.63227357639</v>
@@ -3892,16 +3892,16 @@
         <v>46204.86000238426</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I41" s="9">
         <v>46225</v>
@@ -3919,13 +3919,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>89</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3935,7 +3935,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46156.63227760416</v>
@@ -3947,16 +3947,16 @@
         <v>46210.64958435185</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46254</v>
@@ -3974,10 +3974,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3990,7 +3990,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46156.63228021991</v>
@@ -4002,16 +4002,16 @@
         <v>46227.16739670139</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I43" s="9">
         <v>46216</v>
@@ -4032,7 +4032,7 @@
         <v>91</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4055,7 +4055,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46156.63228315972</v>
@@ -4073,10 +4073,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I44" s="5">
         <v>46216</v>
@@ -4094,13 +4094,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4110,7 +4110,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B45" s="9">
         <v>46156.63228715278</v>
@@ -4122,16 +4122,16 @@
         <v>46199.56229454861</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I45" s="9">
         <v>46218</v>
@@ -4149,13 +4149,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>86</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4165,7 +4165,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46156.63196493055</v>
@@ -4175,7 +4175,7 @@
         <v>46184.58079096065</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4199,7 +4199,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4209,12 +4209,12 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" s="9">
         <v>46156.63229164352</v>
@@ -4226,16 +4226,16 @@
         <v>46197.714709479165</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I47" s="9">
         <v>46150</v>
@@ -4253,13 +4253,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="9">
         <v>46150</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46156.632296261574</v>
@@ -4291,16 +4291,16 @@
         <v>46212.59685061342</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46204</v>
@@ -4318,13 +4318,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46204</v>
@@ -4344,7 +4344,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46156.63230224537</v>
@@ -4362,10 +4362,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4381,13 +4381,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="9">
         <v>46211</v>
@@ -4407,7 +4407,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46156.632315358795</v>
@@ -4417,16 +4417,16 @@
         <v>46243.72746450231</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46301</v>
@@ -4444,10 +4444,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4465,12 +4465,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46156.6323189699</v>
@@ -4480,16 +4480,16 @@
         <v>46156.725962881945</v>
       </c>
       <c r="E51" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I51" s="9">
         <v>46301</v>
@@ -4507,13 +4507,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4523,7 +4523,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46156.63233141204</v>
@@ -4535,7 +4535,7 @@
         <v>46210.64940796296</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4559,7 +4559,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4576,7 +4576,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="9">
         <v>46156.63233460648</v>
@@ -4588,16 +4588,16 @@
         <v>46231.1833272338</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I53" s="9">
         <v>46227</v>
@@ -4615,13 +4615,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q53" s="9">
         <v>46227</v>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B54" s="5">
         <v>46156.63233969908</v>
@@ -4653,16 +4653,16 @@
         <v>46233.16737983796</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I54" s="5">
         <v>46231</v>
@@ -4680,13 +4680,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q54" s="5">
         <v>46231</v>
@@ -4706,7 +4706,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B55" s="9">
         <v>46156.632350671294</v>
@@ -4718,16 +4718,16 @@
         <v>46231.183327164355</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I55" s="9">
         <v>46227</v>
@@ -4745,13 +4745,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q55" s="9">
         <v>46227</v>
@@ -4771,7 +4771,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B56" s="5">
         <v>46156.63235533565</v>
@@ -4783,16 +4783,16 @@
         <v>46233.16738262732</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I56" s="5">
         <v>46231</v>
@@ -4810,13 +4810,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q56" s="5">
         <v>46231</v>
@@ -4836,7 +4836,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B57" s="9">
         <v>46156.63235945602</v>
@@ -4848,16 +4848,16 @@
         <v>46231.18332707176</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I57" s="9">
         <v>46227</v>
@@ -4875,13 +4875,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q57" s="9">
         <v>46227</v>
@@ -4901,7 +4901,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46156.63236322917</v>
@@ -4913,16 +4913,16 @@
         <v>46233.1673805787</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I58" s="5">
         <v>46231</v>
@@ -4940,13 +4940,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q58" s="5">
         <v>46231</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B59" s="9">
         <v>46156.63236744213</v>
@@ -4976,7 +4976,7 @@
         <v>46203.5014815162</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>25</v>
@@ -5000,7 +5000,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -5013,7 +5013,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B60" s="5">
         <v>46156.63237008102</v>
@@ -5025,16 +5025,16 @@
         <v>46258.64932003472</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I60" s="5">
         <v>46233</v>
@@ -5052,13 +5052,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="5">
         <v>46233</v>
@@ -5078,7 +5078,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B61" s="9">
         <v>46156.63237584491</v>
@@ -5090,16 +5090,16 @@
         <v>46211.68096520833</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I61" s="9">
         <v>46233</v>
@@ -5117,13 +5117,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5133,7 +5133,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B62" s="5">
         <v>46156.63239597222</v>
@@ -5143,16 +5143,16 @@
         <v>46254.172488854165</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I62" s="5">
         <v>46244</v>
@@ -5170,13 +5170,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q62" s="5">
         <v>46244</v>
@@ -5185,7 +5185,7 @@
         <v>46261</v>
       </c>
       <c r="S62" s="12" t="s">
-        <v>226</v>
+        <v>98</v>
       </c>
       <c r="T62" s="6">
         <v>0.5</v>
@@ -5206,16 +5206,16 @@
         <v>46211.68097021991</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5233,7 +5233,7 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O63" s="10" t="s">
         <v>228</v>
@@ -5265,10 +5265,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I64" s="5">
         <v>46262</v>
@@ -5286,13 +5286,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5301,13 +5301,13 @@
         <v>46265</v>
       </c>
       <c r="S64" s="12" t="s">
-        <v>226</v>
+        <v>98</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5322,16 +5322,16 @@
         <v>46197.83511621528</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I65" s="9">
         <v>46262</v>
@@ -5377,7 +5377,7 @@
         <v>46212.59671021991</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5436,10 +5436,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I67" s="9">
         <v>46154</v>
@@ -5457,13 +5457,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q67" s="9">
         <v>46154</v>
@@ -5501,10 +5501,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I68" s="5">
         <v>46268</v>
@@ -5522,13 +5522,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q68" s="5">
         <v>46268</v>
@@ -5566,10 +5566,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I69" s="9">
         <v>46294</v>
@@ -5587,13 +5587,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q69" s="9">
         <v>46294</v>
@@ -5631,10 +5631,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I70" s="5">
         <v>46255</v>
@@ -5652,10 +5652,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>244</v>
@@ -5800,7 +5800,7 @@
         <v>46223.58665680556</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5885,7 +5885,7 @@
         <v>246</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>246</v>
@@ -5918,7 +5918,7 @@
         <v>46223.5867387037</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -6003,7 +6003,7 @@
         <v>246</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>246</v>
@@ -6036,7 +6036,7 @@
         <v>46223.58682719908</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6119,7 +6119,7 @@
         <v>246</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>246</v>
@@ -6137,7 +6137,7 @@
         <v>0</v>
       </c>
       <c r="U78" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6152,7 +6152,7 @@
         <v>46223.58691267361</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6235,7 +6235,7 @@
         <v>246</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>246</v>
@@ -6253,7 +6253,7 @@
         <v>0</v>
       </c>
       <c r="U80" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6268,7 +6268,7 @@
         <v>46223.586982106484</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6298,7 +6298,7 @@
         <v>267</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>269</v>
@@ -6351,7 +6351,7 @@
         <v>246</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>272</v>
@@ -6369,7 +6369,7 @@
         <v>0</v>
       </c>
       <c r="U82" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6384,7 +6384,7 @@
         <v>46223.5870543287</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6414,7 +6414,7 @@
         <v>271</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>274</v>
@@ -6532,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="U85" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6547,7 +6547,7 @@
         <v>46156.72692035879</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6577,7 +6577,7 @@
         <v>279</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>283</v>
@@ -6628,7 +6628,7 @@
         <v>276</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>276</v>
@@ -6646,7 +6646,7 @@
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -6661,7 +6661,7 @@
         <v>46223.587235150466</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6691,7 +6691,7 @@
         <v>285</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>287</v>
@@ -6720,10 +6720,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I89" s="9">
         <v>46307</v>
@@ -6744,7 +6744,7 @@
         <v>276</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>276</v>
@@ -6762,7 +6762,7 @@
         <v>1</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -6779,16 +6779,16 @@
         <v>46205.90481071759</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I90" s="5">
         <v>46307</v>
@@ -6809,7 +6809,7 @@
         <v>289</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>291</v>
@@ -6838,10 +6838,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I91" s="9">
         <v>46308</v>
@@ -6862,7 +6862,7 @@
         <v>276</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>294</v>
@@ -6880,7 +6880,7 @@
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6895,16 +6895,16 @@
         <v>46205.9047287037</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -6923,7 +6923,7 @@
         <v>293</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>293</v>
@@ -7041,7 +7041,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7104,7 +7104,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="305">
   <si>
     <t>50001547 - XEMORTIZ (AMERICAS GOLD)</t>
   </si>
@@ -4971,9 +4971,11 @@
       <c r="B59" s="9">
         <v>46156.63236744213</v>
       </c>
-      <c r="C59" s="10"/>
+      <c r="C59" s="9">
+        <v>46260.57962289352</v>
+      </c>
       <c r="D59" s="9">
-        <v>46203.5014815162</v>
+        <v>46260.57963890047</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>215</v>
@@ -5008,8 +5010,12 @@
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
       <c r="S59" s="10"/>
-      <c r="T59" s="10"/>
-      <c r="U59" s="10"/>
+      <c r="T59" s="10">
+        <v>1</v>
+      </c>
+      <c r="U59" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
@@ -5138,9 +5144,11 @@
       <c r="B62" s="5">
         <v>46156.63239597222</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46260.57952762731</v>
+      </c>
       <c r="D62" s="5">
-        <v>46254.172488854165</v>
+        <v>46260.579541666666</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5188,7 +5196,7 @@
         <v>98</v>
       </c>
       <c r="T62" s="6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="U62" s="7" t="s">
         <v>27</v>
@@ -5201,9 +5209,11 @@
       <c r="B63" s="9">
         <v>46156.632400069444</v>
       </c>
-      <c r="C63" s="10"/>
+      <c r="C63" s="9">
+        <v>46260.57942789352</v>
+      </c>
       <c r="D63" s="9">
-        <v>46211.68097021991</v>
+        <v>46260.57943028935</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>191</v>
@@ -5254,9 +5264,11 @@
       <c r="B64" s="5">
         <v>46156.63246734954</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46260.57960524305</v>
+      </c>
       <c r="D64" s="5">
-        <v>46258.16750372685</v>
+        <v>46260.579632037035</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>231</v>
@@ -5304,10 +5316,10 @@
         <v>98</v>
       </c>
       <c r="T64" s="6">
-        <v>0</v>
-      </c>
-      <c r="U64" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U64" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5319,7 +5331,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46197.83511621528</v>
+        <v>46260.579435381944</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>191</v>
@@ -6086,7 +6098,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46243.72800076389</v>
+        <v>46260.58012614583</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>262</v>
@@ -6136,8 +6148,8 @@
       <c r="T78" s="6">
         <v>0</v>
       </c>
-      <c r="U78" s="12" t="s">
-        <v>171</v>
+      <c r="U78" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6202,7 +6214,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46243.728052499995</v>
+        <v>46260.58014068287</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>267</v>
@@ -6252,8 +6264,8 @@
       <c r="T80" s="6">
         <v>0</v>
       </c>
-      <c r="U80" s="11" t="s">
-        <v>102</v>
+      <c r="U80" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6318,7 +6330,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46243.728118784726</v>
+        <v>46260.580162743056</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>271</v>
@@ -6368,8 +6380,8 @@
       <c r="T82" s="6">
         <v>0</v>
       </c>
-      <c r="U82" s="11" t="s">
-        <v>102</v>
+      <c r="U82" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6434,7 +6446,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46252.60758673611</v>
+        <v>46260.57978292824</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>276</v>
@@ -6595,9 +6607,11 @@
       <c r="B87" s="9">
         <v>46156.63276633102</v>
       </c>
-      <c r="C87" s="10"/>
+      <c r="C87" s="9">
+        <v>46260.5797765162</v>
+      </c>
       <c r="D87" s="9">
-        <v>46243.72822305556</v>
+        <v>46260.579793020835</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>285</v>
@@ -6643,10 +6657,10 @@
         <v>33</v>
       </c>
       <c r="T87" s="10">
-        <v>0</v>
-      </c>
-      <c r="U87" s="11" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="U87" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -6709,9 +6723,11 @@
       <c r="B89" s="9">
         <v>46156.63283398148</v>
       </c>
-      <c r="C89" s="10"/>
+      <c r="C89" s="9">
+        <v>46260.57972408565</v>
+      </c>
       <c r="D89" s="9">
-        <v>46252.60758185185</v>
+        <v>46260.579739768524</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>289</v>
@@ -6761,8 +6777,8 @@
       <c r="T89" s="10">
         <v>1</v>
       </c>
-      <c r="U89" s="12" t="s">
-        <v>171</v>
+      <c r="U89" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -726,7 +726,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
+    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
   </si>
   <si>
     <t>1214809612627656</t>
@@ -5028,7 +5028,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46258.64932003472</v>
+        <v>46260.67955381944</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>218</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -726,7 +726,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
+    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6,OT 4075  -ZVRv 1-16-37/6 ,OT 4413  -ZVRv 1-22-185/6  </t>
   </si>
   <si>
     <t>1214809612627656</t>
@@ -5028,7 +5028,7 @@
         <v>46203.50147394676</v>
       </c>
       <c r="D60" s="5">
-        <v>46260.67955381944</v>
+        <v>46261.600823553235</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>218</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -5148,7 +5148,7 @@
         <v>46260.57952762731</v>
       </c>
       <c r="D62" s="5">
-        <v>46260.579541666666</v>
+        <v>46262.17267717593</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5192,8 +5192,8 @@
       <c r="R62" s="5">
         <v>46261</v>
       </c>
-      <c r="S62" s="12" t="s">
-        <v>98</v>
+      <c r="S62" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T62" s="6">
         <v>1</v>
@@ -5504,7 +5504,7 @@
         <v>46210.647080740746</v>
       </c>
       <c r="D68" s="5">
-        <v>46210.64712949074</v>
+        <v>46262.1691583912</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>239</v>
@@ -5548,8 +5548,8 @@
       <c r="R68" s="5">
         <v>46269</v>
       </c>
-      <c r="S68" s="7" t="s">
-        <v>33</v>
+      <c r="S68" s="12" t="s">
+        <v>98</v>
       </c>
       <c r="T68" s="6">
         <v>1</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -5331,7 +5331,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46260.579435381944</v>
+        <v>46265.168551724535</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>191</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -5268,7 +5268,7 @@
         <v>46260.57960524305</v>
       </c>
       <c r="D64" s="5">
-        <v>46260.579632037035</v>
+        <v>46266.17902365741</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>231</v>
@@ -5312,8 +5312,8 @@
       <c r="R64" s="5">
         <v>46265</v>
       </c>
-      <c r="S64" s="12" t="s">
-        <v>98</v>
+      <c r="S64" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T64" s="6">
         <v>1</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -357,430 +357,430 @@
     <t>Fabricación Alabe OT 4317,Generación OC Alabe OT 4317</t>
   </si>
   <si>
+    <t>1214809660726272</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Alabe OT 4317,Alabe OT 4317 </t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1214809612445357</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe OT 4317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Alabe,Alabe OT 4317 </t>
+  </si>
+  <si>
+    <t>1214809612445375</t>
+  </si>
+  <si>
+    <t>rodete OT 4317</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4317,Fabricación Rodete OT 4317</t>
+  </si>
+  <si>
+    <t>1214809528606251</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4317</t>
+  </si>
+  <si>
+    <t>rodete OT 4317,Fabricación Rodete OT 4317</t>
+  </si>
+  <si>
+    <t>1214809528606269</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4317</t>
+  </si>
+  <si>
+    <t>rodete OT 4317,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1214809660744152</t>
+  </si>
+  <si>
+    <t>Motor OT 4317</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor OT 4317,Generación OC motor OT 4317,Fabricación motor OT 4317</t>
+  </si>
+  <si>
+    <t>1214809660744167</t>
+  </si>
+  <si>
+    <t>Generación OC motor OT 4317</t>
+  </si>
+  <si>
+    <t>Motor OT 4317,Fabricación motor OT 4317,Planos motor proveedor OT 4317</t>
+  </si>
+  <si>
+    <t>1214809528630155</t>
+  </si>
+  <si>
+    <t>Fabricación motor OT 4317</t>
+  </si>
+  <si>
+    <t>Motor OT 4317,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214809528630173</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor OT 4317</t>
+  </si>
+  <si>
+    <t>Motor OT 4317,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214809416559834</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4317</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC materiales corte Laser OT 4317,Fabricacion Corte Laser OT 4317 </t>
+  </si>
+  <si>
+    <t>1214809416559849</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales corte Laser OT 4317,Fabricacion Corte Laser OT 4317 </t>
+  </si>
+  <si>
+    <t>1214809533941481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion Corte Laser OT 4317 </t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4317,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>1214809416517093</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4317</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4317,Fabricación Corte Plasma  OT 4317</t>
+  </si>
+  <si>
+    <t>1214809533981000</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4317,Fabricación Corte Plasma  OT 4317</t>
+  </si>
+  <si>
+    <t>1214809533981015</t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma  OT 4317</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4317,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>1214809612514039</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4317</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4317,Generacion OC Fabricación Externa OT 4317</t>
+  </si>
+  <si>
+    <t>1214809612514049</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4317,Fabricación Externa  OT 4317</t>
+  </si>
+  <si>
+    <t>1214809416604370</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa  OT 4317,Control de calidad fabricación externa  OT 4317,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1214809416604385</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4317</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214809416604395</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4317</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4317,Fabricación Mecanizado OT 4317</t>
+  </si>
+  <si>
+    <t>1214809660839754</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4317,Fabricación Mecanizado OT 4317</t>
+  </si>
+  <si>
+    <t>1214809660839769</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4317</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado,Mecanizado OT 4317</t>
+  </si>
+  <si>
+    <t>1214787972061379</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1214809534019503</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214809534019523</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor OT 4317,Planos preliminar</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214809528759377</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Fabricación externa  OT 4317,propuesta Corte Laser OT 4317,Propuesta Corte plasma  OT 4317,Propuesta Mecanizado OT 4317,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214809528759486</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4317 ZVN 1-16-126/4</t>
+  </si>
+  <si>
+    <t>1214809528759496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">check pruebas FAT,OT 4317 ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214809528761692</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214809534064558</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214809534064578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,OT 4317 ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214809534098507</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214809534098527</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214809612618886</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214809612618901</t>
+  </si>
+  <si>
+    <t>1214809660900538</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Preparación Materiales,Armado</t>
+  </si>
+  <si>
+    <t>1214809660900548</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6,OT 4075  -ZVRv 1-16-37/6 ,OT 4413  -ZVRv 1-22-185/6  </t>
+  </si>
+  <si>
+    <t>1214809612627656</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparación Materiales,OT 4317 ZVN 1-16-126/4 </t>
+  </si>
+  <si>
+    <t>1214809660921603</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>1214809660937075</t>
+  </si>
+  <si>
+    <t>OT 4317 ZVN 1-16-126/4 ,check planos</t>
+  </si>
+  <si>
+    <t>OT 4317 ZVN 1-16-126/4 ,Armado</t>
+  </si>
+  <si>
+    <t>1214809528949839</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214809528949854</t>
+  </si>
+  <si>
+    <t>Revestimiento,OT 4317 ZVN 1-16-126/4 ,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214809416824301</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,Recepcion Alabe,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214809528985005</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1214809528985025</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214809660726272</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Alabe OT 4317,Alabe OT 4317 </t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214809612445357</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Alabe,Alabe OT 4317 </t>
-  </si>
-  <si>
-    <t>1214809612445375</t>
-  </si>
-  <si>
-    <t>rodete OT 4317</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4317,Fabricación Rodete OT 4317</t>
-  </si>
-  <si>
-    <t>1214809528606251</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4317</t>
-  </si>
-  <si>
-    <t>rodete OT 4317,Fabricación Rodete OT 4317</t>
-  </si>
-  <si>
-    <t>1214809528606269</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4317</t>
-  </si>
-  <si>
-    <t>rodete OT 4317,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1214809660744152</t>
-  </si>
-  <si>
-    <t>Motor OT 4317</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT 4317,Generación OC motor OT 4317,Fabricación motor OT 4317</t>
-  </si>
-  <si>
-    <t>1214809660744167</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4317</t>
-  </si>
-  <si>
-    <t>Motor OT 4317,Fabricación motor OT 4317,Planos motor proveedor OT 4317</t>
-  </si>
-  <si>
-    <t>1214809528630155</t>
-  </si>
-  <si>
-    <t>Fabricación motor OT 4317</t>
-  </si>
-  <si>
-    <t>Motor OT 4317,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214809528630173</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT 4317</t>
-  </si>
-  <si>
-    <t>Motor OT 4317,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214809416559834</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4317</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC materiales corte Laser OT 4317,Fabricacion Corte Laser OT 4317 </t>
-  </si>
-  <si>
-    <t>1214809416559849</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales corte Laser OT 4317,Fabricacion Corte Laser OT 4317 </t>
-  </si>
-  <si>
-    <t>1214809533941481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion Corte Laser OT 4317 </t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4317,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>1214809416517093</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4317</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4317,Fabricación Corte Plasma  OT 4317</t>
-  </si>
-  <si>
-    <t>1214809533981000</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4317,Fabricación Corte Plasma  OT 4317</t>
-  </si>
-  <si>
-    <t>1214809533981015</t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma  OT 4317</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4317,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>1214809612514039</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4317</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4317,Generacion OC Fabricación Externa OT 4317</t>
-  </si>
-  <si>
-    <t>1214809612514049</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4317,Fabricación Externa  OT 4317</t>
-  </si>
-  <si>
-    <t>1214809416604370</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa  OT 4317,Control de calidad fabricación externa  OT 4317,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1214809416604385</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4317</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1214809416604395</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4317</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4317,Fabricación Mecanizado OT 4317</t>
-  </si>
-  <si>
-    <t>1214809660839754</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4317,Fabricación Mecanizado OT 4317</t>
-  </si>
-  <si>
-    <t>1214809660839769</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4317</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado,Mecanizado OT 4317</t>
-  </si>
-  <si>
-    <t>1214787972061379</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1214809534019503</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214809534019523</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT 4317,Planos preliminar</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214809528759377</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Fabricación externa  OT 4317,propuesta Corte Laser OT 4317,Propuesta Corte plasma  OT 4317,Propuesta Mecanizado OT 4317,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 ,OT 4317 ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214809528759486</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4317 ZVN 1-16-126/4</t>
-  </si>
-  <si>
-    <t>1214809528759496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">check pruebas FAT,OT 4317 ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214809528761692</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214809534064558</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214809534064578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,OT 4317 ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214809534098507</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214809534098527</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214809612618886</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214809612618901</t>
-  </si>
-  <si>
-    <t>1214809660900538</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Preparación Materiales,Armado</t>
-  </si>
-  <si>
-    <t>1214809660900548</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4317 ZVN 1-16-126/4 ,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6,OT 4075  -ZVRv 1-16-37/6 ,OT 4413  -ZVRv 1-22-185/6  </t>
-  </si>
-  <si>
-    <t>1214809612627656</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preparación Materiales,OT 4317 ZVN 1-16-126/4 </t>
-  </si>
-  <si>
-    <t>1214809660921603</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>1214809660937075</t>
-  </si>
-  <si>
-    <t>OT 4317 ZVN 1-16-126/4 ,check planos</t>
-  </si>
-  <si>
-    <t>OT 4317 ZVN 1-16-126/4 ,Armado</t>
-  </si>
-  <si>
-    <t>1214809528949839</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214809528949854</t>
-  </si>
-  <si>
-    <t>Revestimiento,OT 4317 ZVN 1-16-126/4 ,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214809416824301</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,Recepcion Alabe,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214809528985005</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1214809528985025</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
   </si>
   <si>
     <t>1214809528990374</t>
@@ -2785,7 +2785,7 @@
         <v>46210.646711388894</v>
       </c>
       <c r="D23" s="9">
-        <v>46260.20709655093</v>
+        <v>46268.17901107639</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>94</v>
@@ -2829,8 +2829,8 @@
       <c r="R23" s="9">
         <v>46267</v>
       </c>
-      <c r="S23" s="12" t="s">
-        <v>98</v>
+      <c r="S23" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T23" s="10">
         <v>1</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5">
         <v>46156.63214259259</v>
@@ -2853,7 +2853,7 @@
         <v>46195.92922337963</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2886,7 +2886,7 @@
         <v>69</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2897,12 +2897,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B25" s="9">
         <v>46156.63214717593</v>
@@ -2914,7 +2914,7 @@
         <v>46210.64669667824</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
@@ -2944,10 +2944,10 @@
         <v>94</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -2958,12 +2958,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B26" s="5">
         <v>46156.6321521412</v>
@@ -2975,7 +2975,7 @@
         <v>46210.64698900463</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3005,7 +3005,7 @@
         <v>91</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>91</v>
@@ -3028,7 +3028,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B27" s="9">
         <v>46156.63215657407</v>
@@ -3040,7 +3040,7 @@
         <v>46210.64692099537</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3067,13 +3067,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3084,12 +3084,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46156.63216167824</v>
@@ -3101,7 +3101,7 @@
         <v>46210.64695642361</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3128,13 +3128,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3145,12 +3145,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B29" s="9">
         <v>46156.63216756945</v>
@@ -3162,7 +3162,7 @@
         <v>46210.645560289355</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
@@ -3192,7 +3192,7 @@
         <v>91</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>91</v>
@@ -3215,7 +3215,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46156.63217278935</v>
@@ -3227,7 +3227,7 @@
         <v>46195.92957241899</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3254,13 +3254,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3271,12 +3271,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B31" s="9">
         <v>46156.63217837963</v>
@@ -3288,7 +3288,7 @@
         <v>46210.64553332176</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3315,13 +3315,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3332,12 +3332,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46156.63218368056</v>
@@ -3349,7 +3349,7 @@
         <v>46197.78355364583</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3376,13 +3376,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3393,12 +3393,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B33" s="9">
         <v>46156.632188240736</v>
@@ -3410,16 +3410,16 @@
         <v>46227.16739667824</v>
       </c>
       <c r="E33" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I33" s="9">
         <v>46216</v>
@@ -3440,7 +3440,7 @@
         <v>91</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>91</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46156.63219359954</v>
@@ -3475,16 +3475,16 @@
         <v>46199.55917045139</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I34" s="5">
         <v>46216</v>
@@ -3502,13 +3502,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3519,12 +3519,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B35" s="9">
         <v>46156.63219844908</v>
@@ -3536,16 +3536,16 @@
         <v>46199.5597825</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I35" s="9">
         <v>46218</v>
@@ -3563,13 +3563,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3580,12 +3580,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46156.63225444444</v>
@@ -3597,16 +3597,16 @@
         <v>46227.167396689816</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46216</v>
@@ -3627,7 +3627,7 @@
         <v>91</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B37" s="9">
         <v>46156.632258206024</v>
@@ -3668,10 +3668,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I37" s="9">
         <v>46216</v>
@@ -3689,13 +3689,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>82</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3705,7 +3705,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46156.63226241898</v>
@@ -3717,16 +3717,16 @@
         <v>46199.55996042824</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I38" s="5">
         <v>46218</v>
@@ -3744,13 +3744,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B39" s="9">
         <v>46156.63226644676</v>
@@ -3772,16 +3772,16 @@
         <v>46255.203167997686</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="I39" s="9">
         <v>46216</v>
@@ -3802,7 +3802,7 @@
         <v>91</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3825,7 +3825,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46156.632269444446</v>
@@ -3843,10 +3843,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46216</v>
@@ -3864,13 +3864,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3880,7 +3880,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B41" s="9">
         <v>46156.63227357639</v>
@@ -3892,16 +3892,16 @@
         <v>46204.86000238426</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="I41" s="9">
         <v>46225</v>
@@ -3919,13 +3919,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>89</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3935,7 +3935,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46156.63227760416</v>
@@ -3947,16 +3947,16 @@
         <v>46210.64958435185</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46254</v>
@@ -3974,10 +3974,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3990,7 +3990,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="9">
         <v>46156.63228021991</v>
@@ -4002,16 +4002,16 @@
         <v>46227.16739670139</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I43" s="9">
         <v>46216</v>
@@ -4032,7 +4032,7 @@
         <v>91</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4055,7 +4055,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46156.63228315972</v>
@@ -4073,10 +4073,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="I44" s="5">
         <v>46216</v>
@@ -4094,13 +4094,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4110,7 +4110,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B45" s="9">
         <v>46156.63228715278</v>
@@ -4122,16 +4122,16 @@
         <v>46199.56229454861</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="I45" s="9">
         <v>46218</v>
@@ -4149,13 +4149,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>86</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4165,7 +4165,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46156.63196493055</v>
@@ -4175,7 +4175,7 @@
         <v>46184.58079096065</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4199,7 +4199,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4209,12 +4209,12 @@
       <c r="S46" s="6"/>
       <c r="T46" s="6"/>
       <c r="U46" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B47" s="9">
         <v>46156.63229164352</v>
@@ -4226,16 +4226,16 @@
         <v>46197.714709479165</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="I47" s="9">
         <v>46150</v>
@@ -4253,13 +4253,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="9">
         <v>46150</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46156.632296261574</v>
@@ -4291,16 +4291,16 @@
         <v>46212.59685061342</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46204</v>
@@ -4318,13 +4318,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46204</v>
@@ -4344,7 +4344,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46156.63230224537</v>
@@ -4362,10 +4362,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4381,13 +4381,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="9">
         <v>46211</v>
@@ -4407,7 +4407,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46156.632315358795</v>
@@ -4417,16 +4417,16 @@
         <v>46243.72746450231</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46301</v>
@@ -4444,10 +4444,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4465,12 +4465,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46156.6323189699</v>
@@ -4480,16 +4480,16 @@
         <v>46156.725962881945</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I51" s="9">
         <v>46301</v>
@@ -4507,13 +4507,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>191</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>192</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4523,7 +4523,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46156.63233141204</v>
@@ -4535,7 +4535,7 @@
         <v>46210.64940796296</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4559,7 +4559,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4576,7 +4576,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B53" s="9">
         <v>46156.63233460648</v>
@@ -4588,16 +4588,16 @@
         <v>46231.1833272338</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="10" t="s">
+      <c r="H53" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="I53" s="9">
         <v>46227</v>
@@ -4615,13 +4615,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q53" s="9">
         <v>46227</v>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B54" s="5">
         <v>46156.63233969908</v>
@@ -4653,16 +4653,16 @@
         <v>46233.16737983796</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I54" s="5">
         <v>46231</v>
@@ -4680,13 +4680,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="Q54" s="5">
         <v>46231</v>
@@ -4706,7 +4706,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B55" s="9">
         <v>46156.632350671294</v>
@@ -4718,16 +4718,16 @@
         <v>46231.183327164355</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="I55" s="9">
         <v>46227</v>
@@ -4745,13 +4745,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q55" s="9">
         <v>46227</v>
@@ -4771,7 +4771,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B56" s="5">
         <v>46156.63235533565</v>
@@ -4783,16 +4783,16 @@
         <v>46233.16738262732</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I56" s="5">
         <v>46231</v>
@@ -4810,13 +4810,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q56" s="5">
         <v>46231</v>
@@ -4836,7 +4836,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B57" s="9">
         <v>46156.63235945602</v>
@@ -4848,16 +4848,16 @@
         <v>46231.18332707176</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="I57" s="9">
         <v>46227</v>
@@ -4875,13 +4875,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q57" s="9">
         <v>46227</v>
@@ -4901,7 +4901,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B58" s="5">
         <v>46156.63236322917</v>
@@ -4913,16 +4913,16 @@
         <v>46233.1673805787</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I58" s="5">
         <v>46231</v>
@@ -4940,13 +4940,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q58" s="5">
         <v>46231</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B59" s="9">
         <v>46156.63236744213</v>
@@ -4978,7 +4978,7 @@
         <v>46260.57963890047</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>25</v>
@@ -5002,7 +5002,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -5019,7 +5019,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B60" s="5">
         <v>46156.63237008102</v>
@@ -5031,16 +5031,16 @@
         <v>46261.600823553235</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I60" s="5">
         <v>46233</v>
@@ -5058,13 +5058,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q60" s="5">
         <v>46233</v>
@@ -5084,7 +5084,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B61" s="9">
         <v>46156.63237584491</v>
@@ -5096,16 +5096,16 @@
         <v>46211.68096520833</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I61" s="9">
         <v>46233</v>
@@ -5123,13 +5123,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O61" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="P61" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5139,7 +5139,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B62" s="5">
         <v>46156.63239597222</v>
@@ -5151,16 +5151,16 @@
         <v>46262.17267717593</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I62" s="5">
         <v>46244</v>
@@ -5178,13 +5178,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="5">
         <v>46244</v>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B63" s="9">
         <v>46156.632400069444</v>
@@ -5216,16 +5216,16 @@
         <v>46260.57943028935</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5243,13 +5243,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>228</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>229</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5259,7 +5259,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B64" s="5">
         <v>46156.63246734954</v>
@@ -5271,16 +5271,16 @@
         <v>46266.17902365741</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I64" s="5">
         <v>46262</v>
@@ -5298,13 +5298,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B65" s="9">
         <v>46156.632472627316</v>
@@ -5334,16 +5334,16 @@
         <v>46265.168551724535</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="I65" s="9">
         <v>46262</v>
@@ -5361,13 +5361,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5377,7 +5377,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B66" s="5">
         <v>46156.6324928588</v>
@@ -5389,7 +5389,7 @@
         <v>46212.59671021991</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5413,7 +5413,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5430,7 +5430,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B67" s="9">
         <v>46156.63249635417</v>
@@ -5442,16 +5442,16 @@
         <v>46210.64718186343</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="I67" s="9">
         <v>46154</v>
@@ -5469,13 +5469,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q67" s="9">
         <v>46154</v>
@@ -5495,7 +5495,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B68" s="5">
         <v>46156.63250229167</v>
@@ -5507,16 +5507,16 @@
         <v>46262.1691583912</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="I68" s="5">
         <v>46268</v>
@@ -5534,13 +5534,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q68" s="5">
         <v>46268</v>
@@ -5549,7 +5549,7 @@
         <v>46269</v>
       </c>
       <c r="S68" s="12" t="s">
-        <v>98</v>
+        <v>239</v>
       </c>
       <c r="T68" s="6">
         <v>1</v>
@@ -5578,10 +5578,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>199</v>
       </c>
       <c r="I69" s="9">
         <v>46294</v>
@@ -5599,13 +5599,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q69" s="9">
         <v>46294</v>
@@ -5643,10 +5643,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="I70" s="5">
         <v>46255</v>
@@ -5664,10 +5664,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>244</v>
@@ -5812,7 +5812,7 @@
         <v>46223.58665680556</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5897,7 +5897,7 @@
         <v>246</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>246</v>
@@ -5930,7 +5930,7 @@
         <v>46223.5867387037</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -6015,7 +6015,7 @@
         <v>246</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>246</v>
@@ -6048,7 +6048,7 @@
         <v>46223.58682719908</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6131,7 +6131,7 @@
         <v>246</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>246</v>
@@ -6164,7 +6164,7 @@
         <v>46223.58691267361</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6247,7 +6247,7 @@
         <v>246</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>246</v>
@@ -6280,7 +6280,7 @@
         <v>46223.586982106484</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6310,7 +6310,7 @@
         <v>267</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>269</v>
@@ -6363,7 +6363,7 @@
         <v>246</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>272</v>
@@ -6396,7 +6396,7 @@
         <v>46223.5870543287</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6426,7 +6426,7 @@
         <v>271</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>274</v>
@@ -6544,7 +6544,7 @@
         <v>0</v>
       </c>
       <c r="U85" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -6559,7 +6559,7 @@
         <v>46156.72692035879</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6589,7 +6589,7 @@
         <v>279</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>283</v>
@@ -6642,7 +6642,7 @@
         <v>276</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>276</v>
@@ -6675,7 +6675,7 @@
         <v>46223.587235150466</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6705,7 +6705,7 @@
         <v>285</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>287</v>
@@ -6736,10 +6736,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I89" s="9">
         <v>46307</v>
@@ -6760,7 +6760,7 @@
         <v>276</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>276</v>
@@ -6795,16 +6795,16 @@
         <v>46205.90481071759</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I90" s="5">
         <v>46307</v>
@@ -6825,7 +6825,7 @@
         <v>289</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>291</v>
@@ -6854,10 +6854,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I91" s="9">
         <v>46308</v>
@@ -6878,7 +6878,7 @@
         <v>276</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>294</v>
@@ -6896,7 +6896,7 @@
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6911,16 +6911,16 @@
         <v>46205.9047287037</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -6939,7 +6939,7 @@
         <v>293</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>293</v>
@@ -7057,7 +7057,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7120,7 +7120,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="304">
   <si>
     <t>50001547 - XEMORTIZ (AMERICAS GOLD)</t>
   </si>
@@ -571,9 +571,6 @@
   </si>
   <si>
     <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214809534019503</t>
@@ -4170,9 +4167,11 @@
       <c r="B46" s="5">
         <v>46156.63196493055</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46268.89995103009</v>
+      </c>
       <c r="D46" s="5">
-        <v>46184.58079096065</v>
+        <v>46268.899964675926</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4207,14 +4206,16 @@
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="12" t="s">
-        <v>170</v>
+      <c r="T46" s="6">
+        <v>1</v>
+      </c>
+      <c r="U46" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B47" s="9">
         <v>46156.63229164352</v>
@@ -4226,16 +4227,16 @@
         <v>46197.714709479165</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="I47" s="9">
         <v>46150</v>
@@ -4259,7 +4260,7 @@
         <v>60</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q47" s="9">
         <v>46150</v>
@@ -4279,7 +4280,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46156.632296261574</v>
@@ -4291,16 +4292,16 @@
         <v>46212.59685061342</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46204</v>
@@ -4321,10 +4322,10 @@
         <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46204</v>
@@ -4344,7 +4345,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B49" s="9">
         <v>46156.63230224537</v>
@@ -4362,10 +4363,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>181</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>182</v>
       </c>
       <c r="I49" s="10"/>
       <c r="J49" s="9">
@@ -4384,10 +4385,10 @@
         <v>168</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q49" s="9">
         <v>46211</v>
@@ -4407,26 +4408,28 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46156.632315358795</v>
       </c>
-      <c r="C50" s="6"/>
+      <c r="C50" s="5">
+        <v>46268.899935775466</v>
+      </c>
       <c r="D50" s="5">
-        <v>46243.72746450231</v>
+        <v>46268.89995125</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I50" s="5">
         <v>46301</v>
@@ -4447,7 +4450,7 @@
         <v>168</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4462,15 +4465,15 @@
         <v>33</v>
       </c>
       <c r="T50" s="6">
-        <v>0</v>
-      </c>
-      <c r="U50" s="11" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U50" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B51" s="9">
         <v>46156.6323189699</v>
@@ -4480,16 +4483,16 @@
         <v>46156.725962881945</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I51" s="9">
         <v>46301</v>
@@ -4507,13 +4510,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4523,7 +4526,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46156.63233141204</v>
@@ -4535,7 +4538,7 @@
         <v>46210.64940796296</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>25</v>
@@ -4559,7 +4562,7 @@
         <v>26</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4576,7 +4579,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
         <v>46156.63233460648</v>
@@ -4588,16 +4591,16 @@
         <v>46231.1833272338</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="10" t="s">
+      <c r="H53" s="10" t="s">
         <v>197</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>198</v>
       </c>
       <c r="I53" s="9">
         <v>46227</v>
@@ -4615,13 +4618,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>135</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q53" s="9">
         <v>46227</v>
@@ -4641,7 +4644,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46156.63233969908</v>
@@ -4653,7 +4656,7 @@
         <v>46233.16737983796</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4680,13 +4683,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="Q54" s="5">
         <v>46231</v>
@@ -4706,7 +4709,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B55" s="9">
         <v>46156.632350671294</v>
@@ -4718,16 +4721,16 @@
         <v>46231.183327164355</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>197</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>198</v>
       </c>
       <c r="I55" s="9">
         <v>46227</v>
@@ -4745,13 +4748,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>143</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q55" s="9">
         <v>46227</v>
@@ -4771,7 +4774,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B56" s="5">
         <v>46156.63235533565</v>
@@ -4783,7 +4786,7 @@
         <v>46233.16738262732</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4810,13 +4813,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q56" s="5">
         <v>46231</v>
@@ -4836,7 +4839,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B57" s="9">
         <v>46156.63235945602</v>
@@ -4848,16 +4851,16 @@
         <v>46231.18332707176</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>197</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>198</v>
       </c>
       <c r="I57" s="9">
         <v>46227</v>
@@ -4875,13 +4878,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>165</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q57" s="9">
         <v>46227</v>
@@ -4901,7 +4904,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B58" s="5">
         <v>46156.63236322917</v>
@@ -4913,7 +4916,7 @@
         <v>46233.1673805787</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4940,13 +4943,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q58" s="5">
         <v>46231</v>
@@ -4966,7 +4969,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B59" s="9">
         <v>46156.63236744213</v>
@@ -4978,7 +4981,7 @@
         <v>46260.57963890047</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>25</v>
@@ -5002,7 +5005,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>26</v>
@@ -5019,7 +5022,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B60" s="5">
         <v>46156.63237008102</v>
@@ -5031,16 +5034,16 @@
         <v>46261.600823553235</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>219</v>
       </c>
       <c r="I60" s="5">
         <v>46233</v>
@@ -5058,13 +5061,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q60" s="5">
         <v>46233</v>
@@ -5084,7 +5087,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B61" s="9">
         <v>46156.63237584491</v>
@@ -5096,16 +5099,16 @@
         <v>46211.68096520833</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>219</v>
       </c>
       <c r="I61" s="9">
         <v>46233</v>
@@ -5123,13 +5126,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O61" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="P61" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5139,7 +5142,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B62" s="5">
         <v>46156.63239597222</v>
@@ -5151,16 +5154,16 @@
         <v>46262.17267717593</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>219</v>
       </c>
       <c r="I62" s="5">
         <v>46244</v>
@@ -5178,13 +5181,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q62" s="5">
         <v>46244</v>
@@ -5204,7 +5207,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B63" s="9">
         <v>46156.632400069444</v>
@@ -5216,16 +5219,16 @@
         <v>46260.57943028935</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>219</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5243,13 +5246,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5259,7 +5262,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B64" s="5">
         <v>46156.63246734954</v>
@@ -5271,7 +5274,7 @@
         <v>46266.17902365741</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5298,13 +5301,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q64" s="5">
         <v>46262</v>
@@ -5324,7 +5327,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B65" s="9">
         <v>46156.632472627316</v>
@@ -5334,7 +5337,7 @@
         <v>46265.168551724535</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5361,13 +5364,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5377,7 +5380,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B66" s="5">
         <v>46156.6324928588</v>
@@ -5389,7 +5392,7 @@
         <v>46212.59671021991</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5413,7 +5416,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5430,7 +5433,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B67" s="9">
         <v>46156.63249635417</v>
@@ -5442,16 +5445,16 @@
         <v>46210.64718186343</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>197</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>198</v>
       </c>
       <c r="I67" s="9">
         <v>46154</v>
@@ -5469,13 +5472,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>112</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q67" s="9">
         <v>46154</v>
@@ -5495,7 +5498,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B68" s="5">
         <v>46156.63250229167</v>
@@ -5507,16 +5510,16 @@
         <v>46262.1691583912</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>198</v>
       </c>
       <c r="I68" s="5">
         <v>46268</v>
@@ -5534,13 +5537,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q68" s="5">
         <v>46268</v>
@@ -5549,7 +5552,7 @@
         <v>46269</v>
       </c>
       <c r="S68" s="12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="T68" s="6">
         <v>1</v>
@@ -5560,7 +5563,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B69" s="9">
         <v>46156.63250851852</v>
@@ -5572,16 +5575,16 @@
         <v>46210.645706863426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>197</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>198</v>
       </c>
       <c r="I69" s="9">
         <v>46294</v>
@@ -5599,13 +5602,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>121</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q69" s="9">
         <v>46294</v>
@@ -5625,7 +5628,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B70" s="5">
         <v>46156.63251465278</v>
@@ -5637,16 +5640,16 @@
         <v>46259.17218527778</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>198</v>
       </c>
       <c r="I70" s="5">
         <v>46255</v>
@@ -5664,13 +5667,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>153</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q70" s="5">
         <v>46255</v>
@@ -5690,7 +5693,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B71" s="9">
         <v>46156.63251914352</v>
@@ -5700,7 +5703,7 @@
         <v>46252.60737517361</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5724,7 +5727,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5737,7 +5740,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B72" s="5">
         <v>46156.63252219907</v>
@@ -5749,7 +5752,7 @@
         <v>46252.60738498843</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5776,13 +5779,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q72" s="5">
         <v>46266</v>
@@ -5802,7 +5805,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B73" s="9">
         <v>46156.63252934028</v>
@@ -5812,7 +5815,7 @@
         <v>46223.58665680556</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5839,10 +5842,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="O73" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="O73" s="10" t="s">
-        <v>250</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5855,7 +5858,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B74" s="5">
         <v>46156.63254586805</v>
@@ -5867,7 +5870,7 @@
         <v>46243.72785484954</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5894,13 +5897,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q74" s="5">
         <v>46288</v>
@@ -5920,7 +5923,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B75" s="9">
         <v>46156.63255047453</v>
@@ -5930,7 +5933,7 @@
         <v>46223.5867387037</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5957,13 +5960,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O75" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="P75" s="10" t="s">
         <v>255</v>
-      </c>
-      <c r="P75" s="10" t="s">
-        <v>256</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5973,7 +5976,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B76" s="5">
         <v>46156.63257873843</v>
@@ -5985,7 +5988,7 @@
         <v>46243.72789628472</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6012,13 +6015,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q76" s="5">
         <v>46290</v>
@@ -6038,7 +6041,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B77" s="9">
         <v>46156.632582986116</v>
@@ -6048,7 +6051,7 @@
         <v>46223.58682719908</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6075,13 +6078,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6091,7 +6094,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B78" s="5">
         <v>46156.632655671296</v>
@@ -6101,7 +6104,7 @@
         <v>46260.58012614583</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6128,13 +6131,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q78" s="5">
         <v>46296</v>
@@ -6154,7 +6157,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B79" s="9">
         <v>46156.6326615162</v>
@@ -6164,7 +6167,7 @@
         <v>46223.58691267361</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6191,13 +6194,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O79" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="P79" s="10" t="s">
         <v>264</v>
-      </c>
-      <c r="P79" s="10" t="s">
-        <v>265</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6207,7 +6210,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B80" s="5">
         <v>46156.6326856713</v>
@@ -6217,7 +6220,7 @@
         <v>46260.58014068287</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6244,13 +6247,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q80" s="5">
         <v>46300</v>
@@ -6270,7 +6273,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B81" s="9">
         <v>46156.63269413194</v>
@@ -6280,7 +6283,7 @@
         <v>46223.586982106484</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6307,13 +6310,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6323,7 +6326,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B82" s="5">
         <v>46156.632715810185</v>
@@ -6333,7 +6336,7 @@
         <v>46260.580162743056</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6360,13 +6363,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q82" s="5">
         <v>46302</v>
@@ -6386,7 +6389,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B83" s="9">
         <v>46156.63272170139</v>
@@ -6396,7 +6399,7 @@
         <v>46223.5870543287</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6423,13 +6426,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6439,7 +6442,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B84" s="5">
         <v>46156.63273993056</v>
@@ -6449,7 +6452,7 @@
         <v>46260.57978292824</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6473,7 +6476,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6486,7 +6489,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B85" s="9">
         <v>46156.63274356481</v>
@@ -6496,16 +6499,16 @@
         <v>46243.72816118055</v>
       </c>
       <c r="E85" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="F85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" s="10" t="s">
+      <c r="H85" s="10" t="s">
         <v>280</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>281</v>
       </c>
       <c r="I85" s="9">
         <v>46303</v>
@@ -6523,13 +6526,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q85" s="9">
         <v>46303</v>
@@ -6549,7 +6552,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B86" s="5">
         <v>46156.63274915509</v>
@@ -6559,16 +6562,16 @@
         <v>46156.72692035879</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>280</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>281</v>
       </c>
       <c r="I86" s="5">
         <v>46303</v>
@@ -6586,13 +6589,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6602,7 +6605,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B87" s="9">
         <v>46156.63276633102</v>
@@ -6614,7 +6617,7 @@
         <v>46260.579793020835</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6639,13 +6642,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q87" s="9">
         <v>46304</v>
@@ -6665,7 +6668,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B88" s="5">
         <v>46156.63277084491</v>
@@ -6675,7 +6678,7 @@
         <v>46223.587235150466</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6702,13 +6705,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6718,7 +6721,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B89" s="9">
         <v>46156.63283398148</v>
@@ -6730,16 +6733,16 @@
         <v>46260.579739768524</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>219</v>
       </c>
       <c r="I89" s="9">
         <v>46307</v>
@@ -6757,13 +6760,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q89" s="9">
         <v>46307</v>
@@ -6783,7 +6786,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B90" s="5">
         <v>46156.63284013889</v>
@@ -6795,16 +6798,16 @@
         <v>46205.90481071759</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>219</v>
       </c>
       <c r="I90" s="5">
         <v>46307</v>
@@ -6822,13 +6825,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6838,7 +6841,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B91" s="9">
         <v>46156.63286864583</v>
@@ -6848,16 +6851,16 @@
         <v>46243.72830107639</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>219</v>
       </c>
       <c r="I91" s="9">
         <v>46308</v>
@@ -6875,13 +6878,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q91" s="9">
         <v>46308</v>
@@ -6901,7 +6904,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B92" s="5">
         <v>46156.632875972224</v>
@@ -6911,16 +6914,16 @@
         <v>46205.9047287037</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>219</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -6936,13 +6939,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6952,7 +6955,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B93" s="9">
         <v>46156.63290420139</v>
@@ -6962,7 +6965,7 @@
         <v>46156.71731457176</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>25</v>
@@ -6986,7 +6989,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>26</v>
@@ -6999,7 +7002,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B94" s="5">
         <v>46156.63290788194</v>
@@ -7009,16 +7012,16 @@
         <v>46156.72728918982</v>
       </c>
       <c r="E94" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G94" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="F94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G94" s="6" t="s">
+      <c r="H94" s="6" t="s">
         <v>301</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>302</v>
       </c>
       <c r="I94" s="5">
         <v>46309</v>
@@ -7036,13 +7039,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q94" s="5">
         <v>46309</v>
@@ -7062,7 +7065,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B95" s="9">
         <v>46156.63291414352</v>
@@ -7072,7 +7075,7 @@
         <v>46209.559051539356</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7099,13 +7102,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q95" s="9">
         <v>46309</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="303">
   <si>
     <t>50001547 - XEMORTIZ (AMERICAS GOLD)</t>
   </si>
@@ -775,9 +775,6 @@
   </si>
   <si>
     <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214809528990374</t>
@@ -1002,7 +999,7 @@
       <color rgb="FF000000"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1042,11 +1039,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFe8384f"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -1092,7 +1084,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1111,7 +1103,6 @@
     <xf numFmtId="14" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5507,7 +5498,7 @@
         <v>46210.647080740746</v>
       </c>
       <c r="D68" s="5">
-        <v>46262.1691583912</v>
+        <v>46270.182112002316</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>237</v>
@@ -5551,8 +5542,8 @@
       <c r="R68" s="5">
         <v>46269</v>
       </c>
-      <c r="S68" s="12" t="s">
-        <v>238</v>
+      <c r="S68" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T68" s="6">
         <v>1</v>
@@ -5563,7 +5554,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B69" s="9">
         <v>46156.63250851852</v>
@@ -5575,7 +5566,7 @@
         <v>46210.645706863426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5628,7 +5619,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B70" s="5">
         <v>46156.63251465278</v>
@@ -5640,7 +5631,7 @@
         <v>46259.17218527778</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5673,7 +5664,7 @@
         <v>153</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q70" s="5">
         <v>46255</v>
@@ -5693,7 +5684,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B71" s="9">
         <v>46156.63251914352</v>
@@ -5703,7 +5694,7 @@
         <v>46252.60737517361</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5727,7 +5718,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5740,7 +5731,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B72" s="5">
         <v>46156.63252219907</v>
@@ -5752,7 +5743,7 @@
         <v>46252.60738498843</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5779,13 +5770,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q72" s="5">
         <v>46266</v>
@@ -5805,7 +5796,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B73" s="9">
         <v>46156.63252934028</v>
@@ -5842,10 +5833,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="O73" s="10" t="s">
         <v>248</v>
-      </c>
-      <c r="O73" s="10" t="s">
-        <v>249</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5858,7 +5849,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B74" s="5">
         <v>46156.63254586805</v>
@@ -5870,7 +5861,7 @@
         <v>46243.72785484954</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5897,13 +5888,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q74" s="5">
         <v>46288</v>
@@ -5923,7 +5914,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B75" s="9">
         <v>46156.63255047453</v>
@@ -5960,13 +5951,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O75" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="P75" s="10" t="s">
         <v>254</v>
-      </c>
-      <c r="P75" s="10" t="s">
-        <v>255</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5976,7 +5967,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B76" s="5">
         <v>46156.63257873843</v>
@@ -5988,7 +5979,7 @@
         <v>46243.72789628472</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6015,13 +6006,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q76" s="5">
         <v>46290</v>
@@ -6041,7 +6032,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B77" s="9">
         <v>46156.632582986116</v>
@@ -6078,13 +6069,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6094,7 +6085,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B78" s="5">
         <v>46156.632655671296</v>
@@ -6104,7 +6095,7 @@
         <v>46260.58012614583</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6131,13 +6122,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q78" s="5">
         <v>46296</v>
@@ -6157,7 +6148,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B79" s="9">
         <v>46156.6326615162</v>
@@ -6194,13 +6185,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O79" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="P79" s="10" t="s">
         <v>263</v>
-      </c>
-      <c r="P79" s="10" t="s">
-        <v>264</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6210,7 +6201,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B80" s="5">
         <v>46156.6326856713</v>
@@ -6220,7 +6211,7 @@
         <v>46260.58014068287</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6247,13 +6238,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q80" s="5">
         <v>46300</v>
@@ -6273,7 +6264,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B81" s="9">
         <v>46156.63269413194</v>
@@ -6310,13 +6301,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6326,7 +6317,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B82" s="5">
         <v>46156.632715810185</v>
@@ -6336,7 +6327,7 @@
         <v>46260.580162743056</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6363,13 +6354,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q82" s="5">
         <v>46302</v>
@@ -6389,7 +6380,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B83" s="9">
         <v>46156.63272170139</v>
@@ -6426,13 +6417,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>187</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6442,7 +6433,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B84" s="5">
         <v>46156.63273993056</v>
@@ -6452,7 +6443,7 @@
         <v>46260.57978292824</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6476,7 +6467,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6489,7 +6480,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B85" s="9">
         <v>46156.63274356481</v>
@@ -6499,16 +6490,16 @@
         <v>46243.72816118055</v>
       </c>
       <c r="E85" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="F85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" s="10" t="s">
+      <c r="H85" s="10" t="s">
         <v>279</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>280</v>
       </c>
       <c r="I85" s="9">
         <v>46303</v>
@@ -6526,13 +6517,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q85" s="9">
         <v>46303</v>
@@ -6552,7 +6543,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B86" s="5">
         <v>46156.63274915509</v>
@@ -6568,10 +6559,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>279</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>280</v>
       </c>
       <c r="I86" s="5">
         <v>46303</v>
@@ -6589,13 +6580,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6605,7 +6596,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B87" s="9">
         <v>46156.63276633102</v>
@@ -6617,7 +6608,7 @@
         <v>46260.579793020835</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6642,13 +6633,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q87" s="9">
         <v>46304</v>
@@ -6668,7 +6659,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B88" s="5">
         <v>46156.63277084491</v>
@@ -6705,13 +6696,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6721,7 +6712,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B89" s="9">
         <v>46156.63283398148</v>
@@ -6733,7 +6724,7 @@
         <v>46260.579739768524</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6760,13 +6751,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O89" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q89" s="9">
         <v>46307</v>
@@ -6786,7 +6777,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B90" s="5">
         <v>46156.63284013889</v>
@@ -6825,13 +6816,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6841,7 +6832,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B91" s="9">
         <v>46156.63286864583</v>
@@ -6851,7 +6842,7 @@
         <v>46243.72830107639</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6878,13 +6869,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O91" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q91" s="9">
         <v>46308</v>
@@ -6904,7 +6895,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B92" s="5">
         <v>46156.632875972224</v>
@@ -6939,13 +6930,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6955,7 +6946,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B93" s="9">
         <v>46156.63290420139</v>
@@ -6965,7 +6956,7 @@
         <v>46156.71731457176</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>25</v>
@@ -6989,7 +6980,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>26</v>
@@ -7002,7 +6993,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B94" s="5">
         <v>46156.63290788194</v>
@@ -7012,16 +7003,16 @@
         <v>46156.72728918982</v>
       </c>
       <c r="E94" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G94" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="F94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G94" s="6" t="s">
+      <c r="H94" s="6" t="s">
         <v>300</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>301</v>
       </c>
       <c r="I94" s="5">
         <v>46309</v>
@@ -7039,13 +7030,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q94" s="5">
         <v>46309</v>
@@ -7065,7 +7056,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B95" s="9">
         <v>46156.63291414352</v>
@@ -7075,7 +7066,7 @@
         <v>46209.559051539356</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7102,13 +7093,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q95" s="9">
         <v>46309</v>

--- a/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
+++ b/data/50001547 - XEMORTIZ AMERICAS GOLD.xlsx
@@ -1964,7 +1964,7 @@
         <v>46212.59677549769</v>
       </c>
       <c r="D10" s="5">
-        <v>46212.59679202546</v>
+        <v>46271.56543923611</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
